--- a/Consolidated_Portfolios_23.10.2026.xlsx
+++ b/Consolidated_Portfolios_23.10.2026.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="277">
   <si>
     <t xml:space="preserve">CONSOLIDATED PORTFOLIO SUMMARY – ALL MANAGED ACCOUNTS</t>
   </si>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Angel One</t>
   </si>
   <si>
-    <t xml:space="preserve">20.10.2026 + trades of 21–22.10.2026</t>
+    <t xml:space="preserve">20.10.2026 + trades of 21–23.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">20.10.2026 statement prices (only for rows with no trades since)</t>
@@ -255,7 +255,7 @@
     <t xml:space="preserve">• Manish Shilpa is new (23.10.2026): Axis Direct (Shilpa), Axis Direct (Manish), HDFC Securities (Manish) and Manish's Axis mutual fund (UTI Nifty 50 Index Fund – 2 folios, ₹1,99,990 invested) merged into one account. A stock held in more than one demat is one row; the row note lists the split. Statement totals: invested ₹98,57,779, market value ₹1,16,36,410 (equity at live ~11:23 IST prices, MF at statement NAV).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Saloni Mehra is new (Angel One): 26-holding statement of 20.10.2026 (invested ₹1,10,23,244; market value ₹1,13,95,012) rolled forward with the 15 trades of 21–22.10.2026. Buys add cost including all charges; Kotak Mahindra Bank (1,580 sh, realised ≈ ₹62,288) and LIC Housing Finance (700 sh, realised ≈ ₹-29,271) were sold out; Trent is a new position. Statement invested is now the row sum (no printed total after trades). Rows touched by trades have no statement value, so the account's 'Stmt Market Value' covers untraded rows only.</t>
+    <t xml:space="preserve">• Saloni Mehra is new (Angel One): 26-holding statement of 20.10.2026 (invested ₹1,10,23,244; market value ₹1,13,95,012) rolled forward with the 15 trades of 21–22.10.2026 and the 24 buys of 23.10.2026 (₹7,25,477 at executed prices). 21–22.10 buys include all charges; 23.10 charges are not yet shown by Angel One, so those buys are at executed price only. Kotak Mahindra Bank (1,580 sh, realised ≈ ₹62,288) and LIC Housing Finance (700 sh, realised ≈ ₹-29,271) were sold out; Trent is a new position. Statement invested is the row sum (no printed total after trades); rows touched by trades have no statement value, so 'Stmt Market Value' covers untraded rows only.</t>
   </si>
   <si>
     <t xml:space="preserve">SIDE-BY-SIDE HOLDINGS – COMBINED AND BY PORTFOLIO</t>
@@ -322,10 +322,10 @@
     <t xml:space="preserve">Nippon India ETF Nifty 50 BeES</t>
   </si>
   <si>
-    <t xml:space="preserve">HDFC Bank Ltd</t>
+    <t xml:space="preserve">Poonawalla Fincorp Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">Poonawalla Fincorp Ltd</t>
+    <t xml:space="preserve">HDFC Bank Ltd</t>
   </si>
   <si>
     <t xml:space="preserve">AFCOM Holdings Ltd</t>
@@ -334,16 +334,16 @@
     <t xml:space="preserve">Tata Consultancy Services Ltd</t>
   </si>
   <si>
+    <t xml:space="preserve">Bajaj Housing Finance Ltd</t>
+  </si>
+  <si>
     <t xml:space="preserve">LTM Ltd (formerly LTIMindtree)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bajaj Housing Finance Ltd</t>
+    <t xml:space="preserve">L&amp;T Technology Services Ltd</t>
   </si>
   <si>
     <t xml:space="preserve">Connplex Cinemas Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L&amp;T Technology Services Ltd</t>
   </si>
   <si>
     <t xml:space="preserve">Jubilant FoodWorks Ltd</t>
@@ -364,10 +364,10 @@
     <t xml:space="preserve">Nippon India ETF Nifty 1D Rate Liquid BeES</t>
   </si>
   <si>
-    <t xml:space="preserve">UTI Nifty 50 Index Fund - Growth</t>
+    <t xml:space="preserve">Eicher Motors Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">Eicher Motors Ltd</t>
+    <t xml:space="preserve">UTI Nifty 50 Index Fund - Growth</t>
   </si>
   <si>
     <t xml:space="preserve">ICICI Prudential Life Insurance Co Ltd</t>
@@ -541,10 +541,10 @@
     <t xml:space="preserve">Bharti Airtel Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">Utkarsh Small Finance Bank Ltd</t>
+    <t xml:space="preserve">Waaree Renewable Technologies Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">Waaree Renewable Technologies Ltd</t>
+    <t xml:space="preserve">Utkarsh Small Finance Bank Ltd</t>
   </si>
   <si>
     <t xml:space="preserve">Alkyl Amines Chemicals Ltd</t>
@@ -795,25 +795,25 @@
     <t xml:space="preserve">Axis Direct Shilpa 1; Axis Direct Manish 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Holdings as of 20.10.2026 + trades of 21–22.10.2026. Statement prices: 20.10.2026 statement prices (only for rows with no trades since). Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
+    <t xml:space="preserve">Holdings as of 20.10.2026 + trades of 21–23.10.2026. Statement prices: 20.10.2026 statement prices (only for rows with no trades since). Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
   </si>
   <si>
-    <t xml:space="preserve">Angel One trades 21–22.10.2026 (blended into holdings; buys include charges)</t>
+    <t xml:space="preserve">Angel One trades 21–23.10.2026 (blended into holdings; 21–22.10 buys include charges, 23.10 buys at executed price)</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 21.10 buy 362 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 21.10 buy 362 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
     <t xml:space="preserve">21.10.2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 21.10 buy 9 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 21.10 buy 9 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 21.10 buy 79 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 21.10 buy 970 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 21.10 buy 970 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 21.10 buy 79 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
     <t xml:space="preserve">LIC Housing Finance Ltd</t>
@@ -822,25 +822,28 @@
     <t xml:space="preserve">22.10.2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 21.10 buy 547 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 21.10 buy 547 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 22.10 buy 1 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 22.10 buy 1 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 22.10 buy 6 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 22.10 buy 8 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 22.10 buy 6 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 22.10 buy 10 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 22.10 buy 8 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
-    <t xml:space="preserve">Trades 22.10 buy 4 (charges included in cost); no statement value after trades</t>
+    <t xml:space="preserve">Trades 22.10 buy 10 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
-    <t xml:space="preserve">New position, bought 22.10 (charges included in cost); no statement value</t>
+    <t xml:space="preserve">Trades 22.10 buy 4 (charges included in cost); 23.10 buys at executed price, charges not yet known</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New position, bought 22.10 (charges included in cost); no statement value; 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
     <t xml:space="preserve">Holdings as of 04.10.2026 (+ trades of 05.10.2026). Statement prices: LTP 05.10.2026. Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
@@ -900,10 +903,10 @@
     <t xml:space="preserve">Rights entitlement – nil cost</t>
   </si>
   <si>
-    <t xml:space="preserve">{"built": "23.10.2026", "close_date": "22.10.2026", "prev_date": "21.10.2026", "closes": {"Bajaj Finance Ltd": [942.1, 926], "Titan Company Ltd": [4350, 4380.9], "Poonawalla Fincorp Ltd": [432.45, 437.3], "HDFC Bank Ltd": [694.05, 706.95], "HCL Technologies Ltd": [1421.7, 1424.2], "Bajaj Housing Finance Ltd": [81.02, 81.17], "LTM Ltd (formerly LTIMindtree)": [4274, 4298], "Affle 3i Ltd": [1362.8, 1395.3], "L&amp;T Technology Services Ltd": [3954.8, 3996.3], "Fineotex Chemical Ltd": [51.55, 52.73], "AFCOM Holdings Ltd": [1371.45, 1414.9], "Connplex Cinemas Ltd": [234.25, 239.7], "Vinati Organics Ltd": [1089.9, 1096.1], "Persistent Systems Ltd": [5740.5, 5858.5], "Tata Consultancy Services Ltd": [2506.9, 2529], "Tata Elxsi Ltd": [3846.8, 3848.6], "Trent Ltd": [2775.8, 2822], "Avenue Supermarts (DMart) Ltd": [3166, 3250.9], "Nestle India Ltd": [1189.9, 1223.9], "Eicher Motors Ltd": [7084.5, 7170.5], "InterGlobe Aviation Ltd (IndiGo)": [4600, 4641.5], "Waaree Energies Ltd": [2370, 2455], "Rategain Travel Technologies Ltd": [788.1, 779.7], "Shriram Properties Ltd": [65.13, 66.01], "Bagmane Prime Office REIT": [105.54, 105.53], "Bharti Airtel Ltd": [1895, 1891.7], "Orient Electric Ltd": [188.91, 189.6], "Reliance Industries Ltd": [1184.5, 1209], "Jio Financial Services Ltd": [210.8, 211.39], "NCC Ltd": [120.17, 123.2], "Capacite Infraprojects Ltd": [154.93, 161.42], "Indus Towers Ltd": [381.85, 379], "Vedanta Power (VEDPOWER)": [29.51, 30.3], "Moschip Technologies Ltd": [169.62, 173.28], "Godrej Consumer Products Ltd": [860.2, 859], "Vedant Fashions (Manyavar) Ltd": [490.05, 501.7], "Indian Railway Finance Corp Ltd": [77, 76.8], "RITES Ltd": [196.09, 197.42], "Indraprastha Gas Ltd": [140.01, 142.31], "Great Eastern Shipping Co Ltd": [1518.6, 1506.3], "HUDCO Ltd": [151.77, 154.34], "NTPC Green Energy Ltd": [84.35, 84.04], "Brigade Enterprises Ltd": [557.1, 570.2], "GFL Ltd": [54.58, 55.21], "Sonata Software Ltd": [239.75, 240.5], "Syngene International Ltd": [372.5, 376.45], "Ambuja Cements Ltd": [363, 359.9], "Astec LifeSciences Ltd": [669.2, 665.9], "Gujarat Energy": [218.13, 222.02], "Indian Energy Exchange Ltd": [104, 103.28], "Vinyl Chemicals (India) Ltd": [205.95, 201.62], "JK Tyre &amp; Industries Ltd": [323, 327.55], "REC Ltd": [301.1, 302.5], "Shakti Pumps (India) Ltd": [400.65, 403.8], "Ashoka Buildcon Ltd": [101.09, 102.18], "Cyient Ltd": [1143.7, 1169.7], "Utkarsh Small Finance Bank Ltd": [12.17, 12.55], "Orient Cement Ltd": [116.89, 113.81], "Waaree Renewable Technologies Ltd": [718.95, 743.25], "Eureka Forbes Ltd": [316.8, 326.15], "Eternal Ltd": [304.45, 312.35], "VRL Logistics Ltd": [266.55, 284.85], "Kotak Mahindra Bank Ltd": [437, 437.8], "Alkyl Amines Chemicals Ltd": [1704.2, 1721.4], "Pfizer Ltd": [3688.9, 3754.7], "Garware Technical Fibres Ltd": [749.6, 740.7], "Central Depository Services (India) Ltd": [1225, 1237.2], "Abbott India Ltd": [25360, 25680], "Tanla Platforms Ltd": [581.3, 562.1], "Vaibhav Global Ltd": [195.22, 199.32], "Asian Paints Ltd": [2284.8, 2319.4], "Aarti Drugs Ltd": [380.05, 388.6], "Deepak Nitrite Ltd": [1487.4, 1506.2], "Infosys Ltd": [1153.35, 1168], "Dr Lal PathLabs Ltd": [1843.7, 1836.1], "Page Industries Ltd": [34425, 34870], "Clean Science and Technology Ltd": [748.05, 741.1], "Jubilant FoodWorks Ltd": [404.9, 405], "ICICI Prudential Life Insurance Co Ltd": [431, 431.5]}, "screener_urls": {"Bajaj Finance Ltd": "/company/BAJFINANCE/consolidated/", "Titan Company Ltd": "/company/TITAN/consolidated/", "Poonawalla Fincorp Ltd": "/company/POONAWALLA/consolidated/", "HDFC Bank Ltd": "/company/HDFCBANK/consolidated/", "HCL Technologies Ltd": "/company/HCLTECH/consolidated/", "Bajaj Housing Finance Ltd": "/company/BAJAJHFL/", "LTM Ltd (formerly LTIMindtree)": "/company/LTM/", "Affle 3i Ltd": "/company/AFFLE/consolidated/", "L&amp;T Technology Services Ltd": "/company/LTTS/consolidated/", "Fineotex Chemical Ltd": "/company/FCL/consolidated/", "AFCOM Holdings Ltd": "/company/544224/", "Connplex Cinemas Ltd": "/company/CONNPLEX/", "Vinati Organics Ltd": "/company/VINATIORGA/", "Persistent Systems Ltd": "/company/PERSISTENT/consolidated/", "Tata Consultancy Services Ltd": "/company/TCS/consolidated/", "Tata Elxsi Ltd": "/company/TATAELXSI/", "Trent Ltd": "/company/TRENT/consolidated/", "Avenue Supermarts (DMart) Ltd": "/company/DMART/consolidated/", "Nestle India Ltd": "/company/NESTLEIND/", "Eicher Motors Ltd": "/company/EICHERMOT/consolidated/", "InterGlobe Aviation Ltd (IndiGo)": "/company/INDIGO/", "Waaree Energies Ltd": "/company/WAAREEENER/consolidated/", "Rategain Travel Technologies Ltd": "/company/RATEGAIN/consolidated/", "International Gemmological Institute (India) Ltd": "/company/IGIL/", "Shriram Properties Ltd": "/company/SHRIRAMPPS/consolidated/", "Bagmane Prime Office REIT": "/company/BAGMANE/consolidated/", "Bharti Airtel Ltd": "/company/BHARTIARTL/consolidated/", "Orient Electric Ltd": "/company/ORIENTELEC/", "Reliance Industries Ltd": "/company/RELIANCE/", "Jio Financial Services Ltd": "/company/JIOFIN/", "NCC Ltd": "/company/NCC/", "Capacite Infraprojects Ltd": "/company/CAPACITE/", "Indus Towers Ltd": "/company/INDUSTOWER/", "Vedanta Power (VEDPOWER)": "/company/VEDPOWER/consolidated/", "Moschip Technologies Ltd": "/company/MOSCHIP/", "Godrej Consumer Products Ltd": "/company/GODREJCP/", "Vedant Fashions (Manyavar) Ltd": "/company/MANYAVAR/", "Indian Railway Finance Corp Ltd": "/company/IRFC/", "RITES Ltd": "/company/RITES/", "Indraprastha Gas Ltd": "/company/IGL/", "Great Eastern Shipping Co Ltd": "/company/GESHIP/", "HUDCO Ltd": "/company/HUDCO/", "NTPC Green Energy Ltd": "/company/NTPCGREEN/", "Brigade Enterprises Ltd": "/company/BRIGADE/", "GFL Ltd": "/company/GFLLIMITED/", "Sonata Software Ltd": "/company/SONATSOFTW/", "Syngene International Ltd": "/company/SYNGENE/", "Ambuja Cements Ltd": "/company/AMBUJACEM/", "Astec LifeSciences Ltd": "/company/ASTEC/", "Gujarat Energy": "/company/GUJENERGY/consolidated/", "Indian Energy Exchange Ltd": "/company/IEX/", "Vinyl Chemicals (India) Ltd": "/company/VINYLINDIA/", "JK Tyre &amp; Industries Ltd": "/company/JKTYRE/", "REC Ltd": "/company/RECLTD/", "Shakti Pumps (India) Ltd": "/company/SHAKTIPUMP/", "Ashoka Buildcon Ltd": "/company/ASHOKA/", "Cyient Ltd": "/company/CYIENT/", "Utkarsh Small Finance Bank Ltd": "/company/UTKARSHBNK/", "Orient Cement Ltd": "/company/ORIENTCEM/", "Waaree Renewable Technologies Ltd": "/company/WAAREERTL/consolidated/", "Eureka Forbes Ltd": "/company/EUREKAFORB/", "Eternal Ltd": "/company/ETERNAL/consolidated/", "VRL Logistics Ltd": "/company/VRLLOG/", "Kotak Mahindra Bank Ltd": "/company/KOTAKBANK/consolidated/", "Alkyl Amines Chemicals Ltd": "/company/ALKYLAMINE/", "Pfizer Ltd": "/company/PFIZER/", "Garware Technical Fibres Ltd": "/company/GARFIBRES/consolidated/", "Central Depository Services (India) Ltd": "/company/CDSL/consolidated/", "Abbott India Ltd": "/company/ABBOTINDIA/", "Tanla Platforms Ltd": "/company/TANLA/consolidated/", "Vaibhav Global Ltd": "/company/VAIBHAVGBL/consolidated/", "Asian Paints Ltd": "/company/ASIANPAINT/consolidated/", "Aarti Drugs Ltd": "/company/AARTIDRUGS/consolidated/", "Deepak Nitrite Ltd": "/company/DEEPAKNTR/consolidated/", "Infosys Ltd": "/company/INFY/consolidated/", "Dr Lal PathLabs Ltd": "/company/LALPATHLAB/consolidated/", "Page Industries Ltd": "/company/PAGEIND/", "Clean Science and Technology Ltd": "/company/CLEAN/consolidated/", "Jubilant FoodWorks Ltd": "/company/JUBLFOOD/consolidated/", "ICICI Prudential Life Insurance Co Ltd": "/company/ICICILIFE/"}, "notes": ["No exchange close for the 4 ETFs (Nifty 50 BeES, Gold BeES, Liquid BeES, HDFC Gold ETF), the Utkarsh SFB rights entitlement, NEPC Agro and PSL Ltd – these stay at statement price (Liquid BeES holds near ₹1,000).", "Names aligned across statements: LTM Ltd = LTIMindtree (DA); Connplex Cinemas = Connplex Smart Theatres (DA); AFCOM = Afcom Holdings.", "Trades blended into holdings and listed on each tab: Vidushi 05.10.2026 (3 buys, ₹9,889); Dr Umesh 09.10.2026 (13 buys, ₹5.01 L, incl. new Eicher Motors and Rategain).", "Dr Umesh holds ₹36,000 uninvested cash at ICICI Direct – row 'Cash – ICICI Direct' at ₹1 per unit, counted in totals but not as a holding.", "Statement invested/market totals reconcile to transcribed rows within ₹2 (rupee rounding on the statements).", "Gautam: NEPC Agro Foods (144 sh) and PSL Ltd (1,000 sh) still have no cost or price on the statement – carried at nil.", "Manish Shilpa: Axis and HDFC CSVs carry short names (e.g. 'Nip. India Nifty', 'C D S L', 'Waaree Renewab.'); aligned to canonical names. 'Nippon ETF Infra' is carried as Nippon India ETF Infra BeES. ETFs have no exchange close and stay on the statement price.", "Gautam refreshed from HDFC statement of 23.10.2026 (31 lines; invested ₹55,01,448 reconciles to ₹55,01,448.50). Changes vs the 05.10 statement are derived: 16 buys and 1 exit (International Gemmological Institute, 80 sh, valued at the 05.10 statement price).", "Vidushi, Dr Umesh and DA have no new statements since 09.10 and are only repriced to the 22.10.2026 close.", "Manish Shilpa is new (23.10.2026): Axis Direct (Shilpa), Axis Direct (Manish), HDFC Securities (Manish) and Manish's Axis mutual fund (UTI Nifty 50 Index Fund – 2 folios, ₹1,99,990 invested) merged into one account. A stock held in more than one demat is one row; the row note lists the split. Statement totals: invested ₹98,57,779, market value ₹1,16,36,410 (equity at live ~11:23 IST prices, MF at statement NAV).", "Saloni Mehra is new (Angel One): 26-holding statement of 20.10.2026 (invested ₹1,10,23,244; market value ₹1,13,95,012) rolled forward with the 15 trades of 21–22.10.2026. Buys add cost including all charges; Kotak Mahindra Bank (1,580 sh, realised ≈ ₹62,288) and LIC Housing Finance (700 sh, realised ≈ ₹-29,271) were sold out; Trent is a new position. Statement invested is now the row sum (no printed total after trades). Rows touched by trades have no statement value, so the account's 'Stmt Market Value' covers untraded rows only."], "portfolios": [{"key": "Gautam", "tab": "Gautam", "name": "Gautam", "broker": "HDFC Securities", "holdings_date": "23.10.2026", "price_basis": "HDFC statement prices 23.10.2026", "stmt_invested": 5501448.5, "stmt_mv": 5224564.0, "basis_label": "Gautam stmt – 23.10", "stale_prices": false, "rows": [["Bajaj Finance Ltd", "HDFC Securities", 1901, 1912279, 1783138, ""], ["Poonawalla Fincorp Ltd", "HDFC Securities", 1132, 527172, 489024, ""], ["Nippon India ETF Nifty 1D Rate Liquid BeES", "HDFC Securities", 325, 325000, 325000, ""], ["HDFC Bank Ltd", "HDFC Securities", 447, 320122, 310218, ""], ["LTM Ltd (formerly LTIMindtree)", "HDFC Securities", 60, 273840, 256440, "Shown as LTM Limited"], ["Tata Consultancy Services Ltd", "HDFC Securities", 92, 210588, 230644, ""], ["Titan Company Ltd", "HDFC Securities", 47, 223898, 204450, ""], ["Connplex Cinemas Ltd", "HDFC Securities", 800, 211200, 192000, ""], ["AFCOM Holdings Ltd", "HDFC Securities", 120, 199920, 165240, "Shown as AFCOM"], ["Tata Elxsi Ltd", "HDFC Securities", 41, 140474, 157727, ""], ["Eicher Motors Ltd", "HDFC Securities", 20, 147414, 141680, ""], ["Bajaj Housing Finance Ltd", "HDFC Securities", 1600, 132930, 129920, ""], ["L&amp;T Technology Services Ltd", "HDFC Securities", 30, 104531, 119880, ""], ["Persistent Systems Ltd", "HDFC Securities", 19, 105436, 109060, ""], ["InterGlobe Aviation Ltd (IndiGo)", "HDFC Securities", 20, 103860, 92160, "Shown as InterGlobe Aviation Ltd (Indigo)"], ["Affle 3i Ltd", "HDFC Securities", 66, 106115, 89958, ""], ["Trent Ltd", "HDFC Securities", 31, 86006, 86056, ""], ["Avenue Supermarts (DMart) Ltd", "HDFC Securities", 24, 89946, 75984, ""], ["Waaree Energies Ltd", "HDFC Securities", 27, 68363, 63990, ""], ["Rategain Travel Technologies Ltd", "HDFC Securities", 72, 59636, 56808, ""], ["Fineotex Chemical Ltd", "HDFC Securities", 830, 46702, 43575, ""], ["Nestle India Ltd", "HDFC Securities", 22, 27683, 26180, ""], ["Shriram Properties Ltd", "HDFC Securities", 250, 19250, 16925, ""], ["Bagmane Prime Office REIT", "HDFC Securities", 150, 16050, 15900, ""], ["Nippon India ETF Gold BeES", "HDFC Securities", 121, 13310, 14883, ""], ["Vinati Organics Ltd", "HDFC Securities", 10, 11941, 10970, ""], ["Bharti Airtel Ltd", "HDFC Securities", 5, 9610, 9475, ""], ["Orient Electric Ltd", "HDFC Securities", 25, 4500, 3850, ""], ["HDFC Gold ETF", "HDFC Securities", 27, 3672, 3429, ""], ["NEPC Agro Foods Ltd", "HDFC Securities", 144, null, null, "No cost or price on statement (marked *) – carried at nil"], ["PSL Ltd (formerly PSL Holdings Ltd)", "HDFC Securities", 1000, null, null, "No cost or price on statement (marked *) – carried at nil"]], "trades": [["05.10–23.10.2026", "BUY", "Affle 3i Ltd", 8, 1364.62, 10917], ["05.10–23.10.2026", "BUY", "Avenue Supermarts (DMart) Ltd", 3, 3179.0, 9537], ["05.10–23.10.2026", "BUY", "Bajaj Finance Ltd", 237, 932.3, 220956], ["05.10–23.10.2026", "BUY", "Bajaj Housing Finance Ltd", 274, 81.1, 22222], ["05.10–23.10.2026", "BUY", "Eicher Motors Ltd", 3, 7055.0, 21165], ["05.10–23.10.2026", "BUY", "Fineotex Chemical Ltd", 138, 52.29, 7216], ["05.10–23.10.2026", "BUY", "HDFC Bank Ltd", 57, 693.96, 39556], ["05.10–23.10.2026", "SELL", "International Gemmological Institute (India) Ltd", 80, 314.0, 25120], ["05.10–23.10.2026", "BUY", "L&amp;T Technology Services Ltd", 5, 3954.0, 19770], ["05.10–23.10.2026", "BUY", "Nippon India ETF Nifty 1D Rate Liquid BeES", 25, 1000.0, 25000], ["05.10–23.10.2026", "BUY", "Persistent Systems Ltd", 3, 5806.0, 17418], ["05.10–23.10.2026", "BUY", "Poonawalla Fincorp Ltd", 131, 432.84, 56702], ["05.10–23.10.2026", "BUY", "Rategain Travel Technologies Ltd", 9, 789.22, 7103], ["05.10–23.10.2026", "BUY", "Tata Elxsi Ltd", 7, 3852.57, 26968], ["05.10–23.10.2026", "BUY", "Titan Company Ltd", 6, 4349.0, 26094], ["05.10–23.10.2026", "BUY", "Trent Ltd", 3, 2787.33, 8362], ["05.10–23.10.2026", "BUY", "Waaree Energies Ltd", 3, 2367.33, 7102]], "trades_title": "Changes between 05.10 and 23.10 statements (derived; buys at implied avg cost, sells at 05.10 statement price)"}, {"key": "Manish", "tab": "Manish Shilpa", "name": "Manish Shilpa", "broker": "Axis Direct + HDFC Securities", "holdings_date": "23.10.2026 (live, ~11:23 IST)", "price_basis": "Live LTP 23.10.2026 ~11:23 IST (equity); MF NAV per Axis statement 23.10.2026 (three demats + MF merged)", "basis_label": "Manish Shilpa stmt – live 23.10", "stale_prices": false, "stmt_invested": 9857779, "stmt_mv": 11636410.18, "rows": [["Bajaj Housing Finance Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 3762.0, 432693, 292084, "Axis Direct Shilpa 267; Axis Direct Manish 3396; HDFC Securities Manish 99"], ["Nippon India ETF Nifty 1D Rate Liquid BeES", "Axis Direct (Shilpa) + Axis Direct (Manish)", 4.0, 5559, 5559, "Axis Direct Shilpa 1; Axis Direct Manish 3"], ["Eicher Motors Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 6.0, 43747, 41760, "Axis Direct Shilpa 1; Axis Direct Manish 5"], ["Waaree Renewable Technologies Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 5.0, 5105, 3398, "Axis Direct Shilpa 1; Axis Direct Manish 4"], ["Vinati Organics Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 17.0, 29694, 18142, "Axis Direct Shilpa 1; Axis Direct Manish 15; HDFC Securities Manish 1"], ["Nippon India ETF Nifty 50 BeES", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 11160.0, 1687580, 2864693, "Axis Direct Shilpa 10; Axis Direct Manish 11049; HDFC Securities Manish 101"], ["Affle 3i Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 47.0, 76969, 62254, "Axis Direct Shilpa 18; Axis Direct Manish 25; HDFC Securities Manish 4"], ["Eureka Forbes Ltd", "Axis Direct (Shilpa)", 35.0, 19821, 10747, ""], ["HDFC Gold ETF", "Axis Direct (Shilpa) + Axis Direct (Manish)", 168.0, 15354, 20131, "Axis Direct Shilpa 93; Axis Direct Manish 75"], ["Eternal Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 34.0, 10336, 10411, "Axis Direct Shilpa 9; Axis Direct Manish 25"], ["VRL Logistics Ltd", "Axis Direct (Shilpa)", 50.0, 13962, 12668, ""], ["Tata Elxsi Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 32.0, 212270, 120470, "Axis Direct Shilpa 1; Axis Direct Manish 31"], ["Waaree Energies Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 6.0, 18946, 13900, "Axis Direct Shilpa 2; Axis Direct Manish 4"], ["Bajaj Finance Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 3895.0, 2912389, 3625900, "Axis Direct Shilpa 226; Axis Direct Manish 3165; HDFC Securities Manish 504"], ["Persistent Systems Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 11.0, 49823, 63648, "Axis Direct Shilpa 3; Axis Direct Manish 8"], ["Kotak Mahindra Bank Ltd", "Axis Direct (Shilpa) + HDFC Securities (Manish)", 160.0, 63501, 69298, "Axis Direct Shilpa 30; HDFC Securities Manish 130"], ["Trent Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 10.0, 30536, 27130, "Axis Direct Shilpa 3; Axis Direct Manish 7"], ["LTM Ltd (formerly LTIMindtree)", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 66.0, 348137, 276816, "Axis Direct Shilpa 2; Axis Direct Manish 52; HDFC Securities Manish 12"], ["Avenue Supermarts (DMart) Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 6.0, 23637, 18758, "Axis Direct Shilpa 2; Axis Direct Manish 4"], ["HDFC Bank Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 1013.0, 812683, 697943, "Axis Direct Shilpa 58; Axis Direct Manish 899; HDFC Securities Manish 56"], ["L&amp;T Technology Services Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 72.0, 303467, 282588, "Axis Direct Shilpa 2; Axis Direct Manish 64; HDFC Securities Manish 6"], ["Titan Company Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 165.0, 564530, 700725, "Axis Direct Shilpa 7; Axis Direct Manish 153; HDFC Securities Manish 5"], ["Poonawalla Fincorp Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 1394.0, 622513, 578058, "Axis Direct Shilpa 206; Axis Direct Manish 1180; HDFC Securities Manish 8"], ["Alkyl Amines Chemicals Ltd", "Axis Direct (Manish)", 3.0, 12327, 4865, ""], ["Indian Energy Exchange Ltd", "Axis Direct (Manish)", 12.0, 2262, 1209, ""], ["Pfizer Ltd", "Axis Direct (Manish)", 1.0, 6103, 3601, ""], ["Jio Financial Services Ltd", "Axis Direct (Manish)", 32.0, 3256, 6556, ""], ["Garware Technical Fibres Ltd", "Axis Direct (Manish)", 5.0, 3380, 3606, ""], ["Reliance Industries Ltd", "Axis Direct (Manish)", 32.0, 38635, 37526, ""], ["Central Depository Services (India) Ltd", "Axis Direct (Manish)", 134.0, 51658, 158643, ""], ["Connplex Cinemas Ltd", "Axis Direct (Manish)", 800.0, 188075, 175200, ""], ["Tata Consultancy Services Ltd", "Axis Direct (Manish)", 29.0, 97994, 74127, ""], ["Abbott India Ltd", "Axis Direct (Manish)", 3.0, 54700, 74400, ""], ["Tanla Platforms Ltd", "Axis Direct (Manish)", 33.0, 40602, 18610, ""], ["Fineotex Chemical Ltd", "Axis Direct (Manish)", 3500.0, 117474, 167755, ""], ["Nippon India ETF Infra BeES", "Axis Direct (Manish)", 34.0, 14923, 29819, ""], ["Vaibhav Global Ltd", "Axis Direct (Manish)", 5.0, 1680, 936, ""], ["Asian Paints Ltd", "Axis Direct (Manish)", 22.0, 78545, 50046, ""], ["Aarti Drugs Ltd", "Axis Direct (Manish)", 6.0, 3768, 2241, ""], ["Deepak Nitrite Ltd", "Axis Direct (Manish)", 1.0, 2393, 1427, ""], ["Infosys Ltd", "Axis Direct (Manish)", 64.0, 102862, 74240, ""], ["Rategain Travel Technologies Ltd", "Axis Direct (Manish)", 5.0, 3317, 3815, ""], ["AFCOM Holdings Ltd", "Axis Direct (Manish)", 360.0, 362724, 457200, ""], ["Clean Science and Technology Ltd", "Axis Direct (Manish)", 14.0, 22090, 10168, ""], ["Dr Lal PathLabs Ltd", "HDFC Securities (Manish)", 44.0, 52231, 80313, ""], ["Page Industries Ltd", "HDFC Securities (Manish)", 2.0, 93537, 67650, ""], ["UTI Nifty 50 Index Fund - Growth", "Axis Direct (Manish) MF", 2004.589, 199990, 315380.18, "Mutual fund, 2 folios (1,804.130 + 200.459 units); NAV ₹157.3291 per Axis statement 23.10.2026 – no exchange close, statement NAV used"]], "trades_title": "", "trades": []}, {"key": "Saloni", "tab": "Saloni Mehra", "name": "Saloni Mehra", "broker": "Angel One", "holdings_date": "20.10.2026 + trades of 21–22.10.2026", "price_basis": "20.10.2026 statement prices (only for rows with no trades since)", "basis_label": "Saloni stmt – 20.10", "stale_prices": true, "stmt_invested": 11014028, "stmt_mv": 3325492, "rows": [["Bajaj Finance Ltd", "Angel One", 4713, 4439078, null, "Trades 21.10 buy 362 (charges included in cost); no statement value after trades"], ["Titan Company Ltd", "Angel One", 244, 1046469, null, "Trades 21.10 buy 9 (charges included in cost); no statement value after trades"], ["Jubilant FoodWorks Ltd", "Angel One", 2000, 845300, 827000, ""], ["Tata Consultancy Services Ltd", "Angel One", 305, 659410, 750575, ""], ["HDFC Bank Ltd", "Angel One", 1089, 841371, null, "Trades 21.10 buy 79 (charges included in cost); no statement value after trades"], ["AFCOM Holdings Ltd", "Angel One", 360, 361080, 536742, ""], ["LTM Ltd (formerly LTIMindtree)", "Angel One", 83, 323526, 353987, ""], ["ICICI Prudential Life Insurance Co Ltd", "Angel One", 700, 340305, 306600, ""], ["Bajaj Housing Finance Ltd", "Angel One", 3860, 331672, null, "Trades 21.10 buy 547 (charges included in cost); no statement value after trades"], ["Fineotex Chemical Ltd", "Angel One", 4830, 209864, 269562, ""], ["L&amp;T Technology Services Ltd", "Angel One", 72, 245895, null, "Trades 22.10 buy 1 (charges included in cost); no statement value after trades"], ["Tata Elxsi Ltd", "Angel One", 61, 246916, null, "Trades 22.10 buy 6 (charges included in cost); no statement value after trades"], ["Connplex Cinemas Ltd", "Angel One", 800, 170200, 198400, ""], ["Poonawalla Fincorp Ltd", "Angel One", 1267, 552838, null, "Trades 21.10 buy 970 (charges included in cost); no statement value after trades"], ["Affle 3i Ltd", "Angel One", 73, 107884, null, "Trades 22.10 buy 8 (charges included in cost); no statement value after trades"], ["Vinati Organics Ltd", "Angel One", 48, 62798, 53693, ""], ["Rategain Travel Technologies Ltd", "Angel One", 76, 66457, null, "Trades 22.10 buy 10 (charges included in cost); no statement value after trades"], ["Persistent Systems Ltd", "Angel One", 9, 45356, null, "Trades 22.10 buy 1 (charges included in cost); no statement value after trades"], ["Waaree Energies Ltd", "Angel One", 8, 24527, 20120, ""], ["Eicher Motors Ltd", "Angel One", 6, 43513, null, "Trades 22.10 buy 4 (charges included in cost); no statement value after trades"], ["Avenue Supermarts (DMart) Ltd", "Angel One", 7, 25715, null, "Trades 22.10 buy 4 (charges included in cost); no statement value after trades"], ["Nestle India Ltd", "Angel One", 4, 5602, 4971, ""], ["Waaree Renewable Technologies Ltd", "Angel One", 3, 2928, 2479, ""], ["HDFC Gold ETF", "Angel One", 11, 1387, 1363, ""], ["Trent Ltd", "Angel One", 5, 13937, null, "New position, bought 22.10 (charges included in cost); no statement value"]], "trades_title": "Angel One trades 21–22.10.2026 (blended into holdings; buys include charges)", "trades": [["21.10.2026", "SELL", "Kotak Mahindra Bank Ltd", 1580, 445.65, 704127], ["21.10.2026", "BUY", "Bajaj Housing Finance Ltd", 547, 81.76, 44723], ["21.10.2026", "BUY", "Titan Company Ltd", 9, 4419.44, 39775], ["21.10.2026", "BUY", "HDFC Bank Ltd", 79, 710.85, 56157], ["21.10.2026", "BUY", "Poonawalla Fincorp Ltd", 970, 445.53, 432164], ["21.10.2026", "SELL", "LIC Housing Finance Ltd", 700, 512.6, 358820], ["21.10.2026", "BUY", "Bajaj Finance Ltd", 362, 935.65, 338705], ["22.10.2026", "BUY", "Persistent Systems Ltd", 1, 5818.0, 5818], ["22.10.2026", "BUY", "Tata Elxsi Ltd", 6, 3852.22, 23113], ["22.10.2026", "BUY", "L&amp;T Technology Services Ltd", 1, 3930.0, 3930], ["22.10.2026", "BUY", "Trent Ltd", 5, 2780.9, 13904], ["22.10.2026", "BUY", "Affle 3i Ltd", 8, 1380.9, 11047], ["22.10.2026", "BUY", "Eicher Motors Ltd", 4, 7063.5, 28254], ["22.10.2026", "BUY", "Avenue Supermarts (DMart) Ltd", 4, 3191.1, 12764], ["22.10.2026", "BUY", "Rategain Travel Technologies Ltd", 10, 776.5, 7765]]}, {"key": "Vidushi", "tab": "Vidushi Malhotra", "name": "Vidushi Malhotra", "broker": "Zerodha", "holdings_date": "04.10.2026 (+ trades of 05.10.2026)", "price_basis": "LTP 05.10.2026", "stmt_invested": 201361, "stmt_mv": 230319, "basis_label": "Vidushi stmt – LTP 05.10", "stale_prices": false, "rows": [["Bajaj Finance Ltd", "Zerodha", 121, 92928, 117842, ""], ["Titan Company Ltd", "Zerodha", 9, 28441, 41130, ""], ["Poonawalla Fincorp Ltd", "Zerodha", 38, 17192, 17123, ""], ["HDFC Bank Ltd", "Zerodha", 21, 16598, 14863, ""], ["HCL Technologies Ltd", "Zerodha", 9, 10284, 10815, ""], ["Bajaj Housing Finance Ltd", "Zerodha", 121, 13968, 9898, ""], ["LTM Ltd (formerly LTIMindtree)", "Zerodha", 2, 10198, 7972, ""], ["Affle 3i Ltd", "Zerodha", 3, 4954, 4370, ""], ["L&amp;T Technology Services Ltd", "Zerodha", 1, 4607, 3219, ""], ["Fineotex Chemical Ltd", "Zerodha", 50, 1877, 2711, ""], ["Nippon India ETF Nifty 50 BeES", "Zerodha", 1, 251, 257, ""], ["Nippon India ETF Gold BeES", "Zerodha", 1, 63, 121, ""]], "trades_title": "Trades executed 05.10.2026 (already blended into Wtd Avg Cost)", "trades": [["2026-10-05 12:46:57", "BUY", "Poonawalla Fincorp Ltd", 8, 451, 3606], ["2026-10-05 12:46:33", "BUY", "HDFC Bank Ltd", 2, 707, 1414], ["2026-10-05 12:46:00", "BUY", "Bajaj Finance Ltd", 5, 974, 4869]]}, {"key": "Umesh", "tab": "Dr Umesh Choudhry", "name": "Dr Umesh Choudhry", "broker": "ICICI Direct", "holdings_date": "04.10.2026 + trades of 09.10.2026", "price_basis": "NSE live 09.10.2026 ~09:45 IST", "stmt_invested": 5222229.03, "stmt_mv": 5467267.23, "basis_label": "Umesh stmt – NSE live 09.10", "stale_prices": false, "rows": [["Bajaj Finance Ltd", "ICICI Direct", 2412, 1930286, 2318776, ""], ["Titan Company Ltd", "ICICI Direct", 172, 617467, 751984, ""], ["HDFC Bank Ltd", "ICICI Direct", 673, 599414, 472547, ""], ["AFCOM Holdings Ltd", "ICICI Direct", 240, 203179, 342000, "SME"], ["Poonawalla Fincorp Ltd", "ICICI Direct", 769, 346990, 340513, ""], ["Connplex Cinemas Ltd", "ICICI Direct", 800, 183992, 196000, "SME"], ["Bajaj Housing Finance Ltd", "ICICI Direct", 2198, 255800, 180698, ""], ["LTM Ltd (formerly LTIMindtree)", "ICICI Direct", 37, 216602, 149365, "Shown as LTM Limited"], ["Fineotex Chemical Ltd", "ICICI Direct", 2370, 94397, 133502, ""], ["L&amp;T Technology Services Ltd", "ICICI Direct", 32, 151039, 102480, ""], ["Persistent Systems Ltd", "ICICI Direct", 17, 86733, 95634, ""], ["Vinati Organics Ltd", "ICICI Direct", 82, 160741, 92480, ""], ["Tata Elxsi Ltd", "ICICI Direct", 22, 86278, 67571, ""], ["Affle 3i Ltd", "ICICI Direct", 47, 72448, 66876, ""], ["Tata Consultancy Services Ltd", "ICICI Direct", 29, 122603, 63165, ""], ["Eicher Motors Ltd", "ICICI Direct", 3, 20717, 20805, "New position 09.10.2026"], ["Trent Ltd", "ICICI Direct", 5, 14549, 14550, ""], ["Avenue Supermarts (DMart) Ltd", "ICICI Direct", 4, 14740, 14270, ""], ["Rategain Travel Technologies Ltd", "ICICI Direct", 8, 6760, 6727, "New position 09.10.2026"], ["Nestle India Ltd", "ICICI Direct", 1, 1494, 1325, ""], ["Cash – ICICI Direct", "ICICI Direct", 36000, 36000, 36000, "Uninvested cash, valued at ₹1 per unit"]], "trades_title": "Buys on 09.10.2026 (derived: statement 09.10 minus 04.10; already blended into Wtd Avg Cost)", "trades": [["09.10.2026", "BUY", "Bajaj Finance Ltd", 237, 962.39, 228087], ["09.10.2026", "BUY", "Poonawalla Fincorp Ltd", 176, 442.07, 77804], ["09.10.2026", "BUY", "HDFC Bank Ltd", 55, 701.55, 38585], ["09.10.2026", "BUY", "Titan Company Ltd", 6, 4375.0, 26250], ["09.10.2026", "BUY", "Bajaj Housing Finance Ltd", 280, 82.46, 23089], ["09.10.2026", "BUY", "Persistent Systems Ltd", 4, 5588.0, 22352], ["09.10.2026", "BUY", "Tata Elxsi Ltd", 7, 3081.0, 21567], ["09.10.2026", "BUY", "Eicher Motors Ltd", 3, 6905.67, 20717], ["09.10.2026", "BUY", "Avenue Supermarts (DMart) Ltd", 3, 3560.33, 10681], ["09.10.2026", "BUY", "Affle 3i Ltd", 7, 1415.0, 9905], ["09.10.2026", "BUY", "Trent Ltd", 3, 2885.0, 8655], ["09.10.2026", "BUY", "Rategain Travel Technologies Ltd", 8, 845.0, 6760], ["09.10.2026", "BUY", "L&amp;T Technology Services Ltd", 2, 3185.0, 6370]]}, {"key": "DA", "tab": "DA", "name": "DA", "broker": "HDFC Securities + Kotak Securities", "holdings_date": "Post 12.09.2026 trades (file dated 04.10.2026)", "price_basis": "As on statement (date not printed)", "stmt_invested": 4364995, "stmt_mv": 4141021, "basis_label": "DA stmt – older", "stale_prices": true, "rows": [["Bajaj Finance Ltd", "HDFC Sec + Kotak", 915, 964117, 946110, ""], ["Poonawalla Fincorp Ltd", "HDFC Sec + Kotak", 792, 376533, 352440, ""], ["Titan Company Ltd", "HDFC Sec + Kotak", 59, 260113, 295590, ""], ["HDFC Bank Ltd", "HDFC Sec + Kotak", 337, 250961, 238596, ""], ["Reliance Industries Ltd", "HDFC Securities", 146, 198998, 183668, ""], ["AFCOM Holdings Ltd", "Kotak Securities", 120, 169080, 184800, "Shown as Afcom Holdings Ltd"], ["Connplex Cinemas Ltd", "Kotak Securities", 800, 180000, 212000, "Shown as Connplex Smart Theatres Ltd"], ["Bajaj Housing Finance Ltd", "HDFC Sec + Kotak", 1732, 172732, 145488, ""], ["Persistent Systems Ltd", "HDFC Sec + Kotak", 18, 91873, 99288, ""], ["Jio Financial Services Ltd", "HDFC Securities", 374, 94996, 86020, ""], ["Fineotex Chemical Ltd", "HDFC Securities", 2030, 69020, 117131, ""], ["L&amp;T Technology Services Ltd", "HDFC Sec + Kotak", 24, 85824, 80088, ""], ["Affle 3i Ltd", "HDFC Sec + Kotak", 45, 74914, 70560, ""], ["Nestle India Ltd", "Kotak Securities", 52, 65780, 71916, ""], ["Tata Elxsi Ltd", "HDFC Sec + Kotak", 20, 74720, 67660, ""], ["Eicher Motors Ltd", "HDFC Sec + Kotak", 8, 64347, 60240, ""], ["NCC Ltd", "HDFC Securities", 399, 70623, 56259, ""], ["Trent Ltd", "HDFC Sec + Kotak", 18, 53931, 50436, ""], ["Avenue Supermarts (DM</t>
+    <t xml:space="preserve">{"built": "23.10.2026", "close_date": "22.10.2026", "prev_date": "21.10.2026", "closes": {"Bajaj Finance Ltd": [942.1, 926], "Titan Company Ltd": [4350, 4380.9], "Poonawalla Fincorp Ltd": [432.45, 437.3], "HDFC Bank Ltd": [694.05, 706.95], "HCL Technologies Ltd": [1421.7, 1424.2], "Bajaj Housing Finance Ltd": [81.02, 81.17], "LTM Ltd (formerly LTIMindtree)": [4274, 4298], "Affle 3i Ltd": [1362.8, 1395.3], "L&amp;T Technology Services Ltd": [3954.8, 3996.3], "Fineotex Chemical Ltd": [51.55, 52.73], "AFCOM Holdings Ltd": [1371.45, 1414.9], "Connplex Cinemas Ltd": [234.25, 239.7], "Vinati Organics Ltd": [1089.9, 1096.1], "Persistent Systems Ltd": [5740.5, 5858.5], "Tata Consultancy Services Ltd": [2506.9, 2529], "Tata Elxsi Ltd": [3846.8, 3848.6], "Trent Ltd": [2775.8, 2822], "Avenue Supermarts (DMart) Ltd": [3166, 3250.9], "Nestle India Ltd": [1189.9, 1223.9], "Eicher Motors Ltd": [7084.5, 7170.5], "InterGlobe Aviation Ltd (IndiGo)": [4600, 4641.5], "Waaree Energies Ltd": [2370, 2455], "Rategain Travel Technologies Ltd": [788.1, 779.7], "Shriram Properties Ltd": [65.13, 66.01], "Bagmane Prime Office REIT": [105.54, 105.53], "Bharti Airtel Ltd": [1895, 1891.7], "Orient Electric Ltd": [188.91, 189.6], "Reliance Industries Ltd": [1184.5, 1209], "Jio Financial Services Ltd": [210.8, 211.39], "NCC Ltd": [120.17, 123.2], "Capacite Infraprojects Ltd": [154.93, 161.42], "Indus Towers Ltd": [381.85, 379], "Vedanta Power (VEDPOWER)": [29.51, 30.3], "Moschip Technologies Ltd": [169.62, 173.28], "Godrej Consumer Products Ltd": [860.2, 859], "Vedant Fashions (Manyavar) Ltd": [490.05, 501.7], "Indian Railway Finance Corp Ltd": [77, 76.8], "RITES Ltd": [196.09, 197.42], "Indraprastha Gas Ltd": [140.01, 142.31], "Great Eastern Shipping Co Ltd": [1518.6, 1506.3], "HUDCO Ltd": [151.77, 154.34], "NTPC Green Energy Ltd": [84.35, 84.04], "Brigade Enterprises Ltd": [557.1, 570.2], "GFL Ltd": [54.58, 55.21], "Sonata Software Ltd": [239.75, 240.5], "Syngene International Ltd": [372.5, 376.45], "Ambuja Cements Ltd": [363, 359.9], "Astec LifeSciences Ltd": [669.2, 665.9], "Gujarat Energy": [218.13, 222.02], "Indian Energy Exchange Ltd": [104, 103.28], "Vinyl Chemicals (India) Ltd": [205.95, 201.62], "JK Tyre &amp; Industries Ltd": [323, 327.55], "REC Ltd": [301.1, 302.5], "Shakti Pumps (India) Ltd": [400.65, 403.8], "Ashoka Buildcon Ltd": [101.09, 102.18], "Cyient Ltd": [1143.7, 1169.7], "Utkarsh Small Finance Bank Ltd": [12.17, 12.55], "Orient Cement Ltd": [116.89, 113.81], "Waaree Renewable Technologies Ltd": [718.95, 743.25], "Eureka Forbes Ltd": [316.8, 326.15], "Eternal Ltd": [304.45, 312.35], "VRL Logistics Ltd": [266.55, 284.85], "Kotak Mahindra Bank Ltd": [437, 437.8], "Alkyl Amines Chemicals Ltd": [1704.2, 1721.4], "Pfizer Ltd": [3688.9, 3754.7], "Garware Technical Fibres Ltd": [749.6, 740.7], "Central Depository Services (India) Ltd": [1225, 1237.2], "Abbott India Ltd": [25360, 25680], "Tanla Platforms Ltd": [581.3, 562.1], "Vaibhav Global Ltd": [195.22, 199.32], "Asian Paints Ltd": [2284.8, 2319.4], "Aarti Drugs Ltd": [380.05, 388.6], "Deepak Nitrite Ltd": [1487.4, 1506.2], "Infosys Ltd": [1153.35, 1168], "Dr Lal PathLabs Ltd": [1843.7, 1836.1], "Page Industries Ltd": [34425, 34870], "Clean Science and Technology Ltd": [748.05, 741.1], "Jubilant FoodWorks Ltd": [404.9, 405], "ICICI Prudential Life Insurance Co Ltd": [431, 431.5]}, "screener_urls": {"Bajaj Finance Ltd": "/company/BAJFINANCE/consolidated/", "Titan Company Ltd": "/company/TITAN/consolidated/", "Poonawalla Fincorp Ltd": "/company/POONAWALLA/consolidated/", "HDFC Bank Ltd": "/company/HDFCBANK/consolidated/", "HCL Technologies Ltd": "/company/HCLTECH/consolidated/", "Bajaj Housing Finance Ltd": "/company/BAJAJHFL/", "LTM Ltd (formerly LTIMindtree)": "/company/LTM/", "Affle 3i Ltd": "/company/AFFLE/consolidated/", "L&amp;T Technology Services Ltd": "/company/LTTS/consolidated/", "Fineotex Chemical Ltd": "/company/FCL/consolidated/", "AFCOM Holdings Ltd": "/company/544224/", "Connplex Cinemas Ltd": "/company/CONNPLEX/", "Vinati Organics Ltd": "/company/VINATIORGA/", "Persistent Systems Ltd": "/company/PERSISTENT/consolidated/", "Tata Consultancy Services Ltd": "/company/TCS/consolidated/", "Tata Elxsi Ltd": "/company/TATAELXSI/", "Trent Ltd": "/company/TRENT/consolidated/", "Avenue Supermarts (DMart) Ltd": "/company/DMART/consolidated/", "Nestle India Ltd": "/company/NESTLEIND/", "Eicher Motors Ltd": "/company/EICHERMOT/consolidated/", "InterGlobe Aviation Ltd (IndiGo)": "/company/INDIGO/", "Waaree Energies Ltd": "/company/WAAREEENER/consolidated/", "Rategain Travel Technologies Ltd": "/company/RATEGAIN/consolidated/", "International Gemmological Institute (India) Ltd": "/company/IGIL/", "Shriram Properties Ltd": "/company/SHRIRAMPPS/consolidated/", "Bagmane Prime Office REIT": "/company/BAGMANE/consolidated/", "Bharti Airtel Ltd": "/company/BHARTIARTL/consolidated/", "Orient Electric Ltd": "/company/ORIENTELEC/", "Reliance Industries Ltd": "/company/RELIANCE/", "Jio Financial Services Ltd": "/company/JIOFIN/", "NCC Ltd": "/company/NCC/", "Capacite Infraprojects Ltd": "/company/CAPACITE/", "Indus Towers Ltd": "/company/INDUSTOWER/", "Vedanta Power (VEDPOWER)": "/company/VEDPOWER/consolidated/", "Moschip Technologies Ltd": "/company/MOSCHIP/", "Godrej Consumer Products Ltd": "/company/GODREJCP/", "Vedant Fashions (Manyavar) Ltd": "/company/MANYAVAR/", "Indian Railway Finance Corp Ltd": "/company/IRFC/", "RITES Ltd": "/company/RITES/", "Indraprastha Gas Ltd": "/company/IGL/", "Great Eastern Shipping Co Ltd": "/company/GESHIP/", "HUDCO Ltd": "/company/HUDCO/", "NTPC Green Energy Ltd": "/company/NTPCGREEN/", "Brigade Enterprises Ltd": "/company/BRIGADE/", "GFL Ltd": "/company/GFLLIMITED/", "Sonata Software Ltd": "/company/SONATSOFTW/", "Syngene International Ltd": "/company/SYNGENE/", "Ambuja Cements Ltd": "/company/AMBUJACEM/", "Astec LifeSciences Ltd": "/company/ASTEC/", "Gujarat Energy": "/company/GUJENERGY/consolidated/", "Indian Energy Exchange Ltd": "/company/IEX/", "Vinyl Chemicals (India) Ltd": "/company/VINYLINDIA/", "JK Tyre &amp; Industries Ltd": "/company/JKTYRE/", "REC Ltd": "/company/RECLTD/", "Shakti Pumps (India) Ltd": "/company/SHAKTIPUMP/", "Ashoka Buildcon Ltd": "/company/ASHOKA/", "Cyient Ltd": "/company/CYIENT/", "Utkarsh Small Finance Bank Ltd": "/company/UTKARSHBNK/", "Orient Cement Ltd": "/company/ORIENTCEM/", "Waaree Renewable Technologies Ltd": "/company/WAAREERTL/consolidated/", "Eureka Forbes Ltd": "/company/EUREKAFORB/", "Eternal Ltd": "/company/ETERNAL/consolidated/", "VRL Logistics Ltd": "/company/VRLLOG/", "Kotak Mahindra Bank Ltd": "/company/KOTAKBANK/consolidated/", "Alkyl Amines Chemicals Ltd": "/company/ALKYLAMINE/", "Pfizer Ltd": "/company/PFIZER/", "Garware Technical Fibres Ltd": "/company/GARFIBRES/consolidated/", "Central Depository Services (India) Ltd": "/company/CDSL/consolidated/", "Abbott India Ltd": "/company/ABBOTINDIA/", "Tanla Platforms Ltd": "/company/TANLA/consolidated/", "Vaibhav Global Ltd": "/company/VAIBHAVGBL/consolidated/", "Asian Paints Ltd": "/company/ASIANPAINT/consolidated/", "Aarti Drugs Ltd": "/company/AARTIDRUGS/consolidated/", "Deepak Nitrite Ltd": "/company/DEEPAKNTR/consolidated/", "Infosys Ltd": "/company/INFY/consolidated/", "Dr Lal PathLabs Ltd": "/company/LALPATHLAB/consolidated/", "Page Industries Ltd": "/company/PAGEIND/", "Clean Science and Technology Ltd": "/company/CLEAN/consolidated/", "Jubilant FoodWorks Ltd": "/company/JUBLFOOD/consolidated/", "ICICI Prudential Life Insurance Co Ltd": "/company/ICICILIFE/"}, "notes": ["No exchange close for the 4 ETFs (Nifty 50 BeES, Gold BeES, Liquid BeES, HDFC Gold ETF), the Utkarsh SFB rights entitlement, NEPC Agro and PSL Ltd – these stay at statement price (Liquid BeES holds near ₹1,000).", "Names aligned across statements: LTM Ltd = LTIMindtree (DA); Connplex Cinemas = Connplex Smart Theatres (DA); AFCOM = Afcom Holdings.", "Trades blended into holdings and listed on each tab: Vidushi 05.10.2026 (3 buys, ₹9,889); Dr Umesh 09.10.2026 (13 buys, ₹5.01 L, incl. new Eicher Motors and Rategain).", "Dr Umesh holds ₹36,000 uninvested cash at ICICI Direct – row 'Cash – ICICI Direct' at ₹1 per unit, counted in totals but not as a holding.", "Statement invested/market totals reconcile to transcribed rows within ₹2 (rupee rounding on the statements).", "Gautam: NEPC Agro Foods (144 sh) and PSL Ltd (1,000 sh) still have no cost or price on the statement – carried at nil.", "Manish Shilpa: Axis and HDFC CSVs carry short names (e.g. 'Nip. India Nifty', 'C D S L', 'Waaree Renewab.'); aligned to canonical names. 'Nippon ETF Infra' is carried as Nippon India ETF Infra BeES. ETFs have no exchange close and stay on the statement price.", "Gautam refreshed from HDFC statement of 23.10.2026 (31 lines; invested ₹55,01,448 reconciles to ₹55,01,448.50). Changes vs the 05.10 statement are derived: 16 buys and 1 exit (International Gemmological Institute, 80 sh, valued at the 05.10 statement price).", "Vidushi, Dr Umesh and DA have no new statements since 09.10 and are only repriced to the 22.10.2026 close.", "Manish Shilpa is new (23.10.2026): Axis Direct (Shilpa), Axis Direct (Manish), HDFC Securities (Manish) and Manish's Axis mutual fund (UTI Nifty 50 Index Fund – 2 folios, ₹1,99,990 invested) merged into one account. A stock held in more than one demat is one row; the row note lists the split. Statement totals: invested ₹98,57,779, market value ₹1,16,36,410 (equity at live ~11:23 IST prices, MF at statement NAV).", "Saloni Mehra is new (Angel One): 26-holding statement of 20.10.2026 (invested ₹1,10,23,244; market value ₹1,13,95,012) rolled forward with the 15 trades of 21–22.10.2026 and the 24 buys of 23.10.2026 (₹7,25,477 at executed prices). 21–22.10 buys include all charges; 23.10 charges are not yet shown by Angel One, so those buys are at executed price only. Kotak Mahindra Bank (1,580 sh, realised ≈ ₹62,288) and LIC Housing Finance (700 sh, realised ≈ ₹-29,271) were sold out; Trent is a new position. Statement invested is the row sum (no printed total after trades); rows touched by trades have no statement value, so 'Stmt Market Value' covers untraded rows only."], "portfolios": [{"key": "Gautam", "tab": "Gautam", "name": "Gautam", "broker": "HDFC Securities", "holdings_date": "23.10.2026", "price_basis": "HDFC statement prices 23.10.2026", "stmt_invested": 5501448.5, "stmt_mv": 5224564.0, "basis_label": "Gautam stmt – 23.10", "stale_prices": false, "rows": [["Bajaj Finance Ltd", "HDFC Securities", 1901, 1912279, 1783138, ""], ["Poonawalla Fincorp Ltd", "HDFC Securities", 1132, 527172, 489024, ""], ["Nippon India ETF Nifty 1D Rate Liquid BeES", "HDFC Securities", 325, 325000, 325000, ""], ["HDFC Bank Ltd", "HDFC Securities", 447, 320122, 310218, ""], ["LTM Ltd (formerly LTIMindtree)", "HDFC Securities", 60, 273840, 256440, "Shown as LTM Limited"], ["Tata Consultancy Services Ltd", "HDFC Securities", 92, 210588, 230644, ""], ["Titan Company Ltd", "HDFC Securities", 47, 223898, 204450, ""], ["Connplex Cinemas Ltd", "HDFC Securities", 800, 211200, 192000, ""], ["AFCOM Holdings Ltd", "HDFC Securities", 120, 199920, 165240, "Shown as AFCOM"], ["Tata Elxsi Ltd", "HDFC Securities", 41, 140474, 157727, ""], ["Eicher Motors Ltd", "HDFC Securities", 20, 147414, 141680, ""], ["Bajaj Housing Finance Ltd", "HDFC Securities", 1600, 132930, 129920, ""], ["L&amp;T Technology Services Ltd", "HDFC Securities", 30, 104531, 119880, ""], ["Persistent Systems Ltd", "HDFC Securities", 19, 105436, 109060, ""], ["InterGlobe Aviation Ltd (IndiGo)", "HDFC Securities", 20, 103860, 92160, "Shown as InterGlobe Aviation Ltd (Indigo)"], ["Affle 3i Ltd", "HDFC Securities", 66, 106115, 89958, ""], ["Trent Ltd", "HDFC Securities", 31, 86006, 86056, ""], ["Avenue Supermarts (DMart) Ltd", "HDFC Securities", 24, 89946, 75984, ""], ["Waaree Energies Ltd", "HDFC Securities", 27, 68363, 63990, ""], ["Rategain Travel Technologies Ltd", "HDFC Securities", 72, 59636, 56808, ""], ["Fineotex Chemical Ltd", "HDFC Securities", 830, 46702, 43575, ""], ["Nestle India Ltd", "HDFC Securities", 22, 27683, 26180, ""], ["Shriram Properties Ltd", "HDFC Securities", 250, 19250, 16925, ""], ["Bagmane Prime Office REIT", "HDFC Securities", 150, 16050, 15900, ""], ["Nippon India ETF Gold BeES", "HDFC Securities", 121, 13310, 14883, ""], ["Vinati Organics Ltd", "HDFC Securities", 10, 11941, 10970, ""], ["Bharti Airtel Ltd", "HDFC Securities", 5, 9610, 9475, ""], ["Orient Electric Ltd", "HDFC Securities", 25, 4500, 3850, ""], ["HDFC Gold ETF", "HDFC Securities", 27, 3672, 3429, ""], ["NEPC Agro Foods Ltd", "HDFC Securities", 144, null, null, "No cost or price on statement (marked *) – carried at nil"], ["PSL Ltd (formerly PSL Holdings Ltd)", "HDFC Securities", 1000, null, null, "No cost or price on statement (marked *) – carried at nil"]], "trades": [["05.10–23.10.2026", "BUY", "Affle 3i Ltd", 8, 1364.62, 10917], ["05.10–23.10.2026", "BUY", "Avenue Supermarts (DMart) Ltd", 3, 3179.0, 9537], ["05.10–23.10.2026", "BUY", "Bajaj Finance Ltd", 237, 932.3, 220956], ["05.10–23.10.2026", "BUY", "Bajaj Housing Finance Ltd", 274, 81.1, 22222], ["05.10–23.10.2026", "BUY", "Eicher Motors Ltd", 3, 7055.0, 21165], ["05.10–23.10.2026", "BUY", "Fineotex Chemical Ltd", 138, 52.29, 7216], ["05.10–23.10.2026", "BUY", "HDFC Bank Ltd", 57, 693.96, 39556], ["05.10–23.10.2026", "SELL", "International Gemmological Institute (India) Ltd", 80, 314.0, 25120], ["05.10–23.10.2026", "BUY", "L&amp;T Technology Services Ltd", 5, 3954.0, 19770], ["05.10–23.10.2026", "BUY", "Nippon India ETF Nifty 1D Rate Liquid BeES", 25, 1000.0, 25000], ["05.10–23.10.2026", "BUY", "Persistent Systems Ltd", 3, 5806.0, 17418], ["05.10–23.10.2026", "BUY", "Poonawalla Fincorp Ltd", 131, 432.84, 56702], ["05.10–23.10.2026", "BUY", "Rategain Travel Technologies Ltd", 9, 789.22, 7103], ["05.10–23.10.2026", "BUY", "Tata Elxsi Ltd", 7, 3852.57, 26968], ["05.10–23.10.2026", "BUY", "Titan Company Ltd", 6, 4349.0, 26094], ["05.10–23.10.2026", "BUY", "Trent Ltd", 3, 2787.33, 8362], ["05.10–23.10.2026", "BUY", "Waaree Energies Ltd", 3, 2367.33, 7102]], "trades_title": "Changes between 05.10 and 23.10 statements (derived; buys at implied avg cost, sells at 05.10 statement price)"}, {"key": "Manish", "tab": "Manish Shilpa", "name": "Manish Shilpa", "broker": "Axis Direct + HDFC Securities", "holdings_date": "23.10.2026 (live, ~11:23 IST)", "price_basis": "Live LTP 23.10.2026 ~11:23 IST (equity); MF NAV per Axis statement 23.10.2026 (three demats + MF merged)", "basis_label": "Manish Shilpa stmt – live 23.10", "stale_prices": false, "stmt_invested": 9857779, "stmt_mv": 11636410.18, "rows": [["Bajaj Housing Finance Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 3762.0, 432693, 292084, "Axis Direct Shilpa 267; Axis Direct Manish 3396; HDFC Securities Manish 99"], ["Nippon India ETF Nifty 1D Rate Liquid BeES", "Axis Direct (Shilpa) + Axis Direct (Manish)", 4.0, 5559, 5559, "Axis Direct Shilpa 1; Axis Direct Manish 3"], ["Eicher Motors Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 6.0, 43747, 41760, "Axis Direct Shilpa 1; Axis Direct Manish 5"], ["Waaree Renewable Technologies Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 5.0, 5105, 3398, "Axis Direct Shilpa 1; Axis Direct Manish 4"], ["Vinati Organics Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 17.0, 29694, 18142, "Axis Direct Shilpa 1; Axis Direct Manish 15; HDFC Securities Manish 1"], ["Nippon India ETF Nifty 50 BeES", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 11160.0, 1687580, 2864693, "Axis Direct Shilpa 10; Axis Direct Manish 11049; HDFC Securities Manish 101"], ["Affle 3i Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 47.0, 76969, 62254, "Axis Direct Shilpa 18; Axis Direct Manish 25; HDFC Securities Manish 4"], ["Eureka Forbes Ltd", "Axis Direct (Shilpa)", 35.0, 19821, 10747, ""], ["HDFC Gold ETF", "Axis Direct (Shilpa) + Axis Direct (Manish)", 168.0, 15354, 20131, "Axis Direct Shilpa 93; Axis Direct Manish 75"], ["Eternal Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 34.0, 10336, 10411, "Axis Direct Shilpa 9; Axis Direct Manish 25"], ["VRL Logistics Ltd", "Axis Direct (Shilpa)", 50.0, 13962, 12668, ""], ["Tata Elxsi Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 32.0, 212270, 120470, "Axis Direct Shilpa 1; Axis Direct Manish 31"], ["Waaree Energies Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 6.0, 18946, 13900, "Axis Direct Shilpa 2; Axis Direct Manish 4"], ["Bajaj Finance Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 3895.0, 2912389, 3625900, "Axis Direct Shilpa 226; Axis Direct Manish 3165; HDFC Securities Manish 504"], ["Persistent Systems Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 11.0, 49823, 63648, "Axis Direct Shilpa 3; Axis Direct Manish 8"], ["Kotak Mahindra Bank Ltd", "Axis Direct (Shilpa) + HDFC Securities (Manish)", 160.0, 63501, 69298, "Axis Direct Shilpa 30; HDFC Securities Manish 130"], ["Trent Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 10.0, 30536, 27130, "Axis Direct Shilpa 3; Axis Direct Manish 7"], ["LTM Ltd (formerly LTIMindtree)", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 66.0, 348137, 276816, "Axis Direct Shilpa 2; Axis Direct Manish 52; HDFC Securities Manish 12"], ["Avenue Supermarts (DMart) Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish)", 6.0, 23637, 18758, "Axis Direct Shilpa 2; Axis Direct Manish 4"], ["HDFC Bank Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 1013.0, 812683, 697943, "Axis Direct Shilpa 58; Axis Direct Manish 899; HDFC Securities Manish 56"], ["L&amp;T Technology Services Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 72.0, 303467, 282588, "Axis Direct Shilpa 2; Axis Direct Manish 64; HDFC Securities Manish 6"], ["Titan Company Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 165.0, 564530, 700725, "Axis Direct Shilpa 7; Axis Direct Manish 153; HDFC Securities Manish 5"], ["Poonawalla Fincorp Ltd", "Axis Direct (Shilpa) + Axis Direct (Manish) + HDFC Securities (Manish)", 1394.0, 622513, 578058, "Axis Direct Shilpa 206; Axis Direct Manish 1180; HDFC Securities Manish 8"], ["Alkyl Amines Chemicals Ltd", "Axis Direct (Manish)", 3.0, 12327, 4865, ""], ["Indian Energy Exchange Ltd", "Axis Direct (Manish)", 12.0, 2262, 1209, ""], ["Pfizer Ltd", "Axis Direct (Manish)", 1.0, 6103, 3601, ""], ["Jio Financial Services Ltd", "Axis Direct (Manish)", 32.0, 3256, 6556, ""], ["Garware Technical Fibres Ltd", "Axis Direct (Manish)", 5.0, 3380, 3606, ""], ["Reliance Industries Ltd", "Axis Direct (Manish)", 32.0, 38635, 37526, ""], ["Central Depository Services (India) Ltd", "Axis Direct (Manish)", 134.0, 51658, 158643, ""], ["Connplex Cinemas Ltd", "Axis Direct (Manish)", 800.0, 188075, 175200, ""], ["Tata Consultancy Services Ltd", "Axis Direct (Manish)", 29.0, 97994, 74127, ""], ["Abbott India Ltd", "Axis Direct (Manish)", 3.0, 54700, 74400, ""], ["Tanla Platforms Ltd", "Axis Direct (Manish)", 33.0, 40602, 18610, ""], ["Fineotex Chemical Ltd", "Axis Direct (Manish)", 3500.0, 117474, 167755, ""], ["Nippon India ETF Infra BeES", "Axis Direct (Manish)", 34.0, 14923, 29819, ""], ["Vaibhav Global Ltd", "Axis Direct (Manish)", 5.0, 1680, 936, ""], ["Asian Paints Ltd", "Axis Direct (Manish)", 22.0, 78545, 50046, ""], ["Aarti Drugs Ltd", "Axis Direct (Manish)", 6.0, 3768, 2241, ""], ["Deepak Nitrite Ltd", "Axis Direct (Manish)", 1.0, 2393, 1427, ""], ["Infosys Ltd", "Axis Direct (Manish)", 64.0, 102862, 74240, ""], ["Rategain Travel Technologies Ltd", "Axis Direct (Manish)", 5.0, 3317, 3815, ""], ["AFCOM Holdings Ltd", "Axis Direct (Manish)", 360.0, 362724, 457200, ""], ["Clean Science and Technology Ltd", "Axis Direct (Manish)", 14.0, 22090, 10168, ""], ["Dr Lal PathLabs Ltd", "HDFC Securities (Manish)", 44.0, 52231, 80313, ""], ["Page Industries Ltd", "HDFC Securities (Manish)", 2.0, 93537, 67650, ""], ["UTI Nifty 50 Index Fund - Growth", "Axis Direct (Manish) MF", 2004.589, 199990, 315380.18, "Mutual fund, 2 folios (1,804.130 + 200.459 units); NAV ₹157.3291 per Axis statement 23.10.2026 – no exchange close, statement NAV used"]], "trades_title": "", "trades": []}, {"key": "Saloni", "tab": "Saloni Mehra", "name": "Saloni Mehra", "broker": "Angel One", "holdings_date": "20.10.2026 + trades of 21–23.10.2026", "price_basis": "20.10.2026 statement prices (only for rows with no trades since)", "basis_label": "Saloni stmt – 20.10", "stale_prices": true, "stmt_invested": 11739506, "stmt_mv": 2974667, "rows": [["Bajaj Finance Ltd", "Angel One", 4940, 4650978, null, "Trades 21.10 buy 362 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Titan Company Ltd", "Angel One", 250, 1071947, null, "Trades 21.10 buy 9 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Jubilant FoodWorks Ltd", "Angel One", 2000, 845300, 827000, ""], ["Tata Consultancy Services Ltd", "Angel One", 305, 659410, 750575, ""], ["HDFC Bank Ltd", "Angel One", 1140, 876490, null, "Trades 21.10 buy 79 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["AFCOM Holdings Ltd", "Angel One", 360, 361080, 536742, ""], ["LTM Ltd (formerly LTIMindtree)", "Angel One", 83, 323526, 353987, ""], ["ICICI Prudential Life Insurance Co Ltd", "Angel One", 700, 340305, 306600, ""], ["Bajaj Housing Finance Ltd", "Angel One", 4227, 360078, null, "Trades 21.10 buy 547 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Fineotex Chemical Ltd", "Angel One", 5141, 224820, null, "23.10 buys at executed price, charges not yet known"], ["L&amp;T Technology Services Ltd", "Angel One", 78, 269544, null, "Trades 22.10 buy 1 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Tata Elxsi Ltd", "Angel One", 65, 262060, null, "Trades 22.10 buy 6 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Connplex Cinemas Ltd", "Angel One", 800, 170200, 198400, ""], ["Poonawalla Fincorp Ltd", "Angel One", 1918, 824630, null, "Trades 21.10 buy 970 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Affle 3i Ltd", "Angel One", 78, 114527, null, "Trades 22.10 buy 8 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Vinati Organics Ltd", "Angel One", 68, 84214, null, "23.10 buys at executed price, charges not yet known"], ["Rategain Travel Technologies Ltd", "Angel One", 82, 70997, null, "Trades 22.10 buy 10 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Persistent Systems Ltd", "Angel One", 13, 68506, null, "Trades 22.10 buy 1 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Waaree Energies Ltd", "Angel One", 11, 31435, null, "23.10 buys at executed price, charges not yet known"], ["Eicher Motors Ltd", "Angel One", 8, 57444, null, "Trades 22.10 buy 4 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Avenue Supermarts (DMart) Ltd", "Angel One", 10, 35107, null, "Trades 22.10 buy 4 (charges included in cost); 23.10 buys at executed price, charges not yet known"], ["Nestle India Ltd", "Angel One", 7, 9110, null, "23.10 buys at executed price, charges not yet known"], ["Waaree Renewable Technologies Ltd", "Angel One", 5, 4281, null, "23.10 buys at executed price, charges not yet known"], ["HDFC Gold ETF", "Angel One", 11, 1387, 1363, ""], ["Trent Ltd", "Angel One", 8, 22130, null, "New position, bought 22.10 (charges included in cost); no statement value; 23.10 buys at executed price, charges not yet known"]], "trades_title": "Angel One trades 21–23.10.2026 (blended into holdings; 21–22.10 buys include charges, 23.10 buys at executed price)", "trades": [["21.10.2026", "SELL", "Kotak Mahindra Bank Ltd", 1580, 445.65, 704127], ["21.10.2026", "BUY", "Bajaj Housing Finance Ltd", 547, 81.76, 44723], ["21.10.2026", "BUY", "Titan Company Ltd", 9, 4419.44, 39775], ["21.10.2026", "BUY", "HDFC Bank Ltd", 79, 710.85, 56157], ["21.10.2026", "BUY", "Poonawalla Fincorp Ltd", 970, 445.53, 432164], ["21.10.2026", "SELL", "LIC Housing Finance Ltd", 700, 512.6, 358820], ["21.10.2026", "BUY", "Bajaj Finance Ltd", 362, 935.65, 338705], ["22.10.2026", "BUY", "Persistent Systems Ltd", 1, 5818.0, 5818], ["22.10.2026", "BUY", "Tata Elxsi Ltd", 6, 3852.22, 23113], ["22.10.2026", "BUY", "L&amp;T Technology Services Ltd", 1, 3930.0, 3930], ["22.10.2026", "BUY", "Trent Ltd", 5, 2780.9, 13904], ["22.10.2026", "BUY", "Affle 3i Ltd", 8, 1380.9, 11047], ["22.10.2026", "BUY", "Eicher Motors Ltd", 4, 7063.5, 28254], ["22.10.2026", "BUY", "Avenue Supermarts (DMart) Ltd", 4, 3191.1, 12764], ["22.10.2026", "BUY", "Rategain Travel Technologies Ltd", 10, 776.5, 7765], ["23.10.2026", "BUY", "Fineotex Chemical Ltd", 78, 47.85, 3732], ["23.10.2026", "BUY", "Vinati Organics Ltd", 5, 1067.72, 5339], ["23.10.2026", "BUY", "Waaree Renewable Technologies Ltd", 1, 676.4, 676], ["23.10.2026", "BUY", "Waaree Energies Ltd", 1, 2311.9, 2312], ["23.10.2026", "BUY", "Nestle India Ltd", 3, 1169.4, 3508], ["23.10.2026", "BUY", "Avenue Supermarts (DMart) Ltd", 3, 3130.8, 9392], ["23.10.2026", "BUY", "Trent Ltd", 3, 2730.9, 8193], ["23.10.2026", "BUY", "Eicher Motors Ltd", 2, 6965.5, 13931], ["23.10.2026", "BUY", "Rategain Travel Technologies Ltd", 6, 756.6, 4540], ["23.10.2026", "BUY", "Affle 3i Ltd", 5, 1328.62, 6643], ["23.10.2026", "BUY", "Titan Company Ltd", 6, 4246.32, 25478], ["23.10.2026", "BUY", "L&amp;T Technology Services Ltd", 3, 3933.2, 11800], ["23.10.2026", "BUY", "Persistent Systems Ltd", 2, 5795.5, 11591], ["23.10.2026", "BUY", "Tata Elxsi Ltd", 4, 3785.9, 15144], ["23.10.2026", "BUY", "Bajaj Housing Finance Ltd", 367, 77.4, 28406], ["23.10.2026", "BUY", "HDFC Bank Ltd", 51, 688.6, 35119], ["23.10.2026", "BUY", "Poonawalla Fincorp Ltd", 651, 417.5, 271792], ["23.10.2026", "BUY", "Bajaj Finance Ltd", 227, 933.48, 211900], ["23.10.2026", "BUY", "Waaree Renewable Technologies Ltd", 1, 676.95, 677], ["23.10.2026", "BUY", "Waaree Energies Ltd", 2, 2297.9, 4596], ["23.10.2026", "BUY", "Fineotex Chemical Ltd", 233, 48.17, 11224], ["23.10.2026", "BUY", "Vinati Organics Ltd", 15, 1071.81, 16077], ["23.10.2026", "BUY", "Persistent Systems Ltd", 2, 5779.5, 11559], ["23.10.2026", "BUY", "L&amp;T Technology Services Ltd", 3, 3949.8, 11849]]}, {"key": "Vidushi", "tab": "Vidushi Malhotra", "name": "Vidushi Malhotra", "broker": "Zerodha", "holdings_date": "04.10.2026 (+ trades of 05.10.2026)", "price_basis": "LTP 05.10.2026", "stmt_invested": 201361, "stmt_mv": 230319, "basis_label": "Vidushi stmt – LTP 05.10", "stale_prices": false, "rows": [["Bajaj Finance Ltd", "Zerodha", 121, 92928, 117842, ""], ["Titan Company Ltd", "Zerodha", 9, 28441, 41130, ""], ["Poonawalla Fincorp Ltd", "Zerodha", 38, 17192, 17123, ""], ["HDFC Bank Ltd", "Zerodha", 21, 16598, 14863, ""], ["HCL Technologies Ltd", "Zerodha", 9, 10284, 10815, ""], ["Bajaj Housing Finance Ltd", "Zerodha", 121, 13968, 9898, ""], ["LTM Ltd (formerly LTIMindtree)", "Zerodha", 2, 10198, 7972, ""], ["Affle 3i Ltd", "Zerodha", 3, 4954, 4370, ""], ["L&amp;T Technology Services Ltd", "Zerodha", 1, 4607, 3219, ""], ["Fineotex Chemical Ltd", "Zerodha", 50, 1877, 2711, ""], ["Nippon India ETF Nifty 50 BeES", "Zerodha", 1, 251, 257, ""], ["Nippon India ETF Gold BeES", "Zerodha", 1, 63, 121, ""]], "trades_title": "Trades executed 05.10.2026 (already blended into Wtd Avg Cost)", "trades": [["2026-10-05 12:46:57", "BUY", "Poonawalla Fincorp Ltd", 8, 451, 3606], ["2026-10-05 12:46:33", "BUY", "HDFC Bank Ltd", 2, 707, 1414], ["2026-10-05 12:46:00", "BUY", "Bajaj Finance Ltd", 5, 974, 4869]]}, {"key": "Umesh", "tab": "Dr Umesh Choudhry", "name": "Dr Umesh Choudhry", "broker": "ICICI Direct", "holdings_date": "04.10.2026 + trades of 09.10.2026", "price_basis": "NSE live 09.10.2026 ~09:45 IST", "stmt_invested": 5222229.03, "stmt_mv": 5467267.23, "basis_label": "Umesh stmt – NSE live 09.10", "stale_prices": false, "rows": [["Bajaj Finance Ltd", "ICICI Direct", 2412, 1930286, 2318776, ""], ["Titan Company Ltd", "ICICI Direct", 172, 617467, 751984, ""], ["HDFC Bank Ltd", "ICICI Direct", 673, 599414, 472547, ""], ["AFCOM Holdings Ltd", "ICICI Direct", 240, 203179, 342000, "SME"], ["Poonawalla Fincorp Ltd", "ICICI Direct", 769, 346990, 340513, ""], ["Connplex Cinemas Ltd", "ICICI Direct", 800, 183992, 196000, "SME"], ["Bajaj Housing Finance Ltd", "ICICI Direct", 2198, 255800, 180698, ""], ["LTM Ltd (formerly LTIMindtree)", "ICICI Direct", 37, 216602, 149365, "Shown as LTM Limited"], ["Fineotex Chemical Ltd", "ICICI Direct", 2370, 94397, 133502, ""], ["L&amp;T Technology Services Ltd", "ICICI Direct", 32, 151039, 102480, ""], ["Persistent Systems Ltd", "ICICI Direct", 17, 86733, 95634, ""], ["Vinati Organics Ltd", "ICICI Direct", 82, 160741, 92480, ""], ["Tata Elxsi Ltd", "ICICI Direct", 22, 86278, 67571, ""], ["Affle 3i Ltd", "ICICI Direct", 47, 72448, 66876, ""], ["Tata Consultancy Services Ltd", "ICICI Direct", 29, 122603, 63165, ""], ["Eicher Motors Ltd", "ICICI Direct", 3, 20717, 20805, "New position 09.10.2026"], ["Trent Ltd", "ICICI Direct", 5, 14549, 14550, ""], ["Avenue Supermarts (DMart) Ltd", "ICICI Direct", 4, 14740, 14270, ""], ["Rategain Travel Technologies Ltd", "ICICI Direct", 8, 6760, 6727, "New position 09.10.2026"], ["Nestle India Ltd", "ICICI Direct", 1, 1494, 1325, ""], ["Cash – ICICI Direct", "ICICI Direct", 36000, 36000, 36000, "Uninvested cash, valued at ₹1 per unit"]], "trades_title": "Buys on 09.10.2026 (derived: statement 09.10 minus 04.10; already blended into Wtd Avg Cost)", "trades": [["09.10.2026", "BUY", "Bajaj Finance Ltd", 237, 962.39, 228087], ["09.10.2026", "BUY", "Poonawalla Fincorp Ltd", 176, 442.07, 77804], ["09.10.2026", "BUY", "HDFC Bank Ltd"</t>
   </si>
   <si>
-    <t xml:space="preserve">art) Ltd", "HDFC Sec + Kotak", 13, 51822, 47944, ""], ["Capacite Infraprojects Ltd", "HDFC Securities", 230, 64400, 44160, ""], ["HCL Technologies Ltd", "Kotak Securities", 33, 47223, 39798, ""], ["Indus Towers Ltd", "Kotak Securities", 111, 45510, 43068, ""], ["Vedanta Power (VEDPOWER)", "Kotak Securities", 1072, 46096, 36448, ""], ["Moschip Technologies Ltd", "Kotak Securities", 187, 41888, 39270, ""], ["Godrej Consumer Products Ltd", "HDFC Securities", 40, 41520, 34600, ""], ["Vedant Fashions (Manyavar) Ltd", "HDFC Securities", 66, 43428, 38412, ""], ["Tata Consultancy Services Ltd", "HDFC Sec + Kotak", 13, 31148, 28613, ""], ["Indian Railway Finance Corp Ltd", "Kotak Securities", 302, 48018, 24462, ""], ["RITES Ltd", "Kotak Securities", 116, 29696, 24244, ""], ["Indraprastha Gas Ltd", "Kotak Securities", 166, 33864, 25232, ""], ["Great Eastern Shipping Co Ltd", "HDFC Sec + Kotak", 19, 26923, 26828, ""], ["HUDCO Ltd", "Kotak Securities", 124, 28024, 21452, ""], ["LTM Ltd (formerly LTIMindtree)", "HDFC Sec + Kotak", 5, 23660, 21375, "Shown as LTIMindtree Ltd"], ["NTPC Green Energy Ltd", "Kotak Securities", 245, 27195, 21315, ""], ["Brigade Enterprises Ltd", "Kotak Securities", 35, 24710, 22365, ""], ["Waaree Energies Ltd", "HDFC Securities", 8, 14064, 21000, ""], ["GFL Ltd", "Kotak Securities", 380, 18620, 22040, ""], ["Sonata Software Ltd", "Kotak Securities", 67, 28140, 17822, ""], ["Syngene International Ltd", "Kotak Securities", 51, 30804, 19533, ""], ["Ambuja Cements Ltd", "Kotak Securities", 49, 25823, 19208, ""], ["Astec LifeSciences Ltd", "Kotak Securities", 33, 27093, 23100, ""], ["Gujarat Energy", "Kotak Securities", 110, 43010, 26620, "Name as on statement"], ["Indian Energy Exchange Ltd", "Kotak Securities", 150, 24000, 17100, ""], ["Vinyl Chemicals (India) Ltd", "HDFC Securities", 78, 30030, 17160, ""], ["JK Tyre &amp; Industries Ltd", "Kotak Securities", 48, 19392, 16992, ""], ["REC Ltd", "Kotak Securities", 54, 27540, 16902, ""], ["Shakti Pumps (India) Ltd", "Kotak Securities", 33, 17886, 16302, ""], ["Ashoka Buildcon Ltd", "Kotak Securities", 132, 23496, 15048, ""], ["HDFC Gold ETF", "HDFC Securities", 99, 12177, 12771, ""], ["Cyient Ltd", "Kotak Securities", 9, 12114, 9531, ""], ["Utkarsh Small Finance Bank Ltd", "HDFC Securities", 560, 30800, 8120, ""], ["Orient Cement Ltd", "Kotak Securities", 20, 6320, 2520, ""], ["Utkarsh SFB – Rights Entitlement", "HDFC Securities", 344, 0, 1376, "Rights entitlement – nil cost"]]}]}</t>
+    <t xml:space="preserve">, 55, 701.55, 38585], ["09.10.2026", "BUY", "Titan Company Ltd", 6, 4375.0, 26250], ["09.10.2026", "BUY", "Bajaj Housing Finance Ltd", 280, 82.46, 23089], ["09.10.2026", "BUY", "Persistent Systems Ltd", 4, 5588.0, 22352], ["09.10.2026", "BUY", "Tata Elxsi Ltd", 7, 3081.0, 21567], ["09.10.2026", "BUY", "Eicher Motors Ltd", 3, 6905.67, 20717], ["09.10.2026", "BUY", "Avenue Supermarts (DMart) Ltd", 3, 3560.33, 10681], ["09.10.2026", "BUY", "Affle 3i Ltd", 7, 1415.0, 9905], ["09.10.2026", "BUY", "Trent Ltd", 3, 2885.0, 8655], ["09.10.2026", "BUY", "Rategain Travel Technologies Ltd", 8, 845.0, 6760], ["09.10.2026", "BUY", "L&amp;T Technology Services Ltd", 2, 3185.0, 6370]]}, {"key": "DA", "tab": "DA", "name": "DA", "broker": "HDFC Securities + Kotak Securities", "holdings_date": "Post 12.09.2026 trades (file dated 04.10.2026)", "price_basis": "As on statement (date not printed)", "stmt_invested": 4364995, "stmt_mv": 4141021, "basis_label": "DA stmt – older", "stale_prices": true, "rows": [["Bajaj Finance Ltd", "HDFC Sec + Kotak", 915, 964117, 946110, ""], ["Poonawalla Fincorp Ltd", "HDFC Sec + Kotak", 792, 376533, 352440, ""], ["Titan Company Ltd", "HDFC Sec + Kotak", 59, 260113, 295590, ""], ["HDFC Bank Ltd", "HDFC Sec + Kotak", 337, 250961, 238596, ""], ["Reliance Industries Ltd", "HDFC Securities", 146, 198998, 183668, ""], ["AFCOM Holdings Ltd", "Kotak Securities", 120, 169080, 184800, "Shown as Afcom Holdings Ltd"], ["Connplex Cinemas Ltd", "Kotak Securities", 800, 180000, 212000, "Shown as Connplex Smart Theatres Ltd"], ["Bajaj Housing Finance Ltd", "HDFC Sec + Kotak", 1732, 172732, 145488, ""], ["Persistent Systems Ltd", "HDFC Sec + Kotak", 18, 91873, 99288, ""], ["Jio Financial Services Ltd", "HDFC Securities", 374, 94996, 86020, ""], ["Fineotex Chemical Ltd", "HDFC Securities", 2030, 69020, 117131, ""], ["L&amp;T Technology Services Ltd", "HDFC Sec + Kotak", 24, 85824, 80088, ""], ["Affle 3i Ltd", "HDFC Sec + Kotak", 45, 74914, 70560, ""], ["Nestle India Ltd", "Kotak Securities", 52, 65780, 71916, ""], ["Tata Elxsi Ltd", "HDFC Sec + Kotak", 20, 74720, 67660, ""], ["Eicher Motors Ltd", "HDFC Sec + Kotak", 8, 64347, 60240, ""], ["NCC Ltd", "HDFC Securities", 399, 70623, 56259, ""], ["Trent Ltd", "HDFC Sec + Kotak", 18, 53931, 50436, ""], ["Avenue Supermarts (DMart) Ltd", "HDFC Sec + Kotak", 13, 51822, 47944, ""], ["Capacite Infraprojects Ltd", "HDFC Securities", 230, 64400, 44160, ""], ["HCL Technologies Ltd", "Kotak Securities", 33, 47223, 39798, ""], ["Indus Towers Ltd", "Kotak Securities", 111, 45510, 43068, ""], ["Vedanta Power (VEDPOWER)", "Kotak Securities", 1072, 46096, 36448, ""], ["Moschip Technologies Ltd", "Kotak Securities", 187, 41888, 39270, ""], ["Godrej Consumer Products Ltd", "HDFC Securities", 40, 41520, 34600, ""], ["Vedant Fashions (Manyavar) Ltd", "HDFC Securities", 66, 43428, 38412, ""], ["Tata Consultancy Services Ltd", "HDFC Sec + Kotak", 13, 31148, 28613, ""], ["Indian Railway Finance Corp Ltd", "Kotak Securities", 302, 48018, 24462, ""], ["RITES Ltd", "Kotak Securities", 116, 29696, 24244, ""], ["Indraprastha Gas Ltd", "Kotak Securities", 166, 33864, 25232, ""], ["Great Eastern Shipping Co Ltd", "HDFC Sec + Kotak", 19, 26923, 26828, ""], ["HUDCO Ltd", "Kotak Securities", 124, 28024, 21452, ""], ["LTM Ltd (formerly LTIMindtree)", "HDFC Sec + Kotak", 5, 23660, 21375, "Shown as LTIMindtree Ltd"], ["NTPC Green Energy Ltd", "Kotak Securities", 245, 27195, 21315, ""], ["Brigade Enterprises Ltd", "Kotak Securities", 35, 24710, 22365, ""], ["Waaree Energies Ltd", "HDFC Securities", 8, 14064, 21000, ""], ["GFL Ltd", "Kotak Securities", 380, 18620, 22040, ""], ["Sonata Software Ltd", "Kotak Securities", 67, 28140, 17822, ""], ["Syngene International Ltd", "Kotak Securities", 51, 30804, 19533, ""], ["Ambuja Cements Ltd", "Kotak Securities", 49, 25823, 19208, ""], ["Astec LifeSciences Ltd", "Kotak Securities", 33, 27093, 23100, ""], ["Gujarat Energy", "Kotak Securities", 110, 43010, 26620, "Name as on statement"], ["Indian Energy Exchange Ltd", "Kotak Securities", 150, 24000, 17100, ""], ["Vinyl Chemicals (India) Ltd", "HDFC Securities", 78, 30030, 17160, ""], ["JK Tyre &amp; Industries Ltd", "Kotak Securities", 48, 19392, 16992, ""], ["REC Ltd", "Kotak Securities", 54, 27540, 16902, ""], ["Shakti Pumps (India) Ltd", "Kotak Securities", 33, 17886, 16302, ""], ["Ashoka Buildcon Ltd", "Kotak Securities", 132, 23496, 15048, ""], ["HDFC Gold ETF", "HDFC Securities", 99, 12177, 12771, ""], ["Cyient Ltd", "Kotak Securities", 9, 12114, 9531, ""], ["Utkarsh Small Finance Bank Ltd", "HDFC Securities", 560, 30800, 8120, ""], ["Orient Cement Ltd", "Kotak Securities", 20, 6320, 2520, ""], ["Utkarsh SFB – Rights Entitlement", "HDFC Securities", 344, 0, 1376, "Rights entitlement – nil cost"]]}]}</t>
   </si>
 </sst>
 </file>
@@ -1999,7 +2002,7 @@
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">IF($G$12=0,"",G6/$G$12)</f>
-        <v>0.138480020081121</v>
+        <v>0.13580872506888</v>
       </c>
       <c r="K6" s="10" t="n">
         <v>5501448.5</v>
@@ -2047,7 +2050,7 @@
       </c>
       <c r="J7" s="9" t="n">
         <f aca="false">IF($G$12=0,"",G7/$G$12)</f>
-        <v>0.313416433606472</v>
+        <v>0.307370595691684</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>9857779</v>
@@ -2079,33 +2082,33 @@
       </c>
       <c r="F8" s="7" t="n">
         <f aca="false">'Saloni Mehra'!E6</f>
-        <v>11014028</v>
+        <v>11739506</v>
       </c>
       <c r="G8" s="7" t="n">
         <f aca="false">'Saloni Mehra'!H6</f>
-        <v>11167525.65</v>
+        <v>11909700.84</v>
       </c>
       <c r="H8" s="8" t="n">
         <f aca="false">G8-F8</f>
-        <v>153497.65</v>
+        <v>170194.84</v>
       </c>
       <c r="I8" s="9" t="n">
         <f aca="false">IF(F8&gt;0,H8/F8,"")</f>
-        <v>0.0139365589046987</v>
+        <v>0.014497615146668</v>
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">IF($G$12=0,"",G8/$G$12)</f>
-        <v>0.295967965647356</v>
+        <v>0.309548822010042</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>11014028</v>
+        <v>11739506</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>3325492</v>
+        <v>2974667</v>
       </c>
       <c r="M8" s="8" t="n">
         <f aca="false">G8-L8</f>
-        <v>7842033.65</v>
+        <v>8935033.84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2143,7 +2146,7 @@
       </c>
       <c r="J9" s="9" t="n">
         <f aca="false">IF($G$12=0,"",G9/$G$12)</f>
-        <v>0.00599751137093332</v>
+        <v>0.00588181870854315</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>201361</v>
@@ -2191,7 +2194,7 @@
       </c>
       <c r="J10" s="9" t="n">
         <f aca="false">IF($G$12=0,"",G10/$G$12)</f>
-        <v>0.143678906024712</v>
+        <v>0.140907323923531</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>5222229.03</v>
@@ -2239,7 +2242,7 @@
       </c>
       <c r="J11" s="9" t="n">
         <f aca="false">IF($G$12=0,"",G11/$G$12)</f>
-        <v>0.102459163269406</v>
+        <v>0.100482714597319</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>4364995</v>
@@ -2267,19 +2270,19 @@
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">SUM(F6:F11)</f>
-        <v>36161840</v>
+        <v>36887318</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">SUM(G6:G11)</f>
-        <v>37732210.7329212</v>
+        <v>38474385.9229212</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">SUM(H6:H11)</f>
-        <v>1570370.73292115</v>
+        <v>1587067.92292115</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">IF(F12&gt;0,H12/F12,"")</f>
-        <v>0.0434261844231695</v>
+        <v>0.043024757802157</v>
       </c>
       <c r="J12" s="19" t="n">
         <f aca="false">SUM(J6:J11)</f>
@@ -2287,15 +2290,15 @@
       </c>
       <c r="K12" s="18" t="n">
         <f aca="false">SUM(K6:K11)</f>
-        <v>36161840.53</v>
+        <v>36887318.53</v>
       </c>
       <c r="L12" s="18" t="n">
         <f aca="false">SUM(L6:L11)</f>
-        <v>30025073.41</v>
+        <v>29674248.41</v>
       </c>
       <c r="M12" s="18" t="n">
         <f aca="false">SUM(M6:M11)</f>
-        <v>7707137.32292115</v>
+        <v>8800137.51292115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2353,11 +2356,11 @@
       </c>
       <c r="C17" s="7" t="n">
         <f aca="false">LARGE('Side by Side'!$I$7:$I$95,A17)</f>
-        <v>13148889.7</v>
+        <v>13362746.4</v>
       </c>
       <c r="D17" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C17,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.34847917587102</v>
+        <v>0.347315391252005</v>
       </c>
       <c r="E17" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C17,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2369,7 +2372,7 @@
       </c>
       <c r="G17" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C17,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.397591860467318</v>
+        <v>0.390771696327512</v>
       </c>
       <c r="H17" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C17,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2398,11 +2401,11 @@
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">LARGE('Side by Side'!$I$7:$I$95,A18)</f>
-        <v>3027600</v>
+        <v>3053700</v>
       </c>
       <c r="D18" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C18,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0802391363026719</v>
+        <v>0.0793696878260182</v>
       </c>
       <c r="E18" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C18,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2414,7 +2417,7 @@
       </c>
       <c r="G18" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C18,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.095043435158799</v>
+        <v>0.0913121172907648</v>
       </c>
       <c r="H18" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C18,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2447,7 +2450,7 @@
       </c>
       <c r="D19" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C19,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0759284875513932</v>
+        <v>0.0744638185690795</v>
       </c>
       <c r="E19" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C19,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2484,39 +2487,39 @@
       </c>
       <c r="B20" s="28" t="str">
         <f aca="false">INDEX('Side by Side'!$B$7:$B$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>HDFC Bank Ltd</v>
+        <v>Poonawalla Fincorp Ltd</v>
       </c>
       <c r="C20" s="7" t="n">
         <f aca="false">LARGE('Side by Side'!$I$7:$I$95,A20)</f>
-        <v>2484699</v>
+        <v>2613295.35</v>
       </c>
       <c r="D20" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0658508725499117</v>
+        <v>0.0679229905120624</v>
       </c>
       <c r="E20" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0593743560600558</v>
+        <v>0.0936877823754703</v>
       </c>
       <c r="F20" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$Z$7:$Z$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0594519615433891</v>
+        <v>0.0509758715156924</v>
       </c>
       <c r="G20" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0676802072086577</v>
+        <v>0.0696439911583875</v>
       </c>
       <c r="H20" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0644060584698977</v>
+        <v>0.0726166427862461</v>
       </c>
       <c r="I20" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AU$7:$AU$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.086158981982471</v>
+        <v>0.0613418652092944</v>
       </c>
       <c r="J20" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$BB$7:$BB$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0605003104569751</v>
+        <v>0.0885927181878445</v>
       </c>
       <c r="K20" s="30" t="n">
         <f aca="false">INDEX('Side by Side'!$E$7:$E$95,MATCH(C20,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2529,39 +2532,39 @@
       </c>
       <c r="B21" s="28" t="str">
         <f aca="false">INDEX('Side by Side'!$B$7:$B$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>Poonawalla Fincorp Ltd</v>
+        <v>HDFC Bank Ltd</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">LARGE('Side by Side'!$I$7:$I$95,A21)</f>
-        <v>2331770.4</v>
+        <v>2520095.55</v>
       </c>
       <c r="D21" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0617978738777037</v>
+        <v>0.0655006048712178</v>
       </c>
       <c r="E21" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0936877823754703</v>
+        <v>0.0593743560600558</v>
       </c>
       <c r="F21" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$Z$7:$Z$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0509758715156924</v>
+        <v>0.0594519615433891</v>
       </c>
       <c r="G21" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0490631646769488</v>
+        <v>0.0664346662128249</v>
       </c>
       <c r="H21" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0726166427862461</v>
+        <v>0.0644060584698977</v>
       </c>
       <c r="I21" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AU$7:$AU$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0613418652092944</v>
+        <v>0.086158981982471</v>
       </c>
       <c r="J21" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$BB$7:$BB$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0885927181878445</v>
+        <v>0.0605003104569751</v>
       </c>
       <c r="K21" s="30" t="n">
         <f aca="false">INDEX('Side by Side'!$E$7:$E$95,MATCH(C21,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2582,7 +2585,7 @@
       </c>
       <c r="D22" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C22,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0436163152922312</v>
+        <v>0.0427749517119531</v>
       </c>
       <c r="E22" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C22,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2594,7 +2597,7 @@
       </c>
       <c r="G22" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C22,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0442105096037993</v>
+        <v>0.0414554493545112</v>
       </c>
       <c r="H22" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C22,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2627,7 +2630,7 @@
       </c>
       <c r="D23" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C23,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0310935717046752</v>
+        <v>0.030493773243072</v>
       </c>
       <c r="E23" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C23,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2639,7 +2642,7 @@
       </c>
       <c r="G23" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C23,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0684667780458601</v>
+        <v>0.0642001432506175</v>
       </c>
       <c r="H23" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C23,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2664,39 +2667,39 @@
       </c>
       <c r="B24" s="28" t="str">
         <f aca="false">INDEX('Side by Side'!$B$7:$B$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>LTM Ltd (formerly LTIMindtree)</v>
+        <v>Bajaj Housing Finance Ltd</v>
       </c>
       <c r="C24" s="7" t="n">
         <f aca="false">LARGE('Side by Side'!$I$7:$I$95,A24)</f>
-        <v>1081322</v>
+        <v>1105112.8</v>
       </c>
       <c r="D24" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0286577960579594</v>
+        <v>0.0287233382285545</v>
       </c>
       <c r="E24" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0490779483327708</v>
+        <v>0.0248092052654568</v>
       </c>
       <c r="F24" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$Z$7:$Z$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0238530785118798</v>
+        <v>0.0257737145528433</v>
       </c>
       <c r="G24" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0317654967732266</v>
+        <v>0.028755679475153</v>
       </c>
       <c r="H24" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0377729742128285</v>
+        <v>0.043320581522874</v>
       </c>
       <c r="I24" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AU$7:$AU$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0291696338699451</v>
+        <v>0.0328484334697682</v>
       </c>
       <c r="J24" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$BB$7:$BB$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0055276618295168</v>
+        <v>0.0362975297890662</v>
       </c>
       <c r="K24" s="30" t="n">
         <f aca="false">INDEX('Side by Side'!$E$7:$E$95,MATCH(C24,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2709,39 +2712,39 @@
       </c>
       <c r="B25" s="28" t="str">
         <f aca="false">INDEX('Side by Side'!$B$7:$B$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>Bajaj Housing Finance Ltd</v>
+        <v>LTM Ltd (formerly LTIMindtree)</v>
       </c>
       <c r="C25" s="7" t="n">
         <f aca="false">LARGE('Side by Side'!$I$7:$I$95,A25)</f>
-        <v>1075378.46</v>
+        <v>1081322</v>
       </c>
       <c r="D25" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0285002770606743</v>
+        <v>0.0281049839798951</v>
       </c>
       <c r="E25" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0248092052654568</v>
+        <v>0.0490779483327708</v>
       </c>
       <c r="F25" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$Z$7:$Z$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0257737145528433</v>
+        <v>0.0238530785118798</v>
       </c>
       <c r="G25" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0280041622290789</v>
+        <v>0.0297859706776648</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.043320581522874</v>
+        <v>0.0377729742128285</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AU$7:$AU$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0328484334697682</v>
+        <v>0.0291696338699451</v>
       </c>
       <c r="J25" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$BB$7:$BB$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0362975297890662</v>
+        <v>0.0055276618295168</v>
       </c>
       <c r="K25" s="30" t="n">
         <f aca="false">INDEX('Side by Side'!$E$7:$E$95,MATCH(C25,'Side by Side'!$I$7:$I$95,0))</f>
@@ -2754,43 +2757,43 @@
       </c>
       <c r="B26" s="28" t="str">
         <f aca="false">INDEX('Side by Side'!$B$7:$B$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>Connplex Cinemas Ltd</v>
+        <v>L&amp;T Technology Services Ltd</v>
       </c>
       <c r="C26" s="7" t="n">
         <f aca="false">LARGE('Side by Side'!$I$7:$I$95,A26)</f>
-        <v>937000</v>
+        <v>937287.6</v>
       </c>
       <c r="D26" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$L$7:$L$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.024832894277845</v>
+        <v>0.024361340084225</v>
       </c>
       <c r="E26" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$S$7:$S$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0358649489844067</v>
+        <v>0.022706302066734</v>
       </c>
       <c r="F26" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$Z$7:$Z$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0158465808522506</v>
+        <v>0.024078143931284</v>
       </c>
       <c r="G26" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AG$7:$AG$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0167807987080827</v>
+        <v>0.0259011039944812</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AN$7:$AN$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0</v>
+        <v>0.0174759661227064</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$AU$7:$AU$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0345672095715622</v>
+        <v>0.0233436756309267</v>
       </c>
       <c r="J26" s="29" t="n">
         <f aca="false">INDEX('Side by Side'!$BB$7:$BB$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>0.0484737401427912</v>
+        <v>0.024551199255075</v>
       </c>
       <c r="K26" s="30" t="n">
         <f aca="false">INDEX('Side by Side'!$E$7:$E$95,MATCH(C26,'Side by Side'!$I$7:$I$95,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,12 +2888,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3215,19 +3218,19 @@
       <c r="G6" s="44"/>
       <c r="H6" s="45" t="n">
         <f aca="false">SUM(H7:H95)</f>
-        <v>36161840</v>
+        <v>36887318</v>
       </c>
       <c r="I6" s="45" t="n">
         <f aca="false">SUM(I7:I95)</f>
-        <v>37732210.7329211</v>
+        <v>38474385.9229211</v>
       </c>
       <c r="J6" s="45" t="n">
         <f aca="false">I6-H6</f>
-        <v>1570370.73292115</v>
+        <v>1587067.92292114</v>
       </c>
       <c r="K6" s="46" t="n">
         <f aca="false">IF(H6&gt;0,J6/H6,"")</f>
-        <v>0.0434261844231695</v>
+        <v>0.0430247578021569</v>
       </c>
       <c r="L6" s="46" t="n">
         <f aca="false">SUM(L7:L95)</f>
@@ -3290,19 +3293,19 @@
       <c r="AB6" s="44"/>
       <c r="AC6" s="45" t="n">
         <f aca="false">SUM(AC7:AC95)</f>
-        <v>11014028</v>
+        <v>11739506</v>
       </c>
       <c r="AD6" s="45" t="n">
         <f aca="false">SUM(AD7:AD95)</f>
-        <v>11167525.65</v>
+        <v>11909700.84</v>
       </c>
       <c r="AE6" s="45" t="n">
         <f aca="false">AD6-AC6</f>
-        <v>153497.65</v>
+        <v>170194.84</v>
       </c>
       <c r="AF6" s="46" t="n">
         <f aca="false">IF(AC6&gt;0,AE6/AC6,"")</f>
-        <v>0.0139365589046987</v>
+        <v>0.014497615146668</v>
       </c>
       <c r="AG6" s="46" t="n">
         <f aca="false">SUM(AG7:AG95)</f>
@@ -3405,31 +3408,31 @@
       </c>
       <c r="F7" s="50" t="n">
         <f aca="false">M7+T7+AA7+AH7+AO7+AV7</f>
-        <v>13957</v>
+        <v>14184</v>
       </c>
       <c r="G7" s="51" t="n">
         <f aca="false">IF(AND(F7&gt;0,H7&gt;0),H7/F7,"")</f>
-        <v>877.772945475389</v>
+        <v>878.664481105471</v>
       </c>
       <c r="H7" s="52" t="n">
         <f aca="false">O7+V7+AC7+AJ7+AQ7+AX7</f>
-        <v>12251077</v>
+        <v>12462977</v>
       </c>
       <c r="I7" s="53" t="n">
         <f aca="false">P7+W7+AD7+AK7+AR7+AY7</f>
-        <v>13148889.7</v>
+        <v>13362746.4</v>
       </c>
       <c r="J7" s="52" t="n">
         <f aca="false">I7-H7</f>
-        <v>897812.699999999</v>
+        <v>899769.399999999</v>
       </c>
       <c r="K7" s="54" t="n">
         <f aca="false">IF(H7&gt;0,J7/H7,"")</f>
-        <v>0.0732843896091747</v>
+        <v>0.0721953831736991</v>
       </c>
       <c r="L7" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I7/I$6)</f>
-        <v>0.34847917587102</v>
+        <v>0.347315391252005</v>
       </c>
       <c r="M7" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B7)</f>
@@ -3489,31 +3492,31 @@
       </c>
       <c r="AA7" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B7)</f>
-        <v>4713</v>
+        <v>4940</v>
       </c>
       <c r="AB7" s="57" t="n">
         <f aca="false">IF(AND(AA7&gt;0,AC7&gt;0),AC7/AA7,"")</f>
-        <v>941.879482283047</v>
+        <v>941.493522267207</v>
       </c>
       <c r="AC7" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B7)</f>
-        <v>4439078</v>
+        <v>4650978</v>
       </c>
       <c r="AD7" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B7)</f>
-        <v>4440117.3</v>
+        <v>4653974</v>
       </c>
       <c r="AE7" s="8" t="n">
         <f aca="false">AD7-AC7</f>
-        <v>1039.29999999981</v>
+        <v>2996</v>
       </c>
       <c r="AF7" s="9" t="n">
         <f aca="false">IF(AC7&gt;0,AE7/AC7,"")</f>
-        <v>0.000234125194466016</v>
+        <v>0.000644165592698998</v>
       </c>
       <c r="AG7" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD7/AD$6)</f>
-        <v>0.397591860467318</v>
+        <v>0.390771696327512</v>
       </c>
       <c r="AH7" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B7)</f>
@@ -3621,31 +3624,31 @@
       </c>
       <c r="F8" s="50" t="n">
         <f aca="false">M8+T8+AA8+AH8+AO8+AV8</f>
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="G8" s="51" t="n">
         <f aca="false">IF(AND(F8&gt;0,H8&gt;0),H8/F8,"")</f>
-        <v>3938.10057471264</v>
+        <v>3940.73504273504</v>
       </c>
       <c r="H8" s="52" t="n">
         <f aca="false">O8+V8+AC8+AJ8+AQ8+AX8</f>
-        <v>2740918</v>
+        <v>2766396</v>
       </c>
       <c r="I8" s="53" t="n">
         <f aca="false">P8+W8+AD8+AK8+AR8+AY8</f>
-        <v>3027600</v>
+        <v>3053700</v>
       </c>
       <c r="J8" s="52" t="n">
         <f aca="false">I8-H8</f>
-        <v>286682</v>
+        <v>287304</v>
       </c>
       <c r="K8" s="54" t="n">
         <f aca="false">IF(H8&gt;0,J8/H8,"")</f>
-        <v>0.104593424538786</v>
+        <v>0.103854979547397</v>
       </c>
       <c r="L8" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I8/I$6)</f>
-        <v>0.0802391363026719</v>
+        <v>0.0793696878260182</v>
       </c>
       <c r="M8" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B8)</f>
@@ -3705,31 +3708,31 @@
       </c>
       <c r="AA8" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B8)</f>
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AB8" s="57" t="n">
         <f aca="false">IF(AND(AA8&gt;0,AC8&gt;0),AC8/AA8,"")</f>
-        <v>4288.80737704918</v>
+        <v>4287.788</v>
       </c>
       <c r="AC8" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B8)</f>
-        <v>1046469</v>
+        <v>1071947</v>
       </c>
       <c r="AD8" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B8)</f>
-        <v>1061400</v>
+        <v>1087500</v>
       </c>
       <c r="AE8" s="8" t="n">
         <f aca="false">AD8-AC8</f>
-        <v>14931</v>
+        <v>15553</v>
       </c>
       <c r="AF8" s="9" t="n">
         <f aca="false">IF(AC8&gt;0,AE8/AC8,"")</f>
-        <v>0.0142679811824335</v>
+        <v>0.0145091128572588</v>
       </c>
       <c r="AG8" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD8/AD$6)</f>
-        <v>0.095043435158799</v>
+        <v>0.0913121172907648</v>
       </c>
       <c r="AH8" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B8)</f>
@@ -3861,7 +3864,7 @@
       </c>
       <c r="L9" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I9/I$6)</f>
-        <v>0.0759284875513932</v>
+        <v>0.0744638185690795</v>
       </c>
       <c r="M9" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B9)</f>
@@ -4041,7 +4044,7 @@
       </c>
       <c r="C10" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B10,Prices!$A$6:$A$300,0)),"")</f>
-        <v>694.05</v>
+        <v>432.45</v>
       </c>
       <c r="D10" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B10,Prices!$A$6:$A$300,0)),"")</f>
@@ -4053,199 +4056,199 @@
       </c>
       <c r="F10" s="50" t="n">
         <f aca="false">M10+T10+AA10+AH10+AO10+AV10</f>
-        <v>3580</v>
+        <v>6043</v>
       </c>
       <c r="G10" s="51" t="n">
         <f aca="false">IF(AND(F10&gt;0,H10&gt;0),H10/F10,"")</f>
-        <v>793.617039106145</v>
+        <v>449.285123283138</v>
       </c>
       <c r="H10" s="52" t="n">
         <f aca="false">O10+V10+AC10+AJ10+AQ10+AX10</f>
-        <v>2841149</v>
+        <v>2715030</v>
       </c>
       <c r="I10" s="53" t="n">
         <f aca="false">P10+W10+AD10+AK10+AR10+AY10</f>
-        <v>2484699</v>
+        <v>2613295.35</v>
       </c>
       <c r="J10" s="52" t="n">
         <f aca="false">I10-H10</f>
-        <v>-356450</v>
+        <v>-101734.65</v>
       </c>
       <c r="K10" s="54" t="n">
         <f aca="false">IF(H10&gt;0,J10/H10,"")</f>
-        <v>-0.125459805170373</v>
+        <v>-0.0374709119236253</v>
       </c>
       <c r="L10" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I10/I$6)</f>
-        <v>0.0658508725499117</v>
+        <v>0.0679229905120624</v>
       </c>
       <c r="M10" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B10)</f>
-        <v>447</v>
+        <v>1132</v>
       </c>
       <c r="N10" s="57" t="n">
         <f aca="false">IF(AND(M10&gt;0,O10&gt;0),O10/M10,"")</f>
-        <v>716.156599552573</v>
+        <v>465.69964664311</v>
       </c>
       <c r="O10" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$E$7:$E$300,Gautam!$B$7:$B$300,$B10)</f>
-        <v>320122</v>
+        <v>527172</v>
       </c>
       <c r="P10" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$H$7:$H$300,Gautam!$B$7:$B$300,$B10)</f>
-        <v>310240.35</v>
+        <v>489533.4</v>
       </c>
       <c r="Q10" s="8" t="n">
         <f aca="false">P10-O10</f>
-        <v>-9881.65000000002</v>
+        <v>-37638.6</v>
       </c>
       <c r="R10" s="9" t="n">
         <f aca="false">IF(O10&gt;0,Q10/O10,"")</f>
-        <v>-0.0308683876771981</v>
+        <v>-0.0713971910496006</v>
       </c>
       <c r="S10" s="9" t="n">
         <f aca="false">IF(P$6=0,"",P10/P$6)</f>
-        <v>0.0593743560600558</v>
+        <v>0.0936877823754703</v>
       </c>
       <c r="T10" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B10)</f>
-        <v>1013</v>
+        <v>1394</v>
       </c>
       <c r="U10" s="57" t="n">
         <f aca="false">IF(AND(T10&gt;0,V10&gt;0),V10/T10,"")</f>
-        <v>802.253701875617</v>
+        <v>446.56599713056</v>
       </c>
       <c r="V10" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B10)</f>
-        <v>812683</v>
+        <v>622513</v>
       </c>
       <c r="W10" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B10)</f>
-        <v>703072.65</v>
+        <v>602835.3</v>
       </c>
       <c r="X10" s="8" t="n">
         <f aca="false">W10-V10</f>
-        <v>-109610.35</v>
+        <v>-19677.7000000001</v>
       </c>
       <c r="Y10" s="9" t="n">
         <f aca="false">IF(V10&gt;0,X10/V10,"")</f>
-        <v>-0.134874668228571</v>
+        <v>-0.0316101029215455</v>
       </c>
       <c r="Z10" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W10/W$6)</f>
-        <v>0.0594519615433891</v>
+        <v>0.0509758715156924</v>
       </c>
       <c r="AA10" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B10)</f>
-        <v>1089</v>
+        <v>1918</v>
       </c>
       <c r="AB10" s="57" t="n">
         <f aca="false">IF(AND(AA10&gt;0,AC10&gt;0),AC10/AA10,"")</f>
-        <v>772.608815426997</v>
+        <v>429.942648592284</v>
       </c>
       <c r="AC10" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B10)</f>
-        <v>841371</v>
+        <v>824630</v>
       </c>
       <c r="AD10" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B10)</f>
-        <v>755820.45</v>
+        <v>829439.1</v>
       </c>
       <c r="AE10" s="8" t="n">
         <f aca="false">AD10-AC10</f>
-        <v>-85550.5500000001</v>
+        <v>4809.09999999998</v>
       </c>
       <c r="AF10" s="9" t="n">
         <f aca="false">IF(AC10&gt;0,AE10/AC10,"")</f>
-        <v>-0.101679936674784</v>
+        <v>0.00583182760753305</v>
       </c>
       <c r="AG10" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD10/AD$6)</f>
-        <v>0.0676802072086577</v>
+        <v>0.0696439911583875</v>
       </c>
       <c r="AH10" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B10)</f>
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AI10" s="57" t="n">
         <f aca="false">IF(AND(AH10&gt;0,AJ10&gt;0),AJ10/AH10,"")</f>
-        <v>790.380952380952</v>
+        <v>452.421052631579</v>
       </c>
       <c r="AJ10" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$E$7:$E$300,'Vidushi Malhotra'!$B$7:$B$300,$B10)</f>
-        <v>16598</v>
+        <v>17192</v>
       </c>
       <c r="AK10" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$H$7:$H$300,'Vidushi Malhotra'!$B$7:$B$300,$B10)</f>
-        <v>14575.05</v>
+        <v>16433.1</v>
       </c>
       <c r="AL10" s="8" t="n">
         <f aca="false">AK10-AJ10</f>
-        <v>-2022.95</v>
+        <v>-758.900000000002</v>
       </c>
       <c r="AM10" s="9" t="n">
         <f aca="false">IF(AJ10&gt;0,AL10/AJ10,"")</f>
-        <v>-0.121879142065309</v>
+        <v>-0.0441426244765008</v>
       </c>
       <c r="AN10" s="9" t="n">
         <f aca="false">IF(AK$6=0,"",AK10/AK$6)</f>
-        <v>0.0644060584698977</v>
+        <v>0.0726166427862461</v>
       </c>
       <c r="AO10" s="56" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$D$7:$D$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B10)</f>
-        <v>673</v>
+        <v>769</v>
       </c>
       <c r="AP10" s="57" t="n">
         <f aca="false">IF(AND(AO10&gt;0,AQ10&gt;0),AQ10/AO10,"")</f>
-        <v>890.659732540862</v>
+        <v>451.222366710013</v>
       </c>
       <c r="AQ10" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$E$7:$E$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B10)</f>
-        <v>599414</v>
+        <v>346990</v>
       </c>
       <c r="AR10" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$H$7:$H$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B10)</f>
-        <v>467095.65</v>
+        <v>332554.05</v>
       </c>
       <c r="AS10" s="8" t="n">
         <f aca="false">AR10-AQ10</f>
-        <v>-132318.35</v>
+        <v>-14435.95</v>
       </c>
       <c r="AT10" s="9" t="n">
         <f aca="false">IF(AQ10&gt;0,AS10/AQ10,"")</f>
-        <v>-0.22074617876793</v>
+        <v>-0.041603360327387</v>
       </c>
       <c r="AU10" s="9" t="n">
         <f aca="false">IF(AR$6=0,"",AR10/AR$6)</f>
-        <v>0.086158981982471</v>
+        <v>0.0613418652092944</v>
       </c>
       <c r="AV10" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B10)</f>
-        <v>337</v>
+        <v>792</v>
       </c>
       <c r="AW10" s="57" t="n">
         <f aca="false">IF(AND(AV10&gt;0,AX10&gt;0),AX10/AV10,"")</f>
-        <v>744.691394658754</v>
+        <v>475.420454545455</v>
       </c>
       <c r="AX10" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B10)</f>
-        <v>250961</v>
+        <v>376533</v>
       </c>
       <c r="AY10" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B10)</f>
-        <v>233894.85</v>
+        <v>342500.4</v>
       </c>
       <c r="AZ10" s="8" t="n">
         <f aca="false">AY10-AX10</f>
-        <v>-17066.15</v>
+        <v>-34032.6</v>
       </c>
       <c r="BA10" s="9" t="n">
         <f aca="false">IF(AX10&gt;0,AZ10/AX10,"")</f>
-        <v>-0.0680031957156691</v>
+        <v>-0.0903841097593041</v>
       </c>
       <c r="BB10" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY10/AY$6)</f>
-        <v>0.0605003104569751</v>
+        <v>0.0885927181878445</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4257,7 +4260,7 @@
       </c>
       <c r="C11" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B11,Prices!$A$6:$A$300,0)),"")</f>
-        <v>432.45</v>
+        <v>694.05</v>
       </c>
       <c r="D11" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B11,Prices!$A$6:$A$300,0)),"")</f>
@@ -4269,199 +4272,199 @@
       </c>
       <c r="F11" s="50" t="n">
         <f aca="false">M11+T11+AA11+AH11+AO11+AV11</f>
-        <v>5392</v>
+        <v>3631</v>
       </c>
       <c r="G11" s="51" t="n">
         <f aca="false">IF(AND(F11&gt;0,H11&gt;0),H11/F11,"")</f>
-        <v>453.122774480712</v>
+        <v>792.142109611677</v>
       </c>
       <c r="H11" s="52" t="n">
         <f aca="false">O11+V11+AC11+AJ11+AQ11+AX11</f>
-        <v>2443238</v>
+        <v>2876268</v>
       </c>
       <c r="I11" s="53" t="n">
         <f aca="false">P11+W11+AD11+AK11+AR11+AY11</f>
-        <v>2331770.4</v>
+        <v>2520095.55</v>
       </c>
       <c r="J11" s="52" t="n">
         <f aca="false">I11-H11</f>
-        <v>-111467.6</v>
+        <v>-356172.45</v>
       </c>
       <c r="K11" s="54" t="n">
         <f aca="false">IF(H11&gt;0,J11/H11,"")</f>
-        <v>-0.0456228987925039</v>
+        <v>-0.123831454509802</v>
       </c>
       <c r="L11" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I11/I$6)</f>
-        <v>0.0617978738777037</v>
+        <v>0.0655006048712178</v>
       </c>
       <c r="M11" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B11)</f>
-        <v>1132</v>
+        <v>447</v>
       </c>
       <c r="N11" s="57" t="n">
         <f aca="false">IF(AND(M11&gt;0,O11&gt;0),O11/M11,"")</f>
-        <v>465.69964664311</v>
+        <v>716.156599552573</v>
       </c>
       <c r="O11" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$E$7:$E$300,Gautam!$B$7:$B$300,$B11)</f>
-        <v>527172</v>
+        <v>320122</v>
       </c>
       <c r="P11" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$H$7:$H$300,Gautam!$B$7:$B$300,$B11)</f>
-        <v>489533.4</v>
+        <v>310240.35</v>
       </c>
       <c r="Q11" s="8" t="n">
         <f aca="false">P11-O11</f>
-        <v>-37638.6</v>
+        <v>-9881.65000000002</v>
       </c>
       <c r="R11" s="9" t="n">
         <f aca="false">IF(O11&gt;0,Q11/O11,"")</f>
-        <v>-0.0713971910496006</v>
+        <v>-0.0308683876771981</v>
       </c>
       <c r="S11" s="9" t="n">
         <f aca="false">IF(P$6=0,"",P11/P$6)</f>
-        <v>0.0936877823754703</v>
+        <v>0.0593743560600558</v>
       </c>
       <c r="T11" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B11)</f>
-        <v>1394</v>
+        <v>1013</v>
       </c>
       <c r="U11" s="57" t="n">
         <f aca="false">IF(AND(T11&gt;0,V11&gt;0),V11/T11,"")</f>
-        <v>446.56599713056</v>
+        <v>802.253701875617</v>
       </c>
       <c r="V11" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B11)</f>
-        <v>622513</v>
+        <v>812683</v>
       </c>
       <c r="W11" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B11)</f>
-        <v>602835.3</v>
+        <v>703072.65</v>
       </c>
       <c r="X11" s="8" t="n">
         <f aca="false">W11-V11</f>
-        <v>-19677.7000000001</v>
+        <v>-109610.35</v>
       </c>
       <c r="Y11" s="9" t="n">
         <f aca="false">IF(V11&gt;0,X11/V11,"")</f>
-        <v>-0.0316101029215455</v>
+        <v>-0.134874668228571</v>
       </c>
       <c r="Z11" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W11/W$6)</f>
-        <v>0.0509758715156924</v>
+        <v>0.0594519615433891</v>
       </c>
       <c r="AA11" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B11)</f>
-        <v>1267</v>
+        <v>1140</v>
       </c>
       <c r="AB11" s="57" t="n">
         <f aca="false">IF(AND(AA11&gt;0,AC11&gt;0),AC11/AA11,"")</f>
-        <v>436.336227308603</v>
+        <v>768.850877192983</v>
       </c>
       <c r="AC11" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B11)</f>
-        <v>552838</v>
+        <v>876490</v>
       </c>
       <c r="AD11" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B11)</f>
-        <v>547914.15</v>
+        <v>791217</v>
       </c>
       <c r="AE11" s="8" t="n">
         <f aca="false">AD11-AC11</f>
-        <v>-4923.84999999998</v>
+        <v>-85273</v>
       </c>
       <c r="AF11" s="9" t="n">
         <f aca="false">IF(AC11&gt;0,AE11/AC11,"")</f>
-        <v>-0.00890649702082704</v>
+        <v>-0.0972891875549065</v>
       </c>
       <c r="AG11" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD11/AD$6)</f>
-        <v>0.0490631646769488</v>
+        <v>0.0664346662128249</v>
       </c>
       <c r="AH11" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B11)</f>
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AI11" s="57" t="n">
         <f aca="false">IF(AND(AH11&gt;0,AJ11&gt;0),AJ11/AH11,"")</f>
-        <v>452.421052631579</v>
+        <v>790.380952380952</v>
       </c>
       <c r="AJ11" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$E$7:$E$300,'Vidushi Malhotra'!$B$7:$B$300,$B11)</f>
-        <v>17192</v>
+        <v>16598</v>
       </c>
       <c r="AK11" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$H$7:$H$300,'Vidushi Malhotra'!$B$7:$B$300,$B11)</f>
-        <v>16433.1</v>
+        <v>14575.05</v>
       </c>
       <c r="AL11" s="8" t="n">
         <f aca="false">AK11-AJ11</f>
-        <v>-758.900000000002</v>
+        <v>-2022.95</v>
       </c>
       <c r="AM11" s="9" t="n">
         <f aca="false">IF(AJ11&gt;0,AL11/AJ11,"")</f>
-        <v>-0.0441426244765008</v>
+        <v>-0.121879142065309</v>
       </c>
       <c r="AN11" s="9" t="n">
         <f aca="false">IF(AK$6=0,"",AK11/AK$6)</f>
-        <v>0.0726166427862461</v>
+        <v>0.0644060584698977</v>
       </c>
       <c r="AO11" s="56" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$D$7:$D$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B11)</f>
-        <v>769</v>
+        <v>673</v>
       </c>
       <c r="AP11" s="57" t="n">
         <f aca="false">IF(AND(AO11&gt;0,AQ11&gt;0),AQ11/AO11,"")</f>
-        <v>451.222366710013</v>
+        <v>890.659732540862</v>
       </c>
       <c r="AQ11" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$E$7:$E$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B11)</f>
-        <v>346990</v>
+        <v>599414</v>
       </c>
       <c r="AR11" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$H$7:$H$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B11)</f>
-        <v>332554.05</v>
+        <v>467095.65</v>
       </c>
       <c r="AS11" s="8" t="n">
         <f aca="false">AR11-AQ11</f>
-        <v>-14435.95</v>
+        <v>-132318.35</v>
       </c>
       <c r="AT11" s="9" t="n">
         <f aca="false">IF(AQ11&gt;0,AS11/AQ11,"")</f>
-        <v>-0.041603360327387</v>
+        <v>-0.22074617876793</v>
       </c>
       <c r="AU11" s="9" t="n">
         <f aca="false">IF(AR$6=0,"",AR11/AR$6)</f>
-        <v>0.0613418652092944</v>
+        <v>0.086158981982471</v>
       </c>
       <c r="AV11" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B11)</f>
-        <v>792</v>
+        <v>337</v>
       </c>
       <c r="AW11" s="57" t="n">
         <f aca="false">IF(AND(AV11&gt;0,AX11&gt;0),AX11/AV11,"")</f>
-        <v>475.420454545455</v>
+        <v>744.691394658754</v>
       </c>
       <c r="AX11" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B11)</f>
-        <v>376533</v>
+        <v>250961</v>
       </c>
       <c r="AY11" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B11)</f>
-        <v>342500.4</v>
+        <v>233894.85</v>
       </c>
       <c r="AZ11" s="8" t="n">
         <f aca="false">AY11-AX11</f>
-        <v>-34032.6</v>
+        <v>-17066.15</v>
       </c>
       <c r="BA11" s="9" t="n">
         <f aca="false">IF(AX11&gt;0,AZ11/AX11,"")</f>
-        <v>-0.0903841097593041</v>
+        <v>-0.0680031957156691</v>
       </c>
       <c r="BB11" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY11/AY$6)</f>
-        <v>0.0885927181878445</v>
+        <v>0.0605003104569751</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4509,7 +4512,7 @@
       </c>
       <c r="L12" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I12/I$6)</f>
-        <v>0.0436163152922312</v>
+        <v>0.0427749517119531</v>
       </c>
       <c r="M12" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B12)</f>
@@ -4593,7 +4596,7 @@
       </c>
       <c r="AG12" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD12/AD$6)</f>
-        <v>0.0442105096037993</v>
+        <v>0.0414554493545112</v>
       </c>
       <c r="AH12" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B12)</f>
@@ -4725,7 +4728,7 @@
       </c>
       <c r="L13" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I13/I$6)</f>
-        <v>0.0310935717046752</v>
+        <v>0.030493773243072</v>
       </c>
       <c r="M13" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B13)</f>
@@ -4809,7 +4812,7 @@
       </c>
       <c r="AG13" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD13/AD$6)</f>
-        <v>0.0684667780458601</v>
+        <v>0.0642001432506175</v>
       </c>
       <c r="AH13" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B13)</f>
@@ -4905,7 +4908,7 @@
       </c>
       <c r="C14" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B14,Prices!$A$6:$A$300,0)),"")</f>
-        <v>4274</v>
+        <v>81.02</v>
       </c>
       <c r="D14" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B14,Prices!$A$6:$A$300,0)),"")</f>
@@ -4917,199 +4920,199 @@
       </c>
       <c r="F14" s="50" t="n">
         <f aca="false">M14+T14+AA14+AH14+AO14+AV14</f>
-        <v>253</v>
+        <v>13640</v>
       </c>
       <c r="G14" s="51" t="n">
         <f aca="false">IF(AND(F14&gt;0,H14&gt;0),H14/F14,"")</f>
-        <v>4727.12648221344</v>
+        <v>100.307991202346</v>
       </c>
       <c r="H14" s="52" t="n">
         <f aca="false">O14+V14+AC14+AJ14+AQ14+AX14</f>
-        <v>1195963</v>
+        <v>1368201</v>
       </c>
       <c r="I14" s="53" t="n">
         <f aca="false">P14+W14+AD14+AK14+AR14+AY14</f>
-        <v>1081322</v>
+        <v>1105112.8</v>
       </c>
       <c r="J14" s="52" t="n">
         <f aca="false">I14-H14</f>
-        <v>-114641</v>
+        <v>-263088.2</v>
       </c>
       <c r="K14" s="54" t="n">
         <f aca="false">IF(H14&gt;0,J14/H14,"")</f>
-        <v>-0.0958566443945172</v>
+        <v>-0.192287682877004</v>
       </c>
       <c r="L14" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I14/I$6)</f>
-        <v>0.0286577960579594</v>
+        <v>0.0287233382285545</v>
       </c>
       <c r="M14" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B14)</f>
-        <v>60</v>
+        <v>1600</v>
       </c>
       <c r="N14" s="57" t="n">
         <f aca="false">IF(AND(M14&gt;0,O14&gt;0),O14/M14,"")</f>
-        <v>4564</v>
+        <v>83.08125</v>
       </c>
       <c r="O14" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$E$7:$E$300,Gautam!$B$7:$B$300,$B14)</f>
-        <v>273840</v>
+        <v>132930</v>
       </c>
       <c r="P14" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$H$7:$H$300,Gautam!$B$7:$B$300,$B14)</f>
-        <v>256440</v>
+        <v>129632</v>
       </c>
       <c r="Q14" s="8" t="n">
         <f aca="false">P14-O14</f>
-        <v>-17400</v>
+        <v>-3298</v>
       </c>
       <c r="R14" s="9" t="n">
         <f aca="false">IF(O14&gt;0,Q14/O14,"")</f>
-        <v>-0.0635407537248028</v>
+        <v>-0.0248100504024675</v>
       </c>
       <c r="S14" s="9" t="n">
         <f aca="false">IF(P$6=0,"",P14/P$6)</f>
-        <v>0.0490779483327708</v>
+        <v>0.0248092052654568</v>
       </c>
       <c r="T14" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B14)</f>
-        <v>66</v>
+        <v>3762</v>
       </c>
       <c r="U14" s="57" t="n">
         <f aca="false">IF(AND(T14&gt;0,V14&gt;0),V14/T14,"")</f>
-        <v>5274.80303030303</v>
+        <v>115.016746411483</v>
       </c>
       <c r="V14" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B14)</f>
-        <v>348137</v>
+        <v>432693</v>
       </c>
       <c r="W14" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B14)</f>
-        <v>282084</v>
+        <v>304797.24</v>
       </c>
       <c r="X14" s="8" t="n">
         <f aca="false">W14-V14</f>
-        <v>-66053</v>
+        <v>-127895.76</v>
       </c>
       <c r="Y14" s="9" t="n">
         <f aca="false">IF(V14&gt;0,X14/V14,"")</f>
-        <v>-0.189732777613411</v>
+        <v>-0.295580839070658</v>
       </c>
       <c r="Z14" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W14/W$6)</f>
-        <v>0.0238530785118798</v>
+        <v>0.0257737145528433</v>
       </c>
       <c r="AA14" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B14)</f>
-        <v>83</v>
+        <v>4227</v>
       </c>
       <c r="AB14" s="57" t="n">
         <f aca="false">IF(AND(AA14&gt;0,AC14&gt;0),AC14/AA14,"")</f>
-        <v>3897.90361445783</v>
+        <v>85.1852377572747</v>
       </c>
       <c r="AC14" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B14)</f>
-        <v>323526</v>
+        <v>360078</v>
       </c>
       <c r="AD14" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B14)</f>
-        <v>354742</v>
+        <v>342471.54</v>
       </c>
       <c r="AE14" s="8" t="n">
         <f aca="false">AD14-AC14</f>
-        <v>31216</v>
+        <v>-17606.46</v>
       </c>
       <c r="AF14" s="9" t="n">
         <f aca="false">IF(AC14&gt;0,AE14/AC14,"")</f>
-        <v>0.0964868356793581</v>
+        <v>-0.0488962391481846</v>
       </c>
       <c r="AG14" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD14/AD$6)</f>
-        <v>0.0317654967732266</v>
+        <v>0.028755679475153</v>
       </c>
       <c r="AH14" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B14)</f>
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="AI14" s="57" t="n">
         <f aca="false">IF(AND(AH14&gt;0,AJ14&gt;0),AJ14/AH14,"")</f>
-        <v>5099</v>
+        <v>115.438016528926</v>
       </c>
       <c r="AJ14" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$E$7:$E$300,'Vidushi Malhotra'!$B$7:$B$300,$B14)</f>
-        <v>10198</v>
+        <v>13968</v>
       </c>
       <c r="AK14" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$H$7:$H$300,'Vidushi Malhotra'!$B$7:$B$300,$B14)</f>
-        <v>8548</v>
+        <v>9803.42</v>
       </c>
       <c r="AL14" s="8" t="n">
         <f aca="false">AK14-AJ14</f>
-        <v>-1650</v>
+        <v>-4164.58</v>
       </c>
       <c r="AM14" s="9" t="n">
         <f aca="false">IF(AJ14&gt;0,AL14/AJ14,"")</f>
-        <v>-0.161796430672681</v>
+        <v>-0.298151489117984</v>
       </c>
       <c r="AN14" s="9" t="n">
         <f aca="false">IF(AK$6=0,"",AK14/AK$6)</f>
-        <v>0.0377729742128285</v>
+        <v>0.043320581522874</v>
       </c>
       <c r="AO14" s="56" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$D$7:$D$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B14)</f>
-        <v>37</v>
+        <v>2198</v>
       </c>
       <c r="AP14" s="57" t="n">
         <f aca="false">IF(AND(AO14&gt;0,AQ14&gt;0),AQ14/AO14,"")</f>
-        <v>5854.10810810811</v>
+        <v>116.378525932666</v>
       </c>
       <c r="AQ14" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$E$7:$E$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B14)</f>
-        <v>216602</v>
+        <v>255800</v>
       </c>
       <c r="AR14" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$H$7:$H$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B14)</f>
-        <v>158138</v>
+        <v>178081.96</v>
       </c>
       <c r="AS14" s="8" t="n">
         <f aca="false">AR14-AQ14</f>
-        <v>-58464</v>
+        <v>-77718.04</v>
       </c>
       <c r="AT14" s="9" t="n">
         <f aca="false">IF(AQ14&gt;0,AS14/AQ14,"")</f>
-        <v>-0.269914405222482</v>
+        <v>-0.303823455824863</v>
       </c>
       <c r="AU14" s="9" t="n">
         <f aca="false">IF(AR$6=0,"",AR14/AR$6)</f>
-        <v>0.0291696338699451</v>
+        <v>0.0328484334697682</v>
       </c>
       <c r="AV14" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B14)</f>
-        <v>5</v>
+        <v>1732</v>
       </c>
       <c r="AW14" s="57" t="n">
         <f aca="false">IF(AND(AV14&gt;0,AX14&gt;0),AX14/AV14,"")</f>
-        <v>4732</v>
+        <v>99.729792147806</v>
       </c>
       <c r="AX14" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B14)</f>
-        <v>23660</v>
+        <v>172732</v>
       </c>
       <c r="AY14" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B14)</f>
-        <v>21370</v>
+        <v>140326.64</v>
       </c>
       <c r="AZ14" s="8" t="n">
         <f aca="false">AY14-AX14</f>
-        <v>-2290</v>
+        <v>-32405.36</v>
       </c>
       <c r="BA14" s="9" t="n">
         <f aca="false">IF(AX14&gt;0,AZ14/AX14,"")</f>
-        <v>-0.0967878275570583</v>
+        <v>-0.187604844498993</v>
       </c>
       <c r="BB14" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY14/AY$6)</f>
-        <v>0.0055276618295168</v>
+        <v>0.0362975297890662</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5121,7 +5124,7 @@
       </c>
       <c r="C15" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B15,Prices!$A$6:$A$300,0)),"")</f>
-        <v>81.02</v>
+        <v>4274</v>
       </c>
       <c r="D15" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B15,Prices!$A$6:$A$300,0)),"")</f>
@@ -5133,199 +5136,199 @@
       </c>
       <c r="F15" s="50" t="n">
         <f aca="false">M15+T15+AA15+AH15+AO15+AV15</f>
-        <v>13273</v>
+        <v>253</v>
       </c>
       <c r="G15" s="51" t="n">
         <f aca="false">IF(AND(F15&gt;0,H15&gt;0),H15/F15,"")</f>
-        <v>100.941384766066</v>
+        <v>4727.12648221344</v>
       </c>
       <c r="H15" s="52" t="n">
         <f aca="false">O15+V15+AC15+AJ15+AQ15+AX15</f>
-        <v>1339795</v>
+        <v>1195963</v>
       </c>
       <c r="I15" s="53" t="n">
         <f aca="false">P15+W15+AD15+AK15+AR15+AY15</f>
-        <v>1075378.46</v>
+        <v>1081322</v>
       </c>
       <c r="J15" s="52" t="n">
         <f aca="false">I15-H15</f>
-        <v>-264416.54</v>
+        <v>-114641</v>
       </c>
       <c r="K15" s="54" t="n">
         <f aca="false">IF(H15&gt;0,J15/H15,"")</f>
-        <v>-0.197355968636993</v>
+        <v>-0.0958566443945172</v>
       </c>
       <c r="L15" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I15/I$6)</f>
-        <v>0.0285002770606743</v>
+        <v>0.0281049839798951</v>
       </c>
       <c r="M15" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B15)</f>
-        <v>1600</v>
+        <v>60</v>
       </c>
       <c r="N15" s="57" t="n">
         <f aca="false">IF(AND(M15&gt;0,O15&gt;0),O15/M15,"")</f>
-        <v>83.08125</v>
+        <v>4564</v>
       </c>
       <c r="O15" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$E$7:$E$300,Gautam!$B$7:$B$300,$B15)</f>
-        <v>132930</v>
+        <v>273840</v>
       </c>
       <c r="P15" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$H$7:$H$300,Gautam!$B$7:$B$300,$B15)</f>
-        <v>129632</v>
+        <v>256440</v>
       </c>
       <c r="Q15" s="8" t="n">
         <f aca="false">P15-O15</f>
-        <v>-3298</v>
+        <v>-17400</v>
       </c>
       <c r="R15" s="9" t="n">
         <f aca="false">IF(O15&gt;0,Q15/O15,"")</f>
-        <v>-0.0248100504024675</v>
+        <v>-0.0635407537248028</v>
       </c>
       <c r="S15" s="9" t="n">
         <f aca="false">IF(P$6=0,"",P15/P$6)</f>
-        <v>0.0248092052654568</v>
+        <v>0.0490779483327708</v>
       </c>
       <c r="T15" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B15)</f>
-        <v>3762</v>
+        <v>66</v>
       </c>
       <c r="U15" s="57" t="n">
         <f aca="false">IF(AND(T15&gt;0,V15&gt;0),V15/T15,"")</f>
-        <v>115.016746411483</v>
+        <v>5274.80303030303</v>
       </c>
       <c r="V15" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B15)</f>
-        <v>432693</v>
+        <v>348137</v>
       </c>
       <c r="W15" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B15)</f>
-        <v>304797.24</v>
+        <v>282084</v>
       </c>
       <c r="X15" s="8" t="n">
         <f aca="false">W15-V15</f>
-        <v>-127895.76</v>
+        <v>-66053</v>
       </c>
       <c r="Y15" s="9" t="n">
         <f aca="false">IF(V15&gt;0,X15/V15,"")</f>
-        <v>-0.295580839070658</v>
+        <v>-0.189732777613411</v>
       </c>
       <c r="Z15" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W15/W$6)</f>
-        <v>0.0257737145528433</v>
+        <v>0.0238530785118798</v>
       </c>
       <c r="AA15" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B15)</f>
-        <v>3860</v>
+        <v>83</v>
       </c>
       <c r="AB15" s="57" t="n">
         <f aca="false">IF(AND(AA15&gt;0,AC15&gt;0),AC15/AA15,"")</f>
-        <v>85.9253886010363</v>
+        <v>3897.90361445783</v>
       </c>
       <c r="AC15" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B15)</f>
-        <v>331672</v>
+        <v>323526</v>
       </c>
       <c r="AD15" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B15)</f>
-        <v>312737.2</v>
+        <v>354742</v>
       </c>
       <c r="AE15" s="8" t="n">
         <f aca="false">AD15-AC15</f>
-        <v>-18934.8</v>
+        <v>31216</v>
       </c>
       <c r="AF15" s="9" t="n">
         <f aca="false">IF(AC15&gt;0,AE15/AC15,"")</f>
-        <v>-0.0570889312332666</v>
+        <v>0.0964868356793581</v>
       </c>
       <c r="AG15" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD15/AD$6)</f>
-        <v>0.0280041622290789</v>
+        <v>0.0297859706776648</v>
       </c>
       <c r="AH15" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B15)</f>
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="57" t="n">
         <f aca="false">IF(AND(AH15&gt;0,AJ15&gt;0),AJ15/AH15,"")</f>
-        <v>115.438016528926</v>
+        <v>5099</v>
       </c>
       <c r="AJ15" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$E$7:$E$300,'Vidushi Malhotra'!$B$7:$B$300,$B15)</f>
-        <v>13968</v>
+        <v>10198</v>
       </c>
       <c r="AK15" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$H$7:$H$300,'Vidushi Malhotra'!$B$7:$B$300,$B15)</f>
-        <v>9803.42</v>
+        <v>8548</v>
       </c>
       <c r="AL15" s="8" t="n">
         <f aca="false">AK15-AJ15</f>
-        <v>-4164.58</v>
+        <v>-1650</v>
       </c>
       <c r="AM15" s="9" t="n">
         <f aca="false">IF(AJ15&gt;0,AL15/AJ15,"")</f>
-        <v>-0.298151489117984</v>
+        <v>-0.161796430672681</v>
       </c>
       <c r="AN15" s="9" t="n">
         <f aca="false">IF(AK$6=0,"",AK15/AK$6)</f>
-        <v>0.043320581522874</v>
+        <v>0.0377729742128285</v>
       </c>
       <c r="AO15" s="56" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$D$7:$D$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B15)</f>
-        <v>2198</v>
+        <v>37</v>
       </c>
       <c r="AP15" s="57" t="n">
         <f aca="false">IF(AND(AO15&gt;0,AQ15&gt;0),AQ15/AO15,"")</f>
-        <v>116.378525932666</v>
+        <v>5854.10810810811</v>
       </c>
       <c r="AQ15" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$E$7:$E$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B15)</f>
-        <v>255800</v>
+        <v>216602</v>
       </c>
       <c r="AR15" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$H$7:$H$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B15)</f>
-        <v>178081.96</v>
+        <v>158138</v>
       </c>
       <c r="AS15" s="8" t="n">
         <f aca="false">AR15-AQ15</f>
-        <v>-77718.04</v>
+        <v>-58464</v>
       </c>
       <c r="AT15" s="9" t="n">
         <f aca="false">IF(AQ15&gt;0,AS15/AQ15,"")</f>
-        <v>-0.303823455824863</v>
+        <v>-0.269914405222482</v>
       </c>
       <c r="AU15" s="9" t="n">
         <f aca="false">IF(AR$6=0,"",AR15/AR$6)</f>
-        <v>0.0328484334697682</v>
+        <v>0.0291696338699451</v>
       </c>
       <c r="AV15" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B15)</f>
-        <v>1732</v>
+        <v>5</v>
       </c>
       <c r="AW15" s="57" t="n">
         <f aca="false">IF(AND(AV15&gt;0,AX15&gt;0),AX15/AV15,"")</f>
-        <v>99.729792147806</v>
+        <v>4732</v>
       </c>
       <c r="AX15" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B15)</f>
-        <v>172732</v>
+        <v>23660</v>
       </c>
       <c r="AY15" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B15)</f>
-        <v>140326.64</v>
+        <v>21370</v>
       </c>
       <c r="AZ15" s="8" t="n">
         <f aca="false">AY15-AX15</f>
-        <v>-32405.36</v>
+        <v>-2290</v>
       </c>
       <c r="BA15" s="9" t="n">
         <f aca="false">IF(AX15&gt;0,AZ15/AX15,"")</f>
-        <v>-0.187604844498993</v>
+        <v>-0.0967878275570583</v>
       </c>
       <c r="BB15" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY15/AY$6)</f>
-        <v>0.0362975297890662</v>
+        <v>0.0055276618295168</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5337,7 +5340,7 @@
       </c>
       <c r="C16" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B16,Prices!$A$6:$A$300,0)),"")</f>
-        <v>234.25</v>
+        <v>3954.8</v>
       </c>
       <c r="D16" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B16,Prices!$A$6:$A$300,0)),"")</f>
@@ -5345,203 +5348,203 @@
       </c>
       <c r="E16" s="6" t="n">
         <f aca="false">(M16&gt;0)+(T16&gt;0)+(AA16&gt;0)+(AH16&gt;0)+(AO16&gt;0)+(AV16&gt;0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="50" t="n">
         <f aca="false">M16+T16+AA16+AH16+AO16+AV16</f>
-        <v>4000</v>
+        <v>237</v>
       </c>
       <c r="G16" s="51" t="n">
         <f aca="false">IF(AND(F16&gt;0,H16&gt;0),H16/F16,"")</f>
-        <v>233.36675</v>
+        <v>3877.68776371308</v>
       </c>
       <c r="H16" s="52" t="n">
         <f aca="false">O16+V16+AC16+AJ16+AQ16+AX16</f>
-        <v>933467</v>
+        <v>919012</v>
       </c>
       <c r="I16" s="53" t="n">
         <f aca="false">P16+W16+AD16+AK16+AR16+AY16</f>
-        <v>937000</v>
+        <v>937287.6</v>
       </c>
       <c r="J16" s="52" t="n">
         <f aca="false">I16-H16</f>
-        <v>3533</v>
+        <v>18275.6000000001</v>
       </c>
       <c r="K16" s="54" t="n">
         <f aca="false">IF(H16&gt;0,J16/H16,"")</f>
-        <v>0.00378481510326557</v>
+        <v>0.0198861385923145</v>
       </c>
       <c r="L16" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I16/I$6)</f>
-        <v>0.024832894277845</v>
+        <v>0.024361340084225</v>
       </c>
       <c r="M16" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B16)</f>
-        <v>800</v>
+        <v>30</v>
       </c>
       <c r="N16" s="57" t="n">
         <f aca="false">IF(AND(M16&gt;0,O16&gt;0),O16/M16,"")</f>
-        <v>264</v>
+        <v>3484.36666666667</v>
       </c>
       <c r="O16" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$E$7:$E$300,Gautam!$B$7:$B$300,$B16)</f>
-        <v>211200</v>
+        <v>104531</v>
       </c>
       <c r="P16" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$H$7:$H$300,Gautam!$B$7:$B$300,$B16)</f>
-        <v>187400</v>
+        <v>118644</v>
       </c>
       <c r="Q16" s="8" t="n">
         <f aca="false">P16-O16</f>
-        <v>-23800</v>
+        <v>14113</v>
       </c>
       <c r="R16" s="9" t="n">
         <f aca="false">IF(O16&gt;0,Q16/O16,"")</f>
-        <v>-0.112689393939394</v>
+        <v>0.135012580000191</v>
       </c>
       <c r="S16" s="9" t="n">
         <f aca="false">IF(P$6=0,"",P16/P$6)</f>
-        <v>0.0358649489844067</v>
+        <v>0.022706302066734</v>
       </c>
       <c r="T16" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B16)</f>
-        <v>800</v>
+        <v>72</v>
       </c>
       <c r="U16" s="57" t="n">
         <f aca="false">IF(AND(T16&gt;0,V16&gt;0),V16/T16,"")</f>
-        <v>235.09375</v>
+        <v>4214.81944444444</v>
       </c>
       <c r="V16" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B16)</f>
-        <v>188075</v>
+        <v>303467</v>
       </c>
       <c r="W16" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B16)</f>
-        <v>187400</v>
+        <v>284745.6</v>
       </c>
       <c r="X16" s="8" t="n">
         <f aca="false">W16-V16</f>
-        <v>-675</v>
+        <v>-18721.4</v>
       </c>
       <c r="Y16" s="9" t="n">
         <f aca="false">IF(V16&gt;0,X16/V16,"")</f>
-        <v>-0.00358899375249236</v>
+        <v>-0.0616917160679743</v>
       </c>
       <c r="Z16" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W16/W$6)</f>
-        <v>0.0158465808522506</v>
+        <v>0.024078143931284</v>
       </c>
       <c r="AA16" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B16)</f>
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="AB16" s="57" t="n">
         <f aca="false">IF(AND(AA16&gt;0,AC16&gt;0),AC16/AA16,"")</f>
-        <v>212.75</v>
+        <v>3455.69230769231</v>
       </c>
       <c r="AC16" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B16)</f>
-        <v>170200</v>
+        <v>269544</v>
       </c>
       <c r="AD16" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B16)</f>
-        <v>187400</v>
+        <v>308474.4</v>
       </c>
       <c r="AE16" s="8" t="n">
         <f aca="false">AD16-AC16</f>
-        <v>17200</v>
+        <v>38930.4</v>
       </c>
       <c r="AF16" s="9" t="n">
         <f aca="false">IF(AC16&gt;0,AE16/AC16,"")</f>
-        <v>0.101057579318449</v>
+        <v>0.144430593891906</v>
       </c>
       <c r="AG16" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD16/AD$6)</f>
-        <v>0.0167807987080827</v>
+        <v>0.0259011039944812</v>
       </c>
       <c r="AH16" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B16)</f>
-        <v>0</v>
-      </c>
-      <c r="AI16" s="57" t="str">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="57" t="n">
         <f aca="false">IF(AND(AH16&gt;0,AJ16&gt;0),AJ16/AH16,"")</f>
-        <v/>
+        <v>4607</v>
       </c>
       <c r="AJ16" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$E$7:$E$300,'Vidushi Malhotra'!$B$7:$B$300,$B16)</f>
-        <v>0</v>
+        <v>4607</v>
       </c>
       <c r="AK16" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$H$7:$H$300,'Vidushi Malhotra'!$B$7:$B$300,$B16)</f>
-        <v>0</v>
+        <v>3954.8</v>
       </c>
       <c r="AL16" s="8" t="n">
         <f aca="false">AK16-AJ16</f>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="9" t="str">
+        <v>-652.2</v>
+      </c>
+      <c r="AM16" s="9" t="n">
         <f aca="false">IF(AJ16&gt;0,AL16/AJ16,"")</f>
-        <v/>
+        <v>-0.141567180377686</v>
       </c>
       <c r="AN16" s="9" t="n">
         <f aca="false">IF(AK$6=0,"",AK16/AK$6)</f>
-        <v>0</v>
+        <v>0.0174759661227064</v>
       </c>
       <c r="AO16" s="56" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$D$7:$D$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B16)</f>
-        <v>800</v>
+        <v>32</v>
       </c>
       <c r="AP16" s="57" t="n">
         <f aca="false">IF(AND(AO16&gt;0,AQ16&gt;0),AQ16/AO16,"")</f>
-        <v>229.99</v>
+        <v>4719.96875</v>
       </c>
       <c r="AQ16" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$E$7:$E$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B16)</f>
-        <v>183992</v>
+        <v>151039</v>
       </c>
       <c r="AR16" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$H$7:$H$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B16)</f>
-        <v>187400</v>
+        <v>126553.6</v>
       </c>
       <c r="AS16" s="8" t="n">
         <f aca="false">AR16-AQ16</f>
-        <v>3408</v>
+        <v>-24485.4</v>
       </c>
       <c r="AT16" s="9" t="n">
         <f aca="false">IF(AQ16&gt;0,AS16/AQ16,"")</f>
-        <v>0.0185225444584547</v>
+        <v>-0.16211309661743</v>
       </c>
       <c r="AU16" s="9" t="n">
         <f aca="false">IF(AR$6=0,"",AR16/AR$6)</f>
-        <v>0.0345672095715622</v>
+        <v>0.0233436756309267</v>
       </c>
       <c r="AV16" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B16)</f>
-        <v>800</v>
+        <v>24</v>
       </c>
       <c r="AW16" s="57" t="n">
         <f aca="false">IF(AND(AV16&gt;0,AX16&gt;0),AX16/AV16,"")</f>
-        <v>225</v>
+        <v>3576</v>
       </c>
       <c r="AX16" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B16)</f>
-        <v>180000</v>
+        <v>85824</v>
       </c>
       <c r="AY16" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B16)</f>
-        <v>187400</v>
+        <v>94915.2</v>
       </c>
       <c r="AZ16" s="8" t="n">
         <f aca="false">AY16-AX16</f>
-        <v>7400</v>
+        <v>9091.20000000001</v>
       </c>
       <c r="BA16" s="9" t="n">
         <f aca="false">IF(AX16&gt;0,AZ16/AX16,"")</f>
-        <v>0.0411111111111111</v>
+        <v>0.10592841163311</v>
       </c>
       <c r="BB16" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY16/AY$6)</f>
-        <v>0.0484737401427912</v>
+        <v>0.024551199255075</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5553,7 +5556,7 @@
       </c>
       <c r="C17" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B17,Prices!$A$6:$A$300,0)),"")</f>
-        <v>3954.8</v>
+        <v>234.25</v>
       </c>
       <c r="D17" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B17,Prices!$A$6:$A$300,0)),"")</f>
@@ -5561,203 +5564,203 @@
       </c>
       <c r="E17" s="6" t="n">
         <f aca="false">(M17&gt;0)+(T17&gt;0)+(AA17&gt;0)+(AH17&gt;0)+(AO17&gt;0)+(AV17&gt;0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="50" t="n">
         <f aca="false">M17+T17+AA17+AH17+AO17+AV17</f>
-        <v>231</v>
+        <v>4000</v>
       </c>
       <c r="G17" s="51" t="n">
         <f aca="false">IF(AND(F17&gt;0,H17&gt;0),H17/F17,"")</f>
-        <v>3876.0303030303</v>
+        <v>233.36675</v>
       </c>
       <c r="H17" s="52" t="n">
         <f aca="false">O17+V17+AC17+AJ17+AQ17+AX17</f>
-        <v>895363</v>
+        <v>933467</v>
       </c>
       <c r="I17" s="53" t="n">
         <f aca="false">P17+W17+AD17+AK17+AR17+AY17</f>
-        <v>913558.8</v>
+        <v>937000</v>
       </c>
       <c r="J17" s="52" t="n">
         <f aca="false">I17-H17</f>
-        <v>18195.8</v>
+        <v>3533</v>
       </c>
       <c r="K17" s="54" t="n">
         <f aca="false">IF(H17&gt;0,J17/H17,"")</f>
-        <v>0.0203222603569726</v>
+        <v>0.00378481510326557</v>
       </c>
       <c r="L17" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I17/I$6)</f>
-        <v>0.0242116425795037</v>
+        <v>0.0243538649811635</v>
       </c>
       <c r="M17" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B17)</f>
-        <v>30</v>
+        <v>800</v>
       </c>
       <c r="N17" s="57" t="n">
         <f aca="false">IF(AND(M17&gt;0,O17&gt;0),O17/M17,"")</f>
-        <v>3484.36666666667</v>
+        <v>264</v>
       </c>
       <c r="O17" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$E$7:$E$300,Gautam!$B$7:$B$300,$B17)</f>
-        <v>104531</v>
+        <v>211200</v>
       </c>
       <c r="P17" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$H$7:$H$300,Gautam!$B$7:$B$300,$B17)</f>
-        <v>118644</v>
+        <v>187400</v>
       </c>
       <c r="Q17" s="8" t="n">
         <f aca="false">P17-O17</f>
-        <v>14113</v>
+        <v>-23800</v>
       </c>
       <c r="R17" s="9" t="n">
         <f aca="false">IF(O17&gt;0,Q17/O17,"")</f>
-        <v>0.135012580000191</v>
+        <v>-0.112689393939394</v>
       </c>
       <c r="S17" s="9" t="n">
         <f aca="false">IF(P$6=0,"",P17/P$6)</f>
-        <v>0.022706302066734</v>
+        <v>0.0358649489844067</v>
       </c>
       <c r="T17" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B17)</f>
-        <v>72</v>
+        <v>800</v>
       </c>
       <c r="U17" s="57" t="n">
         <f aca="false">IF(AND(T17&gt;0,V17&gt;0),V17/T17,"")</f>
-        <v>4214.81944444444</v>
+        <v>235.09375</v>
       </c>
       <c r="V17" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B17)</f>
-        <v>303467</v>
+        <v>188075</v>
       </c>
       <c r="W17" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B17)</f>
-        <v>284745.6</v>
+        <v>187400</v>
       </c>
       <c r="X17" s="8" t="n">
         <f aca="false">W17-V17</f>
-        <v>-18721.4</v>
+        <v>-675</v>
       </c>
       <c r="Y17" s="9" t="n">
         <f aca="false">IF(V17&gt;0,X17/V17,"")</f>
-        <v>-0.0616917160679743</v>
+        <v>-0.00358899375249236</v>
       </c>
       <c r="Z17" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W17/W$6)</f>
-        <v>0.024078143931284</v>
+        <v>0.0158465808522506</v>
       </c>
       <c r="AA17" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B17)</f>
-        <v>72</v>
+        <v>800</v>
       </c>
       <c r="AB17" s="57" t="n">
         <f aca="false">IF(AND(AA17&gt;0,AC17&gt;0),AC17/AA17,"")</f>
-        <v>3415.20833333333</v>
+        <v>212.75</v>
       </c>
       <c r="AC17" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B17)</f>
-        <v>245895</v>
+        <v>170200</v>
       </c>
       <c r="AD17" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B17)</f>
-        <v>284745.6</v>
+        <v>187400</v>
       </c>
       <c r="AE17" s="8" t="n">
         <f aca="false">AD17-AC17</f>
-        <v>38850.6</v>
+        <v>17200</v>
       </c>
       <c r="AF17" s="9" t="n">
         <f aca="false">IF(AC17&gt;0,AE17/AC17,"")</f>
-        <v>0.15799670591106</v>
+        <v>0.101057579318449</v>
       </c>
       <c r="AG17" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD17/AD$6)</f>
-        <v>0.0254976445923811</v>
+        <v>0.0157350719818752</v>
       </c>
       <c r="AH17" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B17)</f>
-        <v>1</v>
-      </c>
-      <c r="AI17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="57" t="str">
         <f aca="false">IF(AND(AH17&gt;0,AJ17&gt;0),AJ17/AH17,"")</f>
-        <v>4607</v>
+        <v/>
       </c>
       <c r="AJ17" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$E$7:$E$300,'Vidushi Malhotra'!$B$7:$B$300,$B17)</f>
-        <v>4607</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="8" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$H$7:$H$300,'Vidushi Malhotra'!$B$7:$B$300,$B17)</f>
-        <v>3954.8</v>
+        <v>0</v>
       </c>
       <c r="AL17" s="8" t="n">
         <f aca="false">AK17-AJ17</f>
-        <v>-652.2</v>
-      </c>
-      <c r="AM17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="9" t="str">
         <f aca="false">IF(AJ17&gt;0,AL17/AJ17,"")</f>
-        <v>-0.141567180377686</v>
+        <v/>
       </c>
       <c r="AN17" s="9" t="n">
         <f aca="false">IF(AK$6=0,"",AK17/AK$6)</f>
-        <v>0.0174759661227064</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="56" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$D$7:$D$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B17)</f>
-        <v>32</v>
+        <v>800</v>
       </c>
       <c r="AP17" s="57" t="n">
         <f aca="false">IF(AND(AO17&gt;0,AQ17&gt;0),AQ17/AO17,"")</f>
-        <v>4719.96875</v>
+        <v>229.99</v>
       </c>
       <c r="AQ17" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$E$7:$E$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B17)</f>
-        <v>151039</v>
+        <v>183992</v>
       </c>
       <c r="AR17" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$H$7:$H$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B17)</f>
-        <v>126553.6</v>
+        <v>187400</v>
       </c>
       <c r="AS17" s="8" t="n">
         <f aca="false">AR17-AQ17</f>
-        <v>-24485.4</v>
+        <v>3408</v>
       </c>
       <c r="AT17" s="9" t="n">
         <f aca="false">IF(AQ17&gt;0,AS17/AQ17,"")</f>
-        <v>-0.16211309661743</v>
+        <v>0.0185225444584547</v>
       </c>
       <c r="AU17" s="9" t="n">
         <f aca="false">IF(AR$6=0,"",AR17/AR$6)</f>
-        <v>0.0233436756309267</v>
+        <v>0.0345672095715622</v>
       </c>
       <c r="AV17" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B17)</f>
-        <v>24</v>
+        <v>800</v>
       </c>
       <c r="AW17" s="57" t="n">
         <f aca="false">IF(AND(AV17&gt;0,AX17&gt;0),AX17/AV17,"")</f>
-        <v>3576</v>
+        <v>225</v>
       </c>
       <c r="AX17" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B17)</f>
-        <v>85824</v>
+        <v>180000</v>
       </c>
       <c r="AY17" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B17)</f>
-        <v>94915.2</v>
+        <v>187400</v>
       </c>
       <c r="AZ17" s="8" t="n">
         <f aca="false">AY17-AX17</f>
-        <v>9091.20000000001</v>
+        <v>7400</v>
       </c>
       <c r="BA17" s="9" t="n">
         <f aca="false">IF(AX17&gt;0,AZ17/AX17,"")</f>
-        <v>0.10592841163311</v>
+        <v>0.0411111111111111</v>
       </c>
       <c r="BB17" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY17/AY$6)</f>
-        <v>0.024551199255075</v>
+        <v>0.0484737401427912</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5805,7 +5808,7 @@
       </c>
       <c r="L18" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I18/I$6)</f>
-        <v>0.0214617692488782</v>
+        <v>0.021047769329505</v>
       </c>
       <c r="M18" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B18)</f>
@@ -5889,7 +5892,7 @@
       </c>
       <c r="AG18" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD18/AD$6)</f>
-        <v>0.0725138249402633</v>
+        <v>0.0679949908800564</v>
       </c>
       <c r="AH18" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B18)</f>
@@ -5997,31 +6000,31 @@
       </c>
       <c r="F19" s="50" t="n">
         <f aca="false">M19+T19+AA19+AH19+AO19+AV19</f>
-        <v>13610</v>
+        <v>13921</v>
       </c>
       <c r="G19" s="51" t="n">
         <f aca="false">IF(AND(F19&gt;0,H19&gt;0),H19/F19,"")</f>
-        <v>39.6277736958119</v>
+        <v>39.8168235040586</v>
       </c>
       <c r="H19" s="52" t="n">
         <f aca="false">O19+V19+AC19+AJ19+AQ19+AX19</f>
-        <v>539334</v>
+        <v>554290</v>
       </c>
       <c r="I19" s="53" t="n">
         <f aca="false">P19+W19+AD19+AK19+AR19+AY19</f>
-        <v>701595.5</v>
+        <v>717627.55</v>
       </c>
       <c r="J19" s="52" t="n">
         <f aca="false">I19-H19</f>
-        <v>162261.5</v>
+        <v>163337.55</v>
       </c>
       <c r="K19" s="54" t="n">
         <f aca="false">IF(H19&gt;0,J19/H19,"")</f>
-        <v>0.300855314146707</v>
+        <v>0.294678868462357</v>
       </c>
       <c r="L19" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I19/I$6)</f>
-        <v>0.0185940735083371</v>
+        <v>0.0186520858692243</v>
       </c>
       <c r="M19" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B19)</f>
@@ -6081,31 +6084,31 @@
       </c>
       <c r="AA19" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B19)</f>
-        <v>4830</v>
+        <v>5141</v>
       </c>
       <c r="AB19" s="57" t="n">
         <f aca="false">IF(AND(AA19&gt;0,AC19&gt;0),AC19/AA19,"")</f>
-        <v>43.4501035196687</v>
+        <v>43.7307916747714</v>
       </c>
       <c r="AC19" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B19)</f>
-        <v>209864</v>
+        <v>224820</v>
       </c>
       <c r="AD19" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B19)</f>
-        <v>248986.5</v>
+        <v>265018.55</v>
       </c>
       <c r="AE19" s="8" t="n">
         <f aca="false">AD19-AC19</f>
-        <v>39122.5</v>
+        <v>40198.55</v>
       </c>
       <c r="AF19" s="9" t="n">
         <f aca="false">IF(AC19&gt;0,AE19/AC19,"")</f>
-        <v>0.18641834712004</v>
+        <v>0.178803264834089</v>
       </c>
       <c r="AG19" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD19/AD$6)</f>
-        <v>0.022295583444664</v>
+        <v>0.0222523263648997</v>
       </c>
       <c r="AH19" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B19)</f>
@@ -6213,31 +6216,31 @@
       </c>
       <c r="F20" s="50" t="n">
         <f aca="false">M20+T20+AA20+AH20+AO20+AV20</f>
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G20" s="51" t="n">
         <f aca="false">IF(AND(F20&gt;0,H20&gt;0),H20/F20,"")</f>
-        <v>4321.92045454546</v>
+        <v>4310.01111111111</v>
       </c>
       <c r="H20" s="52" t="n">
         <f aca="false">O20+V20+AC20+AJ20+AQ20+AX20</f>
-        <v>760658</v>
+        <v>775802</v>
       </c>
       <c r="I20" s="53" t="n">
         <f aca="false">P20+W20+AD20+AK20+AR20+AY20</f>
-        <v>677036.8</v>
+        <v>692424</v>
       </c>
       <c r="J20" s="52" t="n">
         <f aca="false">I20-H20</f>
-        <v>-83621.2</v>
+        <v>-83378</v>
       </c>
       <c r="K20" s="54" t="n">
         <f aca="false">IF(H20&gt;0,J20/H20,"")</f>
-        <v>-0.109932716148387</v>
+        <v>-0.107473298599385</v>
       </c>
       <c r="L20" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I20/I$6)</f>
-        <v>0.0179432052044936</v>
+        <v>0.0179970123860375</v>
       </c>
       <c r="M20" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B20)</f>
@@ -6297,31 +6300,31 @@
       </c>
       <c r="AA20" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B20)</f>
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AB20" s="57" t="n">
         <f aca="false">IF(AND(AA20&gt;0,AC20&gt;0),AC20/AA20,"")</f>
-        <v>4047.80327868852</v>
+        <v>4031.69230769231</v>
       </c>
       <c r="AC20" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B20)</f>
-        <v>246916</v>
+        <v>262060</v>
       </c>
       <c r="AD20" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B20)</f>
-        <v>234654.8</v>
+        <v>250042</v>
       </c>
       <c r="AE20" s="8" t="n">
         <f aca="false">AD20-AC20</f>
-        <v>-12261.2</v>
+        <v>-12018</v>
       </c>
       <c r="AF20" s="9" t="n">
         <f aca="false">IF(AC20&gt;0,AE20/AC20,"")</f>
-        <v>-0.049657373357741</v>
+        <v>-0.0458597267801267</v>
       </c>
       <c r="AG20" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD20/AD$6)</f>
-        <v>0.0210122463430384</v>
+        <v>0.0209948178681539</v>
       </c>
       <c r="AH20" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B20)</f>
@@ -6429,31 +6432,31 @@
       </c>
       <c r="F21" s="50" t="n">
         <f aca="false">M21+T21+AA21+AH21+AO21+AV21</f>
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G21" s="51" t="n">
         <f aca="false">IF(AND(F21&gt;0,H21&gt;0),H21/F21,"")</f>
-        <v>5124.60810810811</v>
+        <v>5158.60256410256</v>
       </c>
       <c r="H21" s="52" t="n">
         <f aca="false">O21+V21+AC21+AJ21+AQ21+AX21</f>
-        <v>379221</v>
+        <v>402371</v>
       </c>
       <c r="I21" s="53" t="n">
         <f aca="false">P21+W21+AD21+AK21+AR21+AY21</f>
-        <v>424797</v>
+        <v>447759</v>
       </c>
       <c r="J21" s="52" t="n">
         <f aca="false">I21-H21</f>
-        <v>45576</v>
+        <v>45388</v>
       </c>
       <c r="K21" s="54" t="n">
         <f aca="false">IF(H21&gt;0,J21/H21,"")</f>
-        <v>0.120183217701551</v>
+        <v>0.112801369880036</v>
       </c>
       <c r="L21" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I21/I$6)</f>
-        <v>0.0112582059664309</v>
+        <v>0.0116378465636081</v>
       </c>
       <c r="M21" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B21)</f>
@@ -6513,31 +6516,31 @@
       </c>
       <c r="AA21" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B21)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB21" s="57" t="n">
         <f aca="false">IF(AND(AA21&gt;0,AC21&gt;0),AC21/AA21,"")</f>
-        <v>5039.55555555556</v>
+        <v>5269.69230769231</v>
       </c>
       <c r="AC21" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B21)</f>
-        <v>45356</v>
+        <v>68506</v>
       </c>
       <c r="AD21" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B21)</f>
-        <v>51664.5</v>
+        <v>74626.5</v>
       </c>
       <c r="AE21" s="8" t="n">
         <f aca="false">AD21-AC21</f>
-        <v>6308.5</v>
+        <v>6120.5</v>
       </c>
       <c r="AF21" s="9" t="n">
         <f aca="false">IF(AC21&gt;0,AE21/AC21,"")</f>
-        <v>0.139088543963312</v>
+        <v>0.0893425393396199</v>
       </c>
       <c r="AG21" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD21/AD$6)</f>
-        <v>0.00462631576762933</v>
+        <v>0.00626602641011426</v>
       </c>
       <c r="AH21" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B21)</f>
@@ -6645,31 +6648,31 @@
       </c>
       <c r="F22" s="50" t="n">
         <f aca="false">M22+T22+AA22+AH22+AO22+AV22</f>
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G22" s="51" t="n">
         <f aca="false">IF(AND(F22&gt;0,H22&gt;0),H22/F22,"")</f>
-        <v>1577.5231316726</v>
+        <v>1573.17132867133</v>
       </c>
       <c r="H22" s="52" t="n">
         <f aca="false">O22+V22+AC22+AJ22+AQ22+AX22</f>
-        <v>443284</v>
+        <v>449927</v>
       </c>
       <c r="I22" s="53" t="n">
         <f aca="false">P22+W22+AD22+AK22+AR22+AY22</f>
-        <v>382946.8</v>
+        <v>389760.8</v>
       </c>
       <c r="J22" s="52" t="n">
         <f aca="false">I22-H22</f>
-        <v>-60337.2</v>
+        <v>-60166.2</v>
       </c>
       <c r="K22" s="54" t="n">
         <f aca="false">IF(H22&gt;0,J22/H22,"")</f>
-        <v>-0.136114093899171</v>
+        <v>-0.133724359729467</v>
       </c>
       <c r="L22" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I22/I$6)</f>
-        <v>0.0101490687283234</v>
+        <v>0.0101303969030419</v>
       </c>
       <c r="M22" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B22)</f>
@@ -6729,31 +6732,31 @@
       </c>
       <c r="AA22" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B22)</f>
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AB22" s="57" t="n">
         <f aca="false">IF(AND(AA22&gt;0,AC22&gt;0),AC22/AA22,"")</f>
-        <v>1477.86301369863</v>
+        <v>1468.29487179487</v>
       </c>
       <c r="AC22" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B22)</f>
-        <v>107884</v>
+        <v>114527</v>
       </c>
       <c r="AD22" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B22)</f>
-        <v>99484.4</v>
+        <v>106298.4</v>
       </c>
       <c r="AE22" s="8" t="n">
         <f aca="false">AD22-AC22</f>
-        <v>-8399.60000000001</v>
+        <v>-8228.60000000001</v>
       </c>
       <c r="AF22" s="9" t="n">
         <f aca="false">IF(AC22&gt;0,AE22/AC22,"")</f>
-        <v>-0.0778576990100479</v>
+        <v>-0.0718485597282737</v>
       </c>
       <c r="AG22" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD22/AD$6)</f>
-        <v>0.00890836548022614</v>
+        <v>0.0089253627297661</v>
       </c>
       <c r="AH22" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B22)</f>
@@ -6885,7 +6888,7 @@
       </c>
       <c r="L23" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I23/I$6)</f>
-        <v>0.00871934068026789</v>
+        <v>0.00855114362732422</v>
       </c>
       <c r="M23" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B23)</f>
@@ -7065,127 +7068,127 @@
       </c>
       <c r="C24" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B24,Prices!$A$6:$A$300,0)),"")</f>
-        <v>157.329098383758</v>
+        <v>7084.5</v>
       </c>
       <c r="D24" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B24,Prices!$A$6:$A$300,0)),"")</f>
-        <v>Manish Shilpa stmt – live 23.10</v>
+        <v>Close 22.10.2026 (Screener.in)</v>
       </c>
       <c r="E24" s="6" t="n">
         <f aca="false">(M24&gt;0)+(T24&gt;0)+(AA24&gt;0)+(AH24&gt;0)+(AO24&gt;0)+(AV24&gt;0)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F24" s="50" t="n">
         <f aca="false">M24+T24+AA24+AH24+AO24+AV24</f>
-        <v>2004.589</v>
+        <v>45</v>
       </c>
       <c r="G24" s="51" t="n">
         <f aca="false">IF(AND(F24&gt;0,H24&gt;0),H24/F24,"")</f>
-        <v>99.7660867140347</v>
+        <v>7414.86666666667</v>
       </c>
       <c r="H24" s="52" t="n">
         <f aca="false">O24+V24+AC24+AJ24+AQ24+AX24</f>
-        <v>199990</v>
+        <v>333669</v>
       </c>
       <c r="I24" s="53" t="n">
         <f aca="false">P24+W24+AD24+AK24+AR24+AY24</f>
-        <v>315380.18</v>
+        <v>318802.5</v>
       </c>
       <c r="J24" s="52" t="n">
         <f aca="false">I24-H24</f>
-        <v>115390.18</v>
+        <v>-14866.5</v>
       </c>
       <c r="K24" s="54" t="n">
         <f aca="false">IF(H24&gt;0,J24/H24,"")</f>
-        <v>0.576979748987449</v>
+        <v>-0.0445546334840815</v>
       </c>
       <c r="L24" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I24/I$6)</f>
-        <v>0.0083583806480979</v>
+        <v>0.0082860971618542</v>
       </c>
       <c r="M24" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B24)</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="57" t="str">
+        <v>20</v>
+      </c>
+      <c r="N24" s="57" t="n">
         <f aca="false">IF(AND(M24&gt;0,O24&gt;0),O24/M24,"")</f>
-        <v/>
+        <v>7370.7</v>
       </c>
       <c r="O24" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$E$7:$E$300,Gautam!$B$7:$B$300,$B24)</f>
-        <v>0</v>
+        <v>147414</v>
       </c>
       <c r="P24" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$H$7:$H$300,Gautam!$B$7:$B$300,$B24)</f>
-        <v>0</v>
+        <v>141690</v>
       </c>
       <c r="Q24" s="8" t="n">
         <f aca="false">P24-O24</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="9" t="str">
+        <v>-5724</v>
+      </c>
+      <c r="R24" s="9" t="n">
         <f aca="false">IF(O24&gt;0,Q24/O24,"")</f>
-        <v/>
+        <v>-0.0388294191867801</v>
       </c>
       <c r="S24" s="9" t="n">
         <f aca="false">IF(P$6=0,"",P24/P$6)</f>
-        <v>0</v>
+        <v>0.0271168869882635</v>
       </c>
       <c r="T24" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B24)</f>
-        <v>2004.589</v>
+        <v>6</v>
       </c>
       <c r="U24" s="57" t="n">
         <f aca="false">IF(AND(T24&gt;0,V24&gt;0),V24/T24,"")</f>
-        <v>99.7660867140347</v>
+        <v>7291.16666666667</v>
       </c>
       <c r="V24" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B24)</f>
-        <v>199990</v>
+        <v>43747</v>
       </c>
       <c r="W24" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B24)</f>
-        <v>315380.18</v>
+        <v>42507</v>
       </c>
       <c r="X24" s="8" t="n">
         <f aca="false">W24-V24</f>
-        <v>115390.18</v>
+        <v>-1240</v>
       </c>
       <c r="Y24" s="9" t="n">
         <f aca="false">IF(V24&gt;0,X24/V24,"")</f>
-        <v>0.576979748987449</v>
+        <v>-0.0283448007863396</v>
       </c>
       <c r="Z24" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W24/W$6)</f>
-        <v>0.0266686100403808</v>
+        <v>0.00359440027901077</v>
       </c>
       <c r="AA24" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="57" t="str">
+        <v>8</v>
+      </c>
+      <c r="AB24" s="57" t="n">
         <f aca="false">IF(AND(AA24&gt;0,AC24&gt;0),AC24/AA24,"")</f>
-        <v/>
+        <v>7180.5</v>
       </c>
       <c r="AC24" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B24)</f>
-        <v>0</v>
+        <v>57444</v>
       </c>
       <c r="AD24" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B24)</f>
-        <v>0</v>
+        <v>56676</v>
       </c>
       <c r="AE24" s="8" t="n">
         <f aca="false">AD24-AC24</f>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="9" t="str">
+        <v>-768</v>
+      </c>
+      <c r="AF24" s="9" t="n">
         <f aca="false">IF(AC24&gt;0,AE24/AC24,"")</f>
-        <v/>
+        <v>-0.0133695425109672</v>
       </c>
       <c r="AG24" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD24/AD$6)</f>
-        <v>0</v>
+        <v>0.0047588097099507</v>
       </c>
       <c r="AH24" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B24)</f>
@@ -7217,59 +7220,59 @@
       </c>
       <c r="AO24" s="56" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$D$7:$D$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AP24" s="57" t="str">
+        <v>3</v>
+      </c>
+      <c r="AP24" s="57" t="n">
         <f aca="false">IF(AND(AO24&gt;0,AQ24&gt;0),AQ24/AO24,"")</f>
-        <v/>
+        <v>6905.66666666667</v>
       </c>
       <c r="AQ24" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$E$7:$E$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B24)</f>
-        <v>0</v>
+        <v>20717</v>
       </c>
       <c r="AR24" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$H$7:$H$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B24)</f>
-        <v>0</v>
+        <v>21253.5</v>
       </c>
       <c r="AS24" s="8" t="n">
         <f aca="false">AR24-AQ24</f>
-        <v>0</v>
-      </c>
-      <c r="AT24" s="9" t="str">
+        <v>536.5</v>
+      </c>
+      <c r="AT24" s="9" t="n">
         <f aca="false">IF(AQ24&gt;0,AS24/AQ24,"")</f>
-        <v/>
+        <v>0.0258966066515422</v>
       </c>
       <c r="AU24" s="9" t="n">
         <f aca="false">IF(AR$6=0,"",AR24/AR$6)</f>
-        <v>0</v>
+        <v>0.00392035319439273</v>
       </c>
       <c r="AV24" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AW24" s="57" t="str">
+        <v>8</v>
+      </c>
+      <c r="AW24" s="57" t="n">
         <f aca="false">IF(AND(AV24&gt;0,AX24&gt;0),AX24/AV24,"")</f>
-        <v/>
+        <v>8043.375</v>
       </c>
       <c r="AX24" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B24)</f>
-        <v>0</v>
+        <v>64347</v>
       </c>
       <c r="AY24" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B24)</f>
-        <v>0</v>
+        <v>56676</v>
       </c>
       <c r="AZ24" s="8" t="n">
         <f aca="false">AY24-AX24</f>
-        <v>0</v>
-      </c>
-      <c r="BA24" s="9" t="str">
+        <v>-7671</v>
+      </c>
+      <c r="BA24" s="9" t="n">
         <f aca="false">IF(AX24&gt;0,AZ24/AX24,"")</f>
-        <v/>
+        <v>-0.119213016923866</v>
       </c>
       <c r="BB24" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY24/AY$6)</f>
-        <v>0</v>
+        <v>0.0146600730860877</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7281,127 +7284,127 @@
       </c>
       <c r="C25" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B25,Prices!$A$6:$A$300,0)),"")</f>
-        <v>7084.5</v>
+        <v>157.329098383758</v>
       </c>
       <c r="D25" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B25,Prices!$A$6:$A$300,0)),"")</f>
-        <v>Close 22.10.2026 (Screener.in)</v>
+        <v>Manish Shilpa stmt – live 23.10</v>
       </c>
       <c r="E25" s="6" t="n">
         <f aca="false">(M25&gt;0)+(T25&gt;0)+(AA25&gt;0)+(AH25&gt;0)+(AO25&gt;0)+(AV25&gt;0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F25" s="50" t="n">
         <f aca="false">M25+T25+AA25+AH25+AO25+AV25</f>
-        <v>43</v>
+        <v>2004.589</v>
       </c>
       <c r="G25" s="51" t="n">
         <f aca="false">IF(AND(F25&gt;0,H25&gt;0),H25/F25,"")</f>
-        <v>7435.76744186047</v>
+        <v>99.7660867140347</v>
       </c>
       <c r="H25" s="52" t="n">
         <f aca="false">O25+V25+AC25+AJ25+AQ25+AX25</f>
-        <v>319738</v>
+        <v>199990</v>
       </c>
       <c r="I25" s="53" t="n">
         <f aca="false">P25+W25+AD25+AK25+AR25+AY25</f>
-        <v>304633.5</v>
+        <v>315380.18</v>
       </c>
       <c r="J25" s="52" t="n">
         <f aca="false">I25-H25</f>
-        <v>-15104.5</v>
+        <v>115390.18</v>
       </c>
       <c r="K25" s="54" t="n">
         <f aca="false">IF(H25&gt;0,J25/H25,"")</f>
-        <v>-0.0472402404468659</v>
+        <v>0.576979748987449</v>
       </c>
       <c r="L25" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I25/I$6)</f>
-        <v>0.00807356616754525</v>
+        <v>0.00819714655438105</v>
       </c>
       <c r="M25" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B25)</f>
-        <v>20</v>
-      </c>
-      <c r="N25" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="57" t="str">
         <f aca="false">IF(AND(M25&gt;0,O25&gt;0),O25/M25,"")</f>
-        <v>7370.7</v>
+        <v/>
       </c>
       <c r="O25" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$E$7:$E$300,Gautam!$B$7:$B$300,$B25)</f>
-        <v>147414</v>
+        <v>0</v>
       </c>
       <c r="P25" s="8" t="n">
         <f aca="false">SUMIFS(Gautam!$H$7:$H$300,Gautam!$B$7:$B$300,$B25)</f>
-        <v>141690</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="8" t="n">
         <f aca="false">P25-O25</f>
-        <v>-5724</v>
-      </c>
-      <c r="R25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="9" t="str">
         <f aca="false">IF(O25&gt;0,Q25/O25,"")</f>
-        <v>-0.0388294191867801</v>
+        <v/>
       </c>
       <c r="S25" s="9" t="n">
         <f aca="false">IF(P$6=0,"",P25/P$6)</f>
-        <v>0.0271168869882635</v>
+        <v>0</v>
       </c>
       <c r="T25" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B25)</f>
-        <v>6</v>
+        <v>2004.589</v>
       </c>
       <c r="U25" s="57" t="n">
         <f aca="false">IF(AND(T25&gt;0,V25&gt;0),V25/T25,"")</f>
-        <v>7291.16666666667</v>
+        <v>99.7660867140347</v>
       </c>
       <c r="V25" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B25)</f>
-        <v>43747</v>
+        <v>199990</v>
       </c>
       <c r="W25" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B25)</f>
-        <v>42507</v>
+        <v>315380.18</v>
       </c>
       <c r="X25" s="8" t="n">
         <f aca="false">W25-V25</f>
-        <v>-1240</v>
+        <v>115390.18</v>
       </c>
       <c r="Y25" s="9" t="n">
         <f aca="false">IF(V25&gt;0,X25/V25,"")</f>
-        <v>-0.0283448007863396</v>
+        <v>0.576979748987449</v>
       </c>
       <c r="Z25" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W25/W$6)</f>
-        <v>0.00359440027901077</v>
+        <v>0.0266686100403808</v>
       </c>
       <c r="AA25" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B25)</f>
-        <v>6</v>
-      </c>
-      <c r="AB25" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="57" t="str">
         <f aca="false">IF(AND(AA25&gt;0,AC25&gt;0),AC25/AA25,"")</f>
-        <v>7252.16666666667</v>
+        <v/>
       </c>
       <c r="AC25" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B25)</f>
-        <v>43513</v>
+        <v>0</v>
       </c>
       <c r="AD25" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B25)</f>
-        <v>42507</v>
+        <v>0</v>
       </c>
       <c r="AE25" s="8" t="n">
         <f aca="false">AD25-AC25</f>
-        <v>-1006</v>
-      </c>
-      <c r="AF25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="9" t="str">
         <f aca="false">IF(AC25&gt;0,AE25/AC25,"")</f>
-        <v>-0.0231195274975295</v>
+        <v/>
       </c>
       <c r="AG25" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD25/AD$6)</f>
-        <v>0.0038063042192341</v>
+        <v>0</v>
       </c>
       <c r="AH25" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B25)</f>
@@ -7433,59 +7436,59 @@
       </c>
       <c r="AO25" s="56" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$D$7:$D$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B25)</f>
-        <v>3</v>
-      </c>
-      <c r="AP25" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="57" t="str">
         <f aca="false">IF(AND(AO25&gt;0,AQ25&gt;0),AQ25/AO25,"")</f>
-        <v>6905.66666666667</v>
+        <v/>
       </c>
       <c r="AQ25" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$E$7:$E$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B25)</f>
-        <v>20717</v>
+        <v>0</v>
       </c>
       <c r="AR25" s="8" t="n">
         <f aca="false">SUMIFS('Dr Umesh Choudhry'!$H$7:$H$300,'Dr Umesh Choudhry'!$B$7:$B$300,$B25)</f>
-        <v>21253.5</v>
+        <v>0</v>
       </c>
       <c r="AS25" s="8" t="n">
         <f aca="false">AR25-AQ25</f>
-        <v>536.5</v>
-      </c>
-      <c r="AT25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" s="9" t="str">
         <f aca="false">IF(AQ25&gt;0,AS25/AQ25,"")</f>
-        <v>0.0258966066515422</v>
+        <v/>
       </c>
       <c r="AU25" s="9" t="n">
         <f aca="false">IF(AR$6=0,"",AR25/AR$6)</f>
-        <v>0.00392035319439273</v>
+        <v>0</v>
       </c>
       <c r="AV25" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B25)</f>
-        <v>8</v>
-      </c>
-      <c r="AW25" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" s="57" t="str">
         <f aca="false">IF(AND(AV25&gt;0,AX25&gt;0),AX25/AV25,"")</f>
-        <v>8043.375</v>
+        <v/>
       </c>
       <c r="AX25" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B25)</f>
-        <v>64347</v>
+        <v>0</v>
       </c>
       <c r="AY25" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B25)</f>
-        <v>56676</v>
+        <v>0</v>
       </c>
       <c r="AZ25" s="8" t="n">
         <f aca="false">AY25-AX25</f>
-        <v>-7671</v>
-      </c>
-      <c r="BA25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" s="9" t="str">
         <f aca="false">IF(AX25&gt;0,AZ25/AX25,"")</f>
-        <v>-0.119213016923866</v>
+        <v/>
       </c>
       <c r="BB25" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY25/AY$6)</f>
-        <v>0.0146600730860877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7533,7 +7536,7 @@
       </c>
       <c r="L26" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I26/I$6)</f>
-        <v>0.00799582092169247</v>
+        <v>0.00784158064548243</v>
       </c>
       <c r="M26" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B26)</f>
@@ -7617,7 +7620,7 @@
       </c>
       <c r="AG26" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD26/AD$6)</f>
-        <v>0.0270158322851043</v>
+        <v>0.0253322903785046</v>
       </c>
       <c r="AH26" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B26)</f>
@@ -7749,7 +7752,7 @@
       </c>
       <c r="L27" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I27/I$6)</f>
-        <v>0.00558782525339928</v>
+        <v>0.00548003548185005</v>
       </c>
       <c r="M27" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B27)</f>
@@ -7941,31 +7944,31 @@
       </c>
       <c r="F28" s="50" t="n">
         <f aca="false">M28+T28+AA28+AH28+AO28+AV28</f>
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G28" s="51" t="n">
         <f aca="false">IF(AND(F28&gt;0,H28&gt;0),H28/F28,"")</f>
-        <v>2883.46376811594</v>
+        <v>2877.11111111111</v>
       </c>
       <c r="H28" s="52" t="n">
         <f aca="false">O28+V28+AC28+AJ28+AQ28+AX28</f>
-        <v>198959</v>
+        <v>207152</v>
       </c>
       <c r="I28" s="53" t="n">
         <f aca="false">P28+W28+AD28+AK28+AR28+AY28</f>
-        <v>191530.2</v>
+        <v>199857.6</v>
       </c>
       <c r="J28" s="52" t="n">
         <f aca="false">I28-H28</f>
-        <v>-7428.80000000002</v>
+        <v>-7294.39999999999</v>
       </c>
       <c r="K28" s="54" t="n">
         <f aca="false">IF(H28&gt;0,J28/H28,"")</f>
-        <v>-0.0373383460914059</v>
+        <v>-0.0352127906078628</v>
       </c>
       <c r="L28" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I28/I$6)</f>
-        <v>0.00507603970930044</v>
+        <v>0.00519456243955111</v>
       </c>
       <c r="M28" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B28)</f>
@@ -8025,31 +8028,31 @@
       </c>
       <c r="AA28" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B28)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB28" s="57" t="n">
         <f aca="false">IF(AND(AA28&gt;0,AC28&gt;0),AC28/AA28,"")</f>
-        <v>2787.4</v>
+        <v>2766.25</v>
       </c>
       <c r="AC28" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B28)</f>
-        <v>13937</v>
+        <v>22130</v>
       </c>
       <c r="AD28" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B28)</f>
-        <v>13879</v>
+        <v>22206.4</v>
       </c>
       <c r="AE28" s="8" t="n">
         <f aca="false">AD28-AC28</f>
-        <v>-58</v>
+        <v>76.4000000000015</v>
       </c>
       <c r="AF28" s="9" t="n">
         <f aca="false">IF(AC28&gt;0,AE28/AC28,"")</f>
-        <v>-0.00416158427208151</v>
+        <v>0.00345232715770454</v>
       </c>
       <c r="AG28" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD28/AD$6)</f>
-        <v>0.0012427999213953</v>
+        <v>0.00186456404726955</v>
       </c>
       <c r="AH28" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B28)</f>
@@ -8157,31 +8160,31 @@
       </c>
       <c r="F29" s="50" t="n">
         <f aca="false">M29+T29+AA29+AH29+AO29+AV29</f>
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G29" s="51" t="n">
         <f aca="false">IF(AND(F29&gt;0,H29&gt;0),H29/F29,"")</f>
-        <v>1689.00636942675</v>
+        <v>1619.15254237288</v>
       </c>
       <c r="H29" s="52" t="n">
         <f aca="false">O29+V29+AC29+AJ29+AQ29+AX29</f>
-        <v>265174</v>
+        <v>286590</v>
       </c>
       <c r="I29" s="53" t="n">
         <f aca="false">P29+W29+AD29+AK29+AR29+AY29</f>
-        <v>171114.3</v>
+        <v>192912.3</v>
       </c>
       <c r="J29" s="52" t="n">
         <f aca="false">I29-H29</f>
-        <v>-94059.7</v>
+        <v>-93677.7</v>
       </c>
       <c r="K29" s="54" t="n">
         <f aca="false">IF(H29&gt;0,J29/H29,"")</f>
-        <v>-0.354709360646217</v>
+        <v>-0.326870093164451</v>
       </c>
       <c r="L29" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I29/I$6)</f>
-        <v>0.00453496619138469</v>
+        <v>0.00501404493853331</v>
       </c>
       <c r="M29" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B29)</f>
@@ -8241,31 +8244,31 @@
       </c>
       <c r="AA29" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B29)</f>
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="AB29" s="57" t="n">
         <f aca="false">IF(AND(AA29&gt;0,AC29&gt;0),AC29/AA29,"")</f>
-        <v>1308.29166666667</v>
+        <v>1238.44117647059</v>
       </c>
       <c r="AC29" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B29)</f>
-        <v>62798</v>
+        <v>84214</v>
       </c>
       <c r="AD29" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B29)</f>
-        <v>52315.2</v>
+        <v>74113.2</v>
       </c>
       <c r="AE29" s="8" t="n">
         <f aca="false">AD29-AC29</f>
-        <v>-10482.8</v>
+        <v>-10100.8</v>
       </c>
       <c r="AF29" s="9" t="n">
         <f aca="false">IF(AC29&gt;0,AE29/AC29,"")</f>
-        <v>-0.166928883085449</v>
+        <v>-0.119942052390339</v>
       </c>
       <c r="AG29" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD29/AD$6)</f>
-        <v>0.00468458292728434</v>
+        <v>0.00622292709075302</v>
       </c>
       <c r="AH29" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B29)</f>
@@ -8373,31 +8376,31 @@
       </c>
       <c r="F30" s="50" t="n">
         <f aca="false">M30+T30+AA30+AH30+AO30+AV30</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G30" s="51" t="n">
         <f aca="false">IF(AND(F30&gt;0,H30&gt;0),H30/F30,"")</f>
-        <v>3812.22222222222</v>
+        <v>3776.35087719298</v>
       </c>
       <c r="H30" s="52" t="n">
         <f aca="false">O30+V30+AC30+AJ30+AQ30+AX30</f>
-        <v>205860</v>
+        <v>215252</v>
       </c>
       <c r="I30" s="53" t="n">
         <f aca="false">P30+W30+AD30+AK30+AR30+AY30</f>
-        <v>170964</v>
+        <v>180462</v>
       </c>
       <c r="J30" s="52" t="n">
         <f aca="false">I30-H30</f>
-        <v>-34896</v>
+        <v>-34790</v>
       </c>
       <c r="K30" s="54" t="n">
         <f aca="false">IF(H30&gt;0,J30/H30,"")</f>
-        <v>-0.169513261439813</v>
+        <v>-0.161624514522513</v>
       </c>
       <c r="L30" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I30/I$6)</f>
-        <v>0.00453098285732924</v>
+        <v>0.00469044523183643</v>
       </c>
       <c r="M30" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B30)</f>
@@ -8457,31 +8460,31 @@
       </c>
       <c r="AA30" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B30)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB30" s="57" t="n">
         <f aca="false">IF(AND(AA30&gt;0,AC30&gt;0),AC30/AA30,"")</f>
-        <v>3673.57142857143</v>
+        <v>3510.7</v>
       </c>
       <c r="AC30" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B30)</f>
-        <v>25715</v>
+        <v>35107</v>
       </c>
       <c r="AD30" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B30)</f>
-        <v>22162</v>
+        <v>31660</v>
       </c>
       <c r="AE30" s="8" t="n">
         <f aca="false">AD30-AC30</f>
-        <v>-3553</v>
+        <v>-3447</v>
       </c>
       <c r="AF30" s="9" t="n">
         <f aca="false">IF(AC30&gt;0,AE30/AC30,"")</f>
-        <v>-0.13816838421155</v>
+        <v>-0.0981855470419005</v>
       </c>
       <c r="AG30" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD30/AD$6)</f>
-        <v>0.0019845040606645</v>
+        <v>0.00265833713418447</v>
       </c>
       <c r="AH30" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B30)</f>
@@ -8613,7 +8616,7 @@
       </c>
       <c r="L31" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I31/I$6)</f>
-        <v>0.00435039444579323</v>
+        <v>0.00426647485235645</v>
       </c>
       <c r="M31" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B31)</f>
@@ -8805,31 +8808,31 @@
       </c>
       <c r="F32" s="50" t="n">
         <f aca="false">M32+T32+AA32+AH32+AO32+AV32</f>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G32" s="51" t="n">
         <f aca="false">IF(AND(F32&gt;0,H32&gt;0),H32/F32,"")</f>
-        <v>845.776397515528</v>
+        <v>842.574850299401</v>
       </c>
       <c r="H32" s="52" t="n">
         <f aca="false">O32+V32+AC32+AJ32+AQ32+AX32</f>
-        <v>136170</v>
+        <v>140710</v>
       </c>
       <c r="I32" s="53" t="n">
         <f aca="false">P32+W32+AD32+AK32+AR32+AY32</f>
-        <v>126884.1</v>
+        <v>131612.7</v>
       </c>
       <c r="J32" s="52" t="n">
         <f aca="false">I32-H32</f>
-        <v>-9285.89999999999</v>
+        <v>-9097.29999999999</v>
       </c>
       <c r="K32" s="54" t="n">
         <f aca="false">IF(H32&gt;0,J32/H32,"")</f>
-        <v>-0.0681934346772416</v>
+        <v>-0.0646528320659512</v>
       </c>
       <c r="L32" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I32/I$6)</f>
-        <v>0.00336275287176042</v>
+        <v>0.0034207875406685</v>
       </c>
       <c r="M32" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B32)</f>
@@ -8889,31 +8892,31 @@
       </c>
       <c r="AA32" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B32)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AB32" s="57" t="n">
         <f aca="false">IF(AND(AA32&gt;0,AC32&gt;0),AC32/AA32,"")</f>
-        <v>874.434210526316</v>
+        <v>865.817073170732</v>
       </c>
       <c r="AC32" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B32)</f>
-        <v>66457</v>
+        <v>70997</v>
       </c>
       <c r="AD32" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B32)</f>
-        <v>59895.6</v>
+        <v>64624.2</v>
       </c>
       <c r="AE32" s="8" t="n">
         <f aca="false">AD32-AC32</f>
-        <v>-6561.4</v>
+        <v>-6372.8</v>
       </c>
       <c r="AF32" s="9" t="n">
         <f aca="false">IF(AC32&gt;0,AE32/AC32,"")</f>
-        <v>-0.0987315106008397</v>
+        <v>-0.089761539219967</v>
       </c>
       <c r="AG32" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD32/AD$6)</f>
-        <v>0.00536337250320083</v>
+        <v>0.0054261816369856</v>
       </c>
       <c r="AH32" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B32)</f>
@@ -9021,31 +9024,31 @@
       </c>
       <c r="F33" s="50" t="n">
         <f aca="false">M33+T33+AA33+AH33+AO33+AV33</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G33" s="51" t="n">
         <f aca="false">IF(AND(F33&gt;0,H33&gt;0),H33/F33,"")</f>
-        <v>2569.38775510204</v>
+        <v>2554</v>
       </c>
       <c r="H33" s="52" t="n">
         <f aca="false">O33+V33+AC33+AJ33+AQ33+AX33</f>
-        <v>125900</v>
+        <v>132808</v>
       </c>
       <c r="I33" s="53" t="n">
         <f aca="false">P33+W33+AD33+AK33+AR33+AY33</f>
-        <v>116130</v>
+        <v>123240</v>
       </c>
       <c r="J33" s="52" t="n">
         <f aca="false">I33-H33</f>
-        <v>-9770</v>
+        <v>-9568</v>
       </c>
       <c r="K33" s="54" t="n">
         <f aca="false">IF(H33&gt;0,J33/H33,"")</f>
-        <v>-0.0776012708498809</v>
+        <v>-0.072043852779953</v>
       </c>
       <c r="L33" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I33/I$6)</f>
-        <v>0.00307774174224775</v>
+        <v>0.0032031700323144</v>
       </c>
       <c r="M33" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B33)</f>
@@ -9105,31 +9108,31 @@
       </c>
       <c r="AA33" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B33)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AB33" s="57" t="n">
         <f aca="false">IF(AND(AA33&gt;0,AC33&gt;0),AC33/AA33,"")</f>
-        <v>3065.875</v>
+        <v>2857.72727272727</v>
       </c>
       <c r="AC33" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B33)</f>
-        <v>24527</v>
+        <v>31435</v>
       </c>
       <c r="AD33" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B33)</f>
-        <v>18960</v>
+        <v>26070</v>
       </c>
       <c r="AE33" s="8" t="n">
         <f aca="false">AD33-AC33</f>
-        <v>-5567</v>
+        <v>-5365</v>
       </c>
       <c r="AF33" s="9" t="n">
         <f aca="false">IF(AC33&gt;0,AE33/AC33,"")</f>
-        <v>-0.226974354792677</v>
+        <v>-0.170669635756323</v>
       </c>
       <c r="AG33" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD33/AD$6)</f>
-        <v>0.00169777984794689</v>
+        <v>0.00218897186001861</v>
       </c>
       <c r="AH33" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B33)</f>
@@ -9237,31 +9240,31 @@
       </c>
       <c r="F34" s="50" t="n">
         <f aca="false">M34+T34+AA34+AH34+AO34+AV34</f>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G34" s="51" t="n">
         <f aca="false">IF(AND(F34&gt;0,H34&gt;0),H34/F34,"")</f>
-        <v>1272.89873417722</v>
+        <v>1269.10975609756</v>
       </c>
       <c r="H34" s="52" t="n">
         <f aca="false">O34+V34+AC34+AJ34+AQ34+AX34</f>
-        <v>100559</v>
+        <v>104067</v>
       </c>
       <c r="I34" s="53" t="n">
         <f aca="false">P34+W34+AD34+AK34+AR34+AY34</f>
-        <v>94002.1</v>
+        <v>97571.8</v>
       </c>
       <c r="J34" s="52" t="n">
         <f aca="false">I34-H34</f>
-        <v>-6556.89999999999</v>
+        <v>-6495.19999999998</v>
       </c>
       <c r="K34" s="54" t="n">
         <f aca="false">IF(H34&gt;0,J34/H34,"")</f>
-        <v>-0.0652045068069491</v>
+        <v>-0.0624136373682338</v>
       </c>
       <c r="L34" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I34/I$6)</f>
-        <v>0.0024912958497283</v>
+        <v>0.00253601968321141</v>
       </c>
       <c r="M34" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B34)</f>
@@ -9321,31 +9324,31 @@
       </c>
       <c r="AA34" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B34)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AB34" s="57" t="n">
         <f aca="false">IF(AND(AA34&gt;0,AC34&gt;0),AC34/AA34,"")</f>
-        <v>1400.5</v>
+        <v>1301.42857142857</v>
       </c>
       <c r="AC34" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B34)</f>
-        <v>5602</v>
+        <v>9110</v>
       </c>
       <c r="AD34" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B34)</f>
-        <v>4759.6</v>
+        <v>8329.3</v>
       </c>
       <c r="AE34" s="8" t="n">
         <f aca="false">AD34-AC34</f>
-        <v>-842.4</v>
+        <v>-780.699999999999</v>
       </c>
       <c r="AF34" s="9" t="n">
         <f aca="false">IF(AC34&gt;0,AE34/AC34,"")</f>
-        <v>-0.150374866119243</v>
+        <v>-0.0856970362239296</v>
       </c>
       <c r="AG34" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD34/AD$6)</f>
-        <v>0.000426200050859073</v>
+        <v>0.0006993710515402</v>
       </c>
       <c r="AH34" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B34)</f>
@@ -9477,7 +9480,7 @@
       </c>
       <c r="L35" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I35/I$6)</f>
-        <v>0.00243823508384391</v>
+        <v>0.00239120125748884</v>
       </c>
       <c r="M35" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B35)</f>
@@ -9693,7 +9696,7 @@
       </c>
       <c r="L36" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I36/I$6)</f>
-        <v>0.00226821589134526</v>
+        <v>0.00222446175415142</v>
       </c>
       <c r="M36" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B36)</f>
@@ -9909,7 +9912,7 @@
       </c>
       <c r="L37" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I37/I$6)</f>
-        <v>0.00214996148977883</v>
+        <v>0.00210848849316321</v>
       </c>
       <c r="M37" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B37)</f>
@@ -10125,7 +10128,7 @@
       </c>
       <c r="L38" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I38/I$6)</f>
-        <v>0.00201631440411788</v>
+        <v>0.00197741947467121</v>
       </c>
       <c r="M38" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B38)</f>
@@ -10341,7 +10344,7 @@
       </c>
       <c r="L39" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I39/I$6)</f>
-        <v>0.00195627021492269</v>
+        <v>0.00191853354457374</v>
       </c>
       <c r="M39" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B39)</f>
@@ -10557,7 +10560,7 @@
       </c>
       <c r="L40" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I40/I$6)</f>
-        <v>0.00185305866372137</v>
+        <v>0.00181731295569152</v>
       </c>
       <c r="M40" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B40)</f>
@@ -10773,7 +10776,7 @@
       </c>
       <c r="L41" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I41/I$6)</f>
-        <v>0.00182470092959406</v>
+        <v>0.0017895022454142</v>
       </c>
       <c r="M41" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B41)</f>
@@ -10989,7 +10992,7 @@
       </c>
       <c r="L42" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I42/I$6)</f>
-        <v>0.00158250467810258</v>
+        <v>0.00155197798659151</v>
       </c>
       <c r="M42" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B42)</f>
@@ -11205,7 +11208,7 @@
       </c>
       <c r="L43" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I43/I$6)</f>
-        <v>0.00133216684163548</v>
+        <v>0.00130646919487425</v>
       </c>
       <c r="M43" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B43)</f>
@@ -11421,7 +11424,7 @@
       </c>
       <c r="L44" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I44/I$6)</f>
-        <v>0.00127074001413243</v>
+        <v>0.00124622729771588</v>
       </c>
       <c r="M44" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B44)</f>
@@ -11637,7 +11640,7 @@
       </c>
       <c r="L45" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I45/I$6)</f>
-        <v>0.00112332008055439</v>
+        <v>0.00110165111107722</v>
       </c>
       <c r="M45" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B45)</f>
@@ -11853,7 +11856,7 @@
       </c>
       <c r="L46" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I46/I$6)</f>
-        <v>0.00102657647796406</v>
+        <v>0.00100677370335685</v>
       </c>
       <c r="M46" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B46)</f>
@@ -11937,7 +11940,7 @@
       </c>
       <c r="AG46" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD46/AD$6)</f>
-        <v>0.000125094854830264</v>
+        <v>0.000117299335958803</v>
       </c>
       <c r="AH46" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B46)</f>
@@ -12069,7 +12072,7 @@
       </c>
       <c r="L47" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I47/I$6)</f>
-        <v>0.000954091989330225</v>
+        <v>0.00093568744858259</v>
       </c>
       <c r="M47" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B47)</f>
@@ -12285,7 +12288,7 @@
       </c>
       <c r="L48" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I48/I$6)</f>
-        <v>0.000944389403849842</v>
+        <v>0.000926172027056865</v>
       </c>
       <c r="M48" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B48)</f>
@@ -12501,7 +12504,7 @@
       </c>
       <c r="L49" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I49/I$6)</f>
-        <v>0.000911899921357622</v>
+        <v>0.000894309270300827</v>
       </c>
       <c r="M49" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B49)</f>
@@ -12717,7 +12720,7 @@
       </c>
       <c r="L50" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I50/I$6)</f>
-        <v>0.000857180095514007</v>
+        <v>0.000840644995992813</v>
       </c>
       <c r="M50" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B50)</f>
@@ -12933,7 +12936,7 @@
       </c>
       <c r="L51" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I51/I$6)</f>
-        <v>0.00084063296011239</v>
+        <v>0.000824417056676229</v>
       </c>
       <c r="M51" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B51)</f>
@@ -13149,7 +13152,7 @@
       </c>
       <c r="L52" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I52/I$6)</f>
-        <v>0.000838400914908463</v>
+        <v>0.000822228067872906</v>
       </c>
       <c r="M52" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B52)</f>
@@ -13365,7 +13368,7 @@
       </c>
       <c r="L53" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I53/I$6)</f>
-        <v>0.000790279695273277</v>
+        <v>0.000775035111924563</v>
       </c>
       <c r="M53" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B53)</f>
@@ -13581,7 +13584,7 @@
       </c>
       <c r="L54" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I54/I$6)</f>
-        <v>0.00076468882791502</v>
+        <v>0.000749937895248136</v>
       </c>
       <c r="M54" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B54)</f>
@@ -13797,7 +13800,7 @@
       </c>
       <c r="L55" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I55/I$6)</f>
-        <v>0.000635910261655173</v>
+        <v>0.000623643481875701</v>
       </c>
       <c r="M55" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B55)</f>
@@ -14013,7 +14016,7 @@
       </c>
       <c r="L56" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I56/I$6)</f>
-        <v>0.000616290419996807</v>
+        <v>0.000604402109148321</v>
       </c>
       <c r="M56" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B56)</f>
@@ -14229,7 +14232,7 @@
       </c>
       <c r="L57" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I57/I$6)</f>
-        <v>0.000615963378464909</v>
+        <v>0.000604081376284001</v>
       </c>
       <c r="M57" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B57)</f>
@@ -14445,7 +14448,7 @@
       </c>
       <c r="L58" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I58/I$6)</f>
-        <v>0.000602838783049461</v>
+        <v>0.000591209955776027</v>
       </c>
       <c r="M58" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B58)</f>
@@ -14661,7 +14664,7 @@
       </c>
       <c r="L59" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I59/I$6)</f>
-        <v>0.000585271829321471</v>
+        <v>0.00057398187054218</v>
       </c>
       <c r="M59" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B59)</f>
@@ -14877,7 +14880,7 @@
       </c>
       <c r="L60" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I60/I$6)</f>
-        <v>0.00054967359709735</v>
+        <v>0.000539070332182843</v>
       </c>
       <c r="M60" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B60)</f>
@@ -15093,7 +15096,7 @@
       </c>
       <c r="L61" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I61/I$6)</f>
-        <v>0.000547695181347253</v>
+        <v>0.000537130080292935</v>
       </c>
       <c r="M61" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B61)</f>
@@ -15309,7 +15312,7 @@
       </c>
       <c r="L62" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I62/I$6)</f>
-        <v>0.000516760073720983</v>
+        <v>0.000506791714338545</v>
       </c>
       <c r="M62" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B62)</f>
@@ -15525,7 +15528,7 @@
       </c>
       <c r="L63" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I63/I$6)</f>
-        <v>0.000508395867281188</v>
+        <v>0.000498588854372638</v>
       </c>
       <c r="M63" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B63)</f>
@@ -15741,7 +15744,7 @@
       </c>
       <c r="L64" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I64/I$6)</f>
-        <v>0.000503482293536137</v>
+        <v>0.000493770064012438</v>
       </c>
       <c r="M64" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B64)</f>
@@ -15957,7 +15960,7 @@
       </c>
       <c r="L65" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I65/I$6)</f>
-        <v>0.0004987643086489</v>
+        <v>0.000489143089579197</v>
       </c>
       <c r="M65" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B65)</f>
@@ -16173,7 +16176,7 @@
       </c>
       <c r="L66" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I66/I$6)</f>
-        <v>0.000471400950394909</v>
+        <v>0.000462307573553848</v>
       </c>
       <c r="M66" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B66)</f>
@@ -16389,7 +16392,7 @@
       </c>
       <c r="L67" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I67/I$6)</f>
-        <v>0.000446515051006545</v>
+        <v>0.000437901725936652</v>
       </c>
       <c r="M67" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B67)</f>
@@ -16605,7 +16608,7 @@
       </c>
       <c r="L68" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I68/I$6)</f>
-        <v>0.000431527856007483</v>
+        <v>0.000423203635598501</v>
       </c>
       <c r="M68" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B68)</f>
@@ -16821,7 +16824,7 @@
       </c>
       <c r="L69" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I69/I$6)</f>
-        <v>0.000430915646980996</v>
+        <v>0.000422603236152327</v>
       </c>
       <c r="M69" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B69)</f>
@@ -17037,7 +17040,7 @@
       </c>
       <c r="L70" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I70/I$6)</f>
-        <v>0.00042573969793888</v>
+        <v>0.000417527131743766</v>
       </c>
       <c r="M70" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B70)</f>
@@ -17253,7 +17256,7 @@
       </c>
       <c r="L71" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I71/I$6)</f>
-        <v>0.000425717170766909</v>
+        <v>0.000417505039123452</v>
       </c>
       <c r="M71" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B71)</f>
@@ -17469,7 +17472,7 @@
       </c>
       <c r="L72" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I72/I$6)</f>
-        <v>0.000419561952307966</v>
+        <v>0.000411468555514194</v>
       </c>
       <c r="M72" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B72)</f>
@@ -17685,7 +17688,7 @@
       </c>
       <c r="L73" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I73/I$6)</f>
-        <v>0.000410895616738217</v>
+        <v>0.000402969394522902</v>
       </c>
       <c r="M73" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B73)</f>
@@ -17901,7 +17904,7 @@
       </c>
       <c r="L74" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I74/I$6)</f>
-        <v>0.000397697344219149</v>
+        <v>0.000390025718150843</v>
       </c>
       <c r="M74" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B74)</f>
@@ -18117,7 +18120,7 @@
       </c>
       <c r="L75" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I75/I$6)</f>
-        <v>0.000353646917071772</v>
+        <v>0.000346825028649785</v>
       </c>
       <c r="M75" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B75)</f>
@@ -18333,7 +18336,7 @@
       </c>
       <c r="L76" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I76/I$6)</f>
-        <v>0.000353212805216627</v>
+        <v>0.00034639929086068</v>
       </c>
       <c r="M76" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B76)</f>
@@ -18549,7 +18552,7 @@
       </c>
       <c r="L77" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I77/I$6)</f>
-        <v>0.000350402209231392</v>
+        <v>0.000343642911585063</v>
       </c>
       <c r="M77" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B77)</f>
@@ -18765,7 +18768,7 @@
       </c>
       <c r="L78" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I78/I$6)</f>
-        <v>0.000293860332713709</v>
+        <v>0.000288191734163438</v>
       </c>
       <c r="M78" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B78)</f>
@@ -18981,7 +18984,7 @@
       </c>
       <c r="L79" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I79/I$6)</f>
-        <v>0.00027755331046274</v>
+        <v>0.00027219927618808</v>
       </c>
       <c r="M79" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B79)</f>
@@ -19197,7 +19200,7 @@
       </c>
       <c r="L80" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I80/I$6)</f>
-        <v>0.000274335900254277</v>
+        <v>0.000269043930180916</v>
       </c>
       <c r="M80" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B80)</f>
@@ -19413,7 +19416,7 @@
       </c>
       <c r="L81" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I81/I$6)</f>
-        <v>0.000272798752049245</v>
+        <v>0.000267536433735977</v>
       </c>
       <c r="M81" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B81)</f>
@@ -19629,7 +19632,7 @@
       </c>
       <c r="L82" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I82/I$6)</f>
-        <v>0.000251111711080663</v>
+        <v>0.000246267738203334</v>
       </c>
       <c r="M82" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B82)</f>
@@ -19809,7 +19812,7 @@
       </c>
       <c r="C83" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B83,Prices!$A$6:$A$300,0)),"")</f>
-        <v>12.17</v>
+        <v>718.95</v>
       </c>
       <c r="D83" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B83,Prices!$A$6:$A$300,0)),"")</f>
@@ -19817,35 +19820,35 @@
       </c>
       <c r="E83" s="6" t="n">
         <f aca="false">(M83&gt;0)+(T83&gt;0)+(AA83&gt;0)+(AH83&gt;0)+(AO83&gt;0)+(AV83&gt;0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="50" t="n">
         <f aca="false">M83+T83+AA83+AH83+AO83+AV83</f>
-        <v>560</v>
+        <v>10</v>
       </c>
       <c r="G83" s="51" t="n">
         <f aca="false">IF(AND(F83&gt;0,H83&gt;0),H83/F83,"")</f>
-        <v>55</v>
+        <v>938.6</v>
       </c>
       <c r="H83" s="52" t="n">
         <f aca="false">O83+V83+AC83+AJ83+AQ83+AX83</f>
-        <v>30800</v>
+        <v>9386</v>
       </c>
       <c r="I83" s="53" t="n">
         <f aca="false">P83+W83+AD83+AK83+AR83+AY83</f>
-        <v>6815.2</v>
+        <v>7189.5</v>
       </c>
       <c r="J83" s="52" t="n">
         <f aca="false">I83-H83</f>
-        <v>-23984.8</v>
+        <v>-2196.5</v>
       </c>
       <c r="K83" s="54" t="n">
         <f aca="false">IF(H83&gt;0,J83/H83,"")</f>
-        <v>-0.778727272727273</v>
+        <v>-0.234018751331771</v>
       </c>
       <c r="L83" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I83/I$6)</f>
-        <v>0.000180620214602315</v>
+        <v>0.000186864580877348</v>
       </c>
       <c r="M83" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B83)</f>
@@ -19877,59 +19880,59 @@
       </c>
       <c r="T83" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B83)</f>
-        <v>0</v>
-      </c>
-      <c r="U83" s="57" t="str">
+        <v>5</v>
+      </c>
+      <c r="U83" s="57" t="n">
         <f aca="false">IF(AND(T83&gt;0,V83&gt;0),V83/T83,"")</f>
-        <v/>
+        <v>1021</v>
       </c>
       <c r="V83" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B83)</f>
-        <v>0</v>
+        <v>5105</v>
       </c>
       <c r="W83" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B83)</f>
-        <v>0</v>
+        <v>3594.75</v>
       </c>
       <c r="X83" s="8" t="n">
         <f aca="false">W83-V83</f>
-        <v>0</v>
-      </c>
-      <c r="Y83" s="9" t="str">
+        <v>-1510.25</v>
+      </c>
+      <c r="Y83" s="9" t="n">
         <f aca="false">IF(V83&gt;0,X83/V83,"")</f>
-        <v/>
+        <v>-0.295837414299706</v>
       </c>
       <c r="Z83" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W83/W$6)</f>
-        <v>0</v>
+        <v>0.000303972766908367</v>
       </c>
       <c r="AA83" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B83)</f>
-        <v>0</v>
-      </c>
-      <c r="AB83" s="57" t="str">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="57" t="n">
         <f aca="false">IF(AND(AA83&gt;0,AC83&gt;0),AC83/AA83,"")</f>
-        <v/>
+        <v>856.2</v>
       </c>
       <c r="AC83" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B83)</f>
-        <v>0</v>
+        <v>4281</v>
       </c>
       <c r="AD83" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B83)</f>
-        <v>0</v>
+        <v>3594.75</v>
       </c>
       <c r="AE83" s="8" t="n">
         <f aca="false">AD83-AC83</f>
-        <v>0</v>
-      </c>
-      <c r="AF83" s="9" t="str">
+        <v>-686.25</v>
+      </c>
+      <c r="AF83" s="9" t="n">
         <f aca="false">IF(AC83&gt;0,AE83/AC83,"")</f>
-        <v/>
+        <v>-0.160301331464611</v>
       </c>
       <c r="AG83" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD83/AD$6)</f>
-        <v>0</v>
+        <v>0.000301833778051473</v>
       </c>
       <c r="AH83" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B83)</f>
@@ -19989,31 +19992,31 @@
       </c>
       <c r="AV83" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B83)</f>
-        <v>560</v>
-      </c>
-      <c r="AW83" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" s="57" t="str">
         <f aca="false">IF(AND(AV83&gt;0,AX83&gt;0),AX83/AV83,"")</f>
-        <v>55</v>
+        <v/>
       </c>
       <c r="AX83" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B83)</f>
-        <v>30800</v>
+        <v>0</v>
       </c>
       <c r="AY83" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B83)</f>
-        <v>6815.2</v>
+        <v>0</v>
       </c>
       <c r="AZ83" s="8" t="n">
         <f aca="false">AY83-AX83</f>
-        <v>-23984.8</v>
-      </c>
-      <c r="BA83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" s="9" t="str">
         <f aca="false">IF(AX83&gt;0,AZ83/AX83,"")</f>
-        <v>-0.778727272727273</v>
+        <v/>
       </c>
       <c r="BB83" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY83/AY$6)</f>
-        <v>0.00176285076745545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20025,7 +20028,7 @@
       </c>
       <c r="C84" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH($B84,Prices!$A$6:$A$300,0)),"")</f>
-        <v>718.95</v>
+        <v>12.17</v>
       </c>
       <c r="D84" s="49" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$D$6:$D$300,MATCH($B84,Prices!$A$6:$A$300,0)),"")</f>
@@ -20033,35 +20036,35 @@
       </c>
       <c r="E84" s="6" t="n">
         <f aca="false">(M84&gt;0)+(T84&gt;0)+(AA84&gt;0)+(AH84&gt;0)+(AO84&gt;0)+(AV84&gt;0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="50" t="n">
         <f aca="false">M84+T84+AA84+AH84+AO84+AV84</f>
-        <v>8</v>
+        <v>560</v>
       </c>
       <c r="G84" s="51" t="n">
         <f aca="false">IF(AND(F84&gt;0,H84&gt;0),H84/F84,"")</f>
-        <v>1004.125</v>
+        <v>55</v>
       </c>
       <c r="H84" s="52" t="n">
         <f aca="false">O84+V84+AC84+AJ84+AQ84+AX84</f>
-        <v>8033</v>
+        <v>30800</v>
       </c>
       <c r="I84" s="53" t="n">
         <f aca="false">P84+W84+AD84+AK84+AR84+AY84</f>
-        <v>5751.6</v>
+        <v>6815.2</v>
       </c>
       <c r="J84" s="52" t="n">
         <f aca="false">I84-H84</f>
-        <v>-2281.4</v>
+        <v>-23984.8</v>
       </c>
       <c r="K84" s="54" t="n">
         <f aca="false">IF(H84&gt;0,J84/H84,"")</f>
-        <v>-0.28400348562181</v>
+        <v>-0.778727272727273</v>
       </c>
       <c r="L84" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I84/I$6)</f>
-        <v>0.000152432096828659</v>
+        <v>0.000177136030543891</v>
       </c>
       <c r="M84" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B84)</f>
@@ -20093,59 +20096,59 @@
       </c>
       <c r="T84" s="56" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$D$7:$D$300,'Manish Shilpa'!$B$7:$B$300,$B84)</f>
-        <v>5</v>
-      </c>
-      <c r="U84" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="57" t="str">
         <f aca="false">IF(AND(T84&gt;0,V84&gt;0),V84/T84,"")</f>
-        <v>1021</v>
+        <v/>
       </c>
       <c r="V84" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$E$7:$E$300,'Manish Shilpa'!$B$7:$B$300,$B84)</f>
-        <v>5105</v>
+        <v>0</v>
       </c>
       <c r="W84" s="8" t="n">
         <f aca="false">SUMIFS('Manish Shilpa'!$H$7:$H$300,'Manish Shilpa'!$B$7:$B$300,$B84)</f>
-        <v>3594.75</v>
+        <v>0</v>
       </c>
       <c r="X84" s="8" t="n">
         <f aca="false">W84-V84</f>
-        <v>-1510.25</v>
-      </c>
-      <c r="Y84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="9" t="str">
         <f aca="false">IF(V84&gt;0,X84/V84,"")</f>
-        <v>-0.295837414299706</v>
+        <v/>
       </c>
       <c r="Z84" s="9" t="n">
         <f aca="false">IF(W$6=0,"",W84/W$6)</f>
-        <v>0.000303972766908367</v>
+        <v>0</v>
       </c>
       <c r="AA84" s="56" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$D$7:$D$300,'Saloni Mehra'!$B$7:$B$300,$B84)</f>
-        <v>3</v>
-      </c>
-      <c r="AB84" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="57" t="str">
         <f aca="false">IF(AND(AA84&gt;0,AC84&gt;0),AC84/AA84,"")</f>
-        <v>976</v>
+        <v/>
       </c>
       <c r="AC84" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$E$7:$E$300,'Saloni Mehra'!$B$7:$B$300,$B84)</f>
-        <v>2928</v>
+        <v>0</v>
       </c>
       <c r="AD84" s="8" t="n">
         <f aca="false">SUMIFS('Saloni Mehra'!$H$7:$H$300,'Saloni Mehra'!$B$7:$B$300,$B84)</f>
-        <v>2156.85</v>
+        <v>0</v>
       </c>
       <c r="AE84" s="8" t="n">
         <f aca="false">AD84-AC84</f>
-        <v>-771.15</v>
-      </c>
-      <c r="AF84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="9" t="str">
         <f aca="false">IF(AC84&gt;0,AE84/AC84,"")</f>
-        <v>-0.263370901639344</v>
+        <v/>
       </c>
       <c r="AG84" s="9" t="n">
         <f aca="false">IF(AD$6=0,"",AD84/AD$6)</f>
-        <v>0.000193135889506553</v>
+        <v>0</v>
       </c>
       <c r="AH84" s="56" t="n">
         <f aca="false">SUMIFS('Vidushi Malhotra'!$D$7:$D$300,'Vidushi Malhotra'!$B$7:$B$300,$B84)</f>
@@ -20205,31 +20208,31 @@
       </c>
       <c r="AV84" s="56" t="n">
         <f aca="false">SUMIFS(DA!$D$7:$D$300,DA!$B$7:$B$300,$B84)</f>
-        <v>0</v>
-      </c>
-      <c r="AW84" s="57" t="str">
+        <v>560</v>
+      </c>
+      <c r="AW84" s="57" t="n">
         <f aca="false">IF(AND(AV84&gt;0,AX84&gt;0),AX84/AV84,"")</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="AX84" s="8" t="n">
         <f aca="false">SUMIFS(DA!$E$7:$E$300,DA!$B$7:$B$300,$B84)</f>
-        <v>0</v>
+        <v>30800</v>
       </c>
       <c r="AY84" s="8" t="n">
         <f aca="false">SUMIFS(DA!$H$7:$H$300,DA!$B$7:$B$300,$B84)</f>
-        <v>0</v>
+        <v>6815.2</v>
       </c>
       <c r="AZ84" s="8" t="n">
         <f aca="false">AY84-AX84</f>
-        <v>0</v>
-      </c>
-      <c r="BA84" s="9" t="str">
+        <v>-23984.8</v>
+      </c>
+      <c r="BA84" s="9" t="n">
         <f aca="false">IF(AX84&gt;0,AZ84/AX84,"")</f>
-        <v/>
+        <v>-0.778727272727273</v>
       </c>
       <c r="BB84" s="9" t="n">
         <f aca="false">IF(AY$6=0,"",AY84/AY$6)</f>
-        <v>0</v>
+        <v>0.00176285076745545</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20277,7 +20280,7 @@
       </c>
       <c r="L85" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I85/I$6)</f>
-        <v>0.000135496964018047</v>
+        <v>0.000132883212489538</v>
       </c>
       <c r="M85" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B85)</f>
@@ -20493,7 +20496,7 @@
       </c>
       <c r="L86" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I86/I$6)</f>
-        <v>0.000125164942850259</v>
+        <v>0.000122750497160929</v>
       </c>
       <c r="M86" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B86)</f>
@@ -20709,7 +20712,7 @@
       </c>
       <c r="L87" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I87/I$6)</f>
-        <v>9.93315771113801E-005</v>
+        <v>9.74154599246541E-005</v>
       </c>
       <c r="M87" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B87)</f>
@@ -20925,7 +20928,7 @@
       </c>
       <c r="L88" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I88/I$6)</f>
-        <v>9.7765276095563E-005</v>
+        <v>9.58793730298977E-005</v>
       </c>
       <c r="M88" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B88)</f>
@@ -21141,7 +21144,7 @@
       </c>
       <c r="L89" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I89/I$6)</f>
-        <v>6.19576736848944E-005</v>
+        <v>6.07625032582328E-005</v>
       </c>
       <c r="M89" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B89)</f>
@@ -21357,7 +21360,7 @@
       </c>
       <c r="L90" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I90/I$6)</f>
-        <v>6.0433776757492E-005</v>
+        <v>5.92680024723022E-005</v>
       </c>
       <c r="M90" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B90)</f>
@@ -21573,7 +21576,7 @@
       </c>
       <c r="L91" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I91/I$6)</f>
-        <v>3.94199006924938E-005</v>
+        <v>3.86594864172707E-005</v>
       </c>
       <c r="M91" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B91)</f>
@@ -21789,7 +21792,7 @@
       </c>
       <c r="L92" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I92/I$6)</f>
-        <v>3.64675160366219E-005</v>
+        <v>3.57640535902679E-005</v>
       </c>
       <c r="M92" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B92)</f>
@@ -22005,7 +22008,7 @@
       </c>
       <c r="L93" s="55" t="n">
         <f aca="false">IF(I$6=0,"",I93/I$6)</f>
-        <v>2.58691441884787E-005</v>
+        <v>2.53701255155963E-005</v>
       </c>
       <c r="M93" s="56" t="n">
         <f aca="false">SUMIFS(Gautam!$D$7:$D$300,Gautam!$B$7:$B$300,$B93)</f>
@@ -23309,7 +23312,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="59" t="n">
         <v>81.02</v>
@@ -23657,7 +23660,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" s="59" t="n">
         <v>234.25</v>
@@ -23857,7 +23860,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29" s="59" t="n">
         <v>7084.5</v>
@@ -24028,9 +24031,9 @@
         <f aca="false">IFERROR(INDEX('Manish Shilpa'!$M$7:$M$300,MATCH($A32,'Manish Shilpa'!$B$7:$B$300,0)),"")</f>
         <v>47.93</v>
       </c>
-      <c r="G32" s="48" t="n">
+      <c r="G32" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Saloni Mehra'!$M$7:$M$300,MATCH($A32,'Saloni Mehra'!$B$7:$B$300,0)),"")</f>
-        <v>55.8099378881988</v>
+        <v/>
       </c>
       <c r="H32" s="48" t="n">
         <f aca="false">IFERROR(INDEX('Vidushi Malhotra'!$M$7:$M$300,MATCH($A32,'Vidushi Malhotra'!$B$7:$B$300,0)),"")</f>
@@ -24357,7 +24360,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B39" s="59" t="n">
         <v>694.05</v>
@@ -25053,7 +25056,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" s="59" t="n">
         <v>3954.8</v>
@@ -25103,7 +25106,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B54" s="59" t="n">
         <v>4274</v>
@@ -25320,9 +25323,9 @@
         <f aca="false">IFERROR(INDEX('Manish Shilpa'!$M$7:$M$300,MATCH($A58,'Manish Shilpa'!$B$7:$B$300,0)),"")</f>
         <v/>
       </c>
-      <c r="G58" s="48" t="n">
+      <c r="G58" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Saloni Mehra'!$M$7:$M$300,MATCH($A58,'Saloni Mehra'!$B$7:$B$300,0)),"")</f>
-        <v>1242.75</v>
+        <v/>
       </c>
       <c r="H58" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Vidushi Malhotra'!$M$7:$M$300,MATCH($A58,'Vidushi Malhotra'!$B$7:$B$300,0)),"")</f>
@@ -25833,7 +25836,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B69" s="59" t="n">
         <v>432.45</v>
@@ -26579,7 +26582,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B84" s="59"/>
       <c r="C84" s="60" t="n">
@@ -26671,7 +26674,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B86" s="59" t="n">
         <v>12.17</v>
@@ -26892,9 +26895,9 @@
         <f aca="false">IFERROR(INDEX('Manish Shilpa'!$M$7:$M$300,MATCH($A90,'Manish Shilpa'!$B$7:$B$300,0)),"")</f>
         <v>1067.17647058824</v>
       </c>
-      <c r="G90" s="48" t="n">
+      <c r="G90" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Saloni Mehra'!$M$7:$M$300,MATCH($A90,'Saloni Mehra'!$B$7:$B$300,0)),"")</f>
-        <v>1118.60416666667</v>
+        <v/>
       </c>
       <c r="H90" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Vidushi Malhotra'!$M$7:$M$300,MATCH($A90,'Vidushi Malhotra'!$B$7:$B$300,0)),"")</f>
@@ -27042,9 +27045,9 @@
         <f aca="false">IFERROR(INDEX('Manish Shilpa'!$M$7:$M$300,MATCH($A93,'Manish Shilpa'!$B$7:$B$300,0)),"")</f>
         <v>2316.66666666667</v>
       </c>
-      <c r="G93" s="48" t="n">
+      <c r="G93" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Saloni Mehra'!$M$7:$M$300,MATCH($A93,'Saloni Mehra'!$B$7:$B$300,0)),"")</f>
-        <v>2515</v>
+        <v/>
       </c>
       <c r="H93" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Vidushi Malhotra'!$M$7:$M$300,MATCH($A93,'Vidushi Malhotra'!$B$7:$B$300,0)),"")</f>
@@ -27071,7 +27074,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B94" s="59" t="n">
         <v>718.95</v>
@@ -27092,9 +27095,9 @@
         <f aca="false">IFERROR(INDEX('Manish Shilpa'!$M$7:$M$300,MATCH($A94,'Manish Shilpa'!$B$7:$B$300,0)),"")</f>
         <v>679.6</v>
       </c>
-      <c r="G94" s="48" t="n">
+      <c r="G94" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Saloni Mehra'!$M$7:$M$300,MATCH($A94,'Saloni Mehra'!$B$7:$B$300,0)),"")</f>
-        <v>826.333333333333</v>
+        <v/>
       </c>
       <c r="H94" s="48" t="str">
         <f aca="false">IFERROR(INDEX('Vidushi Malhotra'!$M$7:$M$300,MATCH($A94,'Vidushi Malhotra'!$B$7:$B$300,0)),"")</f>
@@ -27369,7 +27372,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>16</v>
@@ -27511,7 +27514,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>16</v>
@@ -27565,7 +27568,7 @@
         <v>202</v>
       </c>
       <c r="S10" s="68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T10" s="68" t="n">
         <v>274</v>
@@ -27582,7 +27585,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>16</v>
@@ -27638,7 +27641,7 @@
         <v>202</v>
       </c>
       <c r="S11" s="68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T11" s="68" t="n">
         <v>3</v>
@@ -27780,7 +27783,7 @@
         <v>202</v>
       </c>
       <c r="S13" s="68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T13" s="68" t="n">
         <v>57</v>
@@ -27797,7 +27800,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>16</v>
@@ -27924,7 +27927,7 @@
         <v>202</v>
       </c>
       <c r="S15" s="68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T15" s="68" t="n">
         <v>5</v>
@@ -28012,7 +28015,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>16</v>
@@ -28083,7 +28086,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
@@ -28137,7 +28140,7 @@
         <v>202</v>
       </c>
       <c r="S18" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T18" s="68" t="n">
         <v>131</v>
@@ -28154,7 +28157,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>16</v>
@@ -29564,7 +29567,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>211</v>
@@ -29619,7 +29622,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>211</v>
@@ -29727,7 +29730,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>218</v>
@@ -29782,7 +29785,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>211</v>
@@ -29837,7 +29840,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>211</v>
@@ -29892,7 +29895,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>211</v>
@@ -29947,7 +29950,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>217</v>
@@ -30644,7 +30647,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>223</v>
@@ -31667,7 +31670,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>223</v>
@@ -31950,7 +31953,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -32050,21 +32053,21 @@
       <c r="D6" s="12"/>
       <c r="E6" s="81" t="n">
         <f aca="false">SUM(E7:E31)</f>
-        <v>11014028</v>
+        <v>11739506</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="81" t="n">
         <f aca="false">SUM(H7:H31)</f>
-        <v>11167525.65</v>
+        <v>11909700.84</v>
       </c>
       <c r="I6" s="81" t="n">
         <f aca="false">H6-E6</f>
-        <v>153497.65</v>
+        <v>170194.84</v>
       </c>
       <c r="J6" s="82" t="n">
         <f aca="false">IF(E6&gt;0,I6/E6,"")</f>
-        <v>0.0139365589046987</v>
+        <v>0.014497615146668</v>
       </c>
       <c r="K6" s="82" t="n">
         <f aca="false">SUM(K7:K31)</f>
@@ -32072,12 +32075,12 @@
       </c>
       <c r="L6" s="81" t="n">
         <f aca="false">SUM(L7:L31)</f>
-        <v>3325492</v>
+        <v>2974667</v>
       </c>
       <c r="M6" s="12"/>
       <c r="N6" s="81" t="n">
         <f aca="false">SUM(N7:N31)</f>
-        <v>-84948.35</v>
+        <v>-61301.5</v>
       </c>
       <c r="O6" s="12"/>
       <c r="Q6" s="24" t="s">
@@ -32110,14 +32113,14 @@
         <v>24</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>4713</v>
+        <v>4940</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>4439078</v>
+        <v>4650978</v>
       </c>
       <c r="F7" s="57" t="n">
         <f aca="false">IF(AND(D7&gt;0,N(E7)&gt;0),E7/D7,"")</f>
-        <v>941.879482283047</v>
+        <v>941.493522267207</v>
       </c>
       <c r="G7" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B7,Prices!$A$6:$A$300,0)),"")</f>
@@ -32125,19 +32128,19 @@
       </c>
       <c r="H7" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G7),D7*G7,0)</f>
-        <v>4440117.3</v>
+        <v>4653974</v>
       </c>
       <c r="I7" s="8" t="n">
         <f aca="false">H7-N(E7)</f>
-        <v>1039.29999999981</v>
+        <v>2996</v>
       </c>
       <c r="J7" s="9" t="n">
         <f aca="false">IF(N(E7)&gt;0,I7/E7,"")</f>
-        <v>0.000234125194466016</v>
+        <v>0.000644165592698998</v>
       </c>
       <c r="K7" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H7/$H$6)</f>
-        <v>0.397591860467318</v>
+        <v>0.390771696327512</v>
       </c>
       <c r="L7" s="10"/>
       <c r="M7" s="57" t="str">
@@ -32181,14 +32184,14 @@
         <v>24</v>
       </c>
       <c r="D8" s="66" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1046469</v>
+        <v>1071947</v>
       </c>
       <c r="F8" s="57" t="n">
         <f aca="false">IF(AND(D8&gt;0,N(E8)&gt;0),E8/D8,"")</f>
-        <v>4288.80737704918</v>
+        <v>4287.788</v>
       </c>
       <c r="G8" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B8,Prices!$A$6:$A$300,0)),"")</f>
@@ -32196,19 +32199,19 @@
       </c>
       <c r="H8" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G8),D8*G8,0)</f>
-        <v>1061400</v>
+        <v>1087500</v>
       </c>
       <c r="I8" s="8" t="n">
         <f aca="false">H8-N(E8)</f>
-        <v>14931</v>
+        <v>15553</v>
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">IF(N(E8)&gt;0,I8/E8,"")</f>
-        <v>0.0142679811824335</v>
+        <v>0.0145091128572588</v>
       </c>
       <c r="K8" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H8/$H$6)</f>
-        <v>0.095043435158799</v>
+        <v>0.0913121172907648</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="57" t="str">
@@ -32229,7 +32232,7 @@
         <v>202</v>
       </c>
       <c r="S8" s="68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T8" s="68" t="n">
         <v>547</v>
@@ -32246,53 +32249,53 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>2000</v>
+        <v>1918</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>845300</v>
+        <v>824630</v>
       </c>
       <c r="F9" s="57" t="n">
         <f aca="false">IF(AND(D9&gt;0,N(E9)&gt;0),E9/D9,"")</f>
-        <v>422.65</v>
+        <v>429.942648592284</v>
       </c>
       <c r="G9" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B9,Prices!$A$6:$A$300,0)),"")</f>
-        <v>404.9</v>
+        <v>432.45</v>
       </c>
       <c r="H9" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G9),D9*G9,0)</f>
-        <v>809800</v>
+        <v>829439.1</v>
       </c>
       <c r="I9" s="8" t="n">
         <f aca="false">H9-N(E9)</f>
-        <v>-35500</v>
+        <v>4809.09999999998</v>
       </c>
       <c r="J9" s="9" t="n">
         <f aca="false">IF(N(E9)&gt;0,I9/E9,"")</f>
-        <v>-0.0419969241689341</v>
+        <v>0.00583182760753305</v>
       </c>
       <c r="K9" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H9/$H$6)</f>
-        <v>0.0725138249402633</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>827000</v>
-      </c>
-      <c r="M9" s="57" t="n">
+        <v>0.0696439911583875</v>
+      </c>
+      <c r="L9" s="10"/>
+      <c r="M9" s="57" t="str">
         <f aca="false">IF(ISNUMBER(L9),L9/D9,"")</f>
-        <v>413.5</v>
-      </c>
-      <c r="N9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N9" s="8" t="str">
         <f aca="false">IF(ISNUMBER(L9),H9-L9,"")</f>
-        <v>-17200</v>
-      </c>
-      <c r="O9" s="67"/>
+        <v/>
+      </c>
+      <c r="O9" s="67" t="s">
+        <v>244</v>
+      </c>
       <c r="Q9" s="68" t="s">
         <v>242</v>
       </c>
@@ -32317,51 +32320,51 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="66" t="n">
-        <v>305</v>
+        <v>2000</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>659410</v>
+        <v>845300</v>
       </c>
       <c r="F10" s="57" t="n">
         <f aca="false">IF(AND(D10&gt;0,N(E10)&gt;0),E10/D10,"")</f>
-        <v>2162</v>
+        <v>422.65</v>
       </c>
       <c r="G10" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B10,Prices!$A$6:$A$300,0)),"")</f>
-        <v>2506.9</v>
+        <v>404.9</v>
       </c>
       <c r="H10" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G10),D10*G10,0)</f>
-        <v>764604.5</v>
+        <v>809800</v>
       </c>
       <c r="I10" s="8" t="n">
         <f aca="false">H10-N(E10)</f>
-        <v>105194.5</v>
+        <v>-35500</v>
       </c>
       <c r="J10" s="9" t="n">
         <f aca="false">IF(N(E10)&gt;0,I10/E10,"")</f>
-        <v>0.159528214616096</v>
+        <v>-0.0419969241689341</v>
       </c>
       <c r="K10" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H10/$H$6)</f>
-        <v>0.0684667780458601</v>
+        <v>0.0679949908800564</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>750575</v>
+        <v>827000</v>
       </c>
       <c r="M10" s="57" t="n">
         <f aca="false">IF(ISNUMBER(L10),L10/D10,"")</f>
-        <v>2460.90163934426</v>
+        <v>413.5</v>
       </c>
       <c r="N10" s="8" t="n">
         <f aca="false">IF(ISNUMBER(L10),H10-L10,"")</f>
-        <v>14029.5</v>
+        <v>-17200</v>
       </c>
       <c r="O10" s="67"/>
       <c r="Q10" s="68" t="s">
@@ -32371,7 +32374,7 @@
         <v>202</v>
       </c>
       <c r="S10" s="68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T10" s="68" t="n">
         <v>79</v>
@@ -32388,20 +32391,20 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="66" t="n">
-        <v>1089</v>
+        <v>1140</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>841371</v>
+        <v>876490</v>
       </c>
       <c r="F11" s="57" t="n">
         <f aca="false">IF(AND(D11&gt;0,N(E11)&gt;0),E11/D11,"")</f>
-        <v>772.608815426997</v>
+        <v>768.850877192983</v>
       </c>
       <c r="G11" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B11,Prices!$A$6:$A$300,0)),"")</f>
@@ -32409,19 +32412,19 @@
       </c>
       <c r="H11" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G11),D11*G11,0)</f>
-        <v>755820.45</v>
+        <v>791217</v>
       </c>
       <c r="I11" s="8" t="n">
         <f aca="false">H11-N(E11)</f>
-        <v>-85550.5500000001</v>
+        <v>-85273</v>
       </c>
       <c r="J11" s="9" t="n">
         <f aca="false">IF(N(E11)&gt;0,I11/E11,"")</f>
-        <v>-0.101679936674784</v>
+        <v>-0.0972891875549065</v>
       </c>
       <c r="K11" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H11/$H$6)</f>
-        <v>0.0676802072086577</v>
+        <v>0.0664346662128249</v>
       </c>
       <c r="L11" s="10"/>
       <c r="M11" s="57" t="str">
@@ -32433,7 +32436,7 @@
         <v/>
       </c>
       <c r="O11" s="67" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q11" s="68" t="s">
         <v>242</v>
@@ -32442,7 +32445,7 @@
         <v>202</v>
       </c>
       <c r="S11" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T11" s="68" t="n">
         <v>970</v>
@@ -32459,53 +32462,53 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="66" t="n">
-        <v>1267</v>
+        <v>305</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>552838</v>
+        <v>659410</v>
       </c>
       <c r="F12" s="57" t="n">
         <f aca="false">IF(AND(D12&gt;0,N(E12)&gt;0),E12/D12,"")</f>
-        <v>436.336227308603</v>
+        <v>2162</v>
       </c>
       <c r="G12" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B12,Prices!$A$6:$A$300,0)),"")</f>
-        <v>432.45</v>
+        <v>2506.9</v>
       </c>
       <c r="H12" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G12),D12*G12,0)</f>
-        <v>547914.15</v>
+        <v>764604.5</v>
       </c>
       <c r="I12" s="8" t="n">
         <f aca="false">H12-N(E12)</f>
-        <v>-4923.84999999998</v>
+        <v>105194.5</v>
       </c>
       <c r="J12" s="9" t="n">
         <f aca="false">IF(N(E12)&gt;0,I12/E12,"")</f>
-        <v>-0.00890649702082704</v>
+        <v>0.159528214616096</v>
       </c>
       <c r="K12" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H12/$H$6)</f>
-        <v>0.0490631646769488</v>
-      </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="57" t="str">
+        <v>0.0642001432506175</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>750575</v>
+      </c>
+      <c r="M12" s="57" t="n">
         <f aca="false">IF(ISNUMBER(L12),L12/D12,"")</f>
-        <v/>
-      </c>
-      <c r="N12" s="8" t="str">
+        <v>2460.90163934426</v>
+      </c>
+      <c r="N12" s="8" t="n">
         <f aca="false">IF(ISNUMBER(L12),H12-L12,"")</f>
-        <v/>
-      </c>
-      <c r="O12" s="67" t="s">
-        <v>245</v>
-      </c>
+        <v>14029.5</v>
+      </c>
+      <c r="O12" s="67"/>
       <c r="Q12" s="68" t="s">
         <v>242</v>
       </c>
@@ -32563,7 +32566,7 @@
       </c>
       <c r="K13" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H13/$H$6)</f>
-        <v>0.0442105096037993</v>
+        <v>0.0414554493545112</v>
       </c>
       <c r="L13" s="10" t="n">
         <v>536742</v>
@@ -32601,7 +32604,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>24</v>
@@ -32634,7 +32637,7 @@
       </c>
       <c r="K14" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H14/$H$6)</f>
-        <v>0.0317654967732266</v>
+        <v>0.0297859706776648</v>
       </c>
       <c r="L14" s="10" t="n">
         <v>353987</v>
@@ -32672,20 +32675,20 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="66" t="n">
-        <v>3860</v>
+        <v>4227</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>331672</v>
+        <v>360078</v>
       </c>
       <c r="F15" s="57" t="n">
         <f aca="false">IF(AND(D15&gt;0,N(E15)&gt;0),E15/D15,"")</f>
-        <v>85.9253886010363</v>
+        <v>85.1852377572747</v>
       </c>
       <c r="G15" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B15,Prices!$A$6:$A$300,0)),"")</f>
@@ -32693,19 +32696,19 @@
       </c>
       <c r="H15" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G15),D15*G15,0)</f>
-        <v>312737.2</v>
+        <v>342471.54</v>
       </c>
       <c r="I15" s="8" t="n">
         <f aca="false">H15-N(E15)</f>
-        <v>-18934.8</v>
+        <v>-17606.46</v>
       </c>
       <c r="J15" s="9" t="n">
         <f aca="false">IF(N(E15)&gt;0,I15/E15,"")</f>
-        <v>-0.0570889312332666</v>
+        <v>-0.0488962391481846</v>
       </c>
       <c r="K15" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H15/$H$6)</f>
-        <v>0.0280041622290789</v>
+        <v>0.028755679475153</v>
       </c>
       <c r="L15" s="10"/>
       <c r="M15" s="57" t="str">
@@ -32743,53 +32746,53 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="66" t="n">
-        <v>700</v>
+        <v>78</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>340305</v>
+        <v>269544</v>
       </c>
       <c r="F16" s="57" t="n">
         <f aca="false">IF(AND(D16&gt;0,N(E16)&gt;0),E16/D16,"")</f>
-        <v>486.15</v>
+        <v>3455.69230769231</v>
       </c>
       <c r="G16" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B16,Prices!$A$6:$A$300,0)),"")</f>
-        <v>431</v>
+        <v>3954.8</v>
       </c>
       <c r="H16" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G16),D16*G16,0)</f>
-        <v>301700</v>
+        <v>308474.4</v>
       </c>
       <c r="I16" s="8" t="n">
         <f aca="false">H16-N(E16)</f>
-        <v>-38605</v>
+        <v>38930.4</v>
       </c>
       <c r="J16" s="9" t="n">
         <f aca="false">IF(N(E16)&gt;0,I16/E16,"")</f>
-        <v>-0.113442353183174</v>
+        <v>0.144430593891906</v>
       </c>
       <c r="K16" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H16/$H$6)</f>
-        <v>0.0270158322851043</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>306600</v>
-      </c>
-      <c r="M16" s="57" t="n">
+        <v>0.0259011039944812</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="57" t="str">
         <f aca="false">IF(ISNUMBER(L16),L16/D16,"")</f>
-        <v>438</v>
-      </c>
-      <c r="N16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N16" s="8" t="str">
         <f aca="false">IF(ISNUMBER(L16),H16-L16,"")</f>
-        <v>-4900</v>
-      </c>
-      <c r="O16" s="67"/>
+        <v/>
+      </c>
+      <c r="O16" s="67" t="s">
+        <v>249</v>
+      </c>
       <c r="Q16" s="68" t="s">
         <v>247</v>
       </c>
@@ -32797,7 +32800,7 @@
         <v>202</v>
       </c>
       <c r="S16" s="68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T16" s="68" t="n">
         <v>1</v>
@@ -32814,53 +32817,53 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="66" t="n">
-        <v>72</v>
+        <v>700</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>245895</v>
+        <v>340305</v>
       </c>
       <c r="F17" s="57" t="n">
         <f aca="false">IF(AND(D17&gt;0,N(E17)&gt;0),E17/D17,"")</f>
-        <v>3415.20833333333</v>
+        <v>486.15</v>
       </c>
       <c r="G17" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B17,Prices!$A$6:$A$300,0)),"")</f>
-        <v>3954.8</v>
+        <v>431</v>
       </c>
       <c r="H17" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G17),D17*G17,0)</f>
-        <v>284745.6</v>
+        <v>301700</v>
       </c>
       <c r="I17" s="8" t="n">
         <f aca="false">H17-N(E17)</f>
-        <v>38850.6</v>
+        <v>-38605</v>
       </c>
       <c r="J17" s="9" t="n">
         <f aca="false">IF(N(E17)&gt;0,I17/E17,"")</f>
-        <v>0.15799670591106</v>
+        <v>-0.113442353183174</v>
       </c>
       <c r="K17" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H17/$H$6)</f>
-        <v>0.0254976445923811</v>
-      </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="57" t="str">
+        <v>0.0253322903785046</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>306600</v>
+      </c>
+      <c r="M17" s="57" t="n">
         <f aca="false">IF(ISNUMBER(L17),L17/D17,"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="8" t="str">
+        <v>438</v>
+      </c>
+      <c r="N17" s="8" t="n">
         <f aca="false">IF(ISNUMBER(L17),H17-L17,"")</f>
-        <v/>
-      </c>
-      <c r="O17" s="67" t="s">
-        <v>249</v>
-      </c>
+        <v>-4900</v>
+      </c>
+      <c r="O17" s="67"/>
       <c r="Q17" s="68" t="s">
         <v>247</v>
       </c>
@@ -32891,14 +32894,14 @@
         <v>24</v>
       </c>
       <c r="D18" s="66" t="n">
-        <v>4830</v>
+        <v>5141</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>209864</v>
+        <v>224820</v>
       </c>
       <c r="F18" s="57" t="n">
         <f aca="false">IF(AND(D18&gt;0,N(E18)&gt;0),E18/D18,"")</f>
-        <v>43.4501035196687</v>
+        <v>43.7307916747714</v>
       </c>
       <c r="G18" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B18,Prices!$A$6:$A$300,0)),"")</f>
@@ -32906,32 +32909,32 @@
       </c>
       <c r="H18" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G18),D18*G18,0)</f>
-        <v>248986.5</v>
+        <v>265018.55</v>
       </c>
       <c r="I18" s="8" t="n">
         <f aca="false">H18-N(E18)</f>
-        <v>39122.5</v>
+        <v>40198.55</v>
       </c>
       <c r="J18" s="9" t="n">
         <f aca="false">IF(N(E18)&gt;0,I18/E18,"")</f>
-        <v>0.18641834712004</v>
+        <v>0.178803264834089</v>
       </c>
       <c r="K18" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H18/$H$6)</f>
-        <v>0.022295583444664</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>269562</v>
-      </c>
-      <c r="M18" s="57" t="n">
+        <v>0.0222523263648997</v>
+      </c>
+      <c r="L18" s="10"/>
+      <c r="M18" s="57" t="str">
         <f aca="false">IF(ISNUMBER(L18),L18/D18,"")</f>
-        <v>55.8099378881988</v>
-      </c>
-      <c r="N18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N18" s="8" t="str">
         <f aca="false">IF(ISNUMBER(L18),H18-L18,"")</f>
-        <v>-20575.5</v>
-      </c>
-      <c r="O18" s="67"/>
+        <v/>
+      </c>
+      <c r="O18" s="67" t="s">
+        <v>250</v>
+      </c>
       <c r="Q18" s="68" t="s">
         <v>247</v>
       </c>
@@ -32962,14 +32965,14 @@
         <v>24</v>
       </c>
       <c r="D19" s="66" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>246916</v>
+        <v>262060</v>
       </c>
       <c r="F19" s="57" t="n">
         <f aca="false">IF(AND(D19&gt;0,N(E19)&gt;0),E19/D19,"")</f>
-        <v>4047.80327868852</v>
+        <v>4031.69230769231</v>
       </c>
       <c r="G19" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B19,Prices!$A$6:$A$300,0)),"")</f>
@@ -32977,19 +32980,19 @@
       </c>
       <c r="H19" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G19),D19*G19,0)</f>
-        <v>234654.8</v>
+        <v>250042</v>
       </c>
       <c r="I19" s="8" t="n">
         <f aca="false">H19-N(E19)</f>
-        <v>-12261.2</v>
+        <v>-12018</v>
       </c>
       <c r="J19" s="9" t="n">
         <f aca="false">IF(N(E19)&gt;0,I19/E19,"")</f>
-        <v>-0.049657373357741</v>
+        <v>-0.0458597267801267</v>
       </c>
       <c r="K19" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H19/$H$6)</f>
-        <v>0.0210122463430384</v>
+        <v>0.0209948178681539</v>
       </c>
       <c r="L19" s="10"/>
       <c r="M19" s="57" t="str">
@@ -33001,7 +33004,7 @@
         <v/>
       </c>
       <c r="O19" s="67" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q19" s="68" t="s">
         <v>247</v>
@@ -33010,7 +33013,7 @@
         <v>202</v>
       </c>
       <c r="S19" s="68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T19" s="68" t="n">
         <v>4</v>
@@ -33027,7 +33030,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>24</v>
@@ -33060,7 +33063,7 @@
       </c>
       <c r="K20" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H20/$H$6)</f>
-        <v>0.0167807987080827</v>
+        <v>0.0157350719818752</v>
       </c>
       <c r="L20" s="10" t="n">
         <v>198400</v>
@@ -33104,14 +33107,14 @@
         <v>24</v>
       </c>
       <c r="D21" s="66" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>107884</v>
+        <v>114527</v>
       </c>
       <c r="F21" s="57" t="n">
         <f aca="false">IF(AND(D21&gt;0,N(E21)&gt;0),E21/D21,"")</f>
-        <v>1477.86301369863</v>
+        <v>1468.29487179487</v>
       </c>
       <c r="G21" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B21,Prices!$A$6:$A$300,0)),"")</f>
@@ -33119,19 +33122,19 @@
       </c>
       <c r="H21" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G21),D21*G21,0)</f>
-        <v>99484.4</v>
+        <v>106298.4</v>
       </c>
       <c r="I21" s="8" t="n">
         <f aca="false">H21-N(E21)</f>
-        <v>-8399.60000000001</v>
+        <v>-8228.60000000001</v>
       </c>
       <c r="J21" s="9" t="n">
         <f aca="false">IF(N(E21)&gt;0,I21/E21,"")</f>
-        <v>-0.0778576990100479</v>
+        <v>-0.0718485597282737</v>
       </c>
       <c r="K21" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H21/$H$6)</f>
-        <v>0.00890836548022614</v>
+        <v>0.0089253627297661</v>
       </c>
       <c r="L21" s="10"/>
       <c r="M21" s="57" t="str">
@@ -33143,7 +33146,7 @@
         <v/>
       </c>
       <c r="O21" s="67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q21" s="68" t="s">
         <v>247</v>
@@ -33169,40 +33172,40 @@
         <v>16</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="66" t="n">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>66457</v>
+        <v>68506</v>
       </c>
       <c r="F22" s="57" t="n">
         <f aca="false">IF(AND(D22&gt;0,N(E22)&gt;0),E22/D22,"")</f>
-        <v>874.434210526316</v>
+        <v>5269.69230769231</v>
       </c>
       <c r="G22" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B22,Prices!$A$6:$A$300,0)),"")</f>
-        <v>788.1</v>
+        <v>5740.5</v>
       </c>
       <c r="H22" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G22),D22*G22,0)</f>
-        <v>59895.6</v>
+        <v>74626.5</v>
       </c>
       <c r="I22" s="8" t="n">
         <f aca="false">H22-N(E22)</f>
-        <v>-6561.4</v>
+        <v>6120.5</v>
       </c>
       <c r="J22" s="9" t="n">
         <f aca="false">IF(N(E22)&gt;0,I22/E22,"")</f>
-        <v>-0.0987315106008397</v>
+        <v>0.0893425393396199</v>
       </c>
       <c r="K22" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H22/$H$6)</f>
-        <v>0.00536337250320083</v>
+        <v>0.00626602641011426</v>
       </c>
       <c r="L22" s="10"/>
       <c r="M22" s="57" t="str">
@@ -33214,14 +33217,25 @@
         <v/>
       </c>
       <c r="O22" s="67" t="s">
-        <v>252</v>
-      </c>
-      <c r="S22" s="69" t="s">
-        <v>208</v>
-      </c>
-      <c r="V22" s="70" t="n">
-        <f aca="false">SUMIFS(V7:V21,R7:R21,"BUY")-SUMIFS(V7:V21,R7:R21,"SELL")</f>
-        <v>-44828</v>
+        <v>249</v>
+      </c>
+      <c r="Q22" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S22" s="68" t="s">
+        <v>91</v>
+      </c>
+      <c r="T22" s="68" t="n">
+        <v>78</v>
+      </c>
+      <c r="U22" s="63" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="V22" s="10" t="n">
+        <v>3732</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33235,14 +33249,14 @@
         <v>24</v>
       </c>
       <c r="D23" s="66" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>62798</v>
+        <v>84214</v>
       </c>
       <c r="F23" s="57" t="n">
         <f aca="false">IF(AND(D23&gt;0,N(E23)&gt;0),E23/D23,"")</f>
-        <v>1308.29166666667</v>
+        <v>1238.44117647059</v>
       </c>
       <c r="G23" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B23,Prices!$A$6:$A$300,0)),"")</f>
@@ -33250,72 +33264,90 @@
       </c>
       <c r="H23" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G23),D23*G23,0)</f>
-        <v>52315.2</v>
+        <v>74113.2</v>
       </c>
       <c r="I23" s="8" t="n">
         <f aca="false">H23-N(E23)</f>
-        <v>-10482.8</v>
+        <v>-10100.8</v>
       </c>
       <c r="J23" s="9" t="n">
         <f aca="false">IF(N(E23)&gt;0,I23/E23,"")</f>
-        <v>-0.166928883085449</v>
+        <v>-0.119942052390339</v>
       </c>
       <c r="K23" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H23/$H$6)</f>
-        <v>0.00468458292728434</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>53693</v>
-      </c>
-      <c r="M23" s="57" t="n">
+        <v>0.00622292709075302</v>
+      </c>
+      <c r="L23" s="10"/>
+      <c r="M23" s="57" t="str">
         <f aca="false">IF(ISNUMBER(L23),L23/D23,"")</f>
-        <v>1118.60416666667</v>
-      </c>
-      <c r="N23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N23" s="8" t="str">
         <f aca="false">IF(ISNUMBER(L23),H23-L23,"")</f>
-        <v>-1377.8</v>
-      </c>
-      <c r="O23" s="67"/>
+        <v/>
+      </c>
+      <c r="O23" s="67" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q23" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R23" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S23" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="T23" s="68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" s="63" t="n">
+        <v>1067.72</v>
+      </c>
+      <c r="V23" s="10" t="n">
+        <v>5339</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>18</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="66" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>45356</v>
+        <v>70997</v>
       </c>
       <c r="F24" s="57" t="n">
         <f aca="false">IF(AND(D24&gt;0,N(E24)&gt;0),E24/D24,"")</f>
-        <v>5039.55555555556</v>
+        <v>865.817073170732</v>
       </c>
       <c r="G24" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B24,Prices!$A$6:$A$300,0)),"")</f>
-        <v>5740.5</v>
+        <v>788.1</v>
       </c>
       <c r="H24" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G24),D24*G24,0)</f>
-        <v>51664.5</v>
+        <v>64624.2</v>
       </c>
       <c r="I24" s="8" t="n">
         <f aca="false">H24-N(E24)</f>
-        <v>6308.5</v>
+        <v>-6372.8</v>
       </c>
       <c r="J24" s="9" t="n">
         <f aca="false">IF(N(E24)&gt;0,I24/E24,"")</f>
-        <v>0.139088543963312</v>
+        <v>-0.089761539219967</v>
       </c>
       <c r="K24" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H24/$H$6)</f>
-        <v>0.00462631576762933</v>
+        <v>0.0054261816369856</v>
       </c>
       <c r="L24" s="10"/>
       <c r="M24" s="57" t="str">
@@ -33327,7 +33359,25 @@
         <v/>
       </c>
       <c r="O24" s="67" t="s">
-        <v>249</v>
+        <v>253</v>
+      </c>
+      <c r="Q24" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R24" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S24" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="T24" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" s="63" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="V24" s="10" t="n">
+        <v>676</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33335,20 +33385,20 @@
         <v>19</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>43513</v>
+        <v>57444</v>
       </c>
       <c r="F25" s="57" t="n">
         <f aca="false">IF(AND(D25&gt;0,N(E25)&gt;0),E25/D25,"")</f>
-        <v>7252.16666666667</v>
+        <v>7180.5</v>
       </c>
       <c r="G25" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B25,Prices!$A$6:$A$300,0)),"")</f>
@@ -33356,19 +33406,19 @@
       </c>
       <c r="H25" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G25),D25*G25,0)</f>
-        <v>42507</v>
+        <v>56676</v>
       </c>
       <c r="I25" s="8" t="n">
         <f aca="false">H25-N(E25)</f>
-        <v>-1006</v>
+        <v>-768</v>
       </c>
       <c r="J25" s="9" t="n">
         <f aca="false">IF(N(E25)&gt;0,I25/E25,"")</f>
-        <v>-0.0231195274975295</v>
+        <v>-0.0133695425109672</v>
       </c>
       <c r="K25" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H25/$H$6)</f>
-        <v>0.0038063042192341</v>
+        <v>0.0047588097099507</v>
       </c>
       <c r="L25" s="10"/>
       <c r="M25" s="57" t="str">
@@ -33380,7 +33430,25 @@
         <v/>
       </c>
       <c r="O25" s="67" t="s">
-        <v>253</v>
+        <v>254</v>
+      </c>
+      <c r="Q25" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R25" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S25" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="T25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="63" t="n">
+        <v>2311.9</v>
+      </c>
+      <c r="V25" s="10" t="n">
+        <v>2312</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33394,14 +33462,14 @@
         <v>24</v>
       </c>
       <c r="D26" s="66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>25715</v>
+        <v>35107</v>
       </c>
       <c r="F26" s="57" t="n">
         <f aca="false">IF(AND(D26&gt;0,N(E26)&gt;0),E26/D26,"")</f>
-        <v>3673.57142857143</v>
+        <v>3510.7</v>
       </c>
       <c r="G26" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B26,Prices!$A$6:$A$300,0)),"")</f>
@@ -33409,19 +33477,19 @@
       </c>
       <c r="H26" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G26),D26*G26,0)</f>
-        <v>22162</v>
+        <v>31660</v>
       </c>
       <c r="I26" s="8" t="n">
         <f aca="false">H26-N(E26)</f>
-        <v>-3553</v>
+        <v>-3447</v>
       </c>
       <c r="J26" s="9" t="n">
         <f aca="false">IF(N(E26)&gt;0,I26/E26,"")</f>
-        <v>-0.13816838421155</v>
+        <v>-0.0981855470419005</v>
       </c>
       <c r="K26" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H26/$H$6)</f>
-        <v>0.0019845040606645</v>
+        <v>0.00265833713418447</v>
       </c>
       <c r="L26" s="10"/>
       <c r="M26" s="57" t="str">
@@ -33433,7 +33501,25 @@
         <v/>
       </c>
       <c r="O26" s="67" t="s">
-        <v>253</v>
+        <v>254</v>
+      </c>
+      <c r="Q26" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R26" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S26" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="T26" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" s="63" t="n">
+        <v>1169.4</v>
+      </c>
+      <c r="V26" s="10" t="n">
+        <v>3508</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33447,14 +33533,14 @@
         <v>24</v>
       </c>
       <c r="D27" s="66" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>24527</v>
+        <v>31435</v>
       </c>
       <c r="F27" s="57" t="n">
         <f aca="false">IF(AND(D27&gt;0,N(E27)&gt;0),E27/D27,"")</f>
-        <v>3065.875</v>
+        <v>2857.72727272727</v>
       </c>
       <c r="G27" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B27,Prices!$A$6:$A$300,0)),"")</f>
@@ -33462,32 +33548,50 @@
       </c>
       <c r="H27" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G27),D27*G27,0)</f>
-        <v>18960</v>
+        <v>26070</v>
       </c>
       <c r="I27" s="8" t="n">
         <f aca="false">H27-N(E27)</f>
-        <v>-5567</v>
+        <v>-5365</v>
       </c>
       <c r="J27" s="9" t="n">
         <f aca="false">IF(N(E27)&gt;0,I27/E27,"")</f>
-        <v>-0.226974354792677</v>
+        <v>-0.170669635756323</v>
       </c>
       <c r="K27" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H27/$H$6)</f>
-        <v>0.00169777984794689</v>
-      </c>
-      <c r="L27" s="10" t="n">
-        <v>20120</v>
-      </c>
-      <c r="M27" s="57" t="n">
+        <v>0.00218897186001861</v>
+      </c>
+      <c r="L27" s="10"/>
+      <c r="M27" s="57" t="str">
         <f aca="false">IF(ISNUMBER(L27),L27/D27,"")</f>
-        <v>2515</v>
-      </c>
-      <c r="N27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N27" s="8" t="str">
         <f aca="false">IF(ISNUMBER(L27),H27-L27,"")</f>
-        <v>-1160</v>
-      </c>
-      <c r="O27" s="67"/>
+        <v/>
+      </c>
+      <c r="O27" s="67" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q27" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R27" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S27" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="T27" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" s="63" t="n">
+        <v>3130.8</v>
+      </c>
+      <c r="V27" s="10" t="n">
+        <v>9392</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
@@ -33500,14 +33604,14 @@
         <v>24</v>
       </c>
       <c r="D28" s="66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>13937</v>
+        <v>22130</v>
       </c>
       <c r="F28" s="57" t="n">
         <f aca="false">IF(AND(D28&gt;0,N(E28)&gt;0),E28/D28,"")</f>
-        <v>2787.4</v>
+        <v>2766.25</v>
       </c>
       <c r="G28" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B28,Prices!$A$6:$A$300,0)),"")</f>
@@ -33515,19 +33619,19 @@
       </c>
       <c r="H28" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G28),D28*G28,0)</f>
-        <v>13879</v>
+        <v>22206.4</v>
       </c>
       <c r="I28" s="8" t="n">
         <f aca="false">H28-N(E28)</f>
-        <v>-58</v>
+        <v>76.4000000000015</v>
       </c>
       <c r="J28" s="9" t="n">
         <f aca="false">IF(N(E28)&gt;0,I28/E28,"")</f>
-        <v>-0.00416158427208151</v>
+        <v>0.00345232715770454</v>
       </c>
       <c r="K28" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H28/$H$6)</f>
-        <v>0.0012427999213953</v>
+        <v>0.00186456404726955</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="57" t="str">
@@ -33539,7 +33643,25 @@
         <v/>
       </c>
       <c r="O28" s="67" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+      <c r="Q28" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R28" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S28" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="T28" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" s="63" t="n">
+        <v>2730.9</v>
+      </c>
+      <c r="V28" s="10" t="n">
+        <v>8193</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33553,14 +33675,14 @@
         <v>24</v>
       </c>
       <c r="D29" s="66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>5602</v>
+        <v>9110</v>
       </c>
       <c r="F29" s="57" t="n">
         <f aca="false">IF(AND(D29&gt;0,N(E29)&gt;0),E29/D29,"")</f>
-        <v>1400.5</v>
+        <v>1301.42857142857</v>
       </c>
       <c r="G29" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B29,Prices!$A$6:$A$300,0)),"")</f>
@@ -33568,52 +33690,70 @@
       </c>
       <c r="H29" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G29),D29*G29,0)</f>
-        <v>4759.6</v>
+        <v>8329.3</v>
       </c>
       <c r="I29" s="8" t="n">
         <f aca="false">H29-N(E29)</f>
-        <v>-842.4</v>
+        <v>-780.699999999999</v>
       </c>
       <c r="J29" s="9" t="n">
         <f aca="false">IF(N(E29)&gt;0,I29/E29,"")</f>
-        <v>-0.150374866119243</v>
+        <v>-0.0856970362239296</v>
       </c>
       <c r="K29" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H29/$H$6)</f>
-        <v>0.000426200050859073</v>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>4971</v>
-      </c>
-      <c r="M29" s="57" t="n">
+        <v>0.0006993710515402</v>
+      </c>
+      <c r="L29" s="10"/>
+      <c r="M29" s="57" t="str">
         <f aca="false">IF(ISNUMBER(L29),L29/D29,"")</f>
-        <v>1242.75</v>
-      </c>
-      <c r="N29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N29" s="8" t="str">
         <f aca="false">IF(ISNUMBER(L29),H29-L29,"")</f>
-        <v>-211.4</v>
-      </c>
-      <c r="O29" s="67"/>
+        <v/>
+      </c>
+      <c r="O29" s="67" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q29" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R29" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S29" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="T29" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" s="63" t="n">
+        <v>6965.5</v>
+      </c>
+      <c r="V29" s="10" t="n">
+        <v>13931</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>24</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>2928</v>
+        <v>4281</v>
       </c>
       <c r="F30" s="57" t="n">
         <f aca="false">IF(AND(D30&gt;0,N(E30)&gt;0),E30/D30,"")</f>
-        <v>976</v>
+        <v>856.2</v>
       </c>
       <c r="G30" s="48" t="n">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B30,Prices!$A$6:$A$300,0)),"")</f>
@@ -33621,32 +33761,50 @@
       </c>
       <c r="H30" s="8" t="n">
         <f aca="false">IF(ISNUMBER(G30),D30*G30,0)</f>
-        <v>2156.85</v>
+        <v>3594.75</v>
       </c>
       <c r="I30" s="8" t="n">
         <f aca="false">H30-N(E30)</f>
-        <v>-771.15</v>
+        <v>-686.25</v>
       </c>
       <c r="J30" s="9" t="n">
         <f aca="false">IF(N(E30)&gt;0,I30/E30,"")</f>
-        <v>-0.263370901639344</v>
+        <v>-0.160301331464611</v>
       </c>
       <c r="K30" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H30/$H$6)</f>
-        <v>0.000193135889506553</v>
-      </c>
-      <c r="L30" s="10" t="n">
-        <v>2479</v>
-      </c>
-      <c r="M30" s="57" t="n">
+        <v>0.000301833778051473</v>
+      </c>
+      <c r="L30" s="10"/>
+      <c r="M30" s="57" t="str">
         <f aca="false">IF(ISNUMBER(L30),L30/D30,"")</f>
-        <v>826.333333333333</v>
-      </c>
-      <c r="N30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N30" s="8" t="str">
         <f aca="false">IF(ISNUMBER(L30),H30-L30,"")</f>
-        <v>-322.15</v>
-      </c>
-      <c r="O30" s="67"/>
+        <v/>
+      </c>
+      <c r="O30" s="67" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q30" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R30" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S30" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="T30" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" s="63" t="n">
+        <v>756.6</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>4540</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
@@ -33686,7 +33844,7 @@
       </c>
       <c r="K31" s="9" t="n">
         <f aca="false">IF($H$6=0,"",H31/$H$6)</f>
-        <v>0.000125094854830264</v>
+        <v>0.000117299335958803</v>
       </c>
       <c r="L31" s="10" t="n">
         <v>1363</v>
@@ -33700,6 +33858,313 @@
         <v>34</v>
       </c>
       <c r="O31" s="67"/>
+      <c r="Q31" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R31" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S31" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="T31" s="68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" s="63" t="n">
+        <v>1328.62</v>
+      </c>
+      <c r="V31" s="10" t="n">
+        <v>6643</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q32" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R32" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S32" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="T32" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" s="63" t="n">
+        <v>4246.32</v>
+      </c>
+      <c r="V32" s="10" t="n">
+        <v>25478</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q33" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R33" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S33" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="T33" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" s="63" t="n">
+        <v>3933.2</v>
+      </c>
+      <c r="V33" s="10" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q34" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R34" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S34" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="T34" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" s="63" t="n">
+        <v>5795.5</v>
+      </c>
+      <c r="V34" s="10" t="n">
+        <v>11591</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q35" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R35" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S35" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="T35" s="68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" s="63" t="n">
+        <v>3785.9</v>
+      </c>
+      <c r="V35" s="10" t="n">
+        <v>15144</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q36" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R36" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S36" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="T36" s="68" t="n">
+        <v>367</v>
+      </c>
+      <c r="U36" s="63" t="n">
+        <v>77.4</v>
+      </c>
+      <c r="V36" s="10" t="n">
+        <v>28406</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q37" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R37" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S37" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="T37" s="68" t="n">
+        <v>51</v>
+      </c>
+      <c r="U37" s="63" t="n">
+        <v>688.6</v>
+      </c>
+      <c r="V37" s="10" t="n">
+        <v>35119</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q38" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R38" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S38" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="T38" s="68" t="n">
+        <v>651</v>
+      </c>
+      <c r="U38" s="63" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="V38" s="10" t="n">
+        <v>271792</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q39" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R39" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S39" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="T39" s="68" t="n">
+        <v>227</v>
+      </c>
+      <c r="U39" s="63" t="n">
+        <v>933.48</v>
+      </c>
+      <c r="V39" s="10" t="n">
+        <v>211900</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q40" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R40" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S40" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="T40" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" s="63" t="n">
+        <v>676.95</v>
+      </c>
+      <c r="V40" s="10" t="n">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q41" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R41" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S41" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="T41" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" s="63" t="n">
+        <v>2297.9</v>
+      </c>
+      <c r="V41" s="10" t="n">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q42" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R42" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S42" s="68" t="s">
+        <v>91</v>
+      </c>
+      <c r="T42" s="68" t="n">
+        <v>233</v>
+      </c>
+      <c r="U42" s="63" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="V42" s="10" t="n">
+        <v>11224</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q43" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R43" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S43" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="T43" s="68" t="n">
+        <v>15</v>
+      </c>
+      <c r="U43" s="63" t="n">
+        <v>1071.81</v>
+      </c>
+      <c r="V43" s="10" t="n">
+        <v>16077</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q44" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R44" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S44" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="T44" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" s="63" t="n">
+        <v>5779.5</v>
+      </c>
+      <c r="V44" s="10" t="n">
+        <v>11559</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q45" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="R45" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S45" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="T45" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" s="63" t="n">
+        <v>3949.8</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>11849</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="S46" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="V46" s="70" t="n">
+        <f aca="false">SUMIFS(V7:V45,R7:R45,"BUY")-SUMIFS(V7:V45,R7:R45,"SELL")</f>
+        <v>680650</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G7:G300">
@@ -33755,7 +34220,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33810,7 +34275,7 @@
         <v>194</v>
       </c>
       <c r="Q5" s="31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33924,13 +34389,13 @@
       </c>
       <c r="O7" s="67"/>
       <c r="Q7" s="68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R7" s="68" t="s">
         <v>202</v>
       </c>
       <c r="S7" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T7" s="68" t="n">
         <v>8</v>
@@ -33995,13 +34460,13 @@
       </c>
       <c r="O8" s="67"/>
       <c r="Q8" s="68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R8" s="68" t="s">
         <v>202</v>
       </c>
       <c r="S8" s="68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T8" s="68" t="n">
         <v>2</v>
@@ -34018,7 +34483,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>28</v>
@@ -34066,7 +34531,7 @@
       </c>
       <c r="O9" s="67"/>
       <c r="Q9" s="68" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R9" s="68" t="s">
         <v>202</v>
@@ -34089,7 +34554,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>28</v>
@@ -34202,7 +34667,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>28</v>
@@ -34255,7 +34720,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>28</v>
@@ -34361,7 +34826,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>28</v>
@@ -34622,7 +35087,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34677,7 +35142,7 @@
         <v>194</v>
       </c>
       <c r="Q5" s="31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34791,7 +35256,7 @@
       </c>
       <c r="O7" s="67"/>
       <c r="Q7" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R7" s="68" t="s">
         <v>202</v>
@@ -34862,13 +35327,13 @@
       </c>
       <c r="O8" s="67"/>
       <c r="Q8" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R8" s="68" t="s">
         <v>202</v>
       </c>
       <c r="S8" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T8" s="68" t="n">
         <v>176</v>
@@ -34885,7 +35350,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>32</v>
@@ -34933,13 +35398,13 @@
       </c>
       <c r="O9" s="67"/>
       <c r="Q9" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R9" s="68" t="s">
         <v>202</v>
       </c>
       <c r="S9" s="68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T9" s="68" t="n">
         <v>55</v>
@@ -34956,7 +35421,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>32</v>
@@ -35004,7 +35469,7 @@
       </c>
       <c r="O10" s="67"/>
       <c r="Q10" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R10" s="68" t="s">
         <v>202</v>
@@ -35074,16 +35539,16 @@
         <v>-12852</v>
       </c>
       <c r="O11" s="67" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q11" s="68" t="s">
         <v>263</v>
-      </c>
-      <c r="Q11" s="68" t="s">
-        <v>262</v>
       </c>
       <c r="R11" s="68" t="s">
         <v>202</v>
       </c>
       <c r="S11" s="68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T11" s="68" t="n">
         <v>280</v>
@@ -35100,7 +35565,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>32</v>
@@ -35147,10 +35612,10 @@
         <v>-8600</v>
       </c>
       <c r="O12" s="67" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q12" s="68" t="s">
         <v>263</v>
-      </c>
-      <c r="Q12" s="68" t="s">
-        <v>262</v>
       </c>
       <c r="R12" s="68" t="s">
         <v>202</v>
@@ -35173,7 +35638,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>32</v>
@@ -35221,7 +35686,7 @@
       </c>
       <c r="O13" s="67"/>
       <c r="Q13" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R13" s="68" t="s">
         <v>202</v>
@@ -35244,7 +35709,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>32</v>
@@ -35294,13 +35759,13 @@
         <v>203</v>
       </c>
       <c r="Q14" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R14" s="68" t="s">
         <v>202</v>
       </c>
       <c r="S14" s="68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T14" s="68" t="n">
         <v>3</v>
@@ -35317,7 +35782,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>32</v>
@@ -35365,7 +35830,7 @@
       </c>
       <c r="O15" s="67"/>
       <c r="Q15" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R15" s="68" t="s">
         <v>202</v>
@@ -35436,7 +35901,7 @@
       </c>
       <c r="O16" s="67"/>
       <c r="Q16" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R16" s="68" t="s">
         <v>202</v>
@@ -35507,7 +35972,7 @@
       </c>
       <c r="O17" s="67"/>
       <c r="Q17" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R17" s="68" t="s">
         <v>202</v>
@@ -35578,7 +36043,7 @@
       </c>
       <c r="O18" s="67"/>
       <c r="Q18" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R18" s="68" t="s">
         <v>202</v>
@@ -35649,13 +36114,13 @@
       </c>
       <c r="O19" s="67"/>
       <c r="Q19" s="68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R19" s="68" t="s">
         <v>202</v>
       </c>
       <c r="S19" s="68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T19" s="68" t="n">
         <v>2</v>
@@ -35832,7 +36297,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35840,7 +36305,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>32</v>
@@ -35887,7 +36352,7 @@
         <v>448.5</v>
       </c>
       <c r="O23" s="67" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36048,7 +36513,7 @@
         <v>-422.2</v>
       </c>
       <c r="O26" s="67" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36152,7 +36617,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36255,7 +36720,7 @@
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D7" s="66" t="n">
         <v>915</v>
@@ -36305,10 +36770,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D8" s="66" t="n">
         <v>792</v>
@@ -36361,7 +36826,7 @@
         <v>80</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" s="66" t="n">
         <v>59</v>
@@ -36411,10 +36876,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D10" s="66" t="n">
         <v>337</v>
@@ -36464,10 +36929,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D11" s="66" t="n">
         <v>800</v>
@@ -36511,7 +36976,7 @@
         <v>-24600</v>
       </c>
       <c r="O11" s="67" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36575,7 +37040,7 @@
         <v>84</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D13" s="66" t="n">
         <v>120</v>
@@ -36619,7 +37084,7 @@
         <v>-20226</v>
       </c>
       <c r="O13" s="67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36627,10 +37092,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D14" s="66" t="n">
         <v>1732</v>
@@ -36736,7 +37201,7 @@
         <v>93</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D16" s="66" t="n">
         <v>18</v>
@@ -36786,10 +37251,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D17" s="66" t="n">
         <v>24</v>
@@ -36895,7 +37360,7 @@
         <v>92</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" s="66" t="n">
         <v>20</v>
@@ -36948,7 +37413,7 @@
         <v>106</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D20" s="66" t="n">
         <v>52</v>
@@ -37001,7 +37466,7 @@
         <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" s="66" t="n">
         <v>45</v>
@@ -37051,10 +37516,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" s="66" t="n">
         <v>8</v>
@@ -37107,7 +37572,7 @@
         <v>100</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" s="66" t="n">
         <v>18</v>
@@ -37213,7 +37678,7 @@
         <v>114</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D25" s="66" t="n">
         <v>33</v>
@@ -37266,7 +37731,7 @@
         <v>117</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D26" s="66" t="n">
         <v>111</v>
@@ -37319,7 +37784,7 @@
         <v>102</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D27" s="66" t="n">
         <v>13</v>
@@ -37478,7 +37943,7 @@
         <v>85</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D30" s="66" t="n">
         <v>13</v>
@@ -37584,7 +38049,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D32" s="66" t="n">
         <v>187</v>
@@ -37637,7 +38102,7 @@
         <v>124</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D33" s="66" t="n">
         <v>1072</v>
@@ -37690,7 +38155,7 @@
         <v>126</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D34" s="66" t="n">
         <v>19</v>
@@ -37743,7 +38208,7 @@
         <v>127</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D35" s="66" t="n">
         <v>110</v>
@@ -37787,7 +38252,7 @@
         <v>-2625.7</v>
       </c>
       <c r="O35" s="67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37798,7 +38263,7 @@
         <v>128</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D36" s="66" t="n">
         <v>302</v>
@@ -37851,7 +38316,7 @@
         <v>129</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D37" s="66" t="n">
         <v>166</v>
@@ -37904,7 +38369,7 @@
         <v>130</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D38" s="66" t="n">
         <v>116</v>
@@ -37957,7 +38422,7 @@
         <v>131</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" s="66" t="n">
         <v>33</v>
@@ -38007,10 +38472,10 @@
         <v>34</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D40" s="66" t="n">
         <v>5</v>
@@ -38054,7 +38519,7 @@
         <v>-5</v>
       </c>
       <c r="O40" s="67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38065,7 +38530,7 @@
         <v>132</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D41" s="66" t="n">
         <v>380</v>
@@ -38118,7 +38583,7 @@
         <v>133</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D42" s="66" t="n">
         <v>245</v>
@@ -38171,7 +38636,7 @@
         <v>134</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D43" s="66" t="n">
         <v>35</v>
@@ -38224,7 +38689,7 @@
         <v>136</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D44" s="66" t="n">
         <v>51</v>
@@ -38330,7 +38795,7 @@
         <v>137</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D46" s="66" t="n">
         <v>124</v>
@@ -38383,7 +38848,7 @@
         <v>138</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D47" s="66" t="n">
         <v>49</v>
@@ -38436,7 +38901,7 @@
         <v>141</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D48" s="66" t="n">
         <v>54</v>
@@ -38542,7 +39007,7 @@
         <v>143</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D50" s="66" t="n">
         <v>67</v>
@@ -38595,7 +39060,7 @@
         <v>139</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D51" s="66" t="n">
         <v>150</v>
@@ -38648,7 +39113,7 @@
         <v>145</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D52" s="66" t="n">
         <v>48</v>
@@ -38701,7 +39166,7 @@
         <v>147</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D53" s="66" t="n">
         <v>132</v>
@@ -38754,7 +39219,7 @@
         <v>149</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D54" s="66" t="n">
         <v>33</v>
@@ -38860,7 +39325,7 @@
         <v>153</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D56" s="66" t="n">
         <v>9</v>
@@ -38910,7 +39375,7 @@
         <v>51</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>16</v>
@@ -38966,7 +39431,7 @@
         <v>161</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D58" s="66" t="n">
         <v>20</v>
@@ -39063,7 +39528,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/Consolidated_Portfolios_23.10.2026.xlsx
+++ b/Consolidated_Portfolios_23.10.2026.xlsx
@@ -636,7 +636,10 @@
     <t xml:space="preserve">Holdings as of 23.10.2026. Statement prices: HDFC statement prices 23.10.2026. Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue = figures from the statement (inputs). Black = formulas. Green = pulled from another sheet.</t>
+    <t xml:space="preserve">Blue = figures from the statement (inputs). Black = formulas. Green figures = pulled from another sheet. Green company names = marked holdings. TOTAL is at the bottom; invested base to be supplied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changes between 05.10 and 23.10 statements (derived; buys at implied avg cost, sells at 05.10 statement price)</t>
   </si>
   <si>
     <t xml:space="preserve">Company</t>
@@ -661,9 +664,6 @@
   </si>
   <si>
     <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes between 05.10 and 23.10 statements (derived; buys at implied avg cost, sells at 05.10 statement price)</t>
   </si>
   <si>
     <t xml:space="preserve">Date / Time</t>
@@ -922,7 +922,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.00;[RED]\(#,##0.00\);\-"/>
     <numFmt numFmtId="170" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1080,6 +1080,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF7F7F7F"/>
@@ -1170,7 +1178,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1B4F72"/>
-        <bgColor rgb="FF0B5345"/>
+        <bgColor rgb="FF1A5276"/>
       </patternFill>
     </fill>
     <fill>
@@ -1275,7 +1283,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="96">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1532,11 +1540,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1544,7 +1548,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1588,47 +1592,79 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1669,29 +1705,29 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF1B4F72"/>
       <rgbColor rgb="FF7E5109"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF117864"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF7F7F7F"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF5DADE2"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFBEBD0"/>
       <rgbColor rgb="FFD4EFDF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF1B4F72"/>
+      <rgbColor rgb="FF1F618D"/>
       <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF1A5276"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF1E8449"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FF00B050"/>
       <rgbColor rgb="FFD6EAF8"/>
       <rgbColor rgb="FFD5F5E3"/>
       <rgbColor rgb="FFFCE4B6"/>
@@ -1699,8 +1735,8 @@
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFE8DAEF"/>
       <rgbColor rgb="FFF5D5D0"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF2874A6"/>
+      <rgbColor rgb="FF52BE80"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
@@ -1708,7 +1744,7 @@
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF27AE60"/>
       <rgbColor rgb="FF0B5345"/>
       <rgbColor rgb="FF145A32"/>
       <rgbColor rgb="FF7B241C"/>
@@ -1898,6 +1934,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF0B5345"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
@@ -1985,11 +2022,11 @@
         <v>31</v>
       </c>
       <c r="F6" s="7" t="n">
-        <f aca="false">Gautam!E6</f>
+        <f aca="false">SUM(Gautam!$E$7:$E$300)</f>
         <v>5501448</v>
       </c>
       <c r="G6" s="7" t="n">
-        <f aca="false">Gautam!H6</f>
+        <f aca="false">Gautam!H38</f>
         <v>5225157.3</v>
       </c>
       <c r="H6" s="8" t="n">
@@ -2033,11 +2070,11 @@
         <v>47</v>
       </c>
       <c r="F7" s="7" t="n">
-        <f aca="false">'Manish Shilpa'!E6</f>
+        <f aca="false">SUM('Manish Shilpa'!$E$7:$E$300)</f>
         <v>9857778</v>
       </c>
       <c r="G7" s="7" t="n">
-        <f aca="false">'Manish Shilpa'!H6</f>
+        <f aca="false">'Manish Shilpa'!H54</f>
         <v>11825894.92</v>
       </c>
       <c r="H7" s="8" t="n">
@@ -2081,11 +2118,11 @@
         <v>25</v>
       </c>
       <c r="F8" s="7" t="n">
-        <f aca="false">'Saloni Mehra'!E6</f>
+        <f aca="false">SUM('Saloni Mehra'!$E$7:$E$300)</f>
         <v>11739506</v>
       </c>
       <c r="G8" s="7" t="n">
-        <f aca="false">'Saloni Mehra'!H6</f>
+        <f aca="false">'Saloni Mehra'!H32</f>
         <v>11909700.84</v>
       </c>
       <c r="H8" s="8" t="n">
@@ -2129,11 +2166,11 @@
         <v>12</v>
       </c>
       <c r="F9" s="7" t="n">
-        <f aca="false">'Vidushi Malhotra'!E6</f>
+        <f aca="false">SUM('Vidushi Malhotra'!$E$7:$E$300)</f>
         <v>201361</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">'Vidushi Malhotra'!H6</f>
+        <f aca="false">'Vidushi Malhotra'!H19</f>
         <v>226299.362921147</v>
       </c>
       <c r="H9" s="8" t="n">
@@ -2177,11 +2214,11 @@
         <v>20</v>
       </c>
       <c r="F10" s="7" t="n">
-        <f aca="false">'Dr Umesh Choudhry'!E6</f>
+        <f aca="false">SUM('Dr Umesh Choudhry'!$E$7:$E$300)</f>
         <v>5222229</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">'Dr Umesh Choudhry'!H6</f>
+        <f aca="false">'Dr Umesh Choudhry'!H28</f>
         <v>5421322.76</v>
       </c>
       <c r="H10" s="8" t="n">
@@ -2225,11 +2262,11 @@
         <v>53</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">DA!E6</f>
+        <f aca="false">SUM(DA!$E$7:$E$300)</f>
         <v>4364996</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">DA!H6</f>
+        <f aca="false">DA!H60</f>
         <v>3866010.74</v>
       </c>
       <c r="H11" s="8" t="n">
@@ -2910,6 +2947,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF117864"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BB95"/>
@@ -22640,6 +22678,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF1A5276"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:M94"/>
@@ -27145,9 +27184,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF1E8449"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -27188,95 +27228,57 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q5" s="31" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="Q5" s="31" t="s">
+      <c r="O6" s="3" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="64" t="n">
-        <f aca="false">SUM(E7:E37)</f>
-        <v>5501448</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="64" t="n">
-        <f aca="false">SUM(H7:H37)</f>
-        <v>5225157.3</v>
-      </c>
-      <c r="I6" s="64" t="n">
-        <f aca="false">H6-E6</f>
-        <v>-276290.7</v>
-      </c>
-      <c r="J6" s="65" t="n">
-        <f aca="false">IF(E6&gt;0,I6/E6,"")</f>
-        <v>-0.050221450788956</v>
-      </c>
-      <c r="K6" s="65" t="n">
-        <f aca="false">SUM(K7:K37)</f>
-        <v>1</v>
-      </c>
-      <c r="L6" s="64" t="n">
-        <f aca="false">SUM(L7:L37)</f>
-        <v>5224564</v>
-      </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="64" t="n">
-        <f aca="false">SUM(N7:N37)</f>
-        <v>593.300000000083</v>
-      </c>
-      <c r="O6" s="4"/>
       <c r="Q6" s="3" t="s">
         <v>196</v>
       </c>
@@ -27300,13 +27302,13 @@
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="64" t="s">
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="65" t="n">
         <v>1901</v>
       </c>
       <c r="E7" s="10" t="n">
@@ -27333,7 +27335,7 @@
         <v>-0.0634566922504509</v>
       </c>
       <c r="K7" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H7/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H7/$H$38)</f>
         <v>0.342751805768603</v>
       </c>
       <c r="L7" s="10" t="n">
@@ -27347,17 +27349,17 @@
         <f aca="false">IF(ISNUMBER(L7),H7-L7,"")</f>
         <v>7794.10000000009</v>
       </c>
-      <c r="O7" s="67"/>
-      <c r="Q7" s="68" t="s">
+      <c r="O7" s="66"/>
+      <c r="Q7" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R7" s="68" t="s">
+      <c r="R7" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S7" s="68" t="s">
+      <c r="S7" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="T7" s="68" t="n">
+      <c r="T7" s="67" t="n">
         <v>8</v>
       </c>
       <c r="U7" s="63" t="n">
@@ -27371,13 +27373,13 @@
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="64" t="s">
         <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="65" t="n">
         <v>1132</v>
       </c>
       <c r="E8" s="10" t="n">
@@ -27404,7 +27406,7 @@
         <v>-0.0713971910496006</v>
       </c>
       <c r="K8" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H8/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H8/$H$38)</f>
         <v>0.0936877823754703</v>
       </c>
       <c r="L8" s="10" t="n">
@@ -27418,17 +27420,17 @@
         <f aca="false">IF(ISNUMBER(L8),H8-L8,"")</f>
         <v>509.399999999965</v>
       </c>
-      <c r="O8" s="67"/>
-      <c r="Q8" s="68" t="s">
+      <c r="O8" s="66"/>
+      <c r="Q8" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R8" s="68" t="s">
+      <c r="R8" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S8" s="68" t="s">
+      <c r="S8" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="T8" s="68" t="n">
+      <c r="T8" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U8" s="63" t="n">
@@ -27448,7 +27450,7 @@
       <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="66" t="n">
+      <c r="D9" s="65" t="n">
         <v>325</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -27475,7 +27477,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H9/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H9/$H$38)</f>
         <v>0.0621990844179945</v>
       </c>
       <c r="L9" s="10" t="n">
@@ -27489,17 +27491,17 @@
         <f aca="false">IF(ISNUMBER(L9),H9-L9,"")</f>
         <v>0</v>
       </c>
-      <c r="O9" s="67"/>
-      <c r="Q9" s="68" t="s">
+      <c r="O9" s="66"/>
+      <c r="Q9" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R9" s="68" t="s">
+      <c r="R9" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S9" s="68" t="s">
+      <c r="S9" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="T9" s="68" t="n">
+      <c r="T9" s="67" t="n">
         <v>237</v>
       </c>
       <c r="U9" s="63" t="n">
@@ -27513,13 +27515,13 @@
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="64" t="s">
         <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="66" t="n">
+      <c r="D10" s="65" t="n">
         <v>447</v>
       </c>
       <c r="E10" s="10" t="n">
@@ -27546,7 +27548,7 @@
         <v>-0.0308683876771981</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H10/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H10/$H$38)</f>
         <v>0.0593743560600558</v>
       </c>
       <c r="L10" s="10" t="n">
@@ -27560,17 +27562,17 @@
         <f aca="false">IF(ISNUMBER(L10),H10-L10,"")</f>
         <v>22.3499999999767</v>
       </c>
-      <c r="O10" s="67"/>
-      <c r="Q10" s="68" t="s">
+      <c r="O10" s="66"/>
+      <c r="Q10" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R10" s="68" t="s">
+      <c r="R10" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S10" s="68" t="s">
+      <c r="S10" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="T10" s="68" t="n">
+      <c r="T10" s="67" t="n">
         <v>274</v>
       </c>
       <c r="U10" s="63" t="n">
@@ -27584,13 +27586,13 @@
       <c r="A11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="64" t="s">
         <v>87</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="65" t="n">
         <v>60</v>
       </c>
       <c r="E11" s="10" t="n">
@@ -27617,7 +27619,7 @@
         <v>-0.0635407537248028</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H11/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H11/$H$38)</f>
         <v>0.0490779483327708</v>
       </c>
       <c r="L11" s="10" t="n">
@@ -27631,19 +27633,19 @@
         <f aca="false">IF(ISNUMBER(L11),H11-L11,"")</f>
         <v>0</v>
       </c>
-      <c r="O11" s="67" t="s">
+      <c r="O11" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="Q11" s="68" t="s">
+      <c r="Q11" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R11" s="68" t="s">
+      <c r="R11" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S11" s="68" t="s">
+      <c r="S11" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="T11" s="68" t="n">
+      <c r="T11" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U11" s="63" t="n">
@@ -27657,13 +27659,13 @@
       <c r="A12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="64" t="s">
         <v>85</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="66" t="n">
+      <c r="D12" s="65" t="n">
         <v>92</v>
       </c>
       <c r="E12" s="10" t="n">
@@ -27690,7 +27692,7 @@
         <v>0.0951944080384448</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H12/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H12/$H$38)</f>
         <v>0.0441393027536224</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -27704,17 +27706,17 @@
         <f aca="false">IF(ISNUMBER(L12),H12-L12,"")</f>
         <v>-9.19999999998254</v>
       </c>
-      <c r="O12" s="67"/>
-      <c r="Q12" s="68" t="s">
+      <c r="O12" s="66"/>
+      <c r="Q12" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R12" s="68" t="s">
+      <c r="R12" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S12" s="68" t="s">
+      <c r="S12" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="T12" s="68" t="n">
+      <c r="T12" s="67" t="n">
         <v>138</v>
       </c>
       <c r="U12" s="63" t="n">
@@ -27728,13 +27730,13 @@
       <c r="A13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="64" t="s">
         <v>80</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="66" t="n">
+      <c r="D13" s="65" t="n">
         <v>47</v>
       </c>
       <c r="E13" s="10" t="n">
@@ -27761,7 +27763,7 @@
         <v>-0.0868609813397172</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H13/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H13/$H$38)</f>
         <v>0.0391280086438737</v>
       </c>
       <c r="L13" s="10" t="n">
@@ -27775,17 +27777,17 @@
         <f aca="false">IF(ISNUMBER(L13),H13-L13,"")</f>
         <v>0</v>
       </c>
-      <c r="O13" s="67"/>
-      <c r="Q13" s="68" t="s">
+      <c r="O13" s="66"/>
+      <c r="Q13" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R13" s="68" t="s">
+      <c r="R13" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S13" s="68" t="s">
+      <c r="S13" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="68" t="n">
+      <c r="T13" s="67" t="n">
         <v>57</v>
       </c>
       <c r="U13" s="63" t="n">
@@ -27799,13 +27801,13 @@
       <c r="A14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="64" t="s">
         <v>89</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="66" t="n">
+      <c r="D14" s="65" t="n">
         <v>800</v>
       </c>
       <c r="E14" s="10" t="n">
@@ -27832,7 +27834,7 @@
         <v>-0.112689393939394</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H14/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H14/$H$38)</f>
         <v>0.0358649489844067</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -27846,17 +27848,17 @@
         <f aca="false">IF(ISNUMBER(L14),H14-L14,"")</f>
         <v>-4600</v>
       </c>
-      <c r="O14" s="67"/>
-      <c r="Q14" s="68" t="s">
+      <c r="O14" s="66"/>
+      <c r="Q14" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R14" s="68" t="s">
+      <c r="R14" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="S14" s="68" t="s">
+      <c r="S14" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="T14" s="68" t="n">
+      <c r="T14" s="67" t="n">
         <v>80</v>
       </c>
       <c r="U14" s="63" t="n">
@@ -27870,13 +27872,13 @@
       <c r="A15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="64" t="s">
         <v>84</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="66" t="n">
+      <c r="D15" s="65" t="n">
         <v>120</v>
       </c>
       <c r="E15" s="10" t="n">
@@ -27903,7 +27905,7 @@
         <v>-0.176800720288115</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H15/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H15/$H$38)</f>
         <v>0.0314964680584831</v>
       </c>
       <c r="L15" s="10" t="n">
@@ -27917,19 +27919,19 @@
         <f aca="false">IF(ISNUMBER(L15),H15-L15,"")</f>
         <v>-666</v>
       </c>
-      <c r="O15" s="67" t="s">
+      <c r="O15" s="66" t="s">
         <v>206</v>
       </c>
-      <c r="Q15" s="68" t="s">
+      <c r="Q15" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R15" s="68" t="s">
+      <c r="R15" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S15" s="68" t="s">
+      <c r="S15" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="T15" s="68" t="n">
+      <c r="T15" s="67" t="n">
         <v>5</v>
       </c>
       <c r="U15" s="63" t="n">
@@ -27943,13 +27945,13 @@
       <c r="A16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="64" t="s">
         <v>92</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="66" t="n">
+      <c r="D16" s="65" t="n">
         <v>41</v>
       </c>
       <c r="E16" s="10" t="n">
@@ -27976,7 +27978,7 @@
         <v>0.122761507467574</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H16/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H16/$H$38)</f>
         <v>0.0301845075553993</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -27990,17 +27992,17 @@
         <f aca="false">IF(ISNUMBER(L16),H16-L16,"")</f>
         <v>-8.19999999998254</v>
       </c>
-      <c r="O16" s="67"/>
-      <c r="Q16" s="68" t="s">
+      <c r="O16" s="66"/>
+      <c r="Q16" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R16" s="68" t="s">
+      <c r="R16" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S16" s="68" t="s">
+      <c r="S16" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="T16" s="68" t="n">
+      <c r="T16" s="67" t="n">
         <v>25</v>
       </c>
       <c r="U16" s="63" t="n">
@@ -28014,13 +28016,13 @@
       <c r="A17" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="64" t="s">
         <v>96</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="66" t="n">
+      <c r="D17" s="65" t="n">
         <v>20</v>
       </c>
       <c r="E17" s="10" t="n">
@@ -28047,7 +28049,7 @@
         <v>-0.0388294191867801</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H17/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H17/$H$38)</f>
         <v>0.0271168869882635</v>
       </c>
       <c r="L17" s="10" t="n">
@@ -28061,17 +28063,17 @@
         <f aca="false">IF(ISNUMBER(L17),H17-L17,"")</f>
         <v>10</v>
       </c>
-      <c r="O17" s="67"/>
-      <c r="Q17" s="68" t="s">
+      <c r="O17" s="66"/>
+      <c r="Q17" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R17" s="68" t="s">
+      <c r="R17" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S17" s="68" t="s">
+      <c r="S17" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="T17" s="68" t="n">
+      <c r="T17" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U17" s="63" t="n">
@@ -28085,13 +28087,13 @@
       <c r="A18" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="64" t="s">
         <v>86</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="66" t="n">
+      <c r="D18" s="65" t="n">
         <v>1600</v>
       </c>
       <c r="E18" s="10" t="n">
@@ -28118,7 +28120,7 @@
         <v>-0.0248100504024675</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H18/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H18/$H$38)</f>
         <v>0.0248092052654568</v>
       </c>
       <c r="L18" s="10" t="n">
@@ -28132,17 +28134,17 @@
         <f aca="false">IF(ISNUMBER(L18),H18-L18,"")</f>
         <v>-288</v>
       </c>
-      <c r="O18" s="67"/>
-      <c r="Q18" s="68" t="s">
+      <c r="O18" s="66"/>
+      <c r="Q18" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R18" s="68" t="s">
+      <c r="R18" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S18" s="68" t="s">
+      <c r="S18" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="T18" s="68" t="n">
+      <c r="T18" s="67" t="n">
         <v>131</v>
       </c>
       <c r="U18" s="63" t="n">
@@ -28156,13 +28158,13 @@
       <c r="A19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="64" t="s">
         <v>88</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="66" t="n">
+      <c r="D19" s="65" t="n">
         <v>30</v>
       </c>
       <c r="E19" s="10" t="n">
@@ -28189,7 +28191,7 @@
         <v>0.135012580000191</v>
       </c>
       <c r="K19" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H19/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H19/$H$38)</f>
         <v>0.022706302066734</v>
       </c>
       <c r="L19" s="10" t="n">
@@ -28203,17 +28205,17 @@
         <f aca="false">IF(ISNUMBER(L19),H19-L19,"")</f>
         <v>-1236</v>
       </c>
-      <c r="O19" s="67"/>
-      <c r="Q19" s="68" t="s">
+      <c r="O19" s="66"/>
+      <c r="Q19" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R19" s="68" t="s">
+      <c r="R19" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S19" s="68" t="s">
+      <c r="S19" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="T19" s="68" t="n">
+      <c r="T19" s="67" t="n">
         <v>9</v>
       </c>
       <c r="U19" s="63" t="n">
@@ -28227,13 +28229,13 @@
       <c r="A20" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="64" t="s">
         <v>93</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="66" t="n">
+      <c r="D20" s="65" t="n">
         <v>19</v>
       </c>
       <c r="E20" s="10" t="n">
@@ -28260,7 +28262,7 @@
         <v>0.0344616639477977</v>
       </c>
       <c r="K20" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H20/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H20/$H$38)</f>
         <v>0.0208739170397798</v>
       </c>
       <c r="L20" s="10" t="n">
@@ -28274,17 +28276,17 @@
         <f aca="false">IF(ISNUMBER(L20),H20-L20,"")</f>
         <v>9.5</v>
       </c>
-      <c r="O20" s="67"/>
-      <c r="Q20" s="68" t="s">
+      <c r="O20" s="66"/>
+      <c r="Q20" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R20" s="68" t="s">
+      <c r="R20" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S20" s="68" t="s">
+      <c r="S20" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="T20" s="68" t="n">
+      <c r="T20" s="67" t="n">
         <v>7</v>
       </c>
       <c r="U20" s="63" t="n">
@@ -28304,7 +28306,7 @@
       <c r="C21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="66" t="n">
+      <c r="D21" s="65" t="n">
         <v>20</v>
       </c>
       <c r="E21" s="10" t="n">
@@ -28331,7 +28333,7 @@
         <v>-0.11419218178317</v>
       </c>
       <c r="K21" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H21/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H21/$H$38)</f>
         <v>0.0176071254352477</v>
       </c>
       <c r="L21" s="10" t="n">
@@ -28345,19 +28347,19 @@
         <f aca="false">IF(ISNUMBER(L21),H21-L21,"")</f>
         <v>-160</v>
       </c>
-      <c r="O21" s="67" t="s">
+      <c r="O21" s="66" t="s">
         <v>207</v>
       </c>
-      <c r="Q21" s="68" t="s">
+      <c r="Q21" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R21" s="68" t="s">
+      <c r="R21" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S21" s="68" t="s">
+      <c r="S21" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="T21" s="68" t="n">
+      <c r="T21" s="67" t="n">
         <v>6</v>
       </c>
       <c r="U21" s="63" t="n">
@@ -28371,13 +28373,13 @@
       <c r="A22" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="64" t="s">
         <v>94</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="66" t="n">
+      <c r="D22" s="65" t="n">
         <v>66</v>
       </c>
       <c r="E22" s="10" t="n">
@@ -28404,7 +28406,7 @@
         <v>-0.152383734627527</v>
       </c>
       <c r="K22" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H22/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H22/$H$38)</f>
         <v>0.0172137975635681</v>
       </c>
       <c r="L22" s="10" t="n">
@@ -28418,17 +28420,17 @@
         <f aca="false">IF(ISNUMBER(L22),H22-L22,"")</f>
         <v>-13.1999999999971</v>
       </c>
-      <c r="O22" s="67"/>
-      <c r="Q22" s="68" t="s">
+      <c r="O22" s="66"/>
+      <c r="Q22" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R22" s="68" t="s">
+      <c r="R22" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S22" s="68" t="s">
+      <c r="S22" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="T22" s="68" t="n">
+      <c r="T22" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U22" s="63" t="n">
@@ -28442,13 +28444,13 @@
       <c r="A23" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="64" t="s">
         <v>100</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="66" t="n">
+      <c r="D23" s="65" t="n">
         <v>31</v>
       </c>
       <c r="E23" s="10" t="n">
@@ -28475,7 +28477,7 @@
         <v>0.000509266795339894</v>
       </c>
       <c r="K23" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H23/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H23/$H$38)</f>
         <v>0.0164683654595432</v>
       </c>
       <c r="L23" s="10" t="n">
@@ -28489,17 +28491,17 @@
         <f aca="false">IF(ISNUMBER(L23),H23-L23,"")</f>
         <v>-6.19999999999709</v>
       </c>
-      <c r="O23" s="67"/>
-      <c r="Q23" s="68" t="s">
+      <c r="O23" s="66"/>
+      <c r="Q23" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="R23" s="68" t="s">
+      <c r="R23" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S23" s="68" t="s">
+      <c r="S23" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="T23" s="68" t="n">
+      <c r="T23" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U23" s="63" t="n">
@@ -28513,13 +28515,13 @@
       <c r="A24" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="64" t="s">
         <v>102</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="65" t="n">
         <v>24</v>
       </c>
       <c r="E24" s="10" t="n">
@@ -28546,7 +28548,7 @@
         <v>-0.155226469214862</v>
       </c>
       <c r="K24" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H24/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H24/$H$38)</f>
         <v>0.0145419545551289</v>
       </c>
       <c r="L24" s="10" t="n">
@@ -28560,11 +28562,11 @@
         <f aca="false">IF(ISNUMBER(L24),H24-L24,"")</f>
         <v>0</v>
       </c>
-      <c r="O24" s="67"/>
-      <c r="S24" s="69" t="s">
+      <c r="O24" s="66"/>
+      <c r="S24" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="V24" s="70" t="n">
+      <c r="V24" s="69" t="n">
         <f aca="false">SUMIFS(V7:V23,R7:R23,"BUY")-SUMIFS(V7:V23,R7:R23,"SELL")</f>
         <v>500968</v>
       </c>
@@ -28573,13 +28575,13 @@
       <c r="A25" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="64" t="s">
         <v>105</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="66" t="n">
+      <c r="D25" s="65" t="n">
         <v>27</v>
       </c>
       <c r="E25" s="10" t="n">
@@ -28606,7 +28608,7 @@
         <v>-0.063967350759914</v>
       </c>
       <c r="K25" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H25/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H25/$H$38)</f>
         <v>0.0122465212674076</v>
       </c>
       <c r="L25" s="10" t="n">
@@ -28620,19 +28622,19 @@
         <f aca="false">IF(ISNUMBER(L25),H25-L25,"")</f>
         <v>0</v>
       </c>
-      <c r="O25" s="67"/>
+      <c r="O25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="64" t="s">
         <v>104</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="66" t="n">
+      <c r="D26" s="65" t="n">
         <v>72</v>
       </c>
       <c r="E26" s="10" t="n">
@@ -28659,7 +28661,7 @@
         <v>-0.0485076128512978</v>
       </c>
       <c r="K26" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H26/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H26/$H$38)</f>
         <v>0.0108596156521451</v>
       </c>
       <c r="L26" s="10" t="n">
@@ -28673,19 +28675,19 @@
         <f aca="false">IF(ISNUMBER(L26),H26-L26,"")</f>
         <v>-64.7999999999956</v>
       </c>
-      <c r="O26" s="67"/>
+      <c r="O26" s="66"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="64" t="s">
         <v>91</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="66" t="n">
+      <c r="D27" s="65" t="n">
         <v>830</v>
       </c>
       <c r="E27" s="10" t="n">
@@ -28712,7 +28714,7 @@
         <v>-0.0838400925013918</v>
       </c>
       <c r="K27" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H27/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H27/$H$38)</f>
         <v>0.00818855730907852</v>
       </c>
       <c r="L27" s="10" t="n">
@@ -28726,19 +28728,19 @@
         <f aca="false">IF(ISNUMBER(L27),H27-L27,"")</f>
         <v>-788.5</v>
       </c>
-      <c r="O27" s="67"/>
+      <c r="O27" s="66"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="64" t="s">
         <v>106</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="66" t="n">
+      <c r="D28" s="65" t="n">
         <v>22</v>
       </c>
       <c r="E28" s="10" t="n">
@@ -28765,7 +28767,7 @@
         <v>-0.0543727197196835</v>
       </c>
       <c r="K28" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H28/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H28/$H$38)</f>
         <v>0.00500995443716116</v>
       </c>
       <c r="L28" s="10" t="n">
@@ -28779,7 +28781,7 @@
         <f aca="false">IF(ISNUMBER(L28),H28-L28,"")</f>
         <v>-2.19999999999709</v>
       </c>
-      <c r="O28" s="67"/>
+      <c r="O28" s="66"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
@@ -28791,7 +28793,7 @@
       <c r="C29" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="66" t="n">
+      <c r="D29" s="65" t="n">
         <v>250</v>
       </c>
       <c r="E29" s="10" t="n">
@@ -28818,7 +28820,7 @@
         <v>-0.154155844155844</v>
       </c>
       <c r="K29" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H29/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H29/$H$38)</f>
         <v>0.00311617412934152</v>
       </c>
       <c r="L29" s="10" t="n">
@@ -28832,7 +28834,7 @@
         <f aca="false">IF(ISNUMBER(L29),H29-L29,"")</f>
         <v>-642.500000000002</v>
       </c>
-      <c r="O29" s="67"/>
+      <c r="O29" s="66"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
@@ -28844,7 +28846,7 @@
       <c r="C30" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="66" t="n">
+      <c r="D30" s="65" t="n">
         <v>150</v>
       </c>
       <c r="E30" s="10" t="n">
@@ -28871,7 +28873,7 @@
         <v>-0.013644859813084</v>
       </c>
       <c r="K30" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H30/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H30/$H$38)</f>
         <v>0.00302976524745006</v>
       </c>
       <c r="L30" s="10" t="n">
@@ -28885,19 +28887,19 @@
         <f aca="false">IF(ISNUMBER(L30),H30-L30,"")</f>
         <v>-68.9999999999982</v>
       </c>
-      <c r="O30" s="67"/>
+      <c r="O30" s="66"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="64" t="s">
         <v>146</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="66" t="n">
+      <c r="D31" s="65" t="n">
         <v>121</v>
       </c>
       <c r="E31" s="10" t="n">
@@ -28924,7 +28926,7 @@
         <v>0.118181818181818</v>
       </c>
       <c r="K31" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H31/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H31/$H$38)</f>
         <v>0.00284833530274773</v>
       </c>
       <c r="L31" s="10" t="n">
@@ -28938,19 +28940,19 @@
         <f aca="false">IF(ISNUMBER(L31),H31-L31,"")</f>
         <v>0</v>
       </c>
-      <c r="O31" s="67"/>
+      <c r="O31" s="66"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="64" t="s">
         <v>101</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="66" t="n">
+      <c r="D32" s="65" t="n">
         <v>10</v>
       </c>
       <c r="E32" s="10" t="n">
@@ -28977,7 +28979,7 @@
         <v>-0.0872623733355665</v>
       </c>
       <c r="K32" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H32/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H32/$H$38)</f>
         <v>0.00208587021868222</v>
       </c>
       <c r="L32" s="10" t="n">
@@ -28991,7 +28993,7 @@
         <f aca="false">IF(ISNUMBER(L32),H32-L32,"")</f>
         <v>-71</v>
       </c>
-      <c r="O32" s="67"/>
+      <c r="O32" s="66"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
@@ -29003,7 +29005,7 @@
       <c r="C33" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="66" t="n">
+      <c r="D33" s="65" t="n">
         <v>5</v>
       </c>
       <c r="E33" s="10" t="n">
@@ -29030,7 +29032,7 @@
         <v>-0.014047866805411</v>
       </c>
       <c r="K33" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H33/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H33/$H$38)</f>
         <v>0.0018133425380323</v>
       </c>
       <c r="L33" s="10" t="n">
@@ -29044,7 +29046,7 @@
         <f aca="false">IF(ISNUMBER(L33),H33-L33,"")</f>
         <v>0</v>
       </c>
-      <c r="O33" s="67"/>
+      <c r="O33" s="66"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
@@ -29056,7 +29058,7 @@
       <c r="C34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="66" t="n">
+      <c r="D34" s="65" t="n">
         <v>25</v>
       </c>
       <c r="E34" s="10" t="n">
@@ -29083,7 +29085,7 @@
         <v>0.0495</v>
       </c>
       <c r="K34" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H34/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H34/$H$38)</f>
         <v>0.000903848387492564</v>
       </c>
       <c r="L34" s="10" t="n">
@@ -29097,19 +29099,19 @@
         <f aca="false">IF(ISNUMBER(L34),H34-L34,"")</f>
         <v>872.75</v>
       </c>
-      <c r="O34" s="67"/>
+      <c r="O34" s="66"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="64" t="s">
         <v>118</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="66" t="n">
+      <c r="D35" s="65" t="n">
         <v>27</v>
       </c>
       <c r="E35" s="10" t="n">
@@ -29136,7 +29138,7 @@
         <v>-0.0661764705882353</v>
       </c>
       <c r="K35" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H35/$H$6)</f>
+        <f aca="false">IF($H$38=0,"",H35/$H$38)</f>
         <v>0.000656248186059394</v>
       </c>
       <c r="L35" s="10" t="n">
@@ -29150,109 +29152,140 @@
         <f aca="false">IF(ISNUMBER(L35),H35-L35,"")</f>
         <v>0</v>
       </c>
-      <c r="O35" s="67"/>
+      <c r="O35" s="66"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="71" t="n">
+      <c r="A36" s="70" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="71" t="s">
+      <c r="B36" s="70" t="s">
         <v>166</v>
       </c>
-      <c r="C36" s="71" t="s">
+      <c r="C36" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="72" t="n">
+      <c r="D36" s="71" t="n">
         <v>144</v>
       </c>
-      <c r="E36" s="73"/>
-      <c r="F36" s="74" t="str">
+      <c r="E36" s="72"/>
+      <c r="F36" s="73" t="str">
         <f aca="false">IF(AND(D36&gt;0,N(E36)&gt;0),E36/D36,"")</f>
         <v/>
       </c>
-      <c r="G36" s="75" t="str">
+      <c r="G36" s="74" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B36,Prices!$A$6:$A$300,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="76" t="n">
+      <c r="H36" s="75" t="n">
         <f aca="false">IF(ISNUMBER(G36),D36*G36,0)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="76" t="n">
+      <c r="I36" s="75" t="n">
         <f aca="false">H36-N(E36)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="77" t="str">
+      <c r="J36" s="76" t="str">
         <f aca="false">IF(N(E36)&gt;0,I36/E36,"")</f>
         <v/>
       </c>
-      <c r="K36" s="77" t="n">
-        <f aca="false">IF($H$6=0,"",H36/$H$6)</f>
-        <v>0</v>
-      </c>
-      <c r="L36" s="73"/>
-      <c r="M36" s="74" t="str">
+      <c r="K36" s="76" t="n">
+        <f aca="false">IF($H$38=0,"",H36/$H$38)</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="72"/>
+      <c r="M36" s="73" t="str">
         <f aca="false">IF(ISNUMBER(L36),L36/D36,"")</f>
         <v/>
       </c>
-      <c r="N36" s="76" t="str">
+      <c r="N36" s="75" t="str">
         <f aca="false">IF(ISNUMBER(L36),H36-L36,"")</f>
         <v/>
       </c>
-      <c r="O36" s="78" t="s">
+      <c r="O36" s="77" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="71" t="n">
+      <c r="A37" s="70" t="n">
         <v>31</v>
       </c>
-      <c r="B37" s="71" t="s">
+      <c r="B37" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="71" t="s">
+      <c r="C37" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="72" t="n">
+      <c r="D37" s="71" t="n">
         <v>1000</v>
       </c>
-      <c r="E37" s="73"/>
-      <c r="F37" s="74" t="str">
+      <c r="E37" s="72"/>
+      <c r="F37" s="73" t="str">
         <f aca="false">IF(AND(D37&gt;0,N(E37)&gt;0),E37/D37,"")</f>
         <v/>
       </c>
-      <c r="G37" s="75" t="str">
+      <c r="G37" s="74" t="str">
         <f aca="false">IFERROR(INDEX(Prices!$C$6:$C$300,MATCH(B37,Prices!$A$6:$A$300,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="76" t="n">
+      <c r="H37" s="75" t="n">
         <f aca="false">IF(ISNUMBER(G37),D37*G37,0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="76" t="n">
+      <c r="I37" s="75" t="n">
         <f aca="false">H37-N(E37)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="77" t="str">
+      <c r="J37" s="76" t="str">
         <f aca="false">IF(N(E37)&gt;0,I37/E37,"")</f>
         <v/>
       </c>
-      <c r="K37" s="77" t="n">
-        <f aca="false">IF($H$6=0,"",H37/$H$6)</f>
-        <v>0</v>
-      </c>
-      <c r="L37" s="73"/>
-      <c r="M37" s="74" t="str">
+      <c r="K37" s="76" t="n">
+        <f aca="false">IF($H$38=0,"",H37/$H$38)</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="72"/>
+      <c r="M37" s="73" t="str">
         <f aca="false">IF(ISNUMBER(L37),L37/D37,"")</f>
         <v/>
       </c>
-      <c r="N37" s="76" t="str">
+      <c r="N37" s="75" t="str">
         <f aca="false">IF(ISNUMBER(L37),H37-L37,"")</f>
         <v/>
       </c>
-      <c r="O37" s="78" t="s">
+      <c r="O37" s="77" t="s">
         <v>209</v>
       </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="78"/>
+      <c r="B38" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="78"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="79" t="n">
+        <f aca="false">SUM(H7:H37)</f>
+        <v>5225157.3</v>
+      </c>
+      <c r="I38" s="78"/>
+      <c r="J38" s="78"/>
+      <c r="K38" s="80" t="n">
+        <f aca="false">SUM(K7:K37)</f>
+        <v>1</v>
+      </c>
+      <c r="L38" s="79" t="n">
+        <f aca="false">SUM(L7:L37)</f>
+        <v>5224564</v>
+      </c>
+      <c r="M38" s="78"/>
+      <c r="N38" s="79" t="n">
+        <f aca="false">SUM(N7:N37)</f>
+        <v>593.300000000083</v>
+      </c>
+      <c r="O38" s="78"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G7:G300">
@@ -29273,9 +29306,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF2874A6"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -29310,104 +29344,64 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="23" t="s">
+      <c r="B6" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="23" t="s">
+      <c r="D6" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="E6" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G6" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="L5" s="23" t="s">
+      <c r="K6" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="L6" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="M6" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="O5" s="23" t="s">
+      <c r="N6" s="23" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="79" t="n">
-        <f aca="false">SUM(E7:E53)</f>
-        <v>9857778</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="79" t="n">
-        <f aca="false">SUM(H7:H53)</f>
-        <v>11825894.92</v>
-      </c>
-      <c r="I6" s="79" t="n">
-        <f aca="false">H6-E6</f>
-        <v>1968116.92</v>
-      </c>
-      <c r="J6" s="80" t="n">
-        <f aca="false">IF(E6&gt;0,I6/E6,"")</f>
-        <v>0.199651170882525</v>
-      </c>
-      <c r="K6" s="80" t="n">
-        <f aca="false">SUM(K7:K53)</f>
-        <v>1</v>
-      </c>
-      <c r="L6" s="79" t="n">
-        <f aca="false">SUM(L7:L53)</f>
-        <v>11636414.18</v>
-      </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="79" t="n">
-        <f aca="false">SUM(N7:N53)</f>
-        <v>189480.74</v>
-      </c>
-      <c r="O6" s="11"/>
+      <c r="O6" s="23" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="64" t="s">
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="65" t="n">
         <v>3895</v>
       </c>
       <c r="E7" s="10" t="n">
@@ -29434,7 +29428,7 @@
         <v>0.25995514335482</v>
       </c>
       <c r="K7" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H7/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H7/$H$54)</f>
         <v>0.310291908123939</v>
       </c>
       <c r="L7" s="10" t="n">
@@ -29448,7 +29442,7 @@
         <f aca="false">IF(ISNUMBER(L7),H7-L7,"")</f>
         <v>43579.5</v>
       </c>
-      <c r="O7" s="67" t="s">
+      <c r="O7" s="66" t="s">
         <v>212</v>
       </c>
     </row>
@@ -29462,7 +29456,7 @@
       <c r="C8" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="65" t="n">
         <v>11160</v>
       </c>
       <c r="E8" s="10" t="n">
@@ -29489,7 +29483,7 @@
         <v>0.697515377048792</v>
       </c>
       <c r="K8" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H8/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H8/$H$54)</f>
         <v>0.2422390034225</v>
       </c>
       <c r="L8" s="10" t="n">
@@ -29503,7 +29497,7 @@
         <f aca="false">IF(ISNUMBER(L8),H8-L8,"")</f>
         <v>0</v>
       </c>
-      <c r="O8" s="67" t="s">
+      <c r="O8" s="66" t="s">
         <v>213</v>
       </c>
     </row>
@@ -29511,13 +29505,13 @@
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="64" t="s">
         <v>80</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D9" s="66" t="n">
+      <c r="D9" s="65" t="n">
         <v>165</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -29544,7 +29538,7 @@
         <v>0.271411616743131</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H9/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H9/$H$54)</f>
         <v>0.0606930811456931</v>
       </c>
       <c r="L9" s="10" t="n">
@@ -29558,7 +29552,7 @@
         <f aca="false">IF(ISNUMBER(L9),H9-L9,"")</f>
         <v>17025</v>
       </c>
-      <c r="O9" s="67" t="s">
+      <c r="O9" s="66" t="s">
         <v>214</v>
       </c>
     </row>
@@ -29566,13 +29560,13 @@
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="64" t="s">
         <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D10" s="66" t="n">
+      <c r="D10" s="65" t="n">
         <v>1013</v>
       </c>
       <c r="E10" s="10" t="n">
@@ -29599,7 +29593,7 @@
         <v>-0.134874668228571</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H10/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H10/$H$54)</f>
         <v>0.0594519615433891</v>
       </c>
       <c r="L10" s="10" t="n">
@@ -29613,7 +29607,7 @@
         <f aca="false">IF(ISNUMBER(L10),H10-L10,"")</f>
         <v>5129.64999999991</v>
       </c>
-      <c r="O10" s="67" t="s">
+      <c r="O10" s="66" t="s">
         <v>215</v>
       </c>
     </row>
@@ -29621,13 +29615,13 @@
       <c r="A11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="64" t="s">
         <v>82</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="65" t="n">
         <v>1394</v>
       </c>
       <c r="E11" s="10" t="n">
@@ -29654,7 +29648,7 @@
         <v>-0.0316101029215455</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H11/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H11/$H$54)</f>
         <v>0.0509758715156924</v>
       </c>
       <c r="L11" s="10" t="n">
@@ -29668,7 +29662,7 @@
         <f aca="false">IF(ISNUMBER(L11),H11-L11,"")</f>
         <v>24777.2999999999</v>
       </c>
-      <c r="O11" s="67" t="s">
+      <c r="O11" s="66" t="s">
         <v>216</v>
       </c>
     </row>
@@ -29676,13 +29670,13 @@
       <c r="A12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="64" t="s">
         <v>84</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D12" s="66" t="n">
+      <c r="D12" s="65" t="n">
         <v>360</v>
       </c>
       <c r="E12" s="10" t="n">
@@ -29709,7 +29703,7 @@
         <v>0.36115062692295</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H12/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H12/$H$54)</f>
         <v>0.0417492294105383</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -29723,7 +29717,7 @@
         <f aca="false">IF(ISNUMBER(L12),H12-L12,"")</f>
         <v>36522</v>
       </c>
-      <c r="O12" s="67"/>
+      <c r="O12" s="66"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
@@ -29735,7 +29729,7 @@
       <c r="C13" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="D13" s="66" t="n">
+      <c r="D13" s="65" t="n">
         <v>2004.589</v>
       </c>
       <c r="E13" s="10" t="n">
@@ -29762,7 +29756,7 @@
         <v>0.576979748987449</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H13/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H13/$H$54)</f>
         <v>0.0266686100403808</v>
       </c>
       <c r="L13" s="10" t="n">
@@ -29776,7 +29770,7 @@
         <f aca="false">IF(ISNUMBER(L13),H13-L13,"")</f>
         <v>0</v>
       </c>
-      <c r="O13" s="67" t="s">
+      <c r="O13" s="66" t="s">
         <v>219</v>
       </c>
     </row>
@@ -29784,13 +29778,13 @@
       <c r="A14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="64" t="s">
         <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="66" t="n">
+      <c r="D14" s="65" t="n">
         <v>3762</v>
       </c>
       <c r="E14" s="10" t="n">
@@ -29817,7 +29811,7 @@
         <v>-0.295580839070658</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H14/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H14/$H$54)</f>
         <v>0.0257737145528433</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -29831,7 +29825,7 @@
         <f aca="false">IF(ISNUMBER(L14),H14-L14,"")</f>
         <v>12713.24</v>
       </c>
-      <c r="O14" s="67" t="s">
+      <c r="O14" s="66" t="s">
         <v>220</v>
       </c>
     </row>
@@ -29839,13 +29833,13 @@
       <c r="A15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="64" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D15" s="66" t="n">
+      <c r="D15" s="65" t="n">
         <v>72</v>
       </c>
       <c r="E15" s="10" t="n">
@@ -29872,7 +29866,7 @@
         <v>-0.0616917160679743</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H15/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H15/$H$54)</f>
         <v>0.024078143931284</v>
       </c>
       <c r="L15" s="10" t="n">
@@ -29886,7 +29880,7 @@
         <f aca="false">IF(ISNUMBER(L15),H15-L15,"")</f>
         <v>2157.60000000004</v>
       </c>
-      <c r="O15" s="67" t="s">
+      <c r="O15" s="66" t="s">
         <v>221</v>
       </c>
     </row>
@@ -29894,13 +29888,13 @@
       <c r="A16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="64" t="s">
         <v>87</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D16" s="66" t="n">
+      <c r="D16" s="65" t="n">
         <v>66</v>
       </c>
       <c r="E16" s="10" t="n">
@@ -29927,7 +29921,7 @@
         <v>-0.189732777613411</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H16/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H16/$H$54)</f>
         <v>0.0238530785118798</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -29941,7 +29935,7 @@
         <f aca="false">IF(ISNUMBER(L16),H16-L16,"")</f>
         <v>5268</v>
       </c>
-      <c r="O16" s="67" t="s">
+      <c r="O16" s="66" t="s">
         <v>222</v>
       </c>
     </row>
@@ -29949,13 +29943,13 @@
       <c r="A17" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="64" t="s">
         <v>89</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D17" s="66" t="n">
+      <c r="D17" s="65" t="n">
         <v>800</v>
       </c>
       <c r="E17" s="10" t="n">
@@ -29982,7 +29976,7 @@
         <v>-0.00358899375249236</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H17/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H17/$H$54)</f>
         <v>0.0158465808522506</v>
       </c>
       <c r="L17" s="10" t="n">
@@ -29996,19 +29990,19 @@
         <f aca="false">IF(ISNUMBER(L17),H17-L17,"")</f>
         <v>12200</v>
       </c>
-      <c r="O17" s="67"/>
+      <c r="O17" s="66"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="64" t="s">
         <v>91</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D18" s="66" t="n">
+      <c r="D18" s="65" t="n">
         <v>3500</v>
       </c>
       <c r="E18" s="10" t="n">
@@ -30035,7 +30029,7 @@
         <v>0.535871767369801</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H18/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H18/$H$54)</f>
         <v>0.0152567734806154</v>
       </c>
       <c r="L18" s="10" t="n">
@@ -30049,7 +30043,7 @@
         <f aca="false">IF(ISNUMBER(L18),H18-L18,"")</f>
         <v>12670</v>
       </c>
-      <c r="O18" s="67"/>
+      <c r="O18" s="66"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
@@ -30061,7 +30055,7 @@
       <c r="C19" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D19" s="66" t="n">
+      <c r="D19" s="65" t="n">
         <v>134</v>
       </c>
       <c r="E19" s="10" t="n">
@@ -30088,7 +30082,7 @@
         <v>2.17762979596578</v>
       </c>
       <c r="K19" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H19/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H19/$H$54)</f>
         <v>0.0138805562801331</v>
       </c>
       <c r="L19" s="10" t="n">
@@ -30102,19 +30096,19 @@
         <f aca="false">IF(ISNUMBER(L19),H19-L19,"")</f>
         <v>5507</v>
       </c>
-      <c r="O19" s="67"/>
+      <c r="O19" s="66"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="64" t="s">
         <v>92</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D20" s="66" t="n">
+      <c r="D20" s="65" t="n">
         <v>32</v>
       </c>
       <c r="E20" s="10" t="n">
@@ -30141,7 +30135,7 @@
         <v>-0.420089508644651</v>
       </c>
       <c r="K20" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H20/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H20/$H$54)</f>
         <v>0.0104091572631697</v>
       </c>
       <c r="L20" s="10" t="n">
@@ -30155,7 +30149,7 @@
         <f aca="false">IF(ISNUMBER(L20),H20-L20,"")</f>
         <v>2627.60000000001</v>
       </c>
-      <c r="O20" s="67" t="s">
+      <c r="O20" s="66" t="s">
         <v>224</v>
       </c>
     </row>
@@ -30169,7 +30163,7 @@
       <c r="C21" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="66" t="n">
+      <c r="D21" s="65" t="n">
         <v>44</v>
       </c>
       <c r="E21" s="10" t="n">
@@ -30196,7 +30190,7 @@
         <v>0.553154257050411</v>
       </c>
       <c r="K21" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H21/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H21/$H$54)</f>
         <v>0.00685975992081621</v>
       </c>
       <c r="L21" s="10" t="n">
@@ -30210,7 +30204,7 @@
         <f aca="false">IF(ISNUMBER(L21),H21-L21,"")</f>
         <v>809.800000000003</v>
       </c>
-      <c r="O21" s="67"/>
+      <c r="O21" s="66"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
@@ -30222,7 +30216,7 @@
       <c r="C22" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D22" s="66" t="n">
+      <c r="D22" s="65" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="10" t="n">
@@ -30249,7 +30243,7 @@
         <v>0.390859232175503</v>
       </c>
       <c r="K22" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H22/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H22/$H$54)</f>
         <v>0.0064333397611485</v>
       </c>
       <c r="L22" s="10" t="n">
@@ -30263,7 +30257,7 @@
         <f aca="false">IF(ISNUMBER(L22),H22-L22,"")</f>
         <v>1680</v>
       </c>
-      <c r="O22" s="67"/>
+      <c r="O22" s="66"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
@@ -30275,7 +30269,7 @@
       <c r="C23" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D23" s="66" t="n">
+      <c r="D23" s="65" t="n">
         <v>64</v>
       </c>
       <c r="E23" s="10" t="n">
@@ -30302,7 +30296,7 @@
         <v>-0.282393886955338</v>
       </c>
       <c r="K23" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H23/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H23/$H$54)</f>
         <v>0.00624176017961776</v>
       </c>
       <c r="L23" s="10" t="n">
@@ -30316,19 +30310,19 @@
         <f aca="false">IF(ISNUMBER(L23),H23-L23,"")</f>
         <v>-425.600000000006</v>
       </c>
-      <c r="O23" s="67"/>
+      <c r="O23" s="66"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="64" t="s">
         <v>85</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="65" t="n">
         <v>29</v>
       </c>
       <c r="E24" s="10" t="n">
@@ -30355,7 +30349,7 @@
         <v>-0.258116823478988</v>
       </c>
       <c r="K24" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H24/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H24/$H$54)</f>
         <v>0.00614753475249043</v>
       </c>
       <c r="L24" s="10" t="n">
@@ -30369,7 +30363,7 @@
         <f aca="false">IF(ISNUMBER(L24),H24-L24,"")</f>
         <v>-1426.89999999999</v>
       </c>
-      <c r="O24" s="67"/>
+      <c r="O24" s="66"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
@@ -30381,7 +30375,7 @@
       <c r="C25" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D25" s="66" t="n">
+      <c r="D25" s="65" t="n">
         <v>160</v>
       </c>
       <c r="E25" s="10" t="n">
@@ -30408,7 +30402,7 @@
         <v>0.101085022283114</v>
       </c>
       <c r="K25" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H25/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H25/$H$54)</f>
         <v>0.00591244894978316</v>
       </c>
       <c r="L25" s="10" t="n">
@@ -30422,7 +30416,7 @@
         <f aca="false">IF(ISNUMBER(L25),H25-L25,"")</f>
         <v>622</v>
       </c>
-      <c r="O25" s="67" t="s">
+      <c r="O25" s="66" t="s">
         <v>227</v>
       </c>
     </row>
@@ -30436,7 +30430,7 @@
       <c r="C26" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D26" s="66" t="n">
+      <c r="D26" s="65" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="10" t="n">
@@ -30463,7 +30457,7 @@
         <v>-0.263927643606273</v>
       </c>
       <c r="K26" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H26/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H26/$H$54)</f>
         <v>0.00582196953936743</v>
       </c>
       <c r="L26" s="10" t="n">
@@ -30477,19 +30471,19 @@
         <f aca="false">IF(ISNUMBER(L26),H26-L26,"")</f>
         <v>1200</v>
       </c>
-      <c r="O26" s="67"/>
+      <c r="O26" s="66"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="64" t="s">
         <v>94</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D27" s="66" t="n">
+      <c r="D27" s="65" t="n">
         <v>47</v>
       </c>
       <c r="E27" s="10" t="n">
@@ -30516,7 +30510,7 @@
         <v>-0.1678260078733</v>
       </c>
       <c r="K27" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H27/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H27/$H$54)</f>
         <v>0.00541621589176103</v>
       </c>
       <c r="L27" s="10" t="n">
@@ -30530,7 +30524,7 @@
         <f aca="false">IF(ISNUMBER(L27),H27-L27,"")</f>
         <v>1797.6</v>
       </c>
-      <c r="O27" s="67" t="s">
+      <c r="O27" s="66" t="s">
         <v>228</v>
       </c>
     </row>
@@ -30538,13 +30532,13 @@
       <c r="A28" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="64" t="s">
         <v>93</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D28" s="66" t="n">
+      <c r="D28" s="65" t="n">
         <v>11</v>
       </c>
       <c r="E28" s="10" t="n">
@@ -30571,7 +30565,7 @@
         <v>0.267396583907031</v>
       </c>
       <c r="K28" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H28/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H28/$H$54)</f>
         <v>0.00533959589757627</v>
       </c>
       <c r="L28" s="10" t="n">
@@ -30585,7 +30579,7 @@
         <f aca="false">IF(ISNUMBER(L28),H28-L28,"")</f>
         <v>-502.5</v>
       </c>
-      <c r="O28" s="67" t="s">
+      <c r="O28" s="66" t="s">
         <v>229</v>
       </c>
     </row>
@@ -30599,7 +30593,7 @@
       <c r="C29" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D29" s="66" t="n">
+      <c r="D29" s="65" t="n">
         <v>22</v>
       </c>
       <c r="E29" s="10" t="n">
@@ -30626,7 +30620,7 @@
         <v>-0.36004074097651</v>
       </c>
       <c r="K29" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H29/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H29/$H$54)</f>
         <v>0.00425046902074114</v>
       </c>
       <c r="L29" s="10" t="n">
@@ -30640,19 +30634,19 @@
         <f aca="false">IF(ISNUMBER(L29),H29-L29,"")</f>
         <v>219.600000000006</v>
       </c>
-      <c r="O29" s="67"/>
+      <c r="O29" s="66"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="64" t="s">
         <v>96</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="66" t="n">
+      <c r="D30" s="65" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="10" t="n">
@@ -30679,7 +30673,7 @@
         <v>-0.0283448007863396</v>
       </c>
       <c r="K30" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H30/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H30/$H$54)</f>
         <v>0.00359440027901077</v>
       </c>
       <c r="L30" s="10" t="n">
@@ -30693,7 +30687,7 @@
         <f aca="false">IF(ISNUMBER(L30),H30-L30,"")</f>
         <v>747</v>
       </c>
-      <c r="O30" s="67" t="s">
+      <c r="O30" s="66" t="s">
         <v>230</v>
       </c>
     </row>
@@ -30707,7 +30701,7 @@
       <c r="C31" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D31" s="66" t="n">
+      <c r="D31" s="65" t="n">
         <v>32</v>
       </c>
       <c r="E31" s="10" t="n">
@@ -30734,7 +30728,7 @@
         <v>-0.0189206677882749</v>
       </c>
       <c r="K31" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H31/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H31/$H$54)</f>
         <v>0.00320516969382982</v>
       </c>
       <c r="L31" s="10" t="n">
@@ -30748,7 +30742,7 @@
         <f aca="false">IF(ISNUMBER(L31),H31-L31,"")</f>
         <v>378</v>
       </c>
-      <c r="O31" s="67"/>
+      <c r="O31" s="66"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
@@ -30760,7 +30754,7 @@
       <c r="C32" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D32" s="66" t="n">
+      <c r="D32" s="65" t="n">
         <v>34</v>
       </c>
       <c r="E32" s="10" t="n">
@@ -30787,7 +30781,7 @@
         <v>0.998190712323259</v>
       </c>
       <c r="K32" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H32/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H32/$H$54)</f>
         <v>0.00252150050391282</v>
       </c>
       <c r="L32" s="10" t="n">
@@ -30801,19 +30795,19 @@
         <f aca="false">IF(ISNUMBER(L32),H32-L32,"")</f>
         <v>0</v>
       </c>
-      <c r="O32" s="67"/>
+      <c r="O32" s="66"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="64" t="s">
         <v>100</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="66" t="n">
+      <c r="D33" s="65" t="n">
         <v>10</v>
       </c>
       <c r="E33" s="10" t="n">
@@ -30840,7 +30834,7 @@
         <v>-0.0909745873722819</v>
       </c>
       <c r="K33" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H33/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H33/$H$54)</f>
         <v>0.00234722193861672</v>
       </c>
       <c r="L33" s="10" t="n">
@@ -30854,7 +30848,7 @@
         <f aca="false">IF(ISNUMBER(L33),H33-L33,"")</f>
         <v>628</v>
       </c>
-      <c r="O33" s="67" t="s">
+      <c r="O33" s="66" t="s">
         <v>231</v>
       </c>
     </row>
@@ -30862,13 +30856,13 @@
       <c r="A34" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="64" t="s">
         <v>118</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D34" s="66" t="n">
+      <c r="D34" s="65" t="n">
         <v>168</v>
       </c>
       <c r="E34" s="10" t="n">
@@ -30895,7 +30889,7 @@
         <v>0.389605314576006</v>
       </c>
       <c r="K34" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H34/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H34/$H$54)</f>
         <v>0.00180417635572903</v>
       </c>
       <c r="L34" s="10" t="n">
@@ -30909,7 +30903,7 @@
         <f aca="false">IF(ISNUMBER(L34),H34-L34,"")</f>
         <v>1205</v>
       </c>
-      <c r="O34" s="67" t="s">
+      <c r="O34" s="66" t="s">
         <v>232</v>
       </c>
     </row>
@@ -30923,7 +30917,7 @@
       <c r="C35" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D35" s="66" t="n">
+      <c r="D35" s="65" t="n">
         <v>33</v>
       </c>
       <c r="E35" s="10" t="n">
@@ -30950,7 +30944,7 @@
         <v>-0.527538052312694</v>
       </c>
       <c r="K35" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H35/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H35/$H$54)</f>
         <v>0.00162210979632144</v>
       </c>
       <c r="L35" s="10" t="n">
@@ -30964,19 +30958,19 @@
         <f aca="false">IF(ISNUMBER(L35),H35-L35,"")</f>
         <v>572.899999999998</v>
       </c>
-      <c r="O35" s="67"/>
+      <c r="O35" s="66"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="64" t="s">
         <v>102</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D36" s="66" t="n">
+      <c r="D36" s="65" t="n">
         <v>6</v>
       </c>
       <c r="E36" s="10" t="n">
@@ -31003,7 +30997,7 @@
         <v>-0.196344713796167</v>
       </c>
       <c r="K36" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H36/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H36/$H$54)</f>
         <v>0.00160630549556752</v>
       </c>
       <c r="L36" s="10" t="n">
@@ -31017,7 +31011,7 @@
         <f aca="false">IF(ISNUMBER(L36),H36-L36,"")</f>
         <v>238</v>
       </c>
-      <c r="O36" s="67" t="s">
+      <c r="O36" s="66" t="s">
         <v>233</v>
       </c>
     </row>
@@ -31025,13 +31019,13 @@
       <c r="A37" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="64" t="s">
         <v>101</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D37" s="66" t="n">
+      <c r="D37" s="65" t="n">
         <v>17</v>
       </c>
       <c r="E37" s="10" t="n">
@@ -31058,7 +31052,7 @@
         <v>-0.376025459688826</v>
       </c>
       <c r="K37" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H37/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H37/$H$54)</f>
         <v>0.00156675669159421</v>
       </c>
       <c r="L37" s="10" t="n">
@@ -31072,7 +31066,7 @@
         <f aca="false">IF(ISNUMBER(L37),H37-L37,"")</f>
         <v>386.300000000003</v>
       </c>
-      <c r="O37" s="67" t="s">
+      <c r="O37" s="66" t="s">
         <v>234</v>
       </c>
     </row>
@@ -31080,13 +31074,13 @@
       <c r="A38" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="64" t="s">
         <v>105</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="66" t="n">
+      <c r="D38" s="65" t="n">
         <v>6</v>
       </c>
       <c r="E38" s="10" t="n">
@@ -31113,7 +31107,7 @@
         <v>-0.249445793307294</v>
       </c>
       <c r="K38" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H38/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H38/$H$54)</f>
         <v>0.00120244599636608</v>
       </c>
       <c r="L38" s="10" t="n">
@@ -31127,7 +31121,7 @@
         <f aca="false">IF(ISNUMBER(L38),H38-L38,"")</f>
         <v>320</v>
       </c>
-      <c r="O38" s="67" t="s">
+      <c r="O38" s="66" t="s">
         <v>233</v>
       </c>
     </row>
@@ -31141,7 +31135,7 @@
       <c r="C39" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D39" s="66" t="n">
+      <c r="D39" s="65" t="n">
         <v>50</v>
       </c>
       <c r="E39" s="10" t="n">
@@ -31168,7 +31162,7 @@
         <v>-0.0454447786850022</v>
       </c>
       <c r="K39" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H39/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H39/$H$54)</f>
         <v>0.00112697602085576</v>
       </c>
       <c r="L39" s="10" t="n">
@@ -31182,7 +31176,7 @@
         <f aca="false">IF(ISNUMBER(L39),H39-L39,"")</f>
         <v>659.5</v>
       </c>
-      <c r="O39" s="67"/>
+      <c r="O39" s="66"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="n">
@@ -31194,7 +31188,7 @@
       <c r="C40" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D40" s="66" t="n">
+      <c r="D40" s="65" t="n">
         <v>35</v>
       </c>
       <c r="E40" s="10" t="n">
@@ -31221,7 +31215,7 @@
         <v>-0.440593310125624</v>
       </c>
       <c r="K40" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H40/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H40/$H$54)</f>
         <v>0.000937603460457604</v>
       </c>
       <c r="L40" s="10" t="n">
@@ -31235,7 +31229,7 @@
         <f aca="false">IF(ISNUMBER(L40),H40-L40,"")</f>
         <v>341</v>
       </c>
-      <c r="O40" s="67"/>
+      <c r="O40" s="66"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="n">
@@ -31247,7 +31241,7 @@
       <c r="C41" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D41" s="66" t="n">
+      <c r="D41" s="65" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="10" t="n">
@@ -31274,7 +31268,7 @@
         <v>-0.525907650520598</v>
       </c>
       <c r="K41" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H41/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H41/$H$54)</f>
         <v>0.000885573571458726</v>
       </c>
       <c r="L41" s="10" t="n">
@@ -31288,7 +31282,7 @@
         <f aca="false">IF(ISNUMBER(L41),H41-L41,"")</f>
         <v>304.699999999999</v>
       </c>
-      <c r="O41" s="67"/>
+      <c r="O41" s="66"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
@@ -31300,7 +31294,7 @@
       <c r="C42" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D42" s="66" t="n">
+      <c r="D42" s="65" t="n">
         <v>34</v>
       </c>
       <c r="E42" s="10" t="n">
@@ -31327,7 +31321,7 @@
         <v>0.00148026315789467</v>
       </c>
       <c r="K42" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H42/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H42/$H$54)</f>
         <v>0.000875307963585389</v>
       </c>
       <c r="L42" s="10" t="n">
@@ -31341,7 +31335,7 @@
         <f aca="false">IF(ISNUMBER(L42),H42-L42,"")</f>
         <v>-59.7000000000007</v>
       </c>
-      <c r="O42" s="67" t="s">
+      <c r="O42" s="66" t="s">
         <v>236</v>
       </c>
     </row>
@@ -31355,7 +31349,7 @@
       <c r="C43" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D43" s="66" t="n">
+      <c r="D43" s="65" t="n">
         <v>32</v>
       </c>
       <c r="E43" s="10" t="n">
@@ -31382,7 +31376,7 @@
         <v>1.07174447174447</v>
       </c>
       <c r="K43" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H43/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H43/$H$54)</f>
         <v>0.000570409262523703</v>
       </c>
       <c r="L43" s="10" t="n">
@@ -31396,7 +31390,7 @@
         <f aca="false">IF(ISNUMBER(L43),H43-L43,"")</f>
         <v>189.6</v>
       </c>
-      <c r="O43" s="67"/>
+      <c r="O43" s="66"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
@@ -31408,7 +31402,7 @@
       <c r="C44" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D44" s="66" t="n">
+      <c r="D44" s="65" t="n">
         <v>3</v>
       </c>
       <c r="E44" s="10" t="n">
@@ -31435,7 +31429,7 @@
         <v>-0.585251886103675</v>
       </c>
       <c r="K44" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H44/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H44/$H$54)</f>
         <v>0.000432322461393899</v>
       </c>
       <c r="L44" s="10" t="n">
@@ -31449,7 +31443,7 @@
         <f aca="false">IF(ISNUMBER(L44),H44-L44,"")</f>
         <v>247.6</v>
       </c>
-      <c r="O44" s="67"/>
+      <c r="O44" s="66"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
@@ -31461,7 +31455,7 @@
       <c r="C45" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D45" s="66" t="n">
+      <c r="D45" s="65" t="n">
         <v>4</v>
       </c>
       <c r="E45" s="10" t="n">
@@ -31488,7 +31482,7 @@
         <v>-0.28044612340349</v>
       </c>
       <c r="K45" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H45/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H45/$H$54)</f>
         <v>0.000338240786600867</v>
       </c>
       <c r="L45" s="10" t="n">
@@ -31502,7 +31496,7 @@
         <f aca="false">IF(ISNUMBER(L45),H45-L45,"")</f>
         <v>-1559</v>
       </c>
-      <c r="O45" s="67" t="s">
+      <c r="O45" s="66" t="s">
         <v>237</v>
       </c>
     </row>
@@ -31510,13 +31504,13 @@
       <c r="A46" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="64" t="s">
         <v>104</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D46" s="66" t="n">
+      <c r="D46" s="65" t="n">
         <v>5</v>
       </c>
       <c r="E46" s="10" t="n">
@@ -31543,7 +31537,7 @@
         <v>0.187971058185107</v>
       </c>
       <c r="K46" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H46/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H46/$H$54)</f>
         <v>0.000333209454900179</v>
       </c>
       <c r="L46" s="10" t="n">
@@ -31557,7 +31551,7 @@
         <f aca="false">IF(ISNUMBER(L46),H46-L46,"")</f>
         <v>125.5</v>
       </c>
-      <c r="O46" s="67"/>
+      <c r="O46" s="66"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
@@ -31569,7 +31563,7 @@
       <c r="C47" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D47" s="66" t="n">
+      <c r="D47" s="65" t="n">
         <v>5</v>
       </c>
       <c r="E47" s="10" t="n">
@@ -31596,7 +31590,7 @@
         <v>0.10887573964497</v>
       </c>
       <c r="K47" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H47/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H47/$H$54)</f>
         <v>0.000316931617045013</v>
       </c>
       <c r="L47" s="10" t="n">
@@ -31610,7 +31604,7 @@
         <f aca="false">IF(ISNUMBER(L47),H47-L47,"")</f>
         <v>142</v>
       </c>
-      <c r="O47" s="67"/>
+      <c r="O47" s="66"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
@@ -31622,7 +31616,7 @@
       <c r="C48" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D48" s="66" t="n">
+      <c r="D48" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="10" t="n">
@@ -31649,7 +31643,7 @@
         <v>-0.395559560871702</v>
       </c>
       <c r="K48" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H48/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H48/$H$54)</f>
         <v>0.000311934109422985</v>
       </c>
       <c r="L48" s="10" t="n">
@@ -31663,7 +31657,7 @@
         <f aca="false">IF(ISNUMBER(L48),H48-L48,"")</f>
         <v>87.9000000000001</v>
       </c>
-      <c r="O48" s="67"/>
+      <c r="O48" s="66"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
@@ -31675,7 +31669,7 @@
       <c r="C49" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D49" s="66" t="n">
+      <c r="D49" s="65" t="n">
         <v>5</v>
       </c>
       <c r="E49" s="10" t="n">
@@ -31702,7 +31696,7 @@
         <v>-0.295837414299706</v>
       </c>
       <c r="K49" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H49/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H49/$H$54)</f>
         <v>0.000303972766908367</v>
       </c>
       <c r="L49" s="10" t="n">
@@ -31716,7 +31710,7 @@
         <f aca="false">IF(ISNUMBER(L49),H49-L49,"")</f>
         <v>196.75</v>
       </c>
-      <c r="O49" s="67" t="s">
+      <c r="O49" s="66" t="s">
         <v>238</v>
       </c>
     </row>
@@ -31730,7 +31724,7 @@
       <c r="C50" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D50" s="66" t="n">
+      <c r="D50" s="65" t="n">
         <v>6</v>
       </c>
       <c r="E50" s="10" t="n">
@@ -31757,7 +31751,7 @@
         <v>-0.394824840764331</v>
       </c>
       <c r="K50" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H50/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H50/$H$54)</f>
         <v>0.000192822616421489</v>
       </c>
       <c r="L50" s="10" t="n">
@@ -31771,7 +31765,7 @@
         <f aca="false">IF(ISNUMBER(L50),H50-L50,"")</f>
         <v>39.3000000000002</v>
       </c>
-      <c r="O50" s="67"/>
+      <c r="O50" s="66"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="n">
@@ -31783,7 +31777,7 @@
       <c r="C51" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D51" s="66" t="n">
+      <c r="D51" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E51" s="10" t="n">
@@ -31810,7 +31804,7 @@
         <v>-0.378437108232344</v>
       </c>
       <c r="K51" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H51/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H51/$H$54)</f>
         <v>0.000125774836497533</v>
       </c>
       <c r="L51" s="10" t="n">
@@ -31824,7 +31818,7 @@
         <f aca="false">IF(ISNUMBER(L51),H51-L51,"")</f>
         <v>60.4000000000001</v>
       </c>
-      <c r="O51" s="67"/>
+      <c r="O51" s="66"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
@@ -31836,7 +31830,7 @@
       <c r="C52" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D52" s="66" t="n">
+      <c r="D52" s="65" t="n">
         <v>12</v>
       </c>
       <c r="E52" s="10" t="n">
@@ -31863,7 +31857,7 @@
         <v>-0.448275862068966</v>
       </c>
       <c r="K52" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H52/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H52/$H$54)</f>
         <v>0.000105531125419471</v>
       </c>
       <c r="L52" s="10" t="n">
@@ -31877,7 +31871,7 @@
         <f aca="false">IF(ISNUMBER(L52),H52-L52,"")</f>
         <v>39</v>
       </c>
-      <c r="O52" s="67"/>
+      <c r="O52" s="66"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="n">
@@ -31889,7 +31883,7 @@
       <c r="C53" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D53" s="66" t="n">
+      <c r="D53" s="65" t="n">
         <v>5</v>
       </c>
       <c r="E53" s="10" t="n">
@@ -31916,7 +31910,7 @@
         <v>-0.418988095238095</v>
       </c>
       <c r="K53" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H53/$H$6)</f>
+        <f aca="false">IF($H$54=0,"",H53/$H$54)</f>
         <v>8.25392079502766E-005</v>
       </c>
       <c r="L53" s="10" t="n">
@@ -31930,7 +31924,38 @@
         <f aca="false">IF(ISNUMBER(L53),H53-L53,"")</f>
         <v>40.1</v>
       </c>
-      <c r="O53" s="67"/>
+      <c r="O53" s="66"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="81"/>
+      <c r="B54" s="81" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="81"/>
+      <c r="D54" s="81"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="82" t="n">
+        <f aca="false">SUM(H7:H53)</f>
+        <v>11825894.92</v>
+      </c>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="83" t="n">
+        <f aca="false">SUM(K7:K53)</f>
+        <v>1</v>
+      </c>
+      <c r="L54" s="82" t="n">
+        <f aca="false">SUM(L7:L53)</f>
+        <v>11636414.18</v>
+      </c>
+      <c r="M54" s="81"/>
+      <c r="N54" s="82" t="n">
+        <f aca="false">SUM(N7:N53)</f>
+        <v>189480.74</v>
+      </c>
+      <c r="O54" s="81"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G7:G300">
@@ -31951,6 +31976,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF27AE60"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:V46"/>
@@ -31994,95 +32020,57 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="N5" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>194</v>
-      </c>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="31" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="81" t="n">
-        <f aca="false">SUM(E7:E31)</f>
-        <v>11739506</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="81" t="n">
-        <f aca="false">SUM(H7:H31)</f>
-        <v>11909700.84</v>
-      </c>
-      <c r="I6" s="81" t="n">
-        <f aca="false">H6-E6</f>
-        <v>170194.84</v>
-      </c>
-      <c r="J6" s="82" t="n">
-        <f aca="false">IF(E6&gt;0,I6/E6,"")</f>
-        <v>0.014497615146668</v>
-      </c>
-      <c r="K6" s="82" t="n">
-        <f aca="false">SUM(K7:K31)</f>
-        <v>1</v>
-      </c>
-      <c r="L6" s="81" t="n">
-        <f aca="false">SUM(L7:L31)</f>
-        <v>2974667</v>
-      </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="81" t="n">
-        <f aca="false">SUM(N7:N31)</f>
-        <v>-61301.5</v>
-      </c>
-      <c r="O6" s="12"/>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>195</v>
+      </c>
       <c r="Q6" s="24" t="s">
         <v>196</v>
       </c>
@@ -32106,13 +32094,13 @@
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="64" t="s">
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="65" t="n">
         <v>4940</v>
       </c>
       <c r="E7" s="10" t="n">
@@ -32139,7 +32127,7 @@
         <v>0.000644165592698998</v>
       </c>
       <c r="K7" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H7/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H7/$H$32)</f>
         <v>0.390771696327512</v>
       </c>
       <c r="L7" s="10"/>
@@ -32151,19 +32139,19 @@
         <f aca="false">IF(ISNUMBER(L7),H7-L7,"")</f>
         <v/>
       </c>
-      <c r="O7" s="67" t="s">
+      <c r="O7" s="66" t="s">
         <v>241</v>
       </c>
-      <c r="Q7" s="68" t="s">
+      <c r="Q7" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="R7" s="68" t="s">
+      <c r="R7" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="S7" s="68" t="s">
+      <c r="S7" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="T7" s="68" t="n">
+      <c r="T7" s="67" t="n">
         <v>1580</v>
       </c>
       <c r="U7" s="63" t="n">
@@ -32177,13 +32165,13 @@
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="64" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="65" t="n">
         <v>250</v>
       </c>
       <c r="E8" s="10" t="n">
@@ -32210,7 +32198,7 @@
         <v>0.0145091128572588</v>
       </c>
       <c r="K8" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H8/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H8/$H$32)</f>
         <v>0.0913121172907648</v>
       </c>
       <c r="L8" s="10"/>
@@ -32222,19 +32210,19 @@
         <f aca="false">IF(ISNUMBER(L8),H8-L8,"")</f>
         <v/>
       </c>
-      <c r="O8" s="67" t="s">
+      <c r="O8" s="66" t="s">
         <v>243</v>
       </c>
-      <c r="Q8" s="68" t="s">
+      <c r="Q8" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="R8" s="68" t="s">
+      <c r="R8" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S8" s="68" t="s">
+      <c r="S8" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="T8" s="68" t="n">
+      <c r="T8" s="67" t="n">
         <v>547</v>
       </c>
       <c r="U8" s="63" t="n">
@@ -32248,13 +32236,13 @@
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="64" t="s">
         <v>82</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="66" t="n">
+      <c r="D9" s="65" t="n">
         <v>1918</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -32281,7 +32269,7 @@
         <v>0.00583182760753305</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H9/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H9/$H$32)</f>
         <v>0.0696439911583875</v>
       </c>
       <c r="L9" s="10"/>
@@ -32293,19 +32281,19 @@
         <f aca="false">IF(ISNUMBER(L9),H9-L9,"")</f>
         <v/>
       </c>
-      <c r="O9" s="67" t="s">
+      <c r="O9" s="66" t="s">
         <v>244</v>
       </c>
-      <c r="Q9" s="68" t="s">
+      <c r="Q9" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="R9" s="68" t="s">
+      <c r="R9" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S9" s="68" t="s">
+      <c r="S9" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="T9" s="68" t="n">
+      <c r="T9" s="67" t="n">
         <v>9</v>
       </c>
       <c r="U9" s="63" t="n">
@@ -32325,7 +32313,7 @@
       <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="66" t="n">
+      <c r="D10" s="65" t="n">
         <v>2000</v>
       </c>
       <c r="E10" s="10" t="n">
@@ -32352,7 +32340,7 @@
         <v>-0.0419969241689341</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H10/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H10/$H$32)</f>
         <v>0.0679949908800564</v>
       </c>
       <c r="L10" s="10" t="n">
@@ -32366,17 +32354,17 @@
         <f aca="false">IF(ISNUMBER(L10),H10-L10,"")</f>
         <v>-17200</v>
       </c>
-      <c r="O10" s="67"/>
-      <c r="Q10" s="68" t="s">
+      <c r="O10" s="66"/>
+      <c r="Q10" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="R10" s="68" t="s">
+      <c r="R10" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S10" s="68" t="s">
+      <c r="S10" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="T10" s="68" t="n">
+      <c r="T10" s="67" t="n">
         <v>79</v>
       </c>
       <c r="U10" s="63" t="n">
@@ -32390,13 +32378,13 @@
       <c r="A11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="64" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="65" t="n">
         <v>1140</v>
       </c>
       <c r="E11" s="10" t="n">
@@ -32423,7 +32411,7 @@
         <v>-0.0972891875549065</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H11/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H11/$H$32)</f>
         <v>0.0664346662128249</v>
       </c>
       <c r="L11" s="10"/>
@@ -32435,19 +32423,19 @@
         <f aca="false">IF(ISNUMBER(L11),H11-L11,"")</f>
         <v/>
       </c>
-      <c r="O11" s="67" t="s">
+      <c r="O11" s="66" t="s">
         <v>245</v>
       </c>
-      <c r="Q11" s="68" t="s">
+      <c r="Q11" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="R11" s="68" t="s">
+      <c r="R11" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S11" s="68" t="s">
+      <c r="S11" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="T11" s="68" t="n">
+      <c r="T11" s="67" t="n">
         <v>970</v>
       </c>
       <c r="U11" s="63" t="n">
@@ -32461,13 +32449,13 @@
       <c r="A12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="64" t="s">
         <v>85</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="66" t="n">
+      <c r="D12" s="65" t="n">
         <v>305</v>
       </c>
       <c r="E12" s="10" t="n">
@@ -32494,7 +32482,7 @@
         <v>0.159528214616096</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H12/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H12/$H$32)</f>
         <v>0.0642001432506175</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -32508,17 +32496,17 @@
         <f aca="false">IF(ISNUMBER(L12),H12-L12,"")</f>
         <v>14029.5</v>
       </c>
-      <c r="O12" s="67"/>
-      <c r="Q12" s="68" t="s">
+      <c r="O12" s="66"/>
+      <c r="Q12" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="R12" s="68" t="s">
+      <c r="R12" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="S12" s="68" t="s">
+      <c r="S12" s="67" t="s">
         <v>246</v>
       </c>
-      <c r="T12" s="68" t="n">
+      <c r="T12" s="67" t="n">
         <v>700</v>
       </c>
       <c r="U12" s="63" t="n">
@@ -32532,13 +32520,13 @@
       <c r="A13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="64" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="66" t="n">
+      <c r="D13" s="65" t="n">
         <v>360</v>
       </c>
       <c r="E13" s="10" t="n">
@@ -32565,7 +32553,7 @@
         <v>0.367347956131605</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H13/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H13/$H$32)</f>
         <v>0.0414554493545112</v>
       </c>
       <c r="L13" s="10" t="n">
@@ -32579,17 +32567,17 @@
         <f aca="false">IF(ISNUMBER(L13),H13-L13,"")</f>
         <v>-43020</v>
       </c>
-      <c r="O13" s="67"/>
-      <c r="Q13" s="68" t="s">
+      <c r="O13" s="66"/>
+      <c r="Q13" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="R13" s="68" t="s">
+      <c r="R13" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S13" s="68" t="s">
+      <c r="S13" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="T13" s="68" t="n">
+      <c r="T13" s="67" t="n">
         <v>362</v>
       </c>
       <c r="U13" s="63" t="n">
@@ -32603,13 +32591,13 @@
       <c r="A14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="64" t="s">
         <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="66" t="n">
+      <c r="D14" s="65" t="n">
         <v>83</v>
       </c>
       <c r="E14" s="10" t="n">
@@ -32636,7 +32624,7 @@
         <v>0.0964868356793581</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H14/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H14/$H$32)</f>
         <v>0.0297859706776648</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -32650,17 +32638,17 @@
         <f aca="false">IF(ISNUMBER(L14),H14-L14,"")</f>
         <v>755</v>
       </c>
-      <c r="O14" s="67"/>
-      <c r="Q14" s="68" t="s">
+      <c r="O14" s="66"/>
+      <c r="Q14" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="R14" s="68" t="s">
+      <c r="R14" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S14" s="68" t="s">
+      <c r="S14" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="T14" s="68" t="n">
+      <c r="T14" s="67" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="63" t="n">
@@ -32674,13 +32662,13 @@
       <c r="A15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="64" t="s">
         <v>86</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="66" t="n">
+      <c r="D15" s="65" t="n">
         <v>4227</v>
       </c>
       <c r="E15" s="10" t="n">
@@ -32707,7 +32695,7 @@
         <v>-0.0488962391481846</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H15/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H15/$H$32)</f>
         <v>0.028755679475153</v>
       </c>
       <c r="L15" s="10"/>
@@ -32719,19 +32707,19 @@
         <f aca="false">IF(ISNUMBER(L15),H15-L15,"")</f>
         <v/>
       </c>
-      <c r="O15" s="67" t="s">
+      <c r="O15" s="66" t="s">
         <v>248</v>
       </c>
-      <c r="Q15" s="68" t="s">
+      <c r="Q15" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="R15" s="68" t="s">
+      <c r="R15" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S15" s="68" t="s">
+      <c r="S15" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="T15" s="68" t="n">
+      <c r="T15" s="67" t="n">
         <v>6</v>
       </c>
       <c r="U15" s="63" t="n">
@@ -32745,13 +32733,13 @@
       <c r="A16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="64" t="s">
         <v>88</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="66" t="n">
+      <c r="D16" s="65" t="n">
         <v>78</v>
       </c>
       <c r="E16" s="10" t="n">
@@ -32778,7 +32766,7 @@
         <v>0.144430593891906</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H16/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H16/$H$32)</f>
         <v>0.0259011039944812</v>
       </c>
       <c r="L16" s="10"/>
@@ -32790,19 +32778,19 @@
         <f aca="false">IF(ISNUMBER(L16),H16-L16,"")</f>
         <v/>
       </c>
-      <c r="O16" s="67" t="s">
+      <c r="O16" s="66" t="s">
         <v>249</v>
       </c>
-      <c r="Q16" s="68" t="s">
+      <c r="Q16" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="R16" s="68" t="s">
+      <c r="R16" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S16" s="68" t="s">
+      <c r="S16" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="T16" s="68" t="n">
+      <c r="T16" s="67" t="n">
         <v>1</v>
       </c>
       <c r="U16" s="63" t="n">
@@ -32822,7 +32810,7 @@
       <c r="C17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="66" t="n">
+      <c r="D17" s="65" t="n">
         <v>700</v>
       </c>
       <c r="E17" s="10" t="n">
@@ -32849,7 +32837,7 @@
         <v>-0.113442353183174</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H17/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H17/$H$32)</f>
         <v>0.0253322903785046</v>
       </c>
       <c r="L17" s="10" t="n">
@@ -32863,17 +32851,17 @@
         <f aca="false">IF(ISNUMBER(L17),H17-L17,"")</f>
         <v>-4900</v>
       </c>
-      <c r="O17" s="67"/>
-      <c r="Q17" s="68" t="s">
+      <c r="O17" s="66"/>
+      <c r="Q17" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="R17" s="68" t="s">
+      <c r="R17" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S17" s="68" t="s">
+      <c r="S17" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="T17" s="68" t="n">
+      <c r="T17" s="67" t="n">
         <v>5</v>
       </c>
       <c r="U17" s="63" t="n">
@@ -32887,13 +32875,13 @@
       <c r="A18" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="64" t="s">
         <v>91</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="66" t="n">
+      <c r="D18" s="65" t="n">
         <v>5141</v>
       </c>
       <c r="E18" s="10" t="n">
@@ -32920,7 +32908,7 @@
         <v>0.178803264834089</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H18/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H18/$H$32)</f>
         <v>0.0222523263648997</v>
       </c>
       <c r="L18" s="10"/>
@@ -32932,19 +32920,19 @@
         <f aca="false">IF(ISNUMBER(L18),H18-L18,"")</f>
         <v/>
       </c>
-      <c r="O18" s="67" t="s">
+      <c r="O18" s="66" t="s">
         <v>250</v>
       </c>
-      <c r="Q18" s="68" t="s">
+      <c r="Q18" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="R18" s="68" t="s">
+      <c r="R18" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S18" s="68" t="s">
+      <c r="S18" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="T18" s="68" t="n">
+      <c r="T18" s="67" t="n">
         <v>8</v>
       </c>
       <c r="U18" s="63" t="n">
@@ -32958,13 +32946,13 @@
       <c r="A19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="64" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="66" t="n">
+      <c r="D19" s="65" t="n">
         <v>65</v>
       </c>
       <c r="E19" s="10" t="n">
@@ -32991,7 +32979,7 @@
         <v>-0.0458597267801267</v>
       </c>
       <c r="K19" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H19/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H19/$H$32)</f>
         <v>0.0209948178681539</v>
       </c>
       <c r="L19" s="10"/>
@@ -33003,19 +32991,19 @@
         <f aca="false">IF(ISNUMBER(L19),H19-L19,"")</f>
         <v/>
       </c>
-      <c r="O19" s="67" t="s">
+      <c r="O19" s="66" t="s">
         <v>251</v>
       </c>
-      <c r="Q19" s="68" t="s">
+      <c r="Q19" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="R19" s="68" t="s">
+      <c r="R19" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S19" s="68" t="s">
+      <c r="S19" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="T19" s="68" t="n">
+      <c r="T19" s="67" t="n">
         <v>4</v>
       </c>
       <c r="U19" s="63" t="n">
@@ -33029,13 +33017,13 @@
       <c r="A20" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="64" t="s">
         <v>89</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="66" t="n">
+      <c r="D20" s="65" t="n">
         <v>800</v>
       </c>
       <c r="E20" s="10" t="n">
@@ -33062,7 +33050,7 @@
         <v>0.101057579318449</v>
       </c>
       <c r="K20" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H20/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H20/$H$32)</f>
         <v>0.0157350719818752</v>
       </c>
       <c r="L20" s="10" t="n">
@@ -33076,17 +33064,17 @@
         <f aca="false">IF(ISNUMBER(L20),H20-L20,"")</f>
         <v>-11000</v>
       </c>
-      <c r="O20" s="67"/>
-      <c r="Q20" s="68" t="s">
+      <c r="O20" s="66"/>
+      <c r="Q20" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="R20" s="68" t="s">
+      <c r="R20" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S20" s="68" t="s">
+      <c r="S20" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="T20" s="68" t="n">
+      <c r="T20" s="67" t="n">
         <v>4</v>
       </c>
       <c r="U20" s="63" t="n">
@@ -33100,13 +33088,13 @@
       <c r="A21" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="64" t="s">
         <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="66" t="n">
+      <c r="D21" s="65" t="n">
         <v>78</v>
       </c>
       <c r="E21" s="10" t="n">
@@ -33133,7 +33121,7 @@
         <v>-0.0718485597282737</v>
       </c>
       <c r="K21" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H21/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H21/$H$32)</f>
         <v>0.0089253627297661</v>
       </c>
       <c r="L21" s="10"/>
@@ -33145,19 +33133,19 @@
         <f aca="false">IF(ISNUMBER(L21),H21-L21,"")</f>
         <v/>
       </c>
-      <c r="O21" s="67" t="s">
+      <c r="O21" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="Q21" s="68" t="s">
+      <c r="Q21" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="R21" s="68" t="s">
+      <c r="R21" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S21" s="68" t="s">
+      <c r="S21" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="T21" s="68" t="n">
+      <c r="T21" s="67" t="n">
         <v>10</v>
       </c>
       <c r="U21" s="63" t="n">
@@ -33171,13 +33159,13 @@
       <c r="A22" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="64" t="s">
         <v>93</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="66" t="n">
+      <c r="D22" s="65" t="n">
         <v>13</v>
       </c>
       <c r="E22" s="10" t="n">
@@ -33204,7 +33192,7 @@
         <v>0.0893425393396199</v>
       </c>
       <c r="K22" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H22/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H22/$H$32)</f>
         <v>0.00626602641011426</v>
       </c>
       <c r="L22" s="10"/>
@@ -33216,19 +33204,19 @@
         <f aca="false">IF(ISNUMBER(L22),H22-L22,"")</f>
         <v/>
       </c>
-      <c r="O22" s="67" t="s">
+      <c r="O22" s="66" t="s">
         <v>249</v>
       </c>
-      <c r="Q22" s="68" t="s">
+      <c r="Q22" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R22" s="68" t="s">
+      <c r="R22" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S22" s="68" t="s">
+      <c r="S22" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="T22" s="68" t="n">
+      <c r="T22" s="67" t="n">
         <v>78</v>
       </c>
       <c r="U22" s="63" t="n">
@@ -33242,13 +33230,13 @@
       <c r="A23" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="64" t="s">
         <v>101</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="66" t="n">
+      <c r="D23" s="65" t="n">
         <v>68</v>
       </c>
       <c r="E23" s="10" t="n">
@@ -33275,7 +33263,7 @@
         <v>-0.119942052390339</v>
       </c>
       <c r="K23" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H23/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H23/$H$32)</f>
         <v>0.00622292709075302</v>
       </c>
       <c r="L23" s="10"/>
@@ -33287,19 +33275,19 @@
         <f aca="false">IF(ISNUMBER(L23),H23-L23,"")</f>
         <v/>
       </c>
-      <c r="O23" s="67" t="s">
+      <c r="O23" s="66" t="s">
         <v>250</v>
       </c>
-      <c r="Q23" s="68" t="s">
+      <c r="Q23" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R23" s="68" t="s">
+      <c r="R23" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S23" s="68" t="s">
+      <c r="S23" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="T23" s="68" t="n">
+      <c r="T23" s="67" t="n">
         <v>5</v>
       </c>
       <c r="U23" s="63" t="n">
@@ -33313,13 +33301,13 @@
       <c r="A24" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="64" t="s">
         <v>104</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="65" t="n">
         <v>82</v>
       </c>
       <c r="E24" s="10" t="n">
@@ -33346,7 +33334,7 @@
         <v>-0.089761539219967</v>
       </c>
       <c r="K24" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H24/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H24/$H$32)</f>
         <v>0.0054261816369856</v>
       </c>
       <c r="L24" s="10"/>
@@ -33358,19 +33346,19 @@
         <f aca="false">IF(ISNUMBER(L24),H24-L24,"")</f>
         <v/>
       </c>
-      <c r="O24" s="67" t="s">
+      <c r="O24" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="Q24" s="68" t="s">
+      <c r="Q24" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R24" s="68" t="s">
+      <c r="R24" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S24" s="68" t="s">
+      <c r="S24" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="T24" s="68" t="n">
+      <c r="T24" s="67" t="n">
         <v>1</v>
       </c>
       <c r="U24" s="63" t="n">
@@ -33384,13 +33372,13 @@
       <c r="A25" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="64" t="s">
         <v>96</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="66" t="n">
+      <c r="D25" s="65" t="n">
         <v>8</v>
       </c>
       <c r="E25" s="10" t="n">
@@ -33417,7 +33405,7 @@
         <v>-0.0133695425109672</v>
       </c>
       <c r="K25" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H25/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H25/$H$32)</f>
         <v>0.0047588097099507</v>
       </c>
       <c r="L25" s="10"/>
@@ -33429,19 +33417,19 @@
         <f aca="false">IF(ISNUMBER(L25),H25-L25,"")</f>
         <v/>
       </c>
-      <c r="O25" s="67" t="s">
+      <c r="O25" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="Q25" s="68" t="s">
+      <c r="Q25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R25" s="68" t="s">
+      <c r="R25" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S25" s="68" t="s">
+      <c r="S25" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="T25" s="68" t="n">
+      <c r="T25" s="67" t="n">
         <v>1</v>
       </c>
       <c r="U25" s="63" t="n">
@@ -33455,13 +33443,13 @@
       <c r="A26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="64" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="66" t="n">
+      <c r="D26" s="65" t="n">
         <v>10</v>
       </c>
       <c r="E26" s="10" t="n">
@@ -33488,7 +33476,7 @@
         <v>-0.0981855470419005</v>
       </c>
       <c r="K26" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H26/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H26/$H$32)</f>
         <v>0.00265833713418447</v>
       </c>
       <c r="L26" s="10"/>
@@ -33500,19 +33488,19 @@
         <f aca="false">IF(ISNUMBER(L26),H26-L26,"")</f>
         <v/>
       </c>
-      <c r="O26" s="67" t="s">
+      <c r="O26" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="Q26" s="68" t="s">
+      <c r="Q26" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R26" s="68" t="s">
+      <c r="R26" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S26" s="68" t="s">
+      <c r="S26" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="T26" s="68" t="n">
+      <c r="T26" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U26" s="63" t="n">
@@ -33526,13 +33514,13 @@
       <c r="A27" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="64" t="s">
         <v>105</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="66" t="n">
+      <c r="D27" s="65" t="n">
         <v>11</v>
       </c>
       <c r="E27" s="10" t="n">
@@ -33559,7 +33547,7 @@
         <v>-0.170669635756323</v>
       </c>
       <c r="K27" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H27/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H27/$H$32)</f>
         <v>0.00218897186001861</v>
       </c>
       <c r="L27" s="10"/>
@@ -33571,19 +33559,19 @@
         <f aca="false">IF(ISNUMBER(L27),H27-L27,"")</f>
         <v/>
       </c>
-      <c r="O27" s="67" t="s">
+      <c r="O27" s="66" t="s">
         <v>250</v>
       </c>
-      <c r="Q27" s="68" t="s">
+      <c r="Q27" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R27" s="68" t="s">
+      <c r="R27" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S27" s="68" t="s">
+      <c r="S27" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="T27" s="68" t="n">
+      <c r="T27" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U27" s="63" t="n">
@@ -33597,13 +33585,13 @@
       <c r="A28" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="64" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="66" t="n">
+      <c r="D28" s="65" t="n">
         <v>8</v>
       </c>
       <c r="E28" s="10" t="n">
@@ -33630,7 +33618,7 @@
         <v>0.00345232715770454</v>
       </c>
       <c r="K28" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H28/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H28/$H$32)</f>
         <v>0.00186456404726955</v>
       </c>
       <c r="L28" s="10"/>
@@ -33642,19 +33630,19 @@
         <f aca="false">IF(ISNUMBER(L28),H28-L28,"")</f>
         <v/>
       </c>
-      <c r="O28" s="67" t="s">
+      <c r="O28" s="66" t="s">
         <v>255</v>
       </c>
-      <c r="Q28" s="68" t="s">
+      <c r="Q28" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R28" s="68" t="s">
+      <c r="R28" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S28" s="68" t="s">
+      <c r="S28" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="T28" s="68" t="n">
+      <c r="T28" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U28" s="63" t="n">
@@ -33668,13 +33656,13 @@
       <c r="A29" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="64" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="66" t="n">
+      <c r="D29" s="65" t="n">
         <v>7</v>
       </c>
       <c r="E29" s="10" t="n">
@@ -33701,7 +33689,7 @@
         <v>-0.0856970362239296</v>
       </c>
       <c r="K29" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H29/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H29/$H$32)</f>
         <v>0.0006993710515402</v>
       </c>
       <c r="L29" s="10"/>
@@ -33713,19 +33701,19 @@
         <f aca="false">IF(ISNUMBER(L29),H29-L29,"")</f>
         <v/>
       </c>
-      <c r="O29" s="67" t="s">
+      <c r="O29" s="66" t="s">
         <v>250</v>
       </c>
-      <c r="Q29" s="68" t="s">
+      <c r="Q29" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R29" s="68" t="s">
+      <c r="R29" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S29" s="68" t="s">
+      <c r="S29" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="T29" s="68" t="n">
+      <c r="T29" s="67" t="n">
         <v>2</v>
       </c>
       <c r="U29" s="63" t="n">
@@ -33745,7 +33733,7 @@
       <c r="C30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="66" t="n">
+      <c r="D30" s="65" t="n">
         <v>5</v>
       </c>
       <c r="E30" s="10" t="n">
@@ -33772,7 +33760,7 @@
         <v>-0.160301331464611</v>
       </c>
       <c r="K30" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H30/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H30/$H$32)</f>
         <v>0.000301833778051473</v>
       </c>
       <c r="L30" s="10"/>
@@ -33784,19 +33772,19 @@
         <f aca="false">IF(ISNUMBER(L30),H30-L30,"")</f>
         <v/>
       </c>
-      <c r="O30" s="67" t="s">
+      <c r="O30" s="66" t="s">
         <v>250</v>
       </c>
-      <c r="Q30" s="68" t="s">
+      <c r="Q30" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R30" s="68" t="s">
+      <c r="R30" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S30" s="68" t="s">
+      <c r="S30" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="T30" s="68" t="n">
+      <c r="T30" s="67" t="n">
         <v>6</v>
       </c>
       <c r="U30" s="63" t="n">
@@ -33810,13 +33798,13 @@
       <c r="A31" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="64" t="s">
         <v>118</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="66" t="n">
+      <c r="D31" s="65" t="n">
         <v>11</v>
       </c>
       <c r="E31" s="10" t="n">
@@ -33843,7 +33831,7 @@
         <v>0.00720980533525595</v>
       </c>
       <c r="K31" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H31/$H$6)</f>
+        <f aca="false">IF($H$32=0,"",H31/$H$32)</f>
         <v>0.000117299335958803</v>
       </c>
       <c r="L31" s="10" t="n">
@@ -33857,17 +33845,17 @@
         <f aca="false">IF(ISNUMBER(L31),H31-L31,"")</f>
         <v>34</v>
       </c>
-      <c r="O31" s="67"/>
-      <c r="Q31" s="68" t="s">
+      <c r="O31" s="66"/>
+      <c r="Q31" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R31" s="68" t="s">
+      <c r="R31" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S31" s="68" t="s">
+      <c r="S31" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="T31" s="68" t="n">
+      <c r="T31" s="67" t="n">
         <v>5</v>
       </c>
       <c r="U31" s="63" t="n">
@@ -33878,16 +33866,45 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q32" s="68" t="s">
+      <c r="A32" s="84"/>
+      <c r="B32" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="85" t="n">
+        <f aca="false">SUM(H7:H31)</f>
+        <v>11909700.84</v>
+      </c>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="86" t="n">
+        <f aca="false">SUM(K7:K31)</f>
+        <v>1</v>
+      </c>
+      <c r="L32" s="85" t="n">
+        <f aca="false">SUM(L7:L31)</f>
+        <v>2974667</v>
+      </c>
+      <c r="M32" s="84"/>
+      <c r="N32" s="85" t="n">
+        <f aca="false">SUM(N7:N31)</f>
+        <v>-61301.5</v>
+      </c>
+      <c r="O32" s="84"/>
+      <c r="Q32" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R32" s="68" t="s">
+      <c r="R32" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S32" s="68" t="s">
+      <c r="S32" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="T32" s="68" t="n">
+      <c r="T32" s="67" t="n">
         <v>6</v>
       </c>
       <c r="U32" s="63" t="n">
@@ -33898,16 +33915,16 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q33" s="68" t="s">
+      <c r="Q33" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R33" s="68" t="s">
+      <c r="R33" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S33" s="68" t="s">
+      <c r="S33" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="T33" s="68" t="n">
+      <c r="T33" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U33" s="63" t="n">
@@ -33918,16 +33935,16 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q34" s="68" t="s">
+      <c r="Q34" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R34" s="68" t="s">
+      <c r="R34" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S34" s="68" t="s">
+      <c r="S34" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="T34" s="68" t="n">
+      <c r="T34" s="67" t="n">
         <v>2</v>
       </c>
       <c r="U34" s="63" t="n">
@@ -33938,16 +33955,16 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q35" s="68" t="s">
+      <c r="Q35" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R35" s="68" t="s">
+      <c r="R35" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S35" s="68" t="s">
+      <c r="S35" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="T35" s="68" t="n">
+      <c r="T35" s="67" t="n">
         <v>4</v>
       </c>
       <c r="U35" s="63" t="n">
@@ -33958,16 +33975,16 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q36" s="68" t="s">
+      <c r="Q36" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R36" s="68" t="s">
+      <c r="R36" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S36" s="68" t="s">
+      <c r="S36" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="T36" s="68" t="n">
+      <c r="T36" s="67" t="n">
         <v>367</v>
       </c>
       <c r="U36" s="63" t="n">
@@ -33978,16 +33995,16 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q37" s="68" t="s">
+      <c r="Q37" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R37" s="68" t="s">
+      <c r="R37" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S37" s="68" t="s">
+      <c r="S37" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="T37" s="68" t="n">
+      <c r="T37" s="67" t="n">
         <v>51</v>
       </c>
       <c r="U37" s="63" t="n">
@@ -33998,16 +34015,16 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q38" s="68" t="s">
+      <c r="Q38" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R38" s="68" t="s">
+      <c r="R38" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S38" s="68" t="s">
+      <c r="S38" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="T38" s="68" t="n">
+      <c r="T38" s="67" t="n">
         <v>651</v>
       </c>
       <c r="U38" s="63" t="n">
@@ -34018,16 +34035,16 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q39" s="68" t="s">
+      <c r="Q39" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R39" s="68" t="s">
+      <c r="R39" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S39" s="68" t="s">
+      <c r="S39" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="T39" s="68" t="n">
+      <c r="T39" s="67" t="n">
         <v>227</v>
       </c>
       <c r="U39" s="63" t="n">
@@ -34038,16 +34055,16 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q40" s="68" t="s">
+      <c r="Q40" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R40" s="68" t="s">
+      <c r="R40" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S40" s="68" t="s">
+      <c r="S40" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="T40" s="68" t="n">
+      <c r="T40" s="67" t="n">
         <v>1</v>
       </c>
       <c r="U40" s="63" t="n">
@@ -34058,16 +34075,16 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q41" s="68" t="s">
+      <c r="Q41" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R41" s="68" t="s">
+      <c r="R41" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S41" s="68" t="s">
+      <c r="S41" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="T41" s="68" t="n">
+      <c r="T41" s="67" t="n">
         <v>2</v>
       </c>
       <c r="U41" s="63" t="n">
@@ -34078,16 +34095,16 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q42" s="68" t="s">
+      <c r="Q42" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R42" s="68" t="s">
+      <c r="R42" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S42" s="68" t="s">
+      <c r="S42" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="T42" s="68" t="n">
+      <c r="T42" s="67" t="n">
         <v>233</v>
       </c>
       <c r="U42" s="63" t="n">
@@ -34098,16 +34115,16 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q43" s="68" t="s">
+      <c r="Q43" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R43" s="68" t="s">
+      <c r="R43" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S43" s="68" t="s">
+      <c r="S43" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="T43" s="68" t="n">
+      <c r="T43" s="67" t="n">
         <v>15</v>
       </c>
       <c r="U43" s="63" t="n">
@@ -34118,16 +34135,16 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q44" s="68" t="s">
+      <c r="Q44" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R44" s="68" t="s">
+      <c r="R44" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S44" s="68" t="s">
+      <c r="S44" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="T44" s="68" t="n">
+      <c r="T44" s="67" t="n">
         <v>2</v>
       </c>
       <c r="U44" s="63" t="n">
@@ -34138,16 +34155,16 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q45" s="68" t="s">
+      <c r="Q45" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="R45" s="68" t="s">
+      <c r="R45" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S45" s="68" t="s">
+      <c r="S45" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="T45" s="68" t="n">
+      <c r="T45" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U45" s="63" t="n">
@@ -34158,10 +34175,10 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S46" s="69" t="s">
+      <c r="S46" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="V46" s="70" t="n">
+      <c r="V46" s="69" t="n">
         <f aca="false">SUMIFS(V7:V45,R7:R45,"BUY")-SUMIFS(V7:V45,R7:R45,"SELL")</f>
         <v>680650</v>
       </c>
@@ -34185,9 +34202,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF1F618D"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -34228,95 +34246,57 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="L5" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="N5" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="O5" s="25" t="s">
-        <v>194</v>
-      </c>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="31" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="83" t="n">
-        <f aca="false">SUM(E7:E18)</f>
-        <v>201361</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="83" t="n">
-        <f aca="false">SUM(H7:H18)</f>
-        <v>226299.362921147</v>
-      </c>
-      <c r="I6" s="83" t="n">
-        <f aca="false">H6-E6</f>
-        <v>24938.362921147</v>
-      </c>
-      <c r="J6" s="84" t="n">
-        <f aca="false">IF(E6&gt;0,I6/E6,"")</f>
-        <v>0.12384902201095</v>
-      </c>
-      <c r="K6" s="84" t="n">
-        <f aca="false">SUM(K7:K18)</f>
-        <v>1</v>
-      </c>
-      <c r="L6" s="83" t="n">
-        <f aca="false">SUM(L7:L18)</f>
-        <v>230321</v>
-      </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="83" t="n">
-        <f aca="false">SUM(N7:N18)</f>
-        <v>-4021.63707885304</v>
-      </c>
-      <c r="O6" s="13"/>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="N6" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>195</v>
+      </c>
       <c r="Q6" s="25" t="s">
         <v>196</v>
       </c>
@@ -34340,13 +34320,13 @@
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="64" t="s">
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="65" t="n">
         <v>121</v>
       </c>
       <c r="E7" s="10" t="n">
@@ -34373,7 +34353,7 @@
         <v>0.226692708333333</v>
       </c>
       <c r="K7" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H7/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H7/$H$19)</f>
         <v>0.503731422521595</v>
       </c>
       <c r="L7" s="10" t="n">
@@ -34387,17 +34367,17 @@
         <f aca="false">IF(ISNUMBER(L7),H7-L7,"")</f>
         <v>-3847.89999999999</v>
       </c>
-      <c r="O7" s="67"/>
-      <c r="Q7" s="68" t="s">
+      <c r="O7" s="66"/>
+      <c r="Q7" s="67" t="s">
         <v>258</v>
       </c>
-      <c r="R7" s="68" t="s">
+      <c r="R7" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S7" s="68" t="s">
+      <c r="S7" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="T7" s="68" t="n">
+      <c r="T7" s="67" t="n">
         <v>8</v>
       </c>
       <c r="U7" s="63" t="n">
@@ -34411,13 +34391,13 @@
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="64" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="65" t="n">
         <v>9</v>
       </c>
       <c r="E8" s="10" t="n">
@@ -34444,7 +34424,7 @@
         <v>0.376533877149186</v>
       </c>
       <c r="K8" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H8/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H8/$H$19)</f>
         <v>0.173000928922817</v>
       </c>
       <c r="L8" s="10" t="n">
@@ -34458,17 +34438,17 @@
         <f aca="false">IF(ISNUMBER(L8),H8-L8,"")</f>
         <v>-1980</v>
       </c>
-      <c r="O8" s="67"/>
-      <c r="Q8" s="68" t="s">
+      <c r="O8" s="66"/>
+      <c r="Q8" s="67" t="s">
         <v>259</v>
       </c>
-      <c r="R8" s="68" t="s">
+      <c r="R8" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S8" s="68" t="s">
+      <c r="S8" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="T8" s="68" t="n">
+      <c r="T8" s="67" t="n">
         <v>2</v>
       </c>
       <c r="U8" s="63" t="n">
@@ -34482,13 +34462,13 @@
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="64" t="s">
         <v>82</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="66" t="n">
+      <c r="D9" s="65" t="n">
         <v>38</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -34515,7 +34495,7 @@
         <v>-0.0441426244765008</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H9/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H9/$H$19)</f>
         <v>0.0726166427862461</v>
       </c>
       <c r="L9" s="10" t="n">
@@ -34529,17 +34509,17 @@
         <f aca="false">IF(ISNUMBER(L9),H9-L9,"")</f>
         <v>-689.900000000002</v>
       </c>
-      <c r="O9" s="67"/>
-      <c r="Q9" s="68" t="s">
+      <c r="O9" s="66"/>
+      <c r="Q9" s="67" t="s">
         <v>260</v>
       </c>
-      <c r="R9" s="68" t="s">
+      <c r="R9" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S9" s="68" t="s">
+      <c r="S9" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="T9" s="68" t="n">
+      <c r="T9" s="67" t="n">
         <v>5</v>
       </c>
       <c r="U9" s="63" t="n">
@@ -34553,13 +34533,13 @@
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="64" t="s">
         <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="66" t="n">
+      <c r="D10" s="65" t="n">
         <v>21</v>
       </c>
       <c r="E10" s="10" t="n">
@@ -34586,7 +34566,7 @@
         <v>-0.121879142065309</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H10/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H10/$H$19)</f>
         <v>0.0644060584698977</v>
       </c>
       <c r="L10" s="10" t="n">
@@ -34600,11 +34580,11 @@
         <f aca="false">IF(ISNUMBER(L10),H10-L10,"")</f>
         <v>-287.950000000001</v>
       </c>
-      <c r="O10" s="67"/>
-      <c r="S10" s="69" t="s">
+      <c r="O10" s="66"/>
+      <c r="S10" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="V10" s="70" t="n">
+      <c r="V10" s="69" t="n">
         <f aca="false">SUMIFS(V7:V9,R7:R9,"BUY")-SUMIFS(V7:V9,R7:R9,"SELL")</f>
         <v>9889</v>
       </c>
@@ -34619,7 +34599,7 @@
       <c r="C11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="65" t="n">
         <v>9</v>
       </c>
       <c r="E11" s="10" t="n">
@@ -34646,7 +34626,7 @@
         <v>0.244194865810969</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H11/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H11/$H$19)</f>
         <v>0.056541476011395</v>
       </c>
       <c r="L11" s="10" t="n">
@@ -34660,19 +34640,19 @@
         <f aca="false">IF(ISNUMBER(L11),H11-L11,"")</f>
         <v>1980.3</v>
       </c>
-      <c r="O11" s="67"/>
+      <c r="O11" s="66"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="64" t="s">
         <v>86</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="66" t="n">
+      <c r="D12" s="65" t="n">
         <v>121</v>
       </c>
       <c r="E12" s="10" t="n">
@@ -34699,7 +34679,7 @@
         <v>-0.298151489117984</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H12/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H12/$H$19)</f>
         <v>0.043320581522874</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -34713,19 +34693,19 @@
         <f aca="false">IF(ISNUMBER(L12),H12-L12,"")</f>
         <v>-94.5799999999999</v>
       </c>
-      <c r="O12" s="67"/>
+      <c r="O12" s="66"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="64" t="s">
         <v>87</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="66" t="n">
+      <c r="D13" s="65" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="10" t="n">
@@ -34752,7 +34732,7 @@
         <v>-0.161796430672681</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H13/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H13/$H$19)</f>
         <v>0.0377729742128285</v>
       </c>
       <c r="L13" s="10" t="n">
@@ -34766,19 +34746,19 @@
         <f aca="false">IF(ISNUMBER(L13),H13-L13,"")</f>
         <v>576</v>
       </c>
-      <c r="O13" s="67"/>
+      <c r="O13" s="66"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="64" t="s">
         <v>94</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="66" t="n">
+      <c r="D14" s="65" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="10" t="n">
@@ -34805,7 +34785,7 @@
         <v>-0.174727492935002</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H14/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H14/$H$19)</f>
         <v>0.0180663345544839</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -34819,19 +34799,19 @@
         <f aca="false">IF(ISNUMBER(L14),H14-L14,"")</f>
         <v>-281.6</v>
       </c>
-      <c r="O14" s="67"/>
+      <c r="O14" s="66"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="64" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="66" t="n">
+      <c r="D15" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="10" t="n">
@@ -34858,7 +34838,7 @@
         <v>-0.141567180377686</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H15/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H15/$H$19)</f>
         <v>0.0174759661227064</v>
       </c>
       <c r="L15" s="10" t="n">
@@ -34872,19 +34852,19 @@
         <f aca="false">IF(ISNUMBER(L15),H15-L15,"")</f>
         <v>735.8</v>
       </c>
-      <c r="O15" s="67"/>
+      <c r="O15" s="66"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="64" t="s">
         <v>91</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="66" t="n">
+      <c r="D16" s="65" t="n">
         <v>50</v>
       </c>
       <c r="E16" s="10" t="n">
@@ -34911,7 +34891,7 @@
         <v>0.373201917954182</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H16/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H16/$H$19)</f>
         <v>0.0113897801864255</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -34925,7 +34905,7 @@
         <f aca="false">IF(ISNUMBER(L16),H16-L16,"")</f>
         <v>-133.5</v>
       </c>
-      <c r="O16" s="67"/>
+      <c r="O16" s="66"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
@@ -34937,7 +34917,7 @@
       <c r="C17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="66" t="n">
+      <c r="D17" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="n">
@@ -34964,7 +34944,7 @@
         <v>0.0226809607448342</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H17/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H17/$H$19)</f>
         <v>0.00113430686606218</v>
       </c>
       <c r="L17" s="10" t="n">
@@ -34978,19 +34958,19 @@
         <f aca="false">IF(ISNUMBER(L17),H17-L17,"")</f>
         <v>-0.307078853046619</v>
       </c>
-      <c r="O17" s="67"/>
+      <c r="O17" s="66"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="64" t="s">
         <v>146</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="66" t="n">
+      <c r="D18" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="10" t="n">
@@ -35017,7 +34997,7 @@
         <v>0.952380952380952</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H18/$H$6)</f>
+        <f aca="false">IF($H$19=0,"",H18/$H$19)</f>
         <v>0.000543527822669385</v>
       </c>
       <c r="L18" s="10" t="n">
@@ -35031,7 +35011,38 @@
         <f aca="false">IF(ISNUMBER(L18),H18-L18,"")</f>
         <v>2</v>
       </c>
-      <c r="O18" s="67"/>
+      <c r="O18" s="66"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="87"/>
+      <c r="B19" s="87" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="88" t="n">
+        <f aca="false">SUM(H7:H18)</f>
+        <v>226299.362921147</v>
+      </c>
+      <c r="I19" s="87"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="89" t="n">
+        <f aca="false">SUM(K7:K18)</f>
+        <v>1</v>
+      </c>
+      <c r="L19" s="88" t="n">
+        <f aca="false">SUM(L7:L18)</f>
+        <v>230321</v>
+      </c>
+      <c r="M19" s="87"/>
+      <c r="N19" s="88" t="n">
+        <f aca="false">SUM(N7:N18)</f>
+        <v>-4021.63707885304</v>
+      </c>
+      <c r="O19" s="87"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G7:G300">
@@ -35052,9 +35063,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF52BE80"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -35095,95 +35107,57 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="O5" s="26" t="s">
-        <v>194</v>
-      </c>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="31" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="85" t="n">
-        <f aca="false">SUM(E7:E27)</f>
-        <v>5222229</v>
-      </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="85" t="n">
-        <f aca="false">SUM(H7:H27)</f>
-        <v>5421322.76</v>
-      </c>
-      <c r="I6" s="85" t="n">
-        <f aca="false">H6-E6</f>
-        <v>199093.760000001</v>
-      </c>
-      <c r="J6" s="86" t="n">
-        <f aca="false">IF(E6&gt;0,I6/E6,"")</f>
-        <v>0.0381242875408184</v>
-      </c>
-      <c r="K6" s="86" t="n">
-        <f aca="false">SUM(K7:K27)</f>
-        <v>1</v>
-      </c>
-      <c r="L6" s="85" t="n">
-        <f aca="false">SUM(L7:L27)</f>
-        <v>5467268</v>
-      </c>
-      <c r="M6" s="14"/>
-      <c r="N6" s="85" t="n">
-        <f aca="false">SUM(N7:N27)</f>
-        <v>-45945.2399999998</v>
-      </c>
-      <c r="O6" s="14"/>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="N6" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>195</v>
+      </c>
       <c r="Q6" s="26" t="s">
         <v>196</v>
       </c>
@@ -35207,13 +35181,13 @@
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="64" t="s">
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="65" t="n">
         <v>2412</v>
       </c>
       <c r="E7" s="10" t="n">
@@ -35240,7 +35214,7 @@
         <v>0.177206486499928</v>
       </c>
       <c r="K7" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H7/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H7/$H$28)</f>
         <v>0.41914958776592</v>
       </c>
       <c r="L7" s="10" t="n">
@@ -35254,17 +35228,17 @@
         <f aca="false">IF(ISNUMBER(L7),H7-L7,"")</f>
         <v>-46430.7999999998</v>
       </c>
-      <c r="O7" s="67"/>
-      <c r="Q7" s="68" t="s">
+      <c r="O7" s="66"/>
+      <c r="Q7" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R7" s="68" t="s">
+      <c r="R7" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S7" s="68" t="s">
+      <c r="S7" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="T7" s="68" t="n">
+      <c r="T7" s="67" t="n">
         <v>237</v>
       </c>
       <c r="U7" s="63" t="n">
@@ -35278,13 +35252,13 @@
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="64" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="65" t="n">
         <v>172</v>
       </c>
       <c r="E8" s="10" t="n">
@@ -35311,7 +35285,7 @@
         <v>0.211724675164827</v>
       </c>
       <c r="K8" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H8/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H8/$H$28)</f>
         <v>0.138010598727016</v>
       </c>
       <c r="L8" s="10" t="n">
@@ -35325,17 +35299,17 @@
         <f aca="false">IF(ISNUMBER(L8),H8-L8,"")</f>
         <v>-3784</v>
       </c>
-      <c r="O8" s="67"/>
-      <c r="Q8" s="68" t="s">
+      <c r="O8" s="66"/>
+      <c r="Q8" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R8" s="68" t="s">
+      <c r="R8" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S8" s="68" t="s">
+      <c r="S8" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="T8" s="68" t="n">
+      <c r="T8" s="67" t="n">
         <v>176</v>
       </c>
       <c r="U8" s="63" t="n">
@@ -35349,13 +35323,13 @@
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="64" t="s">
         <v>83</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="66" t="n">
+      <c r="D9" s="65" t="n">
         <v>673</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -35382,7 +35356,7 @@
         <v>-0.22074617876793</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H9/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H9/$H$28)</f>
         <v>0.086158981982471</v>
       </c>
       <c r="L9" s="10" t="n">
@@ -35396,17 +35370,17 @@
         <f aca="false">IF(ISNUMBER(L9),H9-L9,"")</f>
         <v>-5451.35000000004</v>
       </c>
-      <c r="O9" s="67"/>
-      <c r="Q9" s="68" t="s">
+      <c r="O9" s="66"/>
+      <c r="Q9" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R9" s="68" t="s">
+      <c r="R9" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S9" s="68" t="s">
+      <c r="S9" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="T9" s="68" t="n">
+      <c r="T9" s="67" t="n">
         <v>55</v>
       </c>
       <c r="U9" s="63" t="n">
@@ -35420,13 +35394,13 @@
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="64" t="s">
         <v>82</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="66" t="n">
+      <c r="D10" s="65" t="n">
         <v>769</v>
       </c>
       <c r="E10" s="10" t="n">
@@ -35453,7 +35427,7 @@
         <v>-0.041603360327387</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H10/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H10/$H$28)</f>
         <v>0.0613418652092944</v>
       </c>
       <c r="L10" s="10" t="n">
@@ -35467,17 +35441,17 @@
         <f aca="false">IF(ISNUMBER(L10),H10-L10,"")</f>
         <v>-7958.95000000001</v>
       </c>
-      <c r="O10" s="67"/>
-      <c r="Q10" s="68" t="s">
+      <c r="O10" s="66"/>
+      <c r="Q10" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R10" s="68" t="s">
+      <c r="R10" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S10" s="68" t="s">
+      <c r="S10" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="T10" s="68" t="n">
+      <c r="T10" s="67" t="n">
         <v>6</v>
       </c>
       <c r="U10" s="63" t="n">
@@ -35491,13 +35465,13 @@
       <c r="A11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="64" t="s">
         <v>84</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="65" t="n">
         <v>240</v>
       </c>
       <c r="E11" s="10" t="n">
@@ -35524,7 +35498,7 @@
         <v>0.61999025489839</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H11/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H11/$H$28)</f>
         <v>0.0607135960302057</v>
       </c>
       <c r="L11" s="10" t="n">
@@ -35538,19 +35512,19 @@
         <f aca="false">IF(ISNUMBER(L11),H11-L11,"")</f>
         <v>-12852</v>
       </c>
-      <c r="O11" s="67" t="s">
+      <c r="O11" s="66" t="s">
         <v>264</v>
       </c>
-      <c r="Q11" s="68" t="s">
+      <c r="Q11" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R11" s="68" t="s">
+      <c r="R11" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S11" s="68" t="s">
+      <c r="S11" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="T11" s="68" t="n">
+      <c r="T11" s="67" t="n">
         <v>280</v>
       </c>
       <c r="U11" s="63" t="n">
@@ -35564,13 +35538,13 @@
       <c r="A12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="64" t="s">
         <v>89</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="66" t="n">
+      <c r="D12" s="65" t="n">
         <v>800</v>
       </c>
       <c r="E12" s="10" t="n">
@@ -35597,7 +35571,7 @@
         <v>0.0185225444584547</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H12/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H12/$H$28)</f>
         <v>0.0345672095715622</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -35611,19 +35585,19 @@
         <f aca="false">IF(ISNUMBER(L12),H12-L12,"")</f>
         <v>-8600</v>
       </c>
-      <c r="O12" s="67" t="s">
+      <c r="O12" s="66" t="s">
         <v>264</v>
       </c>
-      <c r="Q12" s="68" t="s">
+      <c r="Q12" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R12" s="68" t="s">
+      <c r="R12" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S12" s="68" t="s">
+      <c r="S12" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="T12" s="68" t="n">
+      <c r="T12" s="67" t="n">
         <v>4</v>
       </c>
       <c r="U12" s="63" t="n">
@@ -35637,13 +35611,13 @@
       <c r="A13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="64" t="s">
         <v>86</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="66" t="n">
+      <c r="D13" s="65" t="n">
         <v>2198</v>
       </c>
       <c r="E13" s="10" t="n">
@@ -35670,7 +35644,7 @@
         <v>-0.303823455824863</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H13/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H13/$H$28)</f>
         <v>0.0328484334697682</v>
       </c>
       <c r="L13" s="10" t="n">
@@ -35684,17 +35658,17 @@
         <f aca="false">IF(ISNUMBER(L13),H13-L13,"")</f>
         <v>-2616.04000000001</v>
       </c>
-      <c r="O13" s="67"/>
-      <c r="Q13" s="68" t="s">
+      <c r="O13" s="66"/>
+      <c r="Q13" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R13" s="68" t="s">
+      <c r="R13" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S13" s="68" t="s">
+      <c r="S13" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="T13" s="68" t="n">
+      <c r="T13" s="67" t="n">
         <v>7</v>
       </c>
       <c r="U13" s="63" t="n">
@@ -35708,13 +35682,13 @@
       <c r="A14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="64" t="s">
         <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="66" t="n">
+      <c r="D14" s="65" t="n">
         <v>37</v>
       </c>
       <c r="E14" s="10" t="n">
@@ -35741,7 +35715,7 @@
         <v>-0.269914405222482</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H14/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H14/$H$28)</f>
         <v>0.0291696338699451</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -35755,19 +35729,19 @@
         <f aca="false">IF(ISNUMBER(L14),H14-L14,"")</f>
         <v>8773</v>
       </c>
-      <c r="O14" s="67" t="s">
+      <c r="O14" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="Q14" s="68" t="s">
+      <c r="Q14" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R14" s="68" t="s">
+      <c r="R14" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S14" s="68" t="s">
+      <c r="S14" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="T14" s="68" t="n">
+      <c r="T14" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U14" s="63" t="n">
@@ -35781,13 +35755,13 @@
       <c r="A15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="64" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="66" t="n">
+      <c r="D15" s="65" t="n">
         <v>32</v>
       </c>
       <c r="E15" s="10" t="n">
@@ -35814,7 +35788,7 @@
         <v>-0.16211309661743</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H15/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H15/$H$28)</f>
         <v>0.0233436756309266</v>
       </c>
       <c r="L15" s="10" t="n">
@@ -35828,17 +35802,17 @@
         <f aca="false">IF(ISNUMBER(L15),H15-L15,"")</f>
         <v>24073.6</v>
       </c>
-      <c r="O15" s="67"/>
-      <c r="Q15" s="68" t="s">
+      <c r="O15" s="66"/>
+      <c r="Q15" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R15" s="68" t="s">
+      <c r="R15" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S15" s="68" t="s">
+      <c r="S15" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="T15" s="68" t="n">
+      <c r="T15" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U15" s="63" t="n">
@@ -35852,13 +35826,13 @@
       <c r="A16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="64" t="s">
         <v>91</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="66" t="n">
+      <c r="D16" s="65" t="n">
         <v>2370</v>
       </c>
       <c r="E16" s="10" t="n">
@@ -35885,7 +35859,7 @@
         <v>0.294251935972542</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H16/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H16/$H$28)</f>
         <v>0.0225357362785019</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -35899,17 +35873,17 @@
         <f aca="false">IF(ISNUMBER(L16),H16-L16,"")</f>
         <v>-11328.5</v>
       </c>
-      <c r="O16" s="67"/>
-      <c r="Q16" s="68" t="s">
+      <c r="O16" s="66"/>
+      <c r="Q16" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R16" s="68" t="s">
+      <c r="R16" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S16" s="68" t="s">
+      <c r="S16" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="T16" s="68" t="n">
+      <c r="T16" s="67" t="n">
         <v>7</v>
       </c>
       <c r="U16" s="63" t="n">
@@ -35923,13 +35897,13 @@
       <c r="A17" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="64" t="s">
         <v>93</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="66" t="n">
+      <c r="D17" s="65" t="n">
         <v>17</v>
       </c>
       <c r="E17" s="10" t="n">
@@ -35956,7 +35930,7 @@
         <v>0.125159973712428</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H17/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H17/$H$28)</f>
         <v>0.0180008651615496</v>
       </c>
       <c r="L17" s="10" t="n">
@@ -35970,17 +35944,17 @@
         <f aca="false">IF(ISNUMBER(L17),H17-L17,"")</f>
         <v>1954.5</v>
       </c>
-      <c r="O17" s="67"/>
-      <c r="Q17" s="68" t="s">
+      <c r="O17" s="66"/>
+      <c r="Q17" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R17" s="68" t="s">
+      <c r="R17" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S17" s="68" t="s">
+      <c r="S17" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="T17" s="68" t="n">
+      <c r="T17" s="67" t="n">
         <v>3</v>
       </c>
       <c r="U17" s="63" t="n">
@@ -35994,13 +35968,13 @@
       <c r="A18" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="64" t="s">
         <v>101</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="66" t="n">
+      <c r="D18" s="65" t="n">
         <v>82</v>
       </c>
       <c r="E18" s="10" t="n">
@@ -36027,7 +36001,7 @@
         <v>-0.444001219352872</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H18/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H18/$H$28)</f>
         <v>0.0164852387427307</v>
       </c>
       <c r="L18" s="10" t="n">
@@ -36041,17 +36015,17 @@
         <f aca="false">IF(ISNUMBER(L18),H18-L18,"")</f>
         <v>-3108.2</v>
       </c>
-      <c r="O18" s="67"/>
-      <c r="Q18" s="68" t="s">
+      <c r="O18" s="66"/>
+      <c r="Q18" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R18" s="68" t="s">
+      <c r="R18" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S18" s="68" t="s">
+      <c r="S18" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="T18" s="68" t="n">
+      <c r="T18" s="67" t="n">
         <v>8</v>
       </c>
       <c r="U18" s="63" t="n">
@@ -36065,13 +36039,13 @@
       <c r="A19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="64" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="66" t="n">
+      <c r="D19" s="65" t="n">
         <v>22</v>
       </c>
       <c r="E19" s="10" t="n">
@@ -36098,7 +36072,7 @@
         <v>-0.0191056816337884</v>
       </c>
       <c r="K19" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H19/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H19/$H$28)</f>
         <v>0.0156105075728788</v>
       </c>
       <c r="L19" s="10" t="n">
@@ -36112,17 +36086,17 @@
         <f aca="false">IF(ISNUMBER(L19),H19-L19,"")</f>
         <v>17058.6</v>
       </c>
-      <c r="O19" s="67"/>
-      <c r="Q19" s="68" t="s">
+      <c r="O19" s="66"/>
+      <c r="Q19" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="R19" s="68" t="s">
+      <c r="R19" s="67" t="s">
         <v>202</v>
       </c>
-      <c r="S19" s="68" t="s">
+      <c r="S19" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="T19" s="68" t="n">
+      <c r="T19" s="67" t="n">
         <v>2</v>
       </c>
       <c r="U19" s="63" t="n">
@@ -36136,13 +36110,13 @@
       <c r="A20" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="64" t="s">
         <v>85</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="66" t="n">
+      <c r="D20" s="65" t="n">
         <v>29</v>
       </c>
       <c r="E20" s="10" t="n">
@@ -36169,7 +36143,7 @@
         <v>-0.407028376140877</v>
       </c>
       <c r="K20" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H20/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H20/$H$28)</f>
         <v>0.0134100298429751</v>
       </c>
       <c r="L20" s="10" t="n">
@@ -36183,11 +36157,11 @@
         <f aca="false">IF(ISNUMBER(L20),H20-L20,"")</f>
         <v>9535.10000000001</v>
       </c>
-      <c r="O20" s="67"/>
-      <c r="S20" s="69" t="s">
+      <c r="O20" s="66"/>
+      <c r="S20" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="V20" s="70" t="n">
+      <c r="V20" s="69" t="n">
         <f aca="false">SUMIFS(V7:V19,R7:R19,"BUY")-SUMIFS(V7:V19,R7:R19,"SELL")</f>
         <v>500822</v>
       </c>
@@ -36196,13 +36170,13 @@
       <c r="A21" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="64" t="s">
         <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="66" t="n">
+      <c r="D21" s="65" t="n">
         <v>47</v>
       </c>
       <c r="E21" s="10" t="n">
@@ -36229,7 +36203,7 @@
         <v>-0.115895538869258</v>
       </c>
       <c r="K21" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H21/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H21/$H$28)</f>
         <v>0.0118147549658158</v>
       </c>
       <c r="L21" s="10" t="n">
@@ -36243,7 +36217,7 @@
         <f aca="false">IF(ISNUMBER(L21),H21-L21,"")</f>
         <v>-2824.4</v>
       </c>
-      <c r="O21" s="67"/>
+      <c r="O21" s="66"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
@@ -36255,7 +36229,7 @@
       <c r="C22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="66" t="n">
+      <c r="D22" s="65" t="n">
         <v>36000</v>
       </c>
       <c r="E22" s="10" t="n">
@@ -36282,7 +36256,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H22/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H22/$H$28)</f>
         <v>0.00664044580883799</v>
       </c>
       <c r="L22" s="10" t="n">
@@ -36296,7 +36270,7 @@
         <f aca="false">IF(ISNUMBER(L22),H22-L22,"")</f>
         <v>0</v>
       </c>
-      <c r="O22" s="67" t="s">
+      <c r="O22" s="66" t="s">
         <v>265</v>
       </c>
     </row>
@@ -36304,13 +36278,13 @@
       <c r="A23" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="64" t="s">
         <v>96</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="66" t="n">
+      <c r="D23" s="65" t="n">
         <v>3</v>
       </c>
       <c r="E23" s="10" t="n">
@@ -36337,7 +36311,7 @@
         <v>0.0258966066515422</v>
       </c>
       <c r="K23" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H23/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H23/$H$28)</f>
         <v>0.00392035319439273</v>
       </c>
       <c r="L23" s="10" t="n">
@@ -36351,7 +36325,7 @@
         <f aca="false">IF(ISNUMBER(L23),H23-L23,"")</f>
         <v>448.5</v>
       </c>
-      <c r="O23" s="67" t="s">
+      <c r="O23" s="66" t="s">
         <v>266</v>
       </c>
     </row>
@@ -36359,13 +36333,13 @@
       <c r="A24" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="64" t="s">
         <v>100</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="65" t="n">
         <v>5</v>
       </c>
       <c r="E24" s="10" t="n">
@@ -36392,7 +36366,7 @@
         <v>-0.0460512750017183</v>
       </c>
       <c r="K24" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H24/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H24/$H$28)</f>
         <v>0.00256007631613507</v>
       </c>
       <c r="L24" s="10" t="n">
@@ -36406,19 +36380,19 @@
         <f aca="false">IF(ISNUMBER(L24),H24-L24,"")</f>
         <v>-671</v>
       </c>
-      <c r="O24" s="67"/>
+      <c r="O24" s="66"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="64" t="s">
         <v>102</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="66" t="n">
+      <c r="D25" s="65" t="n">
         <v>4</v>
       </c>
       <c r="E25" s="10" t="n">
@@ -36445,7 +36419,7 @@
         <v>-0.140841248303935</v>
       </c>
       <c r="K25" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H25/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H25/$H$28)</f>
         <v>0.00233596127008679</v>
       </c>
       <c r="L25" s="10" t="n">
@@ -36459,19 +36433,19 @@
         <f aca="false">IF(ISNUMBER(L25),H25-L25,"")</f>
         <v>-1606</v>
       </c>
-      <c r="O25" s="67"/>
+      <c r="O25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="64" t="s">
         <v>104</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="66" t="n">
+      <c r="D26" s="65" t="n">
         <v>8</v>
       </c>
       <c r="E26" s="10" t="n">
@@ -36498,7 +36472,7 @@
         <v>-0.0673372781065088</v>
       </c>
       <c r="K26" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H26/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H26/$H$28)</f>
         <v>0.00116296340932116</v>
       </c>
       <c r="L26" s="10" t="n">
@@ -36512,7 +36486,7 @@
         <f aca="false">IF(ISNUMBER(L26),H26-L26,"")</f>
         <v>-422.2</v>
       </c>
-      <c r="O26" s="67" t="s">
+      <c r="O26" s="66" t="s">
         <v>266</v>
       </c>
     </row>
@@ -36520,13 +36494,13 @@
       <c r="A27" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="64" t="s">
         <v>106</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="66" t="n">
+      <c r="D27" s="65" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="10" t="n">
@@ -36553,7 +36527,7 @@
         <v>-0.203547523427041</v>
       </c>
       <c r="K27" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H27/$H$6)</f>
+        <f aca="false">IF($H$28=0,"",H27/$H$28)</f>
         <v>0.000219485179664898</v>
       </c>
       <c r="L27" s="10" t="n">
@@ -36567,7 +36541,38 @@
         <f aca="false">IF(ISNUMBER(L27),H27-L27,"")</f>
         <v>-135.1</v>
       </c>
-      <c r="O27" s="67"/>
+      <c r="O27" s="66"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="90"/>
+      <c r="B28" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="91" t="n">
+        <f aca="false">SUM(H7:H27)</f>
+        <v>5421322.76</v>
+      </c>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="92" t="n">
+        <f aca="false">SUM(K7:K27)</f>
+        <v>1</v>
+      </c>
+      <c r="L28" s="91" t="n">
+        <f aca="false">SUM(L7:L27)</f>
+        <v>5467268</v>
+      </c>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91" t="n">
+        <f aca="false">SUM(N7:N27)</f>
+        <v>-45945.2399999998</v>
+      </c>
+      <c r="O28" s="90"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G7:G300">
@@ -36588,9 +36593,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF5DADE2"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -36625,104 +36631,64 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="27" t="s">
+      <c r="B6" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="E6" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G6" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="L5" s="27" t="s">
+      <c r="K6" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="L6" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="N5" s="27" t="s">
+      <c r="M6" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="O5" s="27" t="s">
+      <c r="N6" s="27" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="87" t="n">
-        <f aca="false">SUM(E7:E59)</f>
-        <v>4364996</v>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="87" t="n">
-        <f aca="false">SUM(H7:H59)</f>
-        <v>3866010.74</v>
-      </c>
-      <c r="I6" s="87" t="n">
-        <f aca="false">H6-E6</f>
-        <v>-498985.26</v>
-      </c>
-      <c r="J6" s="88" t="n">
-        <f aca="false">IF(E6&gt;0,I6/E6,"")</f>
-        <v>-0.114315170048266</v>
-      </c>
-      <c r="K6" s="88" t="n">
-        <f aca="false">SUM(K7:K59)</f>
-        <v>1</v>
-      </c>
-      <c r="L6" s="87" t="n">
-        <f aca="false">SUM(L7:L59)</f>
-        <v>4141021</v>
-      </c>
-      <c r="M6" s="15"/>
-      <c r="N6" s="87" t="n">
-        <f aca="false">SUM(N7:N59)</f>
-        <v>-275010.26</v>
-      </c>
-      <c r="O6" s="15"/>
+      <c r="O6" s="27" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="64" t="s">
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="65" t="n">
         <v>915</v>
       </c>
       <c r="E7" s="10" t="n">
@@ -36749,7 +36715,7 @@
         <v>-0.105895342577716</v>
       </c>
       <c r="K7" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H7/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H7/$H$60)</f>
         <v>0.222974419362322</v>
       </c>
       <c r="L7" s="10" t="n">
@@ -36763,19 +36729,19 @@
         <f aca="false">IF(ISNUMBER(L7),H7-L7,"")</f>
         <v>-84088.5</v>
       </c>
-      <c r="O7" s="67"/>
+      <c r="O7" s="66"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="64" t="s">
         <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="65" t="n">
         <v>792</v>
       </c>
       <c r="E8" s="10" t="n">
@@ -36802,7 +36768,7 @@
         <v>-0.0903841097593041</v>
       </c>
       <c r="K8" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H8/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H8/$H$60)</f>
         <v>0.0885927181878445</v>
       </c>
       <c r="L8" s="10" t="n">
@@ -36816,19 +36782,19 @@
         <f aca="false">IF(ISNUMBER(L8),H8-L8,"")</f>
         <v>-9939.60000000004</v>
       </c>
-      <c r="O8" s="67"/>
+      <c r="O8" s="66"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="64" t="s">
         <v>80</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="66" t="n">
+      <c r="D9" s="65" t="n">
         <v>59</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -36855,7 +36821,7 @@
         <v>-0.0133134445414108</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H9/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H9/$H$60)</f>
         <v>0.0663862615135932</v>
       </c>
       <c r="L9" s="10" t="n">
@@ -36869,19 +36835,19 @@
         <f aca="false">IF(ISNUMBER(L9),H9-L9,"")</f>
         <v>-38940</v>
       </c>
-      <c r="O9" s="67"/>
+      <c r="O9" s="66"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="64" t="s">
         <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="66" t="n">
+      <c r="D10" s="65" t="n">
         <v>337</v>
       </c>
       <c r="E10" s="10" t="n">
@@ -36908,7 +36874,7 @@
         <v>-0.0680031957156691</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H10/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H10/$H$60)</f>
         <v>0.0605003104569751</v>
       </c>
       <c r="L10" s="10" t="n">
@@ -36922,19 +36888,19 @@
         <f aca="false">IF(ISNUMBER(L10),H10-L10,"")</f>
         <v>-4701.15000000002</v>
       </c>
-      <c r="O10" s="67"/>
+      <c r="O10" s="66"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="64" t="s">
         <v>89</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D11" s="66" t="n">
+      <c r="D11" s="65" t="n">
         <v>800</v>
       </c>
       <c r="E11" s="10" t="n">
@@ -36961,7 +36927,7 @@
         <v>0.0411111111111111</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H11/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H11/$H$60)</f>
         <v>0.0484737401427912</v>
       </c>
       <c r="L11" s="10" t="n">
@@ -36975,7 +36941,7 @@
         <f aca="false">IF(ISNUMBER(L11),H11-L11,"")</f>
         <v>-24600</v>
       </c>
-      <c r="O11" s="67" t="s">
+      <c r="O11" s="66" t="s">
         <v>270</v>
       </c>
     </row>
@@ -36989,7 +36955,7 @@
       <c r="C12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="66" t="n">
+      <c r="D12" s="65" t="n">
         <v>146</v>
       </c>
       <c r="E12" s="10" t="n">
@@ -37016,7 +36982,7 @@
         <v>-0.130961115187087</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H12/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H12/$H$60)</f>
         <v>0.0447326744881211</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -37030,19 +36996,19 @@
         <f aca="false">IF(ISNUMBER(L12),H12-L12,"")</f>
         <v>-10731</v>
       </c>
-      <c r="O12" s="67"/>
+      <c r="O12" s="66"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="64" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D13" s="66" t="n">
+      <c r="D13" s="65" t="n">
         <v>120</v>
       </c>
       <c r="E13" s="10" t="n">
@@ -37069,7 +37035,7 @@
         <v>-0.0266501064584812</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H13/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H13/$H$60)</f>
         <v>0.0425694627014927</v>
       </c>
       <c r="L13" s="10" t="n">
@@ -37083,7 +37049,7 @@
         <f aca="false">IF(ISNUMBER(L13),H13-L13,"")</f>
         <v>-20226</v>
       </c>
-      <c r="O13" s="67" t="s">
+      <c r="O13" s="66" t="s">
         <v>271</v>
       </c>
     </row>
@@ -37091,13 +37057,13 @@
       <c r="A14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="64" t="s">
         <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D14" s="66" t="n">
+      <c r="D14" s="65" t="n">
         <v>1732</v>
       </c>
       <c r="E14" s="10" t="n">
@@ -37124,7 +37090,7 @@
         <v>-0.187604844498993</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H14/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H14/$H$60)</f>
         <v>0.0362975297890662</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -37138,19 +37104,19 @@
         <f aca="false">IF(ISNUMBER(L14),H14-L14,"")</f>
         <v>-5161.36000000002</v>
       </c>
-      <c r="O14" s="67"/>
+      <c r="O14" s="66"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="64" t="s">
         <v>91</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="66" t="n">
+      <c r="D15" s="65" t="n">
         <v>2030</v>
       </c>
       <c r="E15" s="10" t="n">
@@ -37177,7 +37143,7 @@
         <v>0.516176470588235</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H15/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H15/$H$60)</f>
         <v>0.027068341770825</v>
       </c>
       <c r="L15" s="10" t="n">
@@ -37191,19 +37157,19 @@
         <f aca="false">IF(ISNUMBER(L15),H15-L15,"")</f>
         <v>-12484.5</v>
       </c>
-      <c r="O15" s="67"/>
+      <c r="O15" s="66"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="64" t="s">
         <v>93</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D16" s="66" t="n">
+      <c r="D16" s="65" t="n">
         <v>18</v>
       </c>
       <c r="E16" s="10" t="n">
@@ -37230,7 +37196,7 @@
         <v>0.124693870886985</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H16/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H16/$H$60)</f>
         <v>0.0267275512017848</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -37244,19 +37210,19 @@
         <f aca="false">IF(ISNUMBER(L16),H16-L16,"")</f>
         <v>4041</v>
       </c>
-      <c r="O16" s="67"/>
+      <c r="O16" s="66"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="64" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D17" s="66" t="n">
+      <c r="D17" s="65" t="n">
         <v>24</v>
       </c>
       <c r="E17" s="10" t="n">
@@ -37283,7 +37249,7 @@
         <v>0.10592841163311</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H17/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H17/$H$60)</f>
         <v>0.024551199255075</v>
       </c>
       <c r="L17" s="10" t="n">
@@ -37297,7 +37263,7 @@
         <f aca="false">IF(ISNUMBER(L17),H17-L17,"")</f>
         <v>14827.2</v>
       </c>
-      <c r="O17" s="67"/>
+      <c r="O17" s="66"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
@@ -37309,7 +37275,7 @@
       <c r="C18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="66" t="n">
+      <c r="D18" s="65" t="n">
         <v>374</v>
       </c>
       <c r="E18" s="10" t="n">
@@ -37336,7 +37302,7 @@
         <v>-0.17007874015748</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H18/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H18/$H$60)</f>
         <v>0.0203929076513636</v>
       </c>
       <c r="L18" s="10" t="n">
@@ -37350,19 +37316,19 @@
         <f aca="false">IF(ISNUMBER(L18),H18-L18,"")</f>
         <v>-7180.8</v>
       </c>
-      <c r="O18" s="67"/>
+      <c r="O18" s="66"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="64" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D19" s="66" t="n">
+      <c r="D19" s="65" t="n">
         <v>20</v>
       </c>
       <c r="E19" s="10" t="n">
@@ -37389,7 +37355,7 @@
         <v>0.0296573875802998</v>
       </c>
       <c r="K19" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H19/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H19/$H$60)</f>
         <v>0.0199006172445346</v>
       </c>
       <c r="L19" s="10" t="n">
@@ -37403,19 +37369,19 @@
         <f aca="false">IF(ISNUMBER(L19),H19-L19,"")</f>
         <v>9276</v>
       </c>
-      <c r="O19" s="67"/>
+      <c r="O19" s="66"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="64" t="s">
         <v>106</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D20" s="66" t="n">
+      <c r="D20" s="65" t="n">
         <v>52</v>
       </c>
       <c r="E20" s="10" t="n">
@@ -37442,7 +37408,7 @@
         <v>-0.0593675889328063</v>
       </c>
       <c r="K20" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H20/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H20/$H$60)</f>
         <v>0.0160048184449689</v>
       </c>
       <c r="L20" s="10" t="n">
@@ -37456,19 +37422,19 @@
         <f aca="false">IF(ISNUMBER(L20),H20-L20,"")</f>
         <v>-10041.2</v>
       </c>
-      <c r="O20" s="67"/>
+      <c r="O20" s="66"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="64" t="s">
         <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D21" s="66" t="n">
+      <c r="D21" s="65" t="n">
         <v>45</v>
       </c>
       <c r="E21" s="10" t="n">
@@ -37495,7 +37461,7 @@
         <v>-0.181381317243773</v>
       </c>
       <c r="K21" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H21/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H21/$H$60)</f>
         <v>0.0158628633297589</v>
       </c>
       <c r="L21" s="10" t="n">
@@ -37509,19 +37475,19 @@
         <f aca="false">IF(ISNUMBER(L21),H21-L21,"")</f>
         <v>-9234</v>
       </c>
-      <c r="O21" s="67"/>
+      <c r="O21" s="66"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="64" t="s">
         <v>96</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D22" s="66" t="n">
+      <c r="D22" s="65" t="n">
         <v>8</v>
       </c>
       <c r="E22" s="10" t="n">
@@ -37548,7 +37514,7 @@
         <v>-0.119213016923866</v>
       </c>
       <c r="K22" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H22/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H22/$H$60)</f>
         <v>0.0146600730860877</v>
       </c>
       <c r="L22" s="10" t="n">
@@ -37562,19 +37528,19 @@
         <f aca="false">IF(ISNUMBER(L22),H22-L22,"")</f>
         <v>-3564</v>
       </c>
-      <c r="O22" s="67"/>
+      <c r="O22" s="66"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="64" t="s">
         <v>100</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D23" s="66" t="n">
+      <c r="D23" s="65" t="n">
         <v>18</v>
       </c>
       <c r="E23" s="10" t="n">
@@ -37601,7 +37567,7 @@
         <v>-0.0735495355176058</v>
       </c>
       <c r="K23" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H23/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H23/$H$60)</f>
         <v>0.0129240199679321</v>
       </c>
       <c r="L23" s="10" t="n">
@@ -37615,7 +37581,7 @@
         <f aca="false">IF(ISNUMBER(L23),H23-L23,"")</f>
         <v>-471.599999999999</v>
       </c>
-      <c r="O23" s="67"/>
+      <c r="O23" s="66"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
@@ -37627,7 +37593,7 @@
       <c r="C24" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="65" t="n">
         <v>399</v>
       </c>
       <c r="E24" s="10" t="n">
@@ -37654,7 +37620,7 @@
         <v>-0.321073446327684</v>
       </c>
       <c r="K24" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H24/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H24/$H$60)</f>
         <v>0.0124024047589687</v>
       </c>
       <c r="L24" s="10" t="n">
@@ -37668,7 +37634,7 @@
         <f aca="false">IF(ISNUMBER(L24),H24-L24,"")</f>
         <v>-8311.17</v>
       </c>
-      <c r="O24" s="67"/>
+      <c r="O24" s="66"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
@@ -37680,7 +37646,7 @@
       <c r="C25" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D25" s="66" t="n">
+      <c r="D25" s="65" t="n">
         <v>33</v>
       </c>
       <c r="E25" s="10" t="n">
@@ -37707,7 +37673,7 @@
         <v>-0.00649895178197068</v>
       </c>
       <c r="K25" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H25/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H25/$H$60)</f>
         <v>0.0121355327636777</v>
       </c>
       <c r="L25" s="10" t="n">
@@ -37721,7 +37687,7 @@
         <f aca="false">IF(ISNUMBER(L25),H25-L25,"")</f>
         <v>7118.1</v>
       </c>
-      <c r="O25" s="67"/>
+      <c r="O25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
@@ -37733,7 +37699,7 @@
       <c r="C26" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D26" s="66" t="n">
+      <c r="D26" s="65" t="n">
         <v>111</v>
       </c>
       <c r="E26" s="10" t="n">
@@ -37760,7 +37726,7 @@
         <v>-0.0686585365853657</v>
       </c>
       <c r="K26" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H26/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H26/$H$60)</f>
         <v>0.0109635882698039</v>
       </c>
       <c r="L26" s="10" t="n">
@@ -37774,19 +37740,19 @@
         <f aca="false">IF(ISNUMBER(L26),H26-L26,"")</f>
         <v>-682.649999999994</v>
       </c>
-      <c r="O26" s="67"/>
+      <c r="O26" s="66"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="64" t="s">
         <v>102</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D27" s="66" t="n">
+      <c r="D27" s="65" t="n">
         <v>13</v>
       </c>
       <c r="E27" s="10" t="n">
@@ -37813,7 +37779,7 @@
         <v>-0.205781328393346</v>
       </c>
       <c r="K27" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H27/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H27/$H$60)</f>
         <v>0.0106461163116169</v>
       </c>
       <c r="L27" s="10" t="n">
@@ -37827,7 +37793,7 @@
         <f aca="false">IF(ISNUMBER(L27),H27-L27,"")</f>
         <v>-6786</v>
       </c>
-      <c r="O27" s="67"/>
+      <c r="O27" s="66"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
@@ -37839,7 +37805,7 @@
       <c r="C28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="66" t="n">
+      <c r="D28" s="65" t="n">
         <v>230</v>
       </c>
       <c r="E28" s="10" t="n">
@@ -37866,7 +37832,7 @@
         <v>-0.446678571428571</v>
       </c>
       <c r="K28" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H28/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H28/$H$60)</f>
         <v>0.00921722736859236</v>
       </c>
       <c r="L28" s="10" t="n">
@@ -37880,7 +37846,7 @@
         <f aca="false">IF(ISNUMBER(L28),H28-L28,"")</f>
         <v>-8526.1</v>
       </c>
-      <c r="O28" s="67"/>
+      <c r="O28" s="66"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
@@ -37892,7 +37858,7 @@
       <c r="C29" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="66" t="n">
+      <c r="D29" s="65" t="n">
         <v>40</v>
       </c>
       <c r="E29" s="10" t="n">
@@ -37919,7 +37885,7 @@
         <v>-0.171290944123314</v>
       </c>
       <c r="K29" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H29/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H29/$H$60)</f>
         <v>0.00890013047402967</v>
       </c>
       <c r="L29" s="10" t="n">
@@ -37933,19 +37899,19 @@
         <f aca="false">IF(ISNUMBER(L29),H29-L29,"")</f>
         <v>-192</v>
       </c>
-      <c r="O29" s="67"/>
+      <c r="O29" s="66"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="64" t="s">
         <v>85</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D30" s="66" t="n">
+      <c r="D30" s="65" t="n">
         <v>13</v>
       </c>
       <c r="E30" s="10" t="n">
@@ -37972,7 +37938,7 @@
         <v>0.0462854757929883</v>
       </c>
       <c r="K30" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H30/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H30/$H$60)</f>
         <v>0.00842980068906896</v>
       </c>
       <c r="L30" s="10" t="n">
@@ -37986,7 +37952,7 @@
         <f aca="false">IF(ISNUMBER(L30),H30-L30,"")</f>
         <v>3976.7</v>
       </c>
-      <c r="O30" s="67"/>
+      <c r="O30" s="66"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
@@ -37998,7 +37964,7 @@
       <c r="C31" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="66" t="n">
+      <c r="D31" s="65" t="n">
         <v>66</v>
       </c>
       <c r="E31" s="10" t="n">
@@ -38025,7 +37991,7 @@
         <v>-0.255243161094225</v>
       </c>
       <c r="K31" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H31/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H31/$H$60)</f>
         <v>0.00836606573938281</v>
       </c>
       <c r="L31" s="10" t="n">
@@ -38039,7 +38005,7 @@
         <f aca="false">IF(ISNUMBER(L31),H31-L31,"")</f>
         <v>-6068.7</v>
       </c>
-      <c r="O31" s="67"/>
+      <c r="O31" s="66"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
@@ -38051,7 +38017,7 @@
       <c r="C32" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D32" s="66" t="n">
+      <c r="D32" s="65" t="n">
         <v>187</v>
       </c>
       <c r="E32" s="10" t="n">
@@ -38078,7 +38044,7 @@
         <v>-0.242767857142857</v>
       </c>
       <c r="K32" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H32/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H32/$H$60)</f>
         <v>0.00820456592937453</v>
       </c>
       <c r="L32" s="10" t="n">
@@ -38092,7 +38058,7 @@
         <f aca="false">IF(ISNUMBER(L32),H32-L32,"")</f>
         <v>-7551.06</v>
       </c>
-      <c r="O32" s="67"/>
+      <c r="O32" s="66"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
@@ -38104,7 +38070,7 @@
       <c r="C33" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D33" s="66" t="n">
+      <c r="D33" s="65" t="n">
         <v>1072</v>
       </c>
       <c r="E33" s="10" t="n">
@@ -38131,7 +38097,7 @@
         <v>-0.313720930232558</v>
       </c>
       <c r="K33" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H33/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H33/$H$60)</f>
         <v>0.00818278119941281</v>
       </c>
       <c r="L33" s="10" t="n">
@@ -38145,7 +38111,7 @@
         <f aca="false">IF(ISNUMBER(L33),H33-L33,"")</f>
         <v>-4813.28</v>
       </c>
-      <c r="O33" s="67"/>
+      <c r="O33" s="66"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
@@ -38157,7 +38123,7 @@
       <c r="C34" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D34" s="66" t="n">
+      <c r="D34" s="65" t="n">
         <v>19</v>
       </c>
       <c r="E34" s="10" t="n">
@@ -38184,7 +38150,7 @@
         <v>0.0717007762879322</v>
       </c>
       <c r="K34" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H34/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H34/$H$60)</f>
         <v>0.00746335226166495</v>
       </c>
       <c r="L34" s="10" t="n">
@@ -38198,7 +38164,7 @@
         <f aca="false">IF(ISNUMBER(L34),H34-L34,"")</f>
         <v>2025.4</v>
       </c>
-      <c r="O34" s="67"/>
+      <c r="O34" s="66"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
@@ -38210,7 +38176,7 @@
       <c r="C35" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D35" s="66" t="n">
+      <c r="D35" s="65" t="n">
         <v>110</v>
       </c>
       <c r="E35" s="10" t="n">
@@ -38237,7 +38203,7 @@
         <v>-0.442122762148338</v>
       </c>
       <c r="K35" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H35/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H35/$H$60)</f>
         <v>0.00620647525671385</v>
       </c>
       <c r="L35" s="10" t="n">
@@ -38251,7 +38217,7 @@
         <f aca="false">IF(ISNUMBER(L35),H35-L35,"")</f>
         <v>-2625.7</v>
       </c>
-      <c r="O35" s="67" t="s">
+      <c r="O35" s="66" t="s">
         <v>272</v>
       </c>
     </row>
@@ -38265,7 +38231,7 @@
       <c r="C36" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D36" s="66" t="n">
+      <c r="D36" s="65" t="n">
         <v>302</v>
       </c>
       <c r="E36" s="10" t="n">
@@ -38292,7 +38258,7 @@
         <v>-0.515723270440252</v>
       </c>
       <c r="K36" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H36/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H36/$H$60)</f>
         <v>0.00601498587663003</v>
       </c>
       <c r="L36" s="10" t="n">
@@ -38306,7 +38272,7 @@
         <f aca="false">IF(ISNUMBER(L36),H36-L36,"")</f>
         <v>-1208</v>
       </c>
-      <c r="O36" s="67"/>
+      <c r="O36" s="66"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
@@ -38318,7 +38284,7 @@
       <c r="C37" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D37" s="66" t="n">
+      <c r="D37" s="65" t="n">
         <v>166</v>
       </c>
       <c r="E37" s="10" t="n">
@@ -38345,7 +38311,7 @@
         <v>-0.313676470588235</v>
       </c>
       <c r="K37" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H37/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H37/$H$60)</f>
         <v>0.00601179395585435</v>
       </c>
       <c r="L37" s="10" t="n">
@@ -38359,7 +38325,7 @@
         <f aca="false">IF(ISNUMBER(L37),H37-L37,"")</f>
         <v>-1990.34</v>
       </c>
-      <c r="O37" s="67"/>
+      <c r="O37" s="66"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
@@ -38371,7 +38337,7 @@
       <c r="C38" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D38" s="66" t="n">
+      <c r="D38" s="65" t="n">
         <v>116</v>
       </c>
       <c r="E38" s="10" t="n">
@@ -38398,7 +38364,7 @@
         <v>-0.2340234375</v>
       </c>
       <c r="K38" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H38/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H38/$H$60)</f>
         <v>0.00588369808822621</v>
       </c>
       <c r="L38" s="10" t="n">
@@ -38412,7 +38378,7 @@
         <f aca="false">IF(ISNUMBER(L38),H38-L38,"")</f>
         <v>-1497.56</v>
       </c>
-      <c r="O38" s="67"/>
+      <c r="O38" s="66"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="n">
@@ -38424,7 +38390,7 @@
       <c r="C39" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D39" s="66" t="n">
+      <c r="D39" s="65" t="n">
         <v>33</v>
       </c>
       <c r="E39" s="10" t="n">
@@ -38451,7 +38417,7 @@
         <v>-0.18489646772229</v>
       </c>
       <c r="K39" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H39/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H39/$H$60)</f>
         <v>0.00571224486562083</v>
       </c>
       <c r="L39" s="10" t="n">
@@ -38465,19 +38431,19 @@
         <f aca="false">IF(ISNUMBER(L39),H39-L39,"")</f>
         <v>-1016.4</v>
       </c>
-      <c r="O39" s="67"/>
+      <c r="O39" s="66"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="64" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D40" s="66" t="n">
+      <c r="D40" s="65" t="n">
         <v>5</v>
       </c>
       <c r="E40" s="10" t="n">
@@ -38504,7 +38470,7 @@
         <v>-0.0967878275570583</v>
       </c>
       <c r="K40" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H40/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H40/$H$60)</f>
         <v>0.0055276618295168</v>
       </c>
       <c r="L40" s="10" t="n">
@@ -38518,7 +38484,7 @@
         <f aca="false">IF(ISNUMBER(L40),H40-L40,"")</f>
         <v>-5</v>
       </c>
-      <c r="O40" s="67" t="s">
+      <c r="O40" s="66" t="s">
         <v>273</v>
       </c>
     </row>
@@ -38532,7 +38498,7 @@
       <c r="C41" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D41" s="66" t="n">
+      <c r="D41" s="65" t="n">
         <v>380</v>
       </c>
       <c r="E41" s="10" t="n">
@@ -38559,7 +38525,7 @@
         <v>0.113877551020408</v>
       </c>
       <c r="K41" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H41/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H41/$H$60)</f>
         <v>0.00536480661716941</v>
       </c>
       <c r="L41" s="10" t="n">
@@ -38573,7 +38539,7 @@
         <f aca="false">IF(ISNUMBER(L41),H41-L41,"")</f>
         <v>-1299.6</v>
       </c>
-      <c r="O41" s="67"/>
+      <c r="O41" s="66"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
@@ -38585,7 +38551,7 @@
       <c r="C42" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D42" s="66" t="n">
+      <c r="D42" s="65" t="n">
         <v>245</v>
       </c>
       <c r="E42" s="10" t="n">
@@ -38612,7 +38578,7 @@
         <v>-0.24009009009009</v>
       </c>
       <c r="K42" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H42/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H42/$H$60)</f>
         <v>0.00534549730712854</v>
       </c>
       <c r="L42" s="10" t="n">
@@ -38626,7 +38592,7 @@
         <f aca="false">IF(ISNUMBER(L42),H42-L42,"")</f>
         <v>-649.25</v>
       </c>
-      <c r="O42" s="67"/>
+      <c r="O42" s="66"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="n">
@@ -38638,7 +38604,7 @@
       <c r="C43" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="66" t="n">
+      <c r="D43" s="65" t="n">
         <v>35</v>
       </c>
       <c r="E43" s="10" t="n">
@@ -38665,7 +38631,7 @@
         <v>-0.210906515580737</v>
       </c>
       <c r="K43" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H43/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H43/$H$60)</f>
         <v>0.00504357108951022</v>
       </c>
       <c r="L43" s="10" t="n">
@@ -38679,7 +38645,7 @@
         <f aca="false">IF(ISNUMBER(L43),H43-L43,"")</f>
         <v>-2866.5</v>
       </c>
-      <c r="O43" s="67"/>
+      <c r="O43" s="66"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
@@ -38691,7 +38657,7 @@
       <c r="C44" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D44" s="66" t="n">
+      <c r="D44" s="65" t="n">
         <v>51</v>
       </c>
       <c r="E44" s="10" t="n">
@@ -38718,7 +38684,7 @@
         <v>-0.383278145695364</v>
       </c>
       <c r="K44" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H44/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H44/$H$60)</f>
         <v>0.00491398014067597</v>
       </c>
       <c r="L44" s="10" t="n">
@@ -38732,19 +38698,19 @@
         <f aca="false">IF(ISNUMBER(L44),H44-L44,"")</f>
         <v>-535.5</v>
       </c>
-      <c r="O44" s="67"/>
+      <c r="O44" s="66"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="64" t="s">
         <v>105</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D45" s="66" t="n">
+      <c r="D45" s="65" t="n">
         <v>8</v>
       </c>
       <c r="E45" s="10" t="n">
@@ -38771,7 +38737,7 @@
         <v>0.348122866894198</v>
       </c>
       <c r="K45" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H45/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H45/$H$60)</f>
         <v>0.00490428021935604</v>
       </c>
       <c r="L45" s="10" t="n">
@@ -38785,7 +38751,7 @@
         <f aca="false">IF(ISNUMBER(L45),H45-L45,"")</f>
         <v>-2040</v>
       </c>
-      <c r="O45" s="67"/>
+      <c r="O45" s="66"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
@@ -38797,7 +38763,7 @@
       <c r="C46" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D46" s="66" t="n">
+      <c r="D46" s="65" t="n">
         <v>124</v>
       </c>
       <c r="E46" s="10" t="n">
@@ -38824,7 +38790,7 @@
         <v>-0.328451327433628</v>
       </c>
       <c r="K46" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H46/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H46/$H$60)</f>
         <v>0.004867932674186</v>
       </c>
       <c r="L46" s="10" t="n">
@@ -38838,7 +38804,7 @@
         <f aca="false">IF(ISNUMBER(L46),H46-L46,"")</f>
         <v>-2632.52</v>
       </c>
-      <c r="O46" s="67"/>
+      <c r="O46" s="66"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
@@ -38850,7 +38816,7 @@
       <c r="C47" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D47" s="66" t="n">
+      <c r="D47" s="65" t="n">
         <v>49</v>
       </c>
       <c r="E47" s="10" t="n">
@@ -38877,7 +38843,7 @@
         <v>-0.311195445920304</v>
       </c>
       <c r="K47" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H47/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H47/$H$60)</f>
         <v>0.00460086668046866</v>
       </c>
       <c r="L47" s="10" t="n">
@@ -38891,7 +38857,7 @@
         <f aca="false">IF(ISNUMBER(L47),H47-L47,"")</f>
         <v>-1421</v>
       </c>
-      <c r="O47" s="67"/>
+      <c r="O47" s="66"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
@@ -38903,7 +38869,7 @@
       <c r="C48" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D48" s="66" t="n">
+      <c r="D48" s="65" t="n">
         <v>54</v>
       </c>
       <c r="E48" s="10" t="n">
@@ -38930,7 +38896,7 @@
         <v>-0.409607843137255</v>
       </c>
       <c r="K48" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H48/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H48/$H$60)</f>
         <v>0.00420573068558004</v>
       </c>
       <c r="L48" s="10" t="n">
@@ -38944,7 +38910,7 @@
         <f aca="false">IF(ISNUMBER(L48),H48-L48,"")</f>
         <v>-642.599999999999</v>
       </c>
-      <c r="O48" s="67"/>
+      <c r="O48" s="66"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
@@ -38956,7 +38922,7 @@
       <c r="C49" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="66" t="n">
+      <c r="D49" s="65" t="n">
         <v>78</v>
       </c>
       <c r="E49" s="10" t="n">
@@ -38983,7 +38949,7 @@
         <v>-0.465064935064935</v>
       </c>
       <c r="K49" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H49/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H49/$H$60)</f>
         <v>0.00415521349534585</v>
       </c>
       <c r="L49" s="10" t="n">
@@ -38997,7 +38963,7 @@
         <f aca="false">IF(ISNUMBER(L49),H49-L49,"")</f>
         <v>-1095.9</v>
       </c>
-      <c r="O49" s="67"/>
+      <c r="O49" s="66"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
@@ -39009,7 +38975,7 @@
       <c r="C50" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D50" s="66" t="n">
+      <c r="D50" s="65" t="n">
         <v>67</v>
       </c>
       <c r="E50" s="10" t="n">
@@ -39036,7 +39002,7 @@
         <v>-0.429166666666667</v>
       </c>
       <c r="K50" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H50/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H50/$H$60)</f>
         <v>0.0041549936304626</v>
       </c>
       <c r="L50" s="10" t="n">
@@ -39050,7 +39016,7 @@
         <f aca="false">IF(ISNUMBER(L50),H50-L50,"")</f>
         <v>-1758.75</v>
       </c>
-      <c r="O50" s="67"/>
+      <c r="O50" s="66"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="n">
@@ -39062,7 +39028,7 @@
       <c r="C51" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D51" s="66" t="n">
+      <c r="D51" s="65" t="n">
         <v>150</v>
       </c>
       <c r="E51" s="10" t="n">
@@ -39089,7 +39055,7 @@
         <v>-0.35</v>
       </c>
       <c r="K51" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H51/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H51/$H$60)</f>
         <v>0.00403516726909041</v>
       </c>
       <c r="L51" s="10" t="n">
@@ -39103,7 +39069,7 @@
         <f aca="false">IF(ISNUMBER(L51),H51-L51,"")</f>
         <v>-1500</v>
       </c>
-      <c r="O51" s="67"/>
+      <c r="O51" s="66"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
@@ -39115,7 +39081,7 @@
       <c r="C52" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D52" s="66" t="n">
+      <c r="D52" s="65" t="n">
         <v>48</v>
       </c>
       <c r="E52" s="10" t="n">
@@ -39142,7 +39108,7 @@
         <v>-0.200495049504951</v>
       </c>
       <c r="K52" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H52/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H52/$H$60)</f>
         <v>0.00401033547051139</v>
       </c>
       <c r="L52" s="10" t="n">
@@ -39156,7 +39122,7 @@
         <f aca="false">IF(ISNUMBER(L52),H52-L52,"")</f>
         <v>-1488</v>
       </c>
-      <c r="O52" s="67"/>
+      <c r="O52" s="66"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="n">
@@ -39168,7 +39134,7 @@
       <c r="C53" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D53" s="66" t="n">
+      <c r="D53" s="65" t="n">
         <v>132</v>
       </c>
       <c r="E53" s="10" t="n">
@@ -39195,7 +39161,7 @@
         <v>-0.432078651685393</v>
       </c>
       <c r="K53" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H53/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H53/$H$60)</f>
         <v>0.00345158896273527</v>
       </c>
       <c r="L53" s="10" t="n">
@@ -39209,7 +39175,7 @@
         <f aca="false">IF(ISNUMBER(L53),H53-L53,"")</f>
         <v>-1704.12</v>
       </c>
-      <c r="O53" s="67"/>
+      <c r="O53" s="66"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
@@ -39221,7 +39187,7 @@
       <c r="C54" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D54" s="66" t="n">
+      <c r="D54" s="65" t="n">
         <v>33</v>
       </c>
       <c r="E54" s="10" t="n">
@@ -39248,7 +39214,7 @@
         <v>-0.260793357933579</v>
       </c>
       <c r="K54" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H54/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H54/$H$60)</f>
         <v>0.00341992065960996</v>
       </c>
       <c r="L54" s="10" t="n">
@@ -39262,19 +39228,19 @@
         <f aca="false">IF(ISNUMBER(L54),H54-L54,"")</f>
         <v>-3080.55</v>
       </c>
-      <c r="O54" s="67"/>
+      <c r="O54" s="66"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="64" t="s">
         <v>118</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="66" t="n">
+      <c r="D55" s="65" t="n">
         <v>99</v>
       </c>
       <c r="E55" s="10" t="n">
@@ -39301,7 +39267,7 @@
         <v>0.032520325203252</v>
       </c>
       <c r="K55" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H55/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H55/$H$60)</f>
         <v>0.00325218962014575</v>
       </c>
       <c r="L55" s="10" t="n">
@@ -39315,7 +39281,7 @@
         <f aca="false">IF(ISNUMBER(L55),H55-L55,"")</f>
         <v>-198</v>
       </c>
-      <c r="O55" s="67"/>
+      <c r="O55" s="66"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
@@ -39327,7 +39293,7 @@
       <c r="C56" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D56" s="66" t="n">
+      <c r="D56" s="65" t="n">
         <v>9</v>
       </c>
       <c r="E56" s="10" t="n">
@@ -39354,7 +39320,7 @@
         <v>-0.150297176820208</v>
       </c>
       <c r="K56" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H56/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H56/$H$60)</f>
         <v>0.00266251200326464</v>
       </c>
       <c r="L56" s="10" t="n">
@@ -39368,7 +39334,7 @@
         <f aca="false">IF(ISNUMBER(L56),H56-L56,"")</f>
         <v>762.300000000001</v>
       </c>
-      <c r="O56" s="67"/>
+      <c r="O56" s="66"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="n">
@@ -39380,7 +39346,7 @@
       <c r="C57" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="66" t="n">
+      <c r="D57" s="65" t="n">
         <v>560</v>
       </c>
       <c r="E57" s="10" t="n">
@@ -39407,7 +39373,7 @@
         <v>-0.778727272727273</v>
       </c>
       <c r="K57" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H57/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H57/$H$60)</f>
         <v>0.00176285076745545</v>
       </c>
       <c r="L57" s="10" t="n">
@@ -39421,7 +39387,7 @@
         <f aca="false">IF(ISNUMBER(L57),H57-L57,"")</f>
         <v>-1304.8</v>
       </c>
-      <c r="O57" s="67"/>
+      <c r="O57" s="66"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="n">
@@ -39433,7 +39399,7 @@
       <c r="C58" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D58" s="66" t="n">
+      <c r="D58" s="65" t="n">
         <v>20</v>
       </c>
       <c r="E58" s="10" t="n">
@@ -39460,7 +39426,7 @@
         <v>-0.630094936708861</v>
       </c>
       <c r="K58" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H58/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H58/$H$60)</f>
         <v>0.000604706028312793</v>
       </c>
       <c r="L58" s="10" t="n">
@@ -39474,7 +39440,7 @@
         <f aca="false">IF(ISNUMBER(L58),H58-L58,"")</f>
         <v>-182.2</v>
       </c>
-      <c r="O58" s="67"/>
+      <c r="O58" s="66"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
@@ -39486,7 +39452,7 @@
       <c r="C59" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="66" t="n">
+      <c r="D59" s="65" t="n">
         <v>344</v>
       </c>
       <c r="E59" s="10" t="n">
@@ -39513,7 +39479,7 @@
         <v/>
       </c>
       <c r="K59" s="9" t="n">
-        <f aca="false">IF($H$6=0,"",H59/$H$6)</f>
+        <f aca="false">IF($H$60=0,"",H59/$H$60)</f>
         <v>0.000355922446299257</v>
       </c>
       <c r="L59" s="10" t="n">
@@ -39527,9 +39493,40 @@
         <f aca="false">IF(ISNUMBER(L59),H59-L59,"")</f>
         <v>0</v>
       </c>
-      <c r="O59" s="67" t="s">
+      <c r="O59" s="66" t="s">
         <v>274</v>
       </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="93"/>
+      <c r="B60" s="93" t="s">
+        <v>78</v>
+      </c>
+      <c r="C60" s="93"/>
+      <c r="D60" s="93"/>
+      <c r="E60" s="93"/>
+      <c r="F60" s="93"/>
+      <c r="G60" s="93"/>
+      <c r="H60" s="94" t="n">
+        <f aca="false">SUM(H7:H59)</f>
+        <v>3866010.74</v>
+      </c>
+      <c r="I60" s="93"/>
+      <c r="J60" s="93"/>
+      <c r="K60" s="95" t="n">
+        <f aca="false">SUM(K7:K59)</f>
+        <v>1</v>
+      </c>
+      <c r="L60" s="94" t="n">
+        <f aca="false">SUM(L7:L59)</f>
+        <v>4141021</v>
+      </c>
+      <c r="M60" s="93"/>
+      <c r="N60" s="94" t="n">
+        <f aca="false">SUM(N7:N59)</f>
+        <v>-275010.26</v>
+      </c>
+      <c r="O60" s="93"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G7:G300">

--- a/Consolidated_Portfolios_23.10.2026.xlsx
+++ b/Consolidated_Portfolios_23.10.2026.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="283">
   <si>
     <t xml:space="preserve">CONSOLIDATED PORTFOLIO SUMMARY – ALL MANAGED ACCOUNTS</t>
   </si>
@@ -633,6 +633,9 @@
     <t xml:space="preserve">No exchange close found – statement price used</t>
   </si>
   <si>
+    <t xml:space="preserve">GAUTAM – HDFC Securities – 23.10.2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Holdings as of 23.10.2026. Statement prices: HDFC statement prices 23.10.2026. Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
   </si>
   <si>
@@ -706,6 +709,9 @@
   </si>
   <si>
     <t xml:space="preserve">No cost or price on statement (marked *) – carried at nil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANISH SHILPA – Axis Direct + HDFC Securities – 23.10.2026 (live, ~11:23 IST)</t>
   </si>
   <si>
     <t xml:space="preserve">Holdings as of 23.10.2026 (live, ~11:23 IST). Statement prices: Live LTP 23.10.2026 ~11:23 IST (equity); MF NAV per Axis statement 23.10.2026 (three demats + MF merged). Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
@@ -795,6 +801,9 @@
     <t xml:space="preserve">Axis Direct Shilpa 1; Axis Direct Manish 4</t>
   </si>
   <si>
+    <t xml:space="preserve">SALONI MEHRA – Angel One – 20.10.2026 + trades of 21–23.10.2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Holdings as of 20.10.2026 + trades of 21–23.10.2026. Statement prices: 20.10.2026 statement prices (only for rows with no trades since). Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
   </si>
   <si>
@@ -846,6 +855,9 @@
     <t xml:space="preserve">New position, bought 22.10 (charges included in cost); no statement value; 23.10 buys at executed price, charges not yet known</t>
   </si>
   <si>
+    <t xml:space="preserve">VIDUSHI MALHOTRA – Zerodha – 04.10.2026 (+ trades of 05.10.2026)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Holdings as of 04.10.2026 (+ trades of 05.10.2026). Statement prices: LTP 05.10.2026. Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
   </si>
   <si>
@@ -859,6 +871,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-05 12:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DR UMESH CHOUDHRY – ICICI Direct – 04.10.2026 + trades of 09.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Holdings as of 04.10.2026 + trades of 09.10.2026. Statement prices: NSE live 09.10.2026 ~09:45 IST. Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
@@ -877,6 +892,9 @@
   </si>
   <si>
     <t xml:space="preserve">New position 09.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DA – HDFC Securities + Kotak Securities – Post 12.09.2026 trades (file dated 04.10.2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Holdings as of Post 12.09.2026 trades (file dated 04.10.2026). Statement prices: As on statement (date not printed). Market value uses the common Ref Price from the Prices sheet so all portfolios are valued alike.</t>
@@ -2935,12 +2953,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -27225,22 +27243,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="32" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27248,16 +27266,16 @@
         <v>69</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>74</v>
@@ -27275,37 +27293,37 @@
         <v>10</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N6" s="23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R6" s="23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T6" s="23" t="s">
         <v>73</v>
       </c>
       <c r="U6" s="23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V6" s="23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27361,10 +27379,10 @@
       </c>
       <c r="O7" s="67"/>
       <c r="Q7" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R7" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S7" s="68" t="s">
         <v>94</v>
@@ -27432,10 +27450,10 @@
       </c>
       <c r="O8" s="67"/>
       <c r="Q8" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R8" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S8" s="68" t="s">
         <v>102</v>
@@ -27503,10 +27521,10 @@
       </c>
       <c r="O9" s="67"/>
       <c r="Q9" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R9" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S9" s="68" t="s">
         <v>79</v>
@@ -27574,10 +27592,10 @@
       </c>
       <c r="O10" s="67"/>
       <c r="Q10" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R10" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S10" s="68" t="s">
         <v>86</v>
@@ -27644,13 +27662,13 @@
         <v>0</v>
       </c>
       <c r="O11" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q11" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="R11" s="68" t="s">
         <v>203</v>
-      </c>
-      <c r="Q11" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="R11" s="68" t="s">
-        <v>202</v>
       </c>
       <c r="S11" s="68" t="s">
         <v>96</v>
@@ -27718,10 +27736,10 @@
       </c>
       <c r="O12" s="67"/>
       <c r="Q12" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R12" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S12" s="68" t="s">
         <v>91</v>
@@ -27789,10 +27807,10 @@
       </c>
       <c r="O13" s="67"/>
       <c r="Q13" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R13" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S13" s="68" t="s">
         <v>83</v>
@@ -27860,13 +27878,13 @@
       </c>
       <c r="O14" s="67"/>
       <c r="Q14" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R14" s="68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S14" s="68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="T14" s="68" t="n">
         <v>80</v>
@@ -27930,13 +27948,13 @@
         <v>-666</v>
       </c>
       <c r="O15" s="67" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q15" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R15" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S15" s="68" t="s">
         <v>88</v>
@@ -28004,10 +28022,10 @@
       </c>
       <c r="O16" s="67"/>
       <c r="Q16" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R16" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S16" s="68" t="s">
         <v>95</v>
@@ -28075,10 +28093,10 @@
       </c>
       <c r="O17" s="67"/>
       <c r="Q17" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R17" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S17" s="68" t="s">
         <v>93</v>
@@ -28146,10 +28164,10 @@
       </c>
       <c r="O18" s="67"/>
       <c r="Q18" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R18" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S18" s="68" t="s">
         <v>82</v>
@@ -28217,10 +28235,10 @@
       </c>
       <c r="O19" s="67"/>
       <c r="Q19" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R19" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S19" s="68" t="s">
         <v>104</v>
@@ -28288,10 +28306,10 @@
       </c>
       <c r="O20" s="67"/>
       <c r="Q20" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R20" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S20" s="68" t="s">
         <v>92</v>
@@ -28358,13 +28376,13 @@
         <v>-160</v>
       </c>
       <c r="O21" s="67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q21" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R21" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S21" s="68" t="s">
         <v>80</v>
@@ -28432,10 +28450,10 @@
       </c>
       <c r="O22" s="67"/>
       <c r="Q22" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R22" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S22" s="68" t="s">
         <v>100</v>
@@ -28503,10 +28521,10 @@
       </c>
       <c r="O23" s="67"/>
       <c r="Q23" s="68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R23" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S23" s="68" t="s">
         <v>105</v>
@@ -28574,7 +28592,7 @@
       </c>
       <c r="O24" s="67"/>
       <c r="S24" s="69" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="V24" s="70" t="n">
         <f aca="false">SUMIFS(V7:V23,R7:R23,"BUY")-SUMIFS(V7:V23,R7:R23,"SELL")</f>
@@ -29212,7 +29230,7 @@
         <v/>
       </c>
       <c r="O36" s="78" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29263,7 +29281,7 @@
         <v/>
       </c>
       <c r="O37" s="78" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29341,17 +29359,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29359,16 +29377,16 @@
         <v>69</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F6" s="24" t="s">
         <v>74</v>
@@ -29386,19 +29404,19 @@
         <v>10</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29409,7 +29427,7 @@
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D7" s="66" t="n">
         <v>3895</v>
@@ -29453,7 +29471,7 @@
         <v>43579.5</v>
       </c>
       <c r="O7" s="67" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29464,7 +29482,7 @@
         <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D8" s="66" t="n">
         <v>11160</v>
@@ -29508,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="67" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29519,7 +29537,7 @@
         <v>80</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D9" s="66" t="n">
         <v>165</v>
@@ -29563,7 +29581,7 @@
         <v>17025</v>
       </c>
       <c r="O9" s="67" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29574,7 +29592,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D10" s="66" t="n">
         <v>1013</v>
@@ -29618,7 +29636,7 @@
         <v>5129.64999999991</v>
       </c>
       <c r="O10" s="67" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29629,7 +29647,7 @@
         <v>82</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D11" s="66" t="n">
         <v>1394</v>
@@ -29673,7 +29691,7 @@
         <v>24777.2999999999</v>
       </c>
       <c r="O11" s="67" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29684,7 +29702,7 @@
         <v>84</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D12" s="66" t="n">
         <v>360</v>
@@ -29737,7 +29755,7 @@
         <v>97</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D13" s="66" t="n">
         <v>2004.589</v>
@@ -29781,7 +29799,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="67" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29792,7 +29810,7 @@
         <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D14" s="66" t="n">
         <v>3762</v>
@@ -29836,7 +29854,7 @@
         <v>12713.24</v>
       </c>
       <c r="O14" s="67" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29847,7 +29865,7 @@
         <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D15" s="66" t="n">
         <v>72</v>
@@ -29891,7 +29909,7 @@
         <v>2157.60000000004</v>
       </c>
       <c r="O15" s="67" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29902,7 +29920,7 @@
         <v>87</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D16" s="66" t="n">
         <v>66</v>
@@ -29946,7 +29964,7 @@
         <v>5268</v>
       </c>
       <c r="O16" s="67" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29957,7 +29975,7 @@
         <v>89</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D17" s="66" t="n">
         <v>800</v>
@@ -30010,7 +30028,7 @@
         <v>91</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D18" s="66" t="n">
         <v>3500</v>
@@ -30063,7 +30081,7 @@
         <v>103</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D19" s="66" t="n">
         <v>134</v>
@@ -30116,7 +30134,7 @@
         <v>92</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D20" s="66" t="n">
         <v>32</v>
@@ -30160,7 +30178,7 @@
         <v>2627.60000000001</v>
       </c>
       <c r="O20" s="67" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30171,7 +30189,7 @@
         <v>109</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D21" s="66" t="n">
         <v>44</v>
@@ -30224,7 +30242,7 @@
         <v>110</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D22" s="66" t="n">
         <v>3</v>
@@ -30277,7 +30295,7 @@
         <v>111</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D23" s="66" t="n">
         <v>64</v>
@@ -30330,7 +30348,7 @@
         <v>85</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D24" s="66" t="n">
         <v>29</v>
@@ -30383,7 +30401,7 @@
         <v>112</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D25" s="66" t="n">
         <v>160</v>
@@ -30427,7 +30445,7 @@
         <v>622</v>
       </c>
       <c r="O25" s="67" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30438,7 +30456,7 @@
         <v>113</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D26" s="66" t="n">
         <v>2</v>
@@ -30491,7 +30509,7 @@
         <v>94</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D27" s="66" t="n">
         <v>47</v>
@@ -30535,7 +30553,7 @@
         <v>1797.6</v>
       </c>
       <c r="O27" s="67" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30546,7 +30564,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D28" s="66" t="n">
         <v>11</v>
@@ -30590,7 +30608,7 @@
         <v>-502.5</v>
       </c>
       <c r="O28" s="67" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30601,7 +30619,7 @@
         <v>115</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D29" s="66" t="n">
         <v>22</v>
@@ -30654,7 +30672,7 @@
         <v>96</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D30" s="66" t="n">
         <v>6</v>
@@ -30698,7 +30716,7 @@
         <v>747</v>
       </c>
       <c r="O30" s="67" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30709,7 +30727,7 @@
         <v>99</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D31" s="66" t="n">
         <v>32</v>
@@ -30762,7 +30780,7 @@
         <v>125</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D32" s="66" t="n">
         <v>34</v>
@@ -30815,7 +30833,7 @@
         <v>100</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D33" s="66" t="n">
         <v>10</v>
@@ -30859,7 +30877,7 @@
         <v>628</v>
       </c>
       <c r="O33" s="67" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30870,7 +30888,7 @@
         <v>118</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D34" s="66" t="n">
         <v>168</v>
@@ -30914,7 +30932,7 @@
         <v>1205</v>
       </c>
       <c r="O34" s="67" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30925,7 +30943,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D35" s="66" t="n">
         <v>33</v>
@@ -30978,7 +30996,7 @@
         <v>102</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D36" s="66" t="n">
         <v>6</v>
@@ -31022,7 +31040,7 @@
         <v>238</v>
       </c>
       <c r="O36" s="67" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31033,7 +31051,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D37" s="66" t="n">
         <v>17</v>
@@ -31077,7 +31095,7 @@
         <v>386.300000000003</v>
       </c>
       <c r="O37" s="67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31088,7 +31106,7 @@
         <v>105</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D38" s="66" t="n">
         <v>6</v>
@@ -31132,7 +31150,7 @@
         <v>320</v>
       </c>
       <c r="O38" s="67" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31143,7 +31161,7 @@
         <v>148</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D39" s="66" t="n">
         <v>50</v>
@@ -31196,7 +31214,7 @@
         <v>150</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D40" s="66" t="n">
         <v>35</v>
@@ -31249,7 +31267,7 @@
         <v>151</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D41" s="66" t="n">
         <v>14</v>
@@ -31302,7 +31320,7 @@
         <v>152</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D42" s="66" t="n">
         <v>34</v>
@@ -31346,7 +31364,7 @@
         <v>-59.7000000000007</v>
       </c>
       <c r="O42" s="67" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31357,7 +31375,7 @@
         <v>108</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D43" s="66" t="n">
         <v>32</v>
@@ -31410,7 +31428,7 @@
         <v>157</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D44" s="66" t="n">
         <v>3</v>
@@ -31463,7 +31481,7 @@
         <v>95</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D45" s="66" t="n">
         <v>4</v>
@@ -31507,7 +31525,7 @@
         <v>-1559</v>
       </c>
       <c r="O45" s="67" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31518,7 +31536,7 @@
         <v>104</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D46" s="66" t="n">
         <v>5</v>
@@ -31571,7 +31589,7 @@
         <v>159</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D47" s="66" t="n">
         <v>5</v>
@@ -31624,7 +31642,7 @@
         <v>160</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D48" s="66" t="n">
         <v>1</v>
@@ -31677,7 +31695,7 @@
         <v>155</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D49" s="66" t="n">
         <v>5</v>
@@ -31721,7 +31739,7 @@
         <v>196.75</v>
       </c>
       <c r="O49" s="67" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31732,7 +31750,7 @@
         <v>162</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D50" s="66" t="n">
         <v>6</v>
@@ -31785,7 +31803,7 @@
         <v>163</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D51" s="66" t="n">
         <v>1</v>
@@ -31838,7 +31856,7 @@
         <v>139</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D52" s="66" t="n">
         <v>12</v>
@@ -31891,7 +31909,7 @@
         <v>165</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D53" s="66" t="n">
         <v>5</v>
@@ -32017,22 +32035,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="32" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32040,16 +32058,16 @@
         <v>69</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F6" s="25" t="s">
         <v>74</v>
@@ -32067,37 +32085,37 @@
         <v>10</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R6" s="25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T6" s="25" t="s">
         <v>73</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V6" s="25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32150,13 +32168,13 @@
         <v/>
       </c>
       <c r="O7" s="67" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q7" s="68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="R7" s="68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S7" s="68" t="s">
         <v>112</v>
@@ -32221,13 +32239,13 @@
         <v/>
       </c>
       <c r="O8" s="67" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q8" s="68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="R8" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S8" s="68" t="s">
         <v>86</v>
@@ -32292,13 +32310,13 @@
         <v/>
       </c>
       <c r="O9" s="67" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q9" s="68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="R9" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S9" s="68" t="s">
         <v>80</v>
@@ -32366,10 +32384,10 @@
       </c>
       <c r="O10" s="67"/>
       <c r="Q10" s="68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="R10" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S10" s="68" t="s">
         <v>83</v>
@@ -32434,13 +32452,13 @@
         <v/>
       </c>
       <c r="O11" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q11" s="68" t="s">
         <v>245</v>
       </c>
-      <c r="Q11" s="68" t="s">
-        <v>242</v>
-      </c>
       <c r="R11" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S11" s="68" t="s">
         <v>82</v>
@@ -32508,13 +32526,13 @@
       </c>
       <c r="O12" s="67"/>
       <c r="Q12" s="68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="R12" s="68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S12" s="68" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="T12" s="68" t="n">
         <v>700</v>
@@ -32579,10 +32597,10 @@
       </c>
       <c r="O13" s="67"/>
       <c r="Q13" s="68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="R13" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S13" s="68" t="s">
         <v>79</v>
@@ -32650,10 +32668,10 @@
       </c>
       <c r="O14" s="67"/>
       <c r="Q14" s="68" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R14" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S14" s="68" t="s">
         <v>93</v>
@@ -32718,13 +32736,13 @@
         <v/>
       </c>
       <c r="O15" s="67" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q15" s="68" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R15" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S15" s="68" t="s">
         <v>92</v>
@@ -32789,13 +32807,13 @@
         <v/>
       </c>
       <c r="O16" s="67" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q16" s="68" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R16" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S16" s="68" t="s">
         <v>88</v>
@@ -32863,10 +32881,10 @@
       </c>
       <c r="O17" s="67"/>
       <c r="Q17" s="68" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R17" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S17" s="68" t="s">
         <v>100</v>
@@ -32931,13 +32949,13 @@
         <v/>
       </c>
       <c r="O18" s="67" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q18" s="68" t="s">
         <v>250</v>
       </c>
-      <c r="Q18" s="68" t="s">
-        <v>247</v>
-      </c>
       <c r="R18" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S18" s="68" t="s">
         <v>94</v>
@@ -33002,13 +33020,13 @@
         <v/>
       </c>
       <c r="O19" s="67" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q19" s="68" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R19" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S19" s="68" t="s">
         <v>96</v>
@@ -33076,10 +33094,10 @@
       </c>
       <c r="O20" s="67"/>
       <c r="Q20" s="68" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R20" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S20" s="68" t="s">
         <v>102</v>
@@ -33144,13 +33162,13 @@
         <v/>
       </c>
       <c r="O21" s="67" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q21" s="68" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R21" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S21" s="68" t="s">
         <v>104</v>
@@ -33215,13 +33233,13 @@
         <v/>
       </c>
       <c r="O22" s="67" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q22" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R22" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S22" s="68" t="s">
         <v>91</v>
@@ -33286,13 +33304,13 @@
         <v/>
       </c>
       <c r="O23" s="67" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q23" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R23" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S23" s="68" t="s">
         <v>101</v>
@@ -33357,13 +33375,13 @@
         <v/>
       </c>
       <c r="O24" s="67" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q24" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R24" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S24" s="68" t="s">
         <v>155</v>
@@ -33428,13 +33446,13 @@
         <v/>
       </c>
       <c r="O25" s="67" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q25" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R25" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S25" s="68" t="s">
         <v>105</v>
@@ -33499,13 +33517,13 @@
         <v/>
       </c>
       <c r="O26" s="67" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q26" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R26" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S26" s="68" t="s">
         <v>106</v>
@@ -33570,13 +33588,13 @@
         <v/>
       </c>
       <c r="O27" s="67" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q27" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R27" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S27" s="68" t="s">
         <v>102</v>
@@ -33641,13 +33659,13 @@
         <v/>
       </c>
       <c r="O28" s="67" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q28" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R28" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S28" s="68" t="s">
         <v>100</v>
@@ -33712,13 +33730,13 @@
         <v/>
       </c>
       <c r="O29" s="67" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q29" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R29" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S29" s="68" t="s">
         <v>96</v>
@@ -33783,13 +33801,13 @@
         <v/>
       </c>
       <c r="O30" s="67" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q30" s="68" t="s">
         <v>17</v>
       </c>
       <c r="R30" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S30" s="68" t="s">
         <v>104</v>
@@ -33860,7 +33878,7 @@
         <v>17</v>
       </c>
       <c r="R31" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S31" s="68" t="s">
         <v>94</v>
@@ -33909,7 +33927,7 @@
         <v>17</v>
       </c>
       <c r="R32" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S32" s="68" t="s">
         <v>80</v>
@@ -33929,7 +33947,7 @@
         <v>17</v>
       </c>
       <c r="R33" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S33" s="68" t="s">
         <v>88</v>
@@ -33949,7 +33967,7 @@
         <v>17</v>
       </c>
       <c r="R34" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S34" s="68" t="s">
         <v>93</v>
@@ -33969,7 +33987,7 @@
         <v>17</v>
       </c>
       <c r="R35" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S35" s="68" t="s">
         <v>92</v>
@@ -33989,7 +34007,7 @@
         <v>17</v>
       </c>
       <c r="R36" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S36" s="68" t="s">
         <v>86</v>
@@ -34009,7 +34027,7 @@
         <v>17</v>
       </c>
       <c r="R37" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S37" s="68" t="s">
         <v>83</v>
@@ -34029,7 +34047,7 @@
         <v>17</v>
       </c>
       <c r="R38" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S38" s="68" t="s">
         <v>82</v>
@@ -34049,7 +34067,7 @@
         <v>17</v>
       </c>
       <c r="R39" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S39" s="68" t="s">
         <v>79</v>
@@ -34069,7 +34087,7 @@
         <v>17</v>
       </c>
       <c r="R40" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S40" s="68" t="s">
         <v>155</v>
@@ -34089,7 +34107,7 @@
         <v>17</v>
       </c>
       <c r="R41" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S41" s="68" t="s">
         <v>105</v>
@@ -34109,7 +34127,7 @@
         <v>17</v>
       </c>
       <c r="R42" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S42" s="68" t="s">
         <v>91</v>
@@ -34129,7 +34147,7 @@
         <v>17</v>
       </c>
       <c r="R43" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S43" s="68" t="s">
         <v>101</v>
@@ -34149,7 +34167,7 @@
         <v>17</v>
       </c>
       <c r="R44" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S44" s="68" t="s">
         <v>93</v>
@@ -34169,7 +34187,7 @@
         <v>17</v>
       </c>
       <c r="R45" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S45" s="68" t="s">
         <v>88</v>
@@ -34186,7 +34204,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S46" s="69" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="V46" s="70" t="n">
         <f aca="false">SUMIFS(V7:V45,R7:R45,"BUY")-SUMIFS(V7:V45,R7:R45,"SELL")</f>
@@ -34243,22 +34261,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="32" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34266,16 +34284,16 @@
         <v>69</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F6" s="26" t="s">
         <v>74</v>
@@ -34293,37 +34311,37 @@
         <v>10</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N6" s="26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O6" s="26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R6" s="26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S6" s="26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T6" s="26" t="s">
         <v>73</v>
       </c>
       <c r="U6" s="26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V6" s="26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34379,10 +34397,10 @@
       </c>
       <c r="O7" s="67"/>
       <c r="Q7" s="68" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="R7" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S7" s="68" t="s">
         <v>82</v>
@@ -34450,10 +34468,10 @@
       </c>
       <c r="O8" s="67"/>
       <c r="Q8" s="68" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="R8" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S8" s="68" t="s">
         <v>83</v>
@@ -34521,10 +34539,10 @@
       </c>
       <c r="O9" s="67"/>
       <c r="Q9" s="68" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="R9" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S9" s="68" t="s">
         <v>79</v>
@@ -34592,7 +34610,7 @@
       </c>
       <c r="O10" s="67"/>
       <c r="S10" s="69" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="V10" s="70" t="n">
         <f aca="false">SUMIFS(V7:V9,R7:R9,"BUY")-SUMIFS(V7:V9,R7:R9,"SELL")</f>
@@ -35104,22 +35122,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q5" s="32" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35127,16 +35145,16 @@
         <v>69</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>74</v>
@@ -35154,37 +35172,37 @@
         <v>10</v>
       </c>
       <c r="K6" s="27" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L6" s="27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M6" s="27" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N6" s="27" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O6" s="27" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q6" s="27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R6" s="27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S6" s="27" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T6" s="27" t="s">
         <v>73</v>
       </c>
       <c r="U6" s="27" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V6" s="27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35240,10 +35258,10 @@
       </c>
       <c r="O7" s="67"/>
       <c r="Q7" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R7" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S7" s="68" t="s">
         <v>79</v>
@@ -35311,10 +35329,10 @@
       </c>
       <c r="O8" s="67"/>
       <c r="Q8" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R8" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S8" s="68" t="s">
         <v>82</v>
@@ -35382,10 +35400,10 @@
       </c>
       <c r="O9" s="67"/>
       <c r="Q9" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R9" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S9" s="68" t="s">
         <v>83</v>
@@ -35453,10 +35471,10 @@
       </c>
       <c r="O10" s="67"/>
       <c r="Q10" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R10" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S10" s="68" t="s">
         <v>80</v>
@@ -35523,13 +35541,13 @@
         <v>-12852</v>
       </c>
       <c r="O11" s="67" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q11" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R11" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S11" s="68" t="s">
         <v>86</v>
@@ -35596,13 +35614,13 @@
         <v>-8600</v>
       </c>
       <c r="O12" s="67" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q12" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R12" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S12" s="68" t="s">
         <v>93</v>
@@ -35670,10 +35688,10 @@
       </c>
       <c r="O13" s="67"/>
       <c r="Q13" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R13" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S13" s="68" t="s">
         <v>92</v>
@@ -35740,13 +35758,13 @@
         <v>8773</v>
       </c>
       <c r="O14" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q14" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="R14" s="68" t="s">
         <v>203</v>
-      </c>
-      <c r="Q14" s="68" t="s">
-        <v>263</v>
-      </c>
-      <c r="R14" s="68" t="s">
-        <v>202</v>
       </c>
       <c r="S14" s="68" t="s">
         <v>96</v>
@@ -35814,10 +35832,10 @@
       </c>
       <c r="O15" s="67"/>
       <c r="Q15" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R15" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S15" s="68" t="s">
         <v>102</v>
@@ -35885,10 +35903,10 @@
       </c>
       <c r="O16" s="67"/>
       <c r="Q16" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R16" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S16" s="68" t="s">
         <v>94</v>
@@ -35956,10 +35974,10 @@
       </c>
       <c r="O17" s="67"/>
       <c r="Q17" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R17" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S17" s="68" t="s">
         <v>100</v>
@@ -36027,10 +36045,10 @@
       </c>
       <c r="O18" s="67"/>
       <c r="Q18" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R18" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S18" s="68" t="s">
         <v>104</v>
@@ -36098,10 +36116,10 @@
       </c>
       <c r="O19" s="67"/>
       <c r="Q19" s="68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="R19" s="68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S19" s="68" t="s">
         <v>88</v>
@@ -36169,7 +36187,7 @@
       </c>
       <c r="O20" s="67"/>
       <c r="S20" s="69" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="V20" s="70" t="n">
         <f aca="false">SUMIFS(V7:V19,R7:R19,"BUY")-SUMIFS(V7:V19,R7:R19,"SELL")</f>
@@ -36281,7 +36299,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="67" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36336,7 +36354,7 @@
         <v>448.5</v>
       </c>
       <c r="O23" s="67" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36497,7 +36515,7 @@
         <v>-422.2</v>
       </c>
       <c r="O26" s="67" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36628,17 +36646,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36646,16 +36664,16 @@
         <v>69</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>74</v>
@@ -36673,19 +36691,19 @@
         <v>10</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O6" s="28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36696,7 +36714,7 @@
         <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D7" s="66" t="n">
         <v>915</v>
@@ -36749,7 +36767,7 @@
         <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D8" s="66" t="n">
         <v>792</v>
@@ -36802,7 +36820,7 @@
         <v>80</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D9" s="66" t="n">
         <v>59</v>
@@ -36855,7 +36873,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D10" s="66" t="n">
         <v>337</v>
@@ -36908,7 +36926,7 @@
         <v>89</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D11" s="66" t="n">
         <v>800</v>
@@ -36952,7 +36970,7 @@
         <v>-24600</v>
       </c>
       <c r="O11" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37016,7 +37034,7 @@
         <v>84</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D13" s="66" t="n">
         <v>120</v>
@@ -37060,7 +37078,7 @@
         <v>-20226</v>
       </c>
       <c r="O13" s="67" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37071,7 +37089,7 @@
         <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D14" s="66" t="n">
         <v>1732</v>
@@ -37177,7 +37195,7 @@
         <v>93</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D16" s="66" t="n">
         <v>18</v>
@@ -37230,7 +37248,7 @@
         <v>88</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D17" s="66" t="n">
         <v>24</v>
@@ -37336,7 +37354,7 @@
         <v>92</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D19" s="66" t="n">
         <v>20</v>
@@ -37389,7 +37407,7 @@
         <v>106</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D20" s="66" t="n">
         <v>52</v>
@@ -37442,7 +37460,7 @@
         <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D21" s="66" t="n">
         <v>45</v>
@@ -37495,7 +37513,7 @@
         <v>96</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D22" s="66" t="n">
         <v>8</v>
@@ -37548,7 +37566,7 @@
         <v>100</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D23" s="66" t="n">
         <v>18</v>
@@ -37654,7 +37672,7 @@
         <v>114</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D25" s="66" t="n">
         <v>33</v>
@@ -37707,7 +37725,7 @@
         <v>117</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D26" s="66" t="n">
         <v>111</v>
@@ -37760,7 +37778,7 @@
         <v>102</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D27" s="66" t="n">
         <v>13</v>
@@ -37919,7 +37937,7 @@
         <v>85</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D30" s="66" t="n">
         <v>13</v>
@@ -38025,7 +38043,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D32" s="66" t="n">
         <v>187</v>
@@ -38078,7 +38096,7 @@
         <v>124</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D33" s="66" t="n">
         <v>1072</v>
@@ -38131,7 +38149,7 @@
         <v>126</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D34" s="66" t="n">
         <v>19</v>
@@ -38184,7 +38202,7 @@
         <v>127</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D35" s="66" t="n">
         <v>110</v>
@@ -38228,7 +38246,7 @@
         <v>-2625.7</v>
       </c>
       <c r="O35" s="67" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38239,7 +38257,7 @@
         <v>128</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D36" s="66" t="n">
         <v>302</v>
@@ -38292,7 +38310,7 @@
         <v>129</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D37" s="66" t="n">
         <v>166</v>
@@ -38345,7 +38363,7 @@
         <v>130</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D38" s="66" t="n">
         <v>116</v>
@@ -38398,7 +38416,7 @@
         <v>131</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D39" s="66" t="n">
         <v>33</v>
@@ -38451,7 +38469,7 @@
         <v>87</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D40" s="66" t="n">
         <v>5</v>
@@ -38495,7 +38513,7 @@
         <v>-5</v>
       </c>
       <c r="O40" s="67" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38506,7 +38524,7 @@
         <v>132</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D41" s="66" t="n">
         <v>380</v>
@@ -38559,7 +38577,7 @@
         <v>133</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D42" s="66" t="n">
         <v>245</v>
@@ -38612,7 +38630,7 @@
         <v>134</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D43" s="66" t="n">
         <v>35</v>
@@ -38665,7 +38683,7 @@
         <v>136</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D44" s="66" t="n">
         <v>51</v>
@@ -38771,7 +38789,7 @@
         <v>137</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D46" s="66" t="n">
         <v>124</v>
@@ -38824,7 +38842,7 @@
         <v>138</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D47" s="66" t="n">
         <v>49</v>
@@ -38877,7 +38895,7 @@
         <v>141</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D48" s="66" t="n">
         <v>54</v>
@@ -38983,7 +39001,7 @@
         <v>143</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D50" s="66" t="n">
         <v>67</v>
@@ -39036,7 +39054,7 @@
         <v>139</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D51" s="66" t="n">
         <v>150</v>
@@ -39089,7 +39107,7 @@
         <v>145</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D52" s="66" t="n">
         <v>48</v>
@@ -39142,7 +39160,7 @@
         <v>147</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D53" s="66" t="n">
         <v>132</v>
@@ -39195,7 +39213,7 @@
         <v>149</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D54" s="66" t="n">
         <v>33</v>
@@ -39301,7 +39319,7 @@
         <v>153</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D56" s="66" t="n">
         <v>9</v>
@@ -39407,7 +39425,7 @@
         <v>161</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D58" s="66" t="n">
         <v>20</v>
@@ -39504,7 +39522,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="67" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
